--- a/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
+++ b/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
@@ -33,8 +33,6 @@
     <definedName name="Projekt_Start" localSheetId="2">Weihnachtsmailing!$C$6</definedName>
     <definedName name="Scroll_Schrittweite" localSheetId="1">Sommermailing!$C$7</definedName>
     <definedName name="Scroll_Schrittweite" localSheetId="2">Weihnachtsmailing!$C$7</definedName>
-    <definedName name="Std_Vorlauf_Inhalt">Jahresplanung!$W$6</definedName>
-    <definedName name="Std_Vorlauf_Sel">Jahresplanung!$W$5</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
@@ -57,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="154">
   <si>
     <t xml:space="preserve">Erstellen eines Gantt-Diagramms
 Geben Sie den Titel dieses Projekts in Zelle B2 ein.
@@ -584,6 +582,12 @@
   </si>
   <si>
     <t>Bußgeldmailing 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Vorlauf: Bei Sommer- und Weihnachtsmailing wird er automatisch aus dem Gantt übernommen (Summe der Arbeitsschritte bis zum PAL, graue Felder). Bei allen anderen Maßnahmen individuell eintragen; Zelle leeren = kein Termin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Sommer- und Weihnachtsmailing: Der PAL hier steuert die gleichnamigen Detailblätter. Dauern der Arbeitsschritte im Gantt ändern = Vorlauf und Starttermine hier ändern sich mit. Verknüpfung über den Namen in Spalte „Maßnahme“.</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1891,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2439,6 +2443,27 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="1" fontId="66" fillId="20" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="66" fillId="20" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="66" fillId="20" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="66" fillId="20" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Akzent3" xfId="11" builtinId="37"/>
@@ -2454,7 +2479,7 @@
     <cellStyle name="Überschrift 3" xfId="8" builtinId="18" customBuiltin="1"/>
     <cellStyle name="zAusgeblText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="136">
+  <dxfs count="142">
     <dxf>
       <font>
         <i/>
@@ -3912,6 +3937,57 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border>
+        <left style="thin">
+          <color rgb="FFE30714"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFE30714"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFE30714"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FFE30714"/>
+        </left>
+        <bottom style="thin">
+          <color rgb="FFE30714"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FFE30714"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="thin">
+          <color rgb="FFE30714"/>
+        </right>
+        <bottom style="thin">
+          <color rgb="FFE30714"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Gantt-Tabellenformat" pivot="0" count="4" xr9:uid="{4904D139-63E4-4221-B7C9-C6C5B7A50FAF}">
@@ -4794,36 +4870,6 @@
       <c r="CN4" s="121"/>
     </row>
     <row r="5" spans="2:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="116" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="116"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="116"/>
-      <c r="V5" s="116"/>
-      <c r="W5" s="117">
-        <v>76</v>
-      </c>
-      <c r="X5" s="118"/>
-      <c r="Y5" s="118"/>
-      <c r="Z5" s="118"/>
-      <c r="AA5" s="118"/>
       <c r="AE5" s="116" t="s">
         <v>61</v>
       </c>
@@ -4891,36 +4937,6 @@
       <c r="CN5" s="121"/>
     </row>
     <row r="6" spans="2:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="116" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="116"/>
-      <c r="T6" s="116"/>
-      <c r="U6" s="116"/>
-      <c r="V6" s="116"/>
-      <c r="W6" s="117">
-        <v>58</v>
-      </c>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
-      <c r="Z6" s="118"/>
-      <c r="AA6" s="118"/>
       <c r="AE6" s="116" t="s">
         <v>65</v>
       </c>
@@ -5016,10 +5032,7 @@
       <c r="AA7" s="119"/>
       <c r="AB7" s="119"/>
       <c r="AC7" s="119"/>
-      <c r="AE7" s="120" t="str">
-        <f>IF(AND(Sommermailing!$G$14&gt;=1,Sommermailing!$G$17&gt;=1),"✓ Sommermailing: Zeitplan ok","⚠ Sommermailing: Vorlauf zu kurz")</f>
-        <v>✓ Sommermailing: Zeitplan ok</v>
-      </c>
+      <c r="AE7" s="120"/>
       <c r="AF7" s="120"/>
       <c r="AG7" s="120"/>
       <c r="AH7" s="120"/>
@@ -5037,10 +5050,7 @@
       <c r="AT7" s="120"/>
       <c r="AU7" s="120"/>
       <c r="AV7" s="120"/>
-      <c r="AX7" s="120" t="str">
-        <f>IF(AND(Weihnachtsmailing!$G$14&gt;=1,Weihnachtsmailing!$G$17&gt;=1),"✓ Weihnachtsmailing: Zeitplan ok","⚠ Weihnachtsmailing: Vorlauf zu kurz")</f>
-        <v>✓ Weihnachtsmailing: Zeitplan ok</v>
-      </c>
+      <c r="AX7" s="120"/>
       <c r="AY7" s="120"/>
       <c r="AZ7" s="120"/>
       <c r="BA7" s="120"/>
@@ -5292,155 +5302,155 @@
       <c r="B12" s="163" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="124" t="s">
+      <c r="C12" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="124"/>
-      <c r="E12" s="124"/>
-      <c r="F12" s="124" t="s">
+      <c r="D12" s="191"/>
+      <c r="E12" s="191"/>
+      <c r="F12" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="124"/>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124" t="s">
+      <c r="G12" s="191"/>
+      <c r="H12" s="191"/>
+      <c r="I12" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="124" t="s">
+      <c r="J12" s="191"/>
+      <c r="K12" s="191"/>
+      <c r="L12" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124" t="s">
+      <c r="M12" s="191"/>
+      <c r="N12" s="191"/>
+      <c r="O12" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="124"/>
-      <c r="R12" s="124" t="s">
+      <c r="P12" s="191"/>
+      <c r="Q12" s="191"/>
+      <c r="R12" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="S12" s="124"/>
-      <c r="T12" s="124"/>
-      <c r="U12" s="124" t="s">
+      <c r="S12" s="191"/>
+      <c r="T12" s="191"/>
+      <c r="U12" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="V12" s="124"/>
-      <c r="W12" s="164"/>
+      <c r="V12" s="191"/>
+      <c r="W12" s="192"/>
       <c r="Y12" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="Z12" s="124" t="s">
+      <c r="Z12" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="AA12" s="124"/>
-      <c r="AB12" s="124"/>
-      <c r="AC12" s="124" t="s">
+      <c r="AA12" s="191"/>
+      <c r="AB12" s="191"/>
+      <c r="AC12" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="AD12" s="124"/>
-      <c r="AE12" s="124"/>
-      <c r="AF12" s="124" t="s">
+      <c r="AD12" s="191"/>
+      <c r="AE12" s="191"/>
+      <c r="AF12" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="AG12" s="124"/>
-      <c r="AH12" s="124"/>
-      <c r="AI12" s="124" t="s">
+      <c r="AG12" s="191"/>
+      <c r="AH12" s="191"/>
+      <c r="AI12" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="AJ12" s="124"/>
-      <c r="AK12" s="124"/>
-      <c r="AL12" s="124" t="s">
+      <c r="AJ12" s="191"/>
+      <c r="AK12" s="191"/>
+      <c r="AL12" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="AM12" s="124"/>
-      <c r="AN12" s="124"/>
-      <c r="AO12" s="124" t="s">
+      <c r="AM12" s="191"/>
+      <c r="AN12" s="191"/>
+      <c r="AO12" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="AP12" s="124"/>
-      <c r="AQ12" s="124"/>
-      <c r="AR12" s="124" t="s">
+      <c r="AP12" s="191"/>
+      <c r="AQ12" s="191"/>
+      <c r="AR12" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="AS12" s="124"/>
-      <c r="AT12" s="176"/>
+      <c r="AS12" s="191"/>
+      <c r="AT12" s="193"/>
       <c r="AV12" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="AW12" s="124" t="s">
+      <c r="AW12" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="AX12" s="124"/>
-      <c r="AY12" s="124"/>
-      <c r="AZ12" s="124" t="s">
+      <c r="AX12" s="191"/>
+      <c r="AY12" s="191"/>
+      <c r="AZ12" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="BA12" s="124"/>
-      <c r="BB12" s="124"/>
-      <c r="BC12" s="124" t="s">
+      <c r="BA12" s="191"/>
+      <c r="BB12" s="191"/>
+      <c r="BC12" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="BD12" s="124"/>
-      <c r="BE12" s="124"/>
-      <c r="BF12" s="124" t="s">
+      <c r="BD12" s="191"/>
+      <c r="BE12" s="191"/>
+      <c r="BF12" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="BG12" s="124"/>
-      <c r="BH12" s="124"/>
-      <c r="BI12" s="124" t="s">
+      <c r="BG12" s="191"/>
+      <c r="BH12" s="191"/>
+      <c r="BI12" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="BJ12" s="124"/>
-      <c r="BK12" s="124"/>
-      <c r="BL12" s="124" t="s">
+      <c r="BJ12" s="191"/>
+      <c r="BK12" s="191"/>
+      <c r="BL12" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="BM12" s="124"/>
-      <c r="BN12" s="124"/>
-      <c r="BO12" s="124" t="s">
+      <c r="BM12" s="191"/>
+      <c r="BN12" s="191"/>
+      <c r="BO12" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="BP12" s="124"/>
-      <c r="BQ12" s="176"/>
+      <c r="BP12" s="191"/>
+      <c r="BQ12" s="193"/>
       <c r="BS12" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="BT12" s="124" t="s">
+      <c r="BT12" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="BU12" s="124"/>
-      <c r="BV12" s="124"/>
-      <c r="BW12" s="124" t="s">
+      <c r="BU12" s="191"/>
+      <c r="BV12" s="191"/>
+      <c r="BW12" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="BX12" s="124"/>
-      <c r="BY12" s="124"/>
-      <c r="BZ12" s="124" t="s">
+      <c r="BX12" s="191"/>
+      <c r="BY12" s="191"/>
+      <c r="BZ12" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="CA12" s="124"/>
-      <c r="CB12" s="124"/>
-      <c r="CC12" s="124" t="s">
+      <c r="CA12" s="191"/>
+      <c r="CB12" s="191"/>
+      <c r="CC12" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="CD12" s="124"/>
-      <c r="CE12" s="124"/>
-      <c r="CF12" s="124" t="s">
+      <c r="CD12" s="191"/>
+      <c r="CE12" s="191"/>
+      <c r="CF12" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="CG12" s="124"/>
-      <c r="CH12" s="124"/>
-      <c r="CI12" s="124" t="s">
+      <c r="CG12" s="191"/>
+      <c r="CH12" s="191"/>
+      <c r="CI12" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="CJ12" s="124"/>
-      <c r="CK12" s="124"/>
-      <c r="CL12" s="124" t="s">
+      <c r="CJ12" s="191"/>
+      <c r="CK12" s="191"/>
+      <c r="CL12" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="CM12" s="124"/>
-      <c r="CN12" s="176"/>
+      <c r="CM12" s="191"/>
+      <c r="CN12" s="193"/>
     </row>
     <row r="13" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="165">
@@ -8819,155 +8829,155 @@
       <c r="B28" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="124" t="s">
+      <c r="C28" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="124"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124" t="s">
+      <c r="D28" s="191"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="124" t="s">
+      <c r="G28" s="191"/>
+      <c r="H28" s="191"/>
+      <c r="I28" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="124"/>
-      <c r="K28" s="124"/>
-      <c r="L28" s="124" t="s">
+      <c r="J28" s="191"/>
+      <c r="K28" s="191"/>
+      <c r="L28" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="M28" s="124"/>
-      <c r="N28" s="124"/>
-      <c r="O28" s="124" t="s">
+      <c r="M28" s="191"/>
+      <c r="N28" s="191"/>
+      <c r="O28" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="P28" s="124"/>
-      <c r="Q28" s="124"/>
-      <c r="R28" s="124" t="s">
+      <c r="P28" s="191"/>
+      <c r="Q28" s="191"/>
+      <c r="R28" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="S28" s="124"/>
-      <c r="T28" s="124"/>
-      <c r="U28" s="124" t="s">
+      <c r="S28" s="191"/>
+      <c r="T28" s="191"/>
+      <c r="U28" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="V28" s="124"/>
-      <c r="W28" s="176"/>
+      <c r="V28" s="191"/>
+      <c r="W28" s="193"/>
       <c r="Y28" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="Z28" s="124" t="s">
+      <c r="Z28" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="AA28" s="124"/>
-      <c r="AB28" s="124"/>
-      <c r="AC28" s="124" t="s">
+      <c r="AA28" s="191"/>
+      <c r="AB28" s="191"/>
+      <c r="AC28" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="AD28" s="124"/>
-      <c r="AE28" s="124"/>
-      <c r="AF28" s="124" t="s">
+      <c r="AD28" s="191"/>
+      <c r="AE28" s="191"/>
+      <c r="AF28" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="AG28" s="124"/>
-      <c r="AH28" s="124"/>
-      <c r="AI28" s="124" t="s">
+      <c r="AG28" s="191"/>
+      <c r="AH28" s="191"/>
+      <c r="AI28" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="AJ28" s="124"/>
-      <c r="AK28" s="124"/>
-      <c r="AL28" s="124" t="s">
+      <c r="AJ28" s="191"/>
+      <c r="AK28" s="191"/>
+      <c r="AL28" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="AM28" s="124"/>
-      <c r="AN28" s="124"/>
-      <c r="AO28" s="124" t="s">
+      <c r="AM28" s="191"/>
+      <c r="AN28" s="191"/>
+      <c r="AO28" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="AP28" s="124"/>
-      <c r="AQ28" s="124"/>
-      <c r="AR28" s="124" t="s">
+      <c r="AP28" s="191"/>
+      <c r="AQ28" s="191"/>
+      <c r="AR28" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="AS28" s="124"/>
-      <c r="AT28" s="176"/>
+      <c r="AS28" s="191"/>
+      <c r="AT28" s="193"/>
       <c r="AV28" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="AW28" s="124" t="s">
+      <c r="AW28" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="AX28" s="124"/>
-      <c r="AY28" s="124"/>
-      <c r="AZ28" s="124" t="s">
+      <c r="AX28" s="191"/>
+      <c r="AY28" s="191"/>
+      <c r="AZ28" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="BA28" s="124"/>
-      <c r="BB28" s="124"/>
-      <c r="BC28" s="124" t="s">
+      <c r="BA28" s="191"/>
+      <c r="BB28" s="191"/>
+      <c r="BC28" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="BD28" s="124"/>
-      <c r="BE28" s="124"/>
-      <c r="BF28" s="124" t="s">
+      <c r="BD28" s="191"/>
+      <c r="BE28" s="191"/>
+      <c r="BF28" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="BG28" s="124"/>
-      <c r="BH28" s="124"/>
-      <c r="BI28" s="124" t="s">
+      <c r="BG28" s="191"/>
+      <c r="BH28" s="191"/>
+      <c r="BI28" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="BJ28" s="124"/>
-      <c r="BK28" s="124"/>
-      <c r="BL28" s="124" t="s">
+      <c r="BJ28" s="191"/>
+      <c r="BK28" s="191"/>
+      <c r="BL28" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="BM28" s="124"/>
-      <c r="BN28" s="124"/>
-      <c r="BO28" s="124" t="s">
+      <c r="BM28" s="191"/>
+      <c r="BN28" s="191"/>
+      <c r="BO28" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="BP28" s="124"/>
-      <c r="BQ28" s="176"/>
+      <c r="BP28" s="191"/>
+      <c r="BQ28" s="193"/>
       <c r="BS28" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="BT28" s="124" t="s">
+      <c r="BT28" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="BU28" s="124"/>
-      <c r="BV28" s="124"/>
-      <c r="BW28" s="124" t="s">
+      <c r="BU28" s="191"/>
+      <c r="BV28" s="191"/>
+      <c r="BW28" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="BX28" s="124"/>
-      <c r="BY28" s="124"/>
-      <c r="BZ28" s="124" t="s">
+      <c r="BX28" s="191"/>
+      <c r="BY28" s="191"/>
+      <c r="BZ28" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="CA28" s="124"/>
-      <c r="CB28" s="124"/>
-      <c r="CC28" s="124" t="s">
+      <c r="CA28" s="191"/>
+      <c r="CB28" s="191"/>
+      <c r="CC28" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="CD28" s="124"/>
-      <c r="CE28" s="124"/>
-      <c r="CF28" s="124" t="s">
+      <c r="CD28" s="191"/>
+      <c r="CE28" s="191"/>
+      <c r="CF28" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="CG28" s="124"/>
-      <c r="CH28" s="124"/>
-      <c r="CI28" s="124" t="s">
+      <c r="CG28" s="191"/>
+      <c r="CH28" s="191"/>
+      <c r="CI28" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="CJ28" s="124"/>
-      <c r="CK28" s="124"/>
-      <c r="CL28" s="124" t="s">
+      <c r="CJ28" s="191"/>
+      <c r="CK28" s="191"/>
+      <c r="CL28" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="CM28" s="124"/>
-      <c r="CN28" s="176"/>
+      <c r="CM28" s="191"/>
+      <c r="CN28" s="193"/>
     </row>
     <row r="29" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="177">
@@ -12346,155 +12356,155 @@
       <c r="B44" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="124" t="s">
+      <c r="C44" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-      <c r="F44" s="124" t="s">
+      <c r="D44" s="191"/>
+      <c r="E44" s="191"/>
+      <c r="F44" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="G44" s="124"/>
-      <c r="H44" s="124"/>
-      <c r="I44" s="124" t="s">
+      <c r="G44" s="191"/>
+      <c r="H44" s="191"/>
+      <c r="I44" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="J44" s="124"/>
-      <c r="K44" s="124"/>
-      <c r="L44" s="124" t="s">
+      <c r="J44" s="191"/>
+      <c r="K44" s="191"/>
+      <c r="L44" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="M44" s="124"/>
-      <c r="N44" s="124"/>
-      <c r="O44" s="124" t="s">
+      <c r="M44" s="191"/>
+      <c r="N44" s="191"/>
+      <c r="O44" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="P44" s="124"/>
-      <c r="Q44" s="124"/>
-      <c r="R44" s="124" t="s">
+      <c r="P44" s="191"/>
+      <c r="Q44" s="191"/>
+      <c r="R44" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="S44" s="124"/>
-      <c r="T44" s="124"/>
-      <c r="U44" s="124" t="s">
+      <c r="S44" s="191"/>
+      <c r="T44" s="191"/>
+      <c r="U44" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="V44" s="124"/>
-      <c r="W44" s="176"/>
+      <c r="V44" s="191"/>
+      <c r="W44" s="193"/>
       <c r="Y44" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="Z44" s="124" t="s">
+      <c r="Z44" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="AA44" s="124"/>
-      <c r="AB44" s="124"/>
-      <c r="AC44" s="124" t="s">
+      <c r="AA44" s="191"/>
+      <c r="AB44" s="191"/>
+      <c r="AC44" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="AD44" s="124"/>
-      <c r="AE44" s="124"/>
-      <c r="AF44" s="124" t="s">
+      <c r="AD44" s="191"/>
+      <c r="AE44" s="191"/>
+      <c r="AF44" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="AG44" s="124"/>
-      <c r="AH44" s="124"/>
-      <c r="AI44" s="124" t="s">
+      <c r="AG44" s="191"/>
+      <c r="AH44" s="191"/>
+      <c r="AI44" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="AJ44" s="124"/>
-      <c r="AK44" s="124"/>
-      <c r="AL44" s="124" t="s">
+      <c r="AJ44" s="191"/>
+      <c r="AK44" s="191"/>
+      <c r="AL44" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="AM44" s="124"/>
-      <c r="AN44" s="124"/>
-      <c r="AO44" s="124" t="s">
+      <c r="AM44" s="191"/>
+      <c r="AN44" s="191"/>
+      <c r="AO44" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="AP44" s="124"/>
-      <c r="AQ44" s="124"/>
-      <c r="AR44" s="124" t="s">
+      <c r="AP44" s="191"/>
+      <c r="AQ44" s="191"/>
+      <c r="AR44" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="AS44" s="124"/>
-      <c r="AT44" s="176"/>
+      <c r="AS44" s="191"/>
+      <c r="AT44" s="193"/>
       <c r="AV44" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="AW44" s="124" t="s">
+      <c r="AW44" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="AX44" s="124"/>
-      <c r="AY44" s="124"/>
-      <c r="AZ44" s="124" t="s">
+      <c r="AX44" s="191"/>
+      <c r="AY44" s="191"/>
+      <c r="AZ44" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="BA44" s="124"/>
-      <c r="BB44" s="124"/>
-      <c r="BC44" s="124" t="s">
+      <c r="BA44" s="191"/>
+      <c r="BB44" s="191"/>
+      <c r="BC44" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="BD44" s="124"/>
-      <c r="BE44" s="124"/>
-      <c r="BF44" s="124" t="s">
+      <c r="BD44" s="191"/>
+      <c r="BE44" s="191"/>
+      <c r="BF44" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="BG44" s="124"/>
-      <c r="BH44" s="124"/>
-      <c r="BI44" s="124" t="s">
+      <c r="BG44" s="191"/>
+      <c r="BH44" s="191"/>
+      <c r="BI44" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="BJ44" s="124"/>
-      <c r="BK44" s="124"/>
-      <c r="BL44" s="124" t="s">
+      <c r="BJ44" s="191"/>
+      <c r="BK44" s="191"/>
+      <c r="BL44" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="BM44" s="124"/>
-      <c r="BN44" s="124"/>
-      <c r="BO44" s="124" t="s">
+      <c r="BM44" s="191"/>
+      <c r="BN44" s="191"/>
+      <c r="BO44" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="BP44" s="124"/>
-      <c r="BQ44" s="176"/>
+      <c r="BP44" s="191"/>
+      <c r="BQ44" s="193"/>
       <c r="BS44" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="BT44" s="124" t="s">
+      <c r="BT44" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="BU44" s="124"/>
-      <c r="BV44" s="124"/>
-      <c r="BW44" s="124" t="s">
+      <c r="BU44" s="191"/>
+      <c r="BV44" s="191"/>
+      <c r="BW44" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="BX44" s="124"/>
-      <c r="BY44" s="124"/>
-      <c r="BZ44" s="124" t="s">
+      <c r="BX44" s="191"/>
+      <c r="BY44" s="191"/>
+      <c r="BZ44" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="CA44" s="124"/>
-      <c r="CB44" s="124"/>
-      <c r="CC44" s="124" t="s">
+      <c r="CA44" s="191"/>
+      <c r="CB44" s="191"/>
+      <c r="CC44" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="CD44" s="124"/>
-      <c r="CE44" s="124"/>
-      <c r="CF44" s="124" t="s">
+      <c r="CD44" s="191"/>
+      <c r="CE44" s="191"/>
+      <c r="CF44" s="191" t="s">
         <v>77</v>
       </c>
-      <c r="CG44" s="124"/>
-      <c r="CH44" s="124"/>
-      <c r="CI44" s="124" t="s">
+      <c r="CG44" s="191"/>
+      <c r="CH44" s="191"/>
+      <c r="CI44" s="191" t="s">
         <v>78</v>
       </c>
-      <c r="CJ44" s="124"/>
-      <c r="CK44" s="124"/>
-      <c r="CL44" s="124" t="s">
+      <c r="CJ44" s="191"/>
+      <c r="CK44" s="191"/>
+      <c r="CL44" s="191" t="s">
         <v>79</v>
       </c>
-      <c r="CM44" s="124"/>
-      <c r="CN44" s="176"/>
+      <c r="CM44" s="191"/>
+      <c r="CN44" s="193"/>
     </row>
     <row r="45" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="177">
@@ -16017,7 +16027,6 @@
       <c r="AG62" s="186"/>
       <c r="AH62" s="187"/>
       <c r="AI62" s="137">
-        <f t="shared" ref="AI62:AI81" si="1">IF($B62="","",Std_Vorlauf_Sel)</f>
         <v>76</v>
       </c>
       <c r="AJ62" s="137"/>
@@ -16037,7 +16046,6 @@
       <c r="AU62" s="136"/>
       <c r="AV62" s="136"/>
       <c r="AW62" s="137">
-        <f t="shared" ref="AW62:AW81" si="3">IF($B62="","",Std_Vorlauf_Inhalt)</f>
         <v>58</v>
       </c>
       <c r="AX62" s="137"/>
@@ -16237,7 +16245,6 @@
       <c r="AG64" s="136"/>
       <c r="AH64" s="136"/>
       <c r="AI64" s="137">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="AJ64" s="137"/>
@@ -16257,7 +16264,6 @@
       <c r="AU64" s="136"/>
       <c r="AV64" s="136"/>
       <c r="AW64" s="137">
-        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="AX64" s="137"/>
@@ -16347,8 +16353,8 @@
       <c r="AF65" s="136"/>
       <c r="AG65" s="136"/>
       <c r="AH65" s="136"/>
-      <c r="AI65" s="137">
-        <f t="shared" si="1"/>
+      <c r="AI65" s="194">
+        <f>IF($BD65="","",Sommermailing!$C$4-Sommermailing!$F$11)</f>
         <v>76</v>
       </c>
       <c r="AJ65" s="137"/>
@@ -16367,8 +16373,8 @@
       <c r="AT65" s="136"/>
       <c r="AU65" s="136"/>
       <c r="AV65" s="136"/>
-      <c r="AW65" s="137">
-        <f t="shared" si="3"/>
+      <c r="AW65" s="195">
+        <f>IF($BD65="","",Sommermailing!$C$4-Sommermailing!$F$17)</f>
         <v>58</v>
       </c>
       <c r="AX65" s="137"/>
@@ -16461,7 +16467,6 @@
       <c r="AG66" s="136"/>
       <c r="AH66" s="136"/>
       <c r="AI66" s="137">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="AJ66" s="137"/>
@@ -16481,7 +16486,6 @@
       <c r="AU66" s="136"/>
       <c r="AV66" s="136"/>
       <c r="AW66" s="137">
-        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="AX66" s="137"/>
@@ -16572,7 +16576,6 @@
       <c r="AG67" s="136"/>
       <c r="AH67" s="136"/>
       <c r="AI67" s="137">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="AJ67" s="137"/>
@@ -16592,7 +16595,6 @@
       <c r="AU67" s="136"/>
       <c r="AV67" s="136"/>
       <c r="AW67" s="137">
-        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="AX67" s="137"/>
@@ -16683,7 +16685,6 @@
       <c r="AG68" s="136"/>
       <c r="AH68" s="136"/>
       <c r="AI68" s="137">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="AJ68" s="137"/>
@@ -16703,7 +16704,6 @@
       <c r="AU68" s="136"/>
       <c r="AV68" s="136"/>
       <c r="AW68" s="137">
-        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="AX68" s="137"/>
@@ -16796,7 +16796,6 @@
       <c r="AG69" s="136"/>
       <c r="AH69" s="136"/>
       <c r="AI69" s="137">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="AJ69" s="137"/>
@@ -16816,7 +16815,6 @@
       <c r="AU69" s="136"/>
       <c r="AV69" s="136"/>
       <c r="AW69" s="137">
-        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="AX69" s="137"/>
@@ -16906,8 +16904,8 @@
       <c r="AF70" s="136"/>
       <c r="AG70" s="136"/>
       <c r="AH70" s="136"/>
-      <c r="AI70" s="137">
-        <f t="shared" si="1"/>
+      <c r="AI70" s="196">
+        <f>IF($BD70="","",Weihnachtsmailing!$C$4-Weihnachtsmailing!$F$11)</f>
         <v>76</v>
       </c>
       <c r="AJ70" s="137"/>
@@ -16926,8 +16924,8 @@
       <c r="AT70" s="136"/>
       <c r="AU70" s="136"/>
       <c r="AV70" s="136"/>
-      <c r="AW70" s="137">
-        <f t="shared" si="3"/>
+      <c r="AW70" s="197">
+        <f>IF($BD70="","",Weihnachtsmailing!$C$4-Weihnachtsmailing!$F$17)</f>
         <v>58</v>
       </c>
       <c r="AX70" s="137"/>
@@ -17020,7 +17018,6 @@
       <c r="AG71" s="136"/>
       <c r="AH71" s="136"/>
       <c r="AI71" s="137">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="AJ71" s="137"/>
@@ -17040,7 +17037,6 @@
       <c r="AU71" s="136"/>
       <c r="AV71" s="136"/>
       <c r="AW71" s="137">
-        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="AX71" s="137"/>
@@ -17128,10 +17124,7 @@
       <c r="AF72" s="136"/>
       <c r="AG72" s="136"/>
       <c r="AH72" s="136"/>
-      <c r="AI72" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI72" s="137"/>
       <c r="AJ72" s="137"/>
       <c r="AK72" s="137"/>
       <c r="AL72" s="137"/>
@@ -17148,10 +17141,7 @@
       <c r="AT72" s="136"/>
       <c r="AU72" s="136"/>
       <c r="AV72" s="136"/>
-      <c r="AW72" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW72" s="137"/>
       <c r="AX72" s="137"/>
       <c r="AY72" s="137"/>
       <c r="AZ72" s="137"/>
@@ -17233,10 +17223,7 @@
       <c r="AF73" s="136"/>
       <c r="AG73" s="136"/>
       <c r="AH73" s="136"/>
-      <c r="AI73" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI73" s="137"/>
       <c r="AJ73" s="137"/>
       <c r="AK73" s="137"/>
       <c r="AL73" s="137"/>
@@ -17253,10 +17240,7 @@
       <c r="AT73" s="136"/>
       <c r="AU73" s="136"/>
       <c r="AV73" s="136"/>
-      <c r="AW73" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW73" s="137"/>
       <c r="AX73" s="137"/>
       <c r="AY73" s="137"/>
       <c r="AZ73" s="137"/>
@@ -17338,10 +17322,7 @@
       <c r="AF74" s="136"/>
       <c r="AG74" s="136"/>
       <c r="AH74" s="136"/>
-      <c r="AI74" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI74" s="137"/>
       <c r="AJ74" s="137"/>
       <c r="AK74" s="137"/>
       <c r="AL74" s="137"/>
@@ -17358,10 +17339,7 @@
       <c r="AT74" s="136"/>
       <c r="AU74" s="136"/>
       <c r="AV74" s="136"/>
-      <c r="AW74" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW74" s="137"/>
       <c r="AX74" s="137"/>
       <c r="AY74" s="137"/>
       <c r="AZ74" s="137"/>
@@ -17443,10 +17421,7 @@
       <c r="AF75" s="136"/>
       <c r="AG75" s="136"/>
       <c r="AH75" s="136"/>
-      <c r="AI75" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI75" s="137"/>
       <c r="AJ75" s="137"/>
       <c r="AK75" s="137"/>
       <c r="AL75" s="137"/>
@@ -17463,10 +17438,7 @@
       <c r="AT75" s="136"/>
       <c r="AU75" s="136"/>
       <c r="AV75" s="136"/>
-      <c r="AW75" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW75" s="137"/>
       <c r="AX75" s="137"/>
       <c r="AY75" s="137"/>
       <c r="AZ75" s="137"/>
@@ -17548,10 +17520,7 @@
       <c r="AF76" s="136"/>
       <c r="AG76" s="136"/>
       <c r="AH76" s="136"/>
-      <c r="AI76" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI76" s="137"/>
       <c r="AJ76" s="137"/>
       <c r="AK76" s="137"/>
       <c r="AL76" s="137"/>
@@ -17568,10 +17537,7 @@
       <c r="AT76" s="136"/>
       <c r="AU76" s="136"/>
       <c r="AV76" s="136"/>
-      <c r="AW76" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW76" s="137"/>
       <c r="AX76" s="137"/>
       <c r="AY76" s="137"/>
       <c r="AZ76" s="137"/>
@@ -17653,10 +17619,7 @@
       <c r="AF77" s="136"/>
       <c r="AG77" s="136"/>
       <c r="AH77" s="136"/>
-      <c r="AI77" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI77" s="137"/>
       <c r="AJ77" s="137"/>
       <c r="AK77" s="137"/>
       <c r="AL77" s="137"/>
@@ -17673,10 +17636,7 @@
       <c r="AT77" s="136"/>
       <c r="AU77" s="136"/>
       <c r="AV77" s="136"/>
-      <c r="AW77" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW77" s="137"/>
       <c r="AX77" s="137"/>
       <c r="AY77" s="137"/>
       <c r="AZ77" s="137"/>
@@ -17758,10 +17718,7 @@
       <c r="AF78" s="136"/>
       <c r="AG78" s="136"/>
       <c r="AH78" s="136"/>
-      <c r="AI78" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI78" s="137"/>
       <c r="AJ78" s="137"/>
       <c r="AK78" s="137"/>
       <c r="AL78" s="137"/>
@@ -17778,10 +17735,7 @@
       <c r="AT78" s="136"/>
       <c r="AU78" s="136"/>
       <c r="AV78" s="136"/>
-      <c r="AW78" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW78" s="137"/>
       <c r="AX78" s="137"/>
       <c r="AY78" s="137"/>
       <c r="AZ78" s="137"/>
@@ -17863,10 +17817,7 @@
       <c r="AF79" s="136"/>
       <c r="AG79" s="136"/>
       <c r="AH79" s="136"/>
-      <c r="AI79" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI79" s="137"/>
       <c r="AJ79" s="137"/>
       <c r="AK79" s="137"/>
       <c r="AL79" s="137"/>
@@ -17883,10 +17834,7 @@
       <c r="AT79" s="136"/>
       <c r="AU79" s="136"/>
       <c r="AV79" s="136"/>
-      <c r="AW79" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW79" s="137"/>
       <c r="AX79" s="137"/>
       <c r="AY79" s="137"/>
       <c r="AZ79" s="137"/>
@@ -17968,10 +17916,7 @@
       <c r="AF80" s="136"/>
       <c r="AG80" s="136"/>
       <c r="AH80" s="136"/>
-      <c r="AI80" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI80" s="137"/>
       <c r="AJ80" s="137"/>
       <c r="AK80" s="137"/>
       <c r="AL80" s="137"/>
@@ -17988,10 +17933,7 @@
       <c r="AT80" s="136"/>
       <c r="AU80" s="136"/>
       <c r="AV80" s="136"/>
-      <c r="AW80" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW80" s="137"/>
       <c r="AX80" s="137"/>
       <c r="AY80" s="137"/>
       <c r="AZ80" s="137"/>
@@ -18073,10 +18015,7 @@
       <c r="AF81" s="136"/>
       <c r="AG81" s="136"/>
       <c r="AH81" s="136"/>
-      <c r="AI81" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="AI81" s="137"/>
       <c r="AJ81" s="137"/>
       <c r="AK81" s="137"/>
       <c r="AL81" s="137"/>
@@ -18093,10 +18032,7 @@
       <c r="AT81" s="136"/>
       <c r="AU81" s="136"/>
       <c r="AV81" s="136"/>
-      <c r="AW81" s="137" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="AW81" s="137"/>
       <c r="AX81" s="137"/>
       <c r="AY81" s="137"/>
       <c r="AZ81" s="137"/>
@@ -18333,7 +18269,7 @@
     </row>
     <row r="85" spans="2:92" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="142" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="C85" s="142"/>
       <c r="D85" s="142"/>
@@ -18428,7 +18364,7 @@
     </row>
     <row r="86" spans="2:92" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="142" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="C86" s="142"/>
       <c r="D86" s="142"/>
@@ -18617,7 +18553,7 @@
       <c r="CN87" s="142"/>
     </row>
   </sheetData>
-  <mergeCells count="829">
+  <mergeCells count="739">
     <mergeCell ref="B83:CN83"/>
     <mergeCell ref="B84:CN84"/>
     <mergeCell ref="B85:CN85"/>
@@ -18844,13 +18780,6 @@
     <mergeCell ref="CL51:CN51"/>
     <mergeCell ref="AV57:BQ57"/>
     <mergeCell ref="BS43:CN43"/>
-    <mergeCell ref="BT44:BV44"/>
-    <mergeCell ref="BW44:BY44"/>
-    <mergeCell ref="BZ44:CB44"/>
-    <mergeCell ref="CC44:CE44"/>
-    <mergeCell ref="CF44:CH44"/>
-    <mergeCell ref="CI44:CK44"/>
-    <mergeCell ref="CL44:CN44"/>
     <mergeCell ref="BT45:BV45"/>
     <mergeCell ref="BW45:BY45"/>
     <mergeCell ref="BZ45:CB45"/>
@@ -18895,13 +18824,6 @@
     <mergeCell ref="BO51:BQ51"/>
     <mergeCell ref="Y57:AT57"/>
     <mergeCell ref="AV43:BQ43"/>
-    <mergeCell ref="AW44:AY44"/>
-    <mergeCell ref="AZ44:BB44"/>
-    <mergeCell ref="BC44:BE44"/>
-    <mergeCell ref="BF44:BH44"/>
-    <mergeCell ref="BI44:BK44"/>
-    <mergeCell ref="BL44:BN44"/>
-    <mergeCell ref="BO44:BQ44"/>
     <mergeCell ref="AW45:AY45"/>
     <mergeCell ref="AZ45:BB45"/>
     <mergeCell ref="BC45:BE45"/>
@@ -18946,13 +18868,6 @@
     <mergeCell ref="AR51:AT51"/>
     <mergeCell ref="B57:W57"/>
     <mergeCell ref="Y43:AT43"/>
-    <mergeCell ref="Z44:AB44"/>
-    <mergeCell ref="AC44:AE44"/>
-    <mergeCell ref="AF44:AH44"/>
-    <mergeCell ref="AI44:AK44"/>
-    <mergeCell ref="AL44:AN44"/>
-    <mergeCell ref="AO44:AQ44"/>
-    <mergeCell ref="AR44:AT44"/>
     <mergeCell ref="Z45:AB45"/>
     <mergeCell ref="AC45:AE45"/>
     <mergeCell ref="AF45:AH45"/>
@@ -19012,13 +18927,6 @@
     <mergeCell ref="U47:W47"/>
     <mergeCell ref="BS41:CN41"/>
     <mergeCell ref="B43:W43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="L44:N44"/>
-    <mergeCell ref="O44:Q44"/>
-    <mergeCell ref="R44:T44"/>
-    <mergeCell ref="U44:W44"/>
     <mergeCell ref="BT37:BV37"/>
     <mergeCell ref="BW37:BY37"/>
     <mergeCell ref="BZ37:CB37"/>
@@ -19048,13 +18956,6 @@
     <mergeCell ref="CL35:CN35"/>
     <mergeCell ref="AV41:BQ41"/>
     <mergeCell ref="BS27:CN27"/>
-    <mergeCell ref="BT28:BV28"/>
-    <mergeCell ref="BW28:BY28"/>
-    <mergeCell ref="BZ28:CB28"/>
-    <mergeCell ref="CC28:CE28"/>
-    <mergeCell ref="CF28:CH28"/>
-    <mergeCell ref="CI28:CK28"/>
-    <mergeCell ref="CL28:CN28"/>
     <mergeCell ref="BT29:BV29"/>
     <mergeCell ref="BW29:BY29"/>
     <mergeCell ref="BZ29:CB29"/>
@@ -19099,13 +19000,6 @@
     <mergeCell ref="BO35:BQ35"/>
     <mergeCell ref="Y41:AT41"/>
     <mergeCell ref="AV27:BQ27"/>
-    <mergeCell ref="AW28:AY28"/>
-    <mergeCell ref="AZ28:BB28"/>
-    <mergeCell ref="BC28:BE28"/>
-    <mergeCell ref="BF28:BH28"/>
-    <mergeCell ref="BI28:BK28"/>
-    <mergeCell ref="BL28:BN28"/>
-    <mergeCell ref="BO28:BQ28"/>
     <mergeCell ref="AW29:AY29"/>
     <mergeCell ref="AZ29:BB29"/>
     <mergeCell ref="BC29:BE29"/>
@@ -19150,13 +19044,6 @@
     <mergeCell ref="AR35:AT35"/>
     <mergeCell ref="B41:W41"/>
     <mergeCell ref="Y27:AT27"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="AF28:AH28"/>
-    <mergeCell ref="AI28:AK28"/>
-    <mergeCell ref="AL28:AN28"/>
-    <mergeCell ref="AO28:AQ28"/>
-    <mergeCell ref="AR28:AT28"/>
     <mergeCell ref="Z29:AB29"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF29:AH29"/>
@@ -19216,13 +19103,6 @@
     <mergeCell ref="U31:W31"/>
     <mergeCell ref="BS25:CN25"/>
     <mergeCell ref="B27:W27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="R28:T28"/>
-    <mergeCell ref="U28:W28"/>
     <mergeCell ref="BT21:BV21"/>
     <mergeCell ref="BW21:BY21"/>
     <mergeCell ref="BZ21:CB21"/>
@@ -19252,13 +19132,6 @@
     <mergeCell ref="CL19:CN19"/>
     <mergeCell ref="AV25:BQ25"/>
     <mergeCell ref="BS11:CN11"/>
-    <mergeCell ref="BT12:BV12"/>
-    <mergeCell ref="BW12:BY12"/>
-    <mergeCell ref="BZ12:CB12"/>
-    <mergeCell ref="CC12:CE12"/>
-    <mergeCell ref="CF12:CH12"/>
-    <mergeCell ref="CI12:CK12"/>
-    <mergeCell ref="CL12:CN12"/>
     <mergeCell ref="BT13:BV13"/>
     <mergeCell ref="BW13:BY13"/>
     <mergeCell ref="BZ13:CB13"/>
@@ -19303,13 +19176,6 @@
     <mergeCell ref="BO19:BQ19"/>
     <mergeCell ref="Y25:AT25"/>
     <mergeCell ref="AV11:BQ11"/>
-    <mergeCell ref="AW12:AY12"/>
-    <mergeCell ref="AZ12:BB12"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BF12:BH12"/>
-    <mergeCell ref="BI12:BK12"/>
-    <mergeCell ref="BL12:BN12"/>
-    <mergeCell ref="BO12:BQ12"/>
     <mergeCell ref="AW13:AY13"/>
     <mergeCell ref="AZ13:BB13"/>
     <mergeCell ref="BC13:BE13"/>
@@ -19354,13 +19220,6 @@
     <mergeCell ref="AR19:AT19"/>
     <mergeCell ref="B25:W25"/>
     <mergeCell ref="Y11:AT11"/>
-    <mergeCell ref="Z12:AB12"/>
-    <mergeCell ref="AC12:AE12"/>
-    <mergeCell ref="AF12:AH12"/>
-    <mergeCell ref="AI12:AK12"/>
-    <mergeCell ref="AL12:AN12"/>
-    <mergeCell ref="AO12:AQ12"/>
-    <mergeCell ref="AR12:AT12"/>
     <mergeCell ref="Z13:AB13"/>
     <mergeCell ref="AC13:AE13"/>
     <mergeCell ref="AF13:AH13"/>
@@ -19420,26 +19279,13 @@
     <mergeCell ref="U15:W15"/>
     <mergeCell ref="B9:CN9"/>
     <mergeCell ref="B11:W11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="U12:W12"/>
     <mergeCell ref="Q2:CN2"/>
     <mergeCell ref="B4:V4"/>
     <mergeCell ref="W4:AA4"/>
-    <mergeCell ref="B5:V5"/>
-    <mergeCell ref="W5:AA5"/>
-    <mergeCell ref="B6:V6"/>
-    <mergeCell ref="W6:AA6"/>
     <mergeCell ref="B7:AC7"/>
     <mergeCell ref="AE4:BQ4"/>
     <mergeCell ref="AE5:BQ5"/>
     <mergeCell ref="AE6:BQ6"/>
-    <mergeCell ref="AE7:AV7"/>
-    <mergeCell ref="AX7:BQ7"/>
     <mergeCell ref="BV4:CN4"/>
     <mergeCell ref="BV5:CN5"/>
     <mergeCell ref="BV6:CN6"/>
@@ -19449,517 +19295,632 @@
     <mergeCell ref="CF7:CN7"/>
   </mergeCells>
   <conditionalFormatting sqref="C13 F13 I13 L13 O13 R13 U13 C15 F15 I15 L15 O15 R15 U15 C17 F17 I17 L17 O17 R17 U17 C19 F19 I19 L19 O19 R19 U19 C21 F21 I21 L21 O21 R21 U21 C23 F23 I23 L23 O23 R23 U23">
-    <cfRule type="expression" dxfId="130" priority="1">
+    <cfRule type="expression" dxfId="136" priority="1">
       <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13 G13 J13 M13 P13 S13 V13 D15 G15 J15 M15 P15 S15 V15 D17 G17 J17 M17 P17 S17 V17 D19 G19 J19 M19 P19 S19 V19 D21 G21 J21 M21 P21 S21 V21 D23 G23 J23 M23 P23 S23 V23">
-    <cfRule type="expression" dxfId="131" priority="2">
+  <conditionalFormatting sqref="C12 F12 I12 L12 O12 R12 U12 C14 F14 I14 L14 O14 R14 U14 C16 F16 I16 L16 O16 R16 U16 C18 F18 I18 L18 O18 R18 U18 C20 F20 I20 L20 O20 R20 U20 C22 F22 I22 L22 O22 R22 U22">
+    <cfRule type="expression" dxfId="137" priority="2">
       <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13 H13 K13 N13 Q13 T13 W13 E15 H15 K15 N15 Q15 T15 W15 E17 H17 K17 N17 Q17 T17 W17 E19 H19 K19 N19 Q19 T19 W19 E21 H21 K21 N21 Q21 T21 W21 E23 H23 K23 N23 Q23 T23 W23">
-    <cfRule type="expression" dxfId="132" priority="3">
+  <conditionalFormatting sqref="D12 G12 J12 M12 P12 S12 V12 D14 G14 J14 M14 P14 S14 V14 D16 G16 J16 M16 P16 S16 V16 D18 G18 J18 M18 P18 S18 V18 D20 G20 J20 M20 P20 S20 V20 D22 G22 J22 M22 P22 S22 V22">
+    <cfRule type="expression" dxfId="137" priority="3">
+      <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12 H12 K12 N12 Q12 T12 W12 E14 H14 K14 N14 Q14 T14 W14 E16 H16 K16 N16 Q16 T16 W16 E18 H18 K18 N18 Q18 T18 W18 E20 H20 K20 N20 Q20 T20 W20 E22 H22 K22 N22 Q22 T22 W22">
+    <cfRule type="expression" dxfId="137" priority="4">
+      <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13 I13 L13 O13 R13 U13 X13 F15 I15 L15 O15 R15 U15 X15 F17 I17 L17 O17 R17 U17 X17 F19 I19 L19 O19 R19 U19 X19 F21 I21 L21 O21 R21 U21 X21 F23 I23 L23 O23 R23 U23 X23">
+    <cfRule type="expression" dxfId="138" priority="5">
       <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14 F14 I14 L14 O14 R14 U14 C16 F16 I16 L16 O16 R16 U16 C18 F18 I18 L18 O18 R18 U18 C20 F20 I20 L20 O20 R20 U20 C22 F22 I22 L22 O22 R22 U22 C24 F24 I24 L24 O24 R24 U24">
-    <cfRule type="expression" dxfId="133" priority="4">
+    <cfRule type="expression" dxfId="139" priority="6">
       <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14 G14 J14 M14 P14 S14 V14 D16 G16 J16 M16 P16 S16 V16 D18 G18 J18 M18 P18 S18 V18 D20 G20 J20 M20 P20 S20 V20 D22 G22 J22 M22 P22 S22 V22 D24 G24 J24 M24 P24 S24 V24">
-    <cfRule type="expression" dxfId="134" priority="5">
+    <cfRule type="expression" dxfId="140" priority="7">
       <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14 H14 K14 N14 Q14 T14 W14 E16 H16 K16 N16 Q16 T16 W16 E18 H18 K18 N18 Q18 T18 W18 E20 H20 K20 N20 Q20 T20 W20 E22 H22 K22 N22 Q22 T22 W22 E24 H24 K24 N24 Q24 T24 W24">
-    <cfRule type="expression" dxfId="135" priority="6">
+    <cfRule type="expression" dxfId="141" priority="8">
       <formula>AND(ISNUMBER(C13),DATE(Planungsjahr,1,C13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z13 AC13 AF13 AI13 AL13 AO13 AR13 Z15 AC15 AF15 AI15 AL15 AO15 AR15 Z17 AC17 AF17 AI17 AL17 AO17 AR17 Z19 AC19 AF19 AI19 AL19 AO19 AR19 Z21 AC21 AF21 AI21 AL21 AO21 AR21 Z23 AC23 AF23 AI23 AL23 AO23 AR23">
-    <cfRule type="expression" dxfId="130" priority="7">
+    <cfRule type="expression" dxfId="136" priority="9">
       <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA13 AD13 AG13 AJ13 AM13 AP13 AS13 AA15 AD15 AG15 AJ15 AM15 AP15 AS15 AA17 AD17 AG17 AJ17 AM17 AP17 AS17 AA19 AD19 AG19 AJ19 AM19 AP19 AS19 AA21 AD21 AG21 AJ21 AM21 AP21 AS21 AA23 AD23 AG23 AJ23 AM23 AP23 AS23">
-    <cfRule type="expression" dxfId="131" priority="8">
+  <conditionalFormatting sqref="Z12 AC12 AF12 AI12 AL12 AO12 AR12 Z14 AC14 AF14 AI14 AL14 AO14 AR14 Z16 AC16 AF16 AI16 AL16 AO16 AR16 Z18 AC18 AF18 AI18 AL18 AO18 AR18 Z20 AC20 AF20 AI20 AL20 AO20 AR20 Z22 AC22 AF22 AI22 AL22 AO22 AR22">
+    <cfRule type="expression" dxfId="137" priority="10">
       <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB13 AE13 AH13 AK13 AN13 AQ13 AT13 AB15 AE15 AH15 AK15 AN15 AQ15 AT15 AB17 AE17 AH17 AK17 AN17 AQ17 AT17 AB19 AE19 AH19 AK19 AN19 AQ19 AT19 AB21 AE21 AH21 AK21 AN21 AQ21 AT21 AB23 AE23 AH23 AK23 AN23 AQ23 AT23">
-    <cfRule type="expression" dxfId="132" priority="9">
+  <conditionalFormatting sqref="AA12 AD12 AG12 AJ12 AM12 AP12 AS12 AA14 AD14 AG14 AJ14 AM14 AP14 AS14 AA16 AD16 AG16 AJ16 AM16 AP16 AS16 AA18 AD18 AG18 AJ18 AM18 AP18 AS18 AA20 AD20 AG20 AJ20 AM20 AP20 AS20 AA22 AD22 AG22 AJ22 AM22 AP22 AS22">
+    <cfRule type="expression" dxfId="137" priority="11">
+      <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB12 AE12 AH12 AK12 AN12 AQ12 AT12 AB14 AE14 AH14 AK14 AN14 AQ14 AT14 AB16 AE16 AH16 AK16 AN16 AQ16 AT16 AB18 AE18 AH18 AK18 AN18 AQ18 AT18 AB20 AE20 AH20 AK20 AN20 AQ20 AT20 AB22 AE22 AH22 AK22 AN22 AQ22 AT22">
+    <cfRule type="expression" dxfId="137" priority="12">
+      <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC13 AF13 AI13 AL13 AO13 AR13 AU13 AC15 AF15 AI15 AL15 AO15 AR15 AU15 AC17 AF17 AI17 AL17 AO17 AR17 AU17 AC19 AF19 AI19 AL19 AO19 AR19 AU19 AC21 AF21 AI21 AL21 AO21 AR21 AU21 AC23 AF23 AI23 AL23 AO23 AR23 AU23">
+    <cfRule type="expression" dxfId="138" priority="13">
       <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z14 AC14 AF14 AI14 AL14 AO14 AR14 Z16 AC16 AF16 AI16 AL16 AO16 AR16 Z18 AC18 AF18 AI18 AL18 AO18 AR18 Z20 AC20 AF20 AI20 AL20 AO20 AR20 Z22 AC22 AF22 AI22 AL22 AO22 AR22 Z24 AC24 AF24 AI24 AL24 AO24 AR24">
-    <cfRule type="expression" dxfId="133" priority="10">
+    <cfRule type="expression" dxfId="139" priority="14">
       <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA14 AD14 AG14 AJ14 AM14 AP14 AS14 AA16 AD16 AG16 AJ16 AM16 AP16 AS16 AA18 AD18 AG18 AJ18 AM18 AP18 AS18 AA20 AD20 AG20 AJ20 AM20 AP20 AS20 AA22 AD22 AG22 AJ22 AM22 AP22 AS22 AA24 AD24 AG24 AJ24 AM24 AP24 AS24">
-    <cfRule type="expression" dxfId="134" priority="11">
+    <cfRule type="expression" dxfId="140" priority="15">
       <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB14 AE14 AH14 AK14 AN14 AQ14 AT14 AB16 AE16 AH16 AK16 AN16 AQ16 AT16 AB18 AE18 AH18 AK18 AN18 AQ18 AT18 AB20 AE20 AH20 AK20 AN20 AQ20 AT20 AB22 AE22 AH22 AK22 AN22 AQ22 AT22 AB24 AE24 AH24 AK24 AN24 AQ24 AT24">
-    <cfRule type="expression" dxfId="135" priority="12">
+    <cfRule type="expression" dxfId="141" priority="16">
       <formula>AND(ISNUMBER(Z13),DATE(Planungsjahr,2,Z13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW13 AZ13 BC13 BF13 BI13 BL13 BO13 AW15 AZ15 BC15 BF15 BI15 BL15 BO15 AW17 AZ17 BC17 BF17 BI17 BL17 BO17 AW19 AZ19 BC19 BF19 BI19 BL19 BO19 AW21 AZ21 BC21 BF21 BI21 BL21 BO21 AW23 AZ23 BC23 BF23 BI23 BL23 BO23">
-    <cfRule type="expression" dxfId="130" priority="13">
+    <cfRule type="expression" dxfId="136" priority="17">
       <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AX13 BA13 BD13 BG13 BJ13 BM13 BP13 AX15 BA15 BD15 BG15 BJ15 BM15 BP15 AX17 BA17 BD17 BG17 BJ17 BM17 BP17 AX19 BA19 BD19 BG19 BJ19 BM19 BP19 AX21 BA21 BD21 BG21 BJ21 BM21 BP21 AX23 BA23 BD23 BG23 BJ23 BM23 BP23">
-    <cfRule type="expression" dxfId="131" priority="14">
+  <conditionalFormatting sqref="AW12 AZ12 BC12 BF12 BI12 BL12 BO12 AW14 AZ14 BC14 BF14 BI14 BL14 BO14 AW16 AZ16 BC16 BF16 BI16 BL16 BO16 AW18 AZ18 BC18 BF18 BI18 BL18 BO18 AW20 AZ20 BC20 BF20 BI20 BL20 BO20 AW22 AZ22 BC22 BF22 BI22 BL22 BO22">
+    <cfRule type="expression" dxfId="137" priority="18">
       <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY13 BB13 BE13 BH13 BK13 BN13 BQ13 AY15 BB15 BE15 BH15 BK15 BN15 BQ15 AY17 BB17 BE17 BH17 BK17 BN17 BQ17 AY19 BB19 BE19 BH19 BK19 BN19 BQ19 AY21 BB21 BE21 BH21 BK21 BN21 BQ21 AY23 BB23 BE23 BH23 BK23 BN23 BQ23">
-    <cfRule type="expression" dxfId="132" priority="15">
+  <conditionalFormatting sqref="AX12 BA12 BD12 BG12 BJ12 BM12 BP12 AX14 BA14 BD14 BG14 BJ14 BM14 BP14 AX16 BA16 BD16 BG16 BJ16 BM16 BP16 AX18 BA18 BD18 BG18 BJ18 BM18 BP18 AX20 BA20 BD20 BG20 BJ20 BM20 BP20 AX22 BA22 BD22 BG22 BJ22 BM22 BP22">
+    <cfRule type="expression" dxfId="137" priority="19">
+      <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AY12 BB12 BE12 BH12 BK12 BN12 BQ12 AY14 BB14 BE14 BH14 BK14 BN14 BQ14 AY16 BB16 BE16 BH16 BK16 BN16 BQ16 AY18 BB18 BE18 BH18 BK18 BN18 BQ18 AY20 BB20 BE20 BH20 BK20 BN20 BQ20 AY22 BB22 BE22 BH22 BK22 BN22 BQ22">
+    <cfRule type="expression" dxfId="137" priority="20">
+      <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AZ13 BC13 BF13 BI13 BL13 BO13 BR13 AZ15 BC15 BF15 BI15 BL15 BO15 BR15 AZ17 BC17 BF17 BI17 BL17 BO17 BR17 AZ19 BC19 BF19 BI19 BL19 BO19 BR19 AZ21 BC21 BF21 BI21 BL21 BO21 BR21 AZ23 BC23 BF23 BI23 BL23 BO23 BR23">
+    <cfRule type="expression" dxfId="138" priority="21">
       <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW14 AZ14 BC14 BF14 BI14 BL14 BO14 AW16 AZ16 BC16 BF16 BI16 BL16 BO16 AW18 AZ18 BC18 BF18 BI18 BL18 BO18 AW20 AZ20 BC20 BF20 BI20 BL20 BO20 AW22 AZ22 BC22 BF22 BI22 BL22 BO22 AW24 AZ24 BC24 BF24 BI24 BL24 BO24">
-    <cfRule type="expression" dxfId="133" priority="16">
+    <cfRule type="expression" dxfId="139" priority="22">
       <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX14 BA14 BD14 BG14 BJ14 BM14 BP14 AX16 BA16 BD16 BG16 BJ16 BM16 BP16 AX18 BA18 BD18 BG18 BJ18 BM18 BP18 AX20 BA20 BD20 BG20 BJ20 BM20 BP20 AX22 BA22 BD22 BG22 BJ22 BM22 BP22 AX24 BA24 BD24 BG24 BJ24 BM24 BP24">
-    <cfRule type="expression" dxfId="134" priority="17">
+    <cfRule type="expression" dxfId="140" priority="23">
       <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY14 BB14 BE14 BH14 BK14 BN14 BQ14 AY16 BB16 BE16 BH16 BK16 BN16 BQ16 AY18 BB18 BE18 BH18 BK18 BN18 BQ18 AY20 BB20 BE20 BH20 BK20 BN20 BQ20 AY22 BB22 BE22 BH22 BK22 BN22 BQ22 AY24 BB24 BE24 BH24 BK24 BN24 BQ24">
-    <cfRule type="expression" dxfId="135" priority="18">
+    <cfRule type="expression" dxfId="141" priority="24">
       <formula>AND(ISNUMBER(AW13),DATE(Planungsjahr,3,AW13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT13 BW13 BZ13 CC13 CF13 CI13 CL13 BT15 BW15 BZ15 CC15 CF15 CI15 CL15 BT17 BW17 BZ17 CC17 CF17 CI17 CL17 BT19 BW19 BZ19 CC19 CF19 CI19 CL19 BT21 BW21 BZ21 CC21 CF21 CI21 CL21 BT23 BW23 BZ23 CC23 CF23 CI23 CL23">
-    <cfRule type="expression" dxfId="130" priority="19">
+    <cfRule type="expression" dxfId="136" priority="25">
       <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU13 BX13 CA13 CD13 CG13 CJ13 CM13 BU15 BX15 CA15 CD15 CG15 CJ15 CM15 BU17 BX17 CA17 CD17 CG17 CJ17 CM17 BU19 BX19 CA19 CD19 CG19 CJ19 CM19 BU21 BX21 CA21 CD21 CG21 CJ21 CM21 BU23 BX23 CA23 CD23 CG23 CJ23 CM23">
-    <cfRule type="expression" dxfId="131" priority="20">
+  <conditionalFormatting sqref="BT12 BW12 BZ12 CC12 CF12 CI12 CL12 BT14 BW14 BZ14 CC14 CF14 CI14 CL14 BT16 BW16 BZ16 CC16 CF16 CI16 CL16 BT18 BW18 BZ18 CC18 CF18 CI18 CL18 BT20 BW20 BZ20 CC20 CF20 CI20 CL20 BT22 BW22 BZ22 CC22 CF22 CI22 CL22">
+    <cfRule type="expression" dxfId="137" priority="26">
       <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV13 BY13 CB13 CE13 CH13 CK13 CN13 BV15 BY15 CB15 CE15 CH15 CK15 CN15 BV17 BY17 CB17 CE17 CH17 CK17 CN17 BV19 BY19 CB19 CE19 CH19 CK19 CN19 BV21 BY21 CB21 CE21 CH21 CK21 CN21 BV23 BY23 CB23 CE23 CH23 CK23 CN23">
-    <cfRule type="expression" dxfId="132" priority="21">
+  <conditionalFormatting sqref="BU12 BX12 CA12 CD12 CG12 CJ12 CM12 BU14 BX14 CA14 CD14 CG14 CJ14 CM14 BU16 BX16 CA16 CD16 CG16 CJ16 CM16 BU18 BX18 CA18 CD18 CG18 CJ18 CM18 BU20 BX20 CA20 CD20 CG20 CJ20 CM20 BU22 BX22 CA22 CD22 CG22 CJ22 CM22">
+    <cfRule type="expression" dxfId="137" priority="27">
+      <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BV12 BY12 CB12 CE12 CH12 CK12 CN12 BV14 BY14 CB14 CE14 CH14 CK14 CN14 BV16 BY16 CB16 CE16 CH16 CK16 CN16 BV18 BY18 CB18 CE18 CH18 CK18 CN18 BV20 BY20 CB20 CE20 CH20 CK20 CN20 BV22 BY22 CB22 CE22 CH22 CK22 CN22">
+    <cfRule type="expression" dxfId="137" priority="28">
+      <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BW13 BZ13 CC13 CF13 CI13 CL13 CO13 BW15 BZ15 CC15 CF15 CI15 CL15 CO15 BW17 BZ17 CC17 CF17 CI17 CL17 CO17 BW19 BZ19 CC19 CF19 CI19 CL19 CO19 BW21 BZ21 CC21 CF21 CI21 CL21 CO21 BW23 BZ23 CC23 CF23 CI23 CL23 CO23">
+    <cfRule type="expression" dxfId="138" priority="29">
       <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT14 BW14 BZ14 CC14 CF14 CI14 CL14 BT16 BW16 BZ16 CC16 CF16 CI16 CL16 BT18 BW18 BZ18 CC18 CF18 CI18 CL18 BT20 BW20 BZ20 CC20 CF20 CI20 CL20 BT22 BW22 BZ22 CC22 CF22 CI22 CL22 BT24 BW24 BZ24 CC24 CF24 CI24 CL24">
-    <cfRule type="expression" dxfId="133" priority="22">
+    <cfRule type="expression" dxfId="139" priority="30">
       <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU14 BX14 CA14 CD14 CG14 CJ14 CM14 BU16 BX16 CA16 CD16 CG16 CJ16 CM16 BU18 BX18 CA18 CD18 CG18 CJ18 CM18 BU20 BX20 CA20 CD20 CG20 CJ20 CM20 BU22 BX22 CA22 CD22 CG22 CJ22 CM22 BU24 BX24 CA24 CD24 CG24 CJ24 CM24">
-    <cfRule type="expression" dxfId="134" priority="23">
+    <cfRule type="expression" dxfId="140" priority="31">
       <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BV14 BY14 CB14 CE14 CH14 CK14 CN14 BV16 BY16 CB16 CE16 CH16 CK16 CN16 BV18 BY18 CB18 CE18 CH18 CK18 CN18 BV20 BY20 CB20 CE20 CH20 CK20 CN20 BV22 BY22 CB22 CE22 CH22 CK22 CN22 BV24 BY24 CB24 CE24 CH24 CK24 CN24">
-    <cfRule type="expression" dxfId="135" priority="24">
+    <cfRule type="expression" dxfId="141" priority="32">
       <formula>AND(ISNUMBER(BT13),DATE(Planungsjahr,4,BT13)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29 F29 I29 L29 O29 R29 U29 C31 F31 I31 L31 O31 R31 U31 C33 F33 I33 L33 O33 R33 U33 C35 F35 I35 L35 O35 R35 U35 C37 F37 I37 L37 O37 R37 U37 C39 F39 I39 L39 O39 R39 U39">
-    <cfRule type="expression" dxfId="130" priority="25">
+    <cfRule type="expression" dxfId="136" priority="33">
       <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29 G29 J29 M29 P29 S29 V29 D31 G31 J31 M31 P31 S31 V31 D33 G33 J33 M33 P33 S33 V33 D35 G35 J35 M35 P35 S35 V35 D37 G37 J37 M37 P37 S37 V37 D39 G39 J39 M39 P39 S39 V39">
-    <cfRule type="expression" dxfId="131" priority="26">
+  <conditionalFormatting sqref="C28 F28 I28 L28 O28 R28 U28 C30 F30 I30 L30 O30 R30 U30 C32 F32 I32 L32 O32 R32 U32 C34 F34 I34 L34 O34 R34 U34 C36 F36 I36 L36 O36 R36 U36 C38 F38 I38 L38 O38 R38 U38">
+    <cfRule type="expression" dxfId="137" priority="34">
       <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E29 H29 K29 N29 Q29 T29 W29 E31 H31 K31 N31 Q31 T31 W31 E33 H33 K33 N33 Q33 T33 W33 E35 H35 K35 N35 Q35 T35 W35 E37 H37 K37 N37 Q37 T37 W37 E39 H39 K39 N39 Q39 T39 W39">
-    <cfRule type="expression" dxfId="132" priority="27">
+  <conditionalFormatting sqref="D28 G28 J28 M28 P28 S28 V28 D30 G30 J30 M30 P30 S30 V30 D32 G32 J32 M32 P32 S32 V32 D34 G34 J34 M34 P34 S34 V34 D36 G36 J36 M36 P36 S36 V36 D38 G38 J38 M38 P38 S38 V38">
+    <cfRule type="expression" dxfId="137" priority="35">
+      <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28 H28 K28 N28 Q28 T28 W28 E30 H30 K30 N30 Q30 T30 W30 E32 H32 K32 N32 Q32 T32 W32 E34 H34 K34 N34 Q34 T34 W34 E36 H36 K36 N36 Q36 T36 W36 E38 H38 K38 N38 Q38 T38 W38">
+    <cfRule type="expression" dxfId="137" priority="36">
+      <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F29 I29 L29 O29 R29 U29 X29 F31 I31 L31 O31 R31 U31 X31 F33 I33 L33 O33 R33 U33 X33 F35 I35 L35 O35 R35 U35 X35 F37 I37 L37 O37 R37 U37 X37 F39 I39 L39 O39 R39 U39 X39">
+    <cfRule type="expression" dxfId="138" priority="37">
       <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30 F30 I30 L30 O30 R30 U30 C32 F32 I32 L32 O32 R32 U32 C34 F34 I34 L34 O34 R34 U34 C36 F36 I36 L36 O36 R36 U36 C38 F38 I38 L38 O38 R38 U38 C40 F40 I40 L40 O40 R40 U40">
-    <cfRule type="expression" dxfId="133" priority="28">
+    <cfRule type="expression" dxfId="139" priority="38">
       <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30 G30 J30 M30 P30 S30 V30 D32 G32 J32 M32 P32 S32 V32 D34 G34 J34 M34 P34 S34 V34 D36 G36 J36 M36 P36 S36 V36 D38 G38 J38 M38 P38 S38 V38 D40 G40 J40 M40 P40 S40 V40">
-    <cfRule type="expression" dxfId="134" priority="29">
+    <cfRule type="expression" dxfId="140" priority="39">
       <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30 H30 K30 N30 Q30 T30 W30 E32 H32 K32 N32 Q32 T32 W32 E34 H34 K34 N34 Q34 T34 W34 E36 H36 K36 N36 Q36 T36 W36 E38 H38 K38 N38 Q38 T38 W38 E40 H40 K40 N40 Q40 T40 W40">
-    <cfRule type="expression" dxfId="135" priority="30">
+    <cfRule type="expression" dxfId="141" priority="40">
       <formula>AND(ISNUMBER(C29),DATE(Planungsjahr,5,C29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z29 AC29 AF29 AI29 AL29 AO29 AR29 Z31 AC31 AF31 AI31 AL31 AO31 AR31 Z33 AC33 AF33 AI33 AL33 AO33 AR33 Z35 AC35 AF35 AI35 AL35 AO35 AR35 Z37 AC37 AF37 AI37 AL37 AO37 AR37 Z39 AC39 AF39 AI39 AL39 AO39 AR39">
-    <cfRule type="expression" dxfId="130" priority="31">
+    <cfRule type="expression" dxfId="136" priority="41">
       <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA29 AD29 AG29 AJ29 AM29 AP29 AS29 AA31 AD31 AG31 AJ31 AM31 AP31 AS31 AA33 AD33 AG33 AJ33 AM33 AP33 AS33 AA35 AD35 AG35 AJ35 AM35 AP35 AS35 AA37 AD37 AG37 AJ37 AM37 AP37 AS37 AA39 AD39 AG39 AJ39 AM39 AP39 AS39">
-    <cfRule type="expression" dxfId="131" priority="32">
+  <conditionalFormatting sqref="Z28 AC28 AF28 AI28 AL28 AO28 AR28 Z30 AC30 AF30 AI30 AL30 AO30 AR30 Z32 AC32 AF32 AI32 AL32 AO32 AR32 Z34 AC34 AF34 AI34 AL34 AO34 AR34 Z36 AC36 AF36 AI36 AL36 AO36 AR36 Z38 AC38 AF38 AI38 AL38 AO38 AR38">
+    <cfRule type="expression" dxfId="137" priority="42">
       <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB29 AE29 AH29 AK29 AN29 AQ29 AT29 AB31 AE31 AH31 AK31 AN31 AQ31 AT31 AB33 AE33 AH33 AK33 AN33 AQ33 AT33 AB35 AE35 AH35 AK35 AN35 AQ35 AT35 AB37 AE37 AH37 AK37 AN37 AQ37 AT37 AB39 AE39 AH39 AK39 AN39 AQ39 AT39">
-    <cfRule type="expression" dxfId="132" priority="33">
+  <conditionalFormatting sqref="AA28 AD28 AG28 AJ28 AM28 AP28 AS28 AA30 AD30 AG30 AJ30 AM30 AP30 AS30 AA32 AD32 AG32 AJ32 AM32 AP32 AS32 AA34 AD34 AG34 AJ34 AM34 AP34 AS34 AA36 AD36 AG36 AJ36 AM36 AP36 AS36 AA38 AD38 AG38 AJ38 AM38 AP38 AS38">
+    <cfRule type="expression" dxfId="137" priority="43">
+      <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB28 AE28 AH28 AK28 AN28 AQ28 AT28 AB30 AE30 AH30 AK30 AN30 AQ30 AT30 AB32 AE32 AH32 AK32 AN32 AQ32 AT32 AB34 AE34 AH34 AK34 AN34 AQ34 AT34 AB36 AE36 AH36 AK36 AN36 AQ36 AT36 AB38 AE38 AH38 AK38 AN38 AQ38 AT38">
+    <cfRule type="expression" dxfId="137" priority="44">
+      <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC29 AF29 AI29 AL29 AO29 AR29 AU29 AC31 AF31 AI31 AL31 AO31 AR31 AU31 AC33 AF33 AI33 AL33 AO33 AR33 AU33 AC35 AF35 AI35 AL35 AO35 AR35 AU35 AC37 AF37 AI37 AL37 AO37 AR37 AU37 AC39 AF39 AI39 AL39 AO39 AR39 AU39">
+    <cfRule type="expression" dxfId="138" priority="45">
       <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z30 AC30 AF30 AI30 AL30 AO30 AR30 Z32 AC32 AF32 AI32 AL32 AO32 AR32 Z34 AC34 AF34 AI34 AL34 AO34 AR34 Z36 AC36 AF36 AI36 AL36 AO36 AR36 Z38 AC38 AF38 AI38 AL38 AO38 AR38 Z40 AC40 AF40 AI40 AL40 AO40 AR40">
-    <cfRule type="expression" dxfId="133" priority="34">
+    <cfRule type="expression" dxfId="139" priority="46">
       <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA30 AD30 AG30 AJ30 AM30 AP30 AS30 AA32 AD32 AG32 AJ32 AM32 AP32 AS32 AA34 AD34 AG34 AJ34 AM34 AP34 AS34 AA36 AD36 AG36 AJ36 AM36 AP36 AS36 AA38 AD38 AG38 AJ38 AM38 AP38 AS38 AA40 AD40 AG40 AJ40 AM40 AP40 AS40">
-    <cfRule type="expression" dxfId="134" priority="35">
+    <cfRule type="expression" dxfId="140" priority="47">
       <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB30 AE30 AH30 AK30 AN30 AQ30 AT30 AB32 AE32 AH32 AK32 AN32 AQ32 AT32 AB34 AE34 AH34 AK34 AN34 AQ34 AT34 AB36 AE36 AH36 AK36 AN36 AQ36 AT36 AB38 AE38 AH38 AK38 AN38 AQ38 AT38 AB40 AE40 AH40 AK40 AN40 AQ40 AT40">
-    <cfRule type="expression" dxfId="135" priority="36">
+    <cfRule type="expression" dxfId="141" priority="48">
       <formula>AND(ISNUMBER(Z29),DATE(Planungsjahr,6,Z29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW29 AZ29 BC29 BF29 BI29 BL29 BO29 AW31 AZ31 BC31 BF31 BI31 BL31 BO31 AW33 AZ33 BC33 BF33 BI33 BL33 BO33 AW35 AZ35 BC35 BF35 BI35 BL35 BO35 AW37 AZ37 BC37 BF37 BI37 BL37 BO37 AW39 AZ39 BC39 BF39 BI39 BL39 BO39">
-    <cfRule type="expression" dxfId="130" priority="37">
+    <cfRule type="expression" dxfId="136" priority="49">
       <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AX29 BA29 BD29 BG29 BJ29 BM29 BP29 AX31 BA31 BD31 BG31 BJ31 BM31 BP31 AX33 BA33 BD33 BG33 BJ33 BM33 BP33 AX35 BA35 BD35 BG35 BJ35 BM35 BP35 AX37 BA37 BD37 BG37 BJ37 BM37 BP37 AX39 BA39 BD39 BG39 BJ39 BM39 BP39">
-    <cfRule type="expression" dxfId="131" priority="38">
+  <conditionalFormatting sqref="AW28 AZ28 BC28 BF28 BI28 BL28 BO28 AW30 AZ30 BC30 BF30 BI30 BL30 BO30 AW32 AZ32 BC32 BF32 BI32 BL32 BO32 AW34 AZ34 BC34 BF34 BI34 BL34 BO34 AW36 AZ36 BC36 BF36 BI36 BL36 BO36 AW38 AZ38 BC38 BF38 BI38 BL38 BO38">
+    <cfRule type="expression" dxfId="137" priority="50">
       <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY29 BB29 BE29 BH29 BK29 BN29 BQ29 AY31 BB31 BE31 BH31 BK31 BN31 BQ31 AY33 BB33 BE33 BH33 BK33 BN33 BQ33 AY35 BB35 BE35 BH35 BK35 BN35 BQ35 AY37 BB37 BE37 BH37 BK37 BN37 BQ37 AY39 BB39 BE39 BH39 BK39 BN39 BQ39">
-    <cfRule type="expression" dxfId="132" priority="39">
+  <conditionalFormatting sqref="AX28 BA28 BD28 BG28 BJ28 BM28 BP28 AX30 BA30 BD30 BG30 BJ30 BM30 BP30 AX32 BA32 BD32 BG32 BJ32 BM32 BP32 AX34 BA34 BD34 BG34 BJ34 BM34 BP34 AX36 BA36 BD36 BG36 BJ36 BM36 BP36 AX38 BA38 BD38 BG38 BJ38 BM38 BP38">
+    <cfRule type="expression" dxfId="137" priority="51">
+      <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AY28 BB28 BE28 BH28 BK28 BN28 BQ28 AY30 BB30 BE30 BH30 BK30 BN30 BQ30 AY32 BB32 BE32 BH32 BK32 BN32 BQ32 AY34 BB34 BE34 BH34 BK34 BN34 BQ34 AY36 BB36 BE36 BH36 BK36 BN36 BQ36 AY38 BB38 BE38 BH38 BK38 BN38 BQ38">
+    <cfRule type="expression" dxfId="137" priority="52">
+      <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AZ29 BC29 BF29 BI29 BL29 BO29 BR29 AZ31 BC31 BF31 BI31 BL31 BO31 BR31 AZ33 BC33 BF33 BI33 BL33 BO33 BR33 AZ35 BC35 BF35 BI35 BL35 BO35 BR35 AZ37 BC37 BF37 BI37 BL37 BO37 BR37 AZ39 BC39 BF39 BI39 BL39 BO39 BR39">
+    <cfRule type="expression" dxfId="138" priority="53">
       <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW30 AZ30 BC30 BF30 BI30 BL30 BO30 AW32 AZ32 BC32 BF32 BI32 BL32 BO32 AW34 AZ34 BC34 BF34 BI34 BL34 BO34 AW36 AZ36 BC36 BF36 BI36 BL36 BO36 AW38 AZ38 BC38 BF38 BI38 BL38 BO38 AW40 AZ40 BC40 BF40 BI40 BL40 BO40">
-    <cfRule type="expression" dxfId="133" priority="40">
+    <cfRule type="expression" dxfId="139" priority="54">
       <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX30 BA30 BD30 BG30 BJ30 BM30 BP30 AX32 BA32 BD32 BG32 BJ32 BM32 BP32 AX34 BA34 BD34 BG34 BJ34 BM34 BP34 AX36 BA36 BD36 BG36 BJ36 BM36 BP36 AX38 BA38 BD38 BG38 BJ38 BM38 BP38 AX40 BA40 BD40 BG40 BJ40 BM40 BP40">
-    <cfRule type="expression" dxfId="134" priority="41">
+    <cfRule type="expression" dxfId="140" priority="55">
       <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY30 BB30 BE30 BH30 BK30 BN30 BQ30 AY32 BB32 BE32 BH32 BK32 BN32 BQ32 AY34 BB34 BE34 BH34 BK34 BN34 BQ34 AY36 BB36 BE36 BH36 BK36 BN36 BQ36 AY38 BB38 BE38 BH38 BK38 BN38 BQ38 AY40 BB40 BE40 BH40 BK40 BN40 BQ40">
-    <cfRule type="expression" dxfId="135" priority="42">
+    <cfRule type="expression" dxfId="141" priority="56">
       <formula>AND(ISNUMBER(AW29),DATE(Planungsjahr,7,AW29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT29 BW29 BZ29 CC29 CF29 CI29 CL29 BT31 BW31 BZ31 CC31 CF31 CI31 CL31 BT33 BW33 BZ33 CC33 CF33 CI33 CL33 BT35 BW35 BZ35 CC35 CF35 CI35 CL35 BT37 BW37 BZ37 CC37 CF37 CI37 CL37 BT39 BW39 BZ39 CC39 CF39 CI39 CL39">
-    <cfRule type="expression" dxfId="130" priority="43">
+    <cfRule type="expression" dxfId="136" priority="57">
       <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU29 BX29 CA29 CD29 CG29 CJ29 CM29 BU31 BX31 CA31 CD31 CG31 CJ31 CM31 BU33 BX33 CA33 CD33 CG33 CJ33 CM33 BU35 BX35 CA35 CD35 CG35 CJ35 CM35 BU37 BX37 CA37 CD37 CG37 CJ37 CM37 BU39 BX39 CA39 CD39 CG39 CJ39 CM39">
-    <cfRule type="expression" dxfId="131" priority="44">
+  <conditionalFormatting sqref="BT28 BW28 BZ28 CC28 CF28 CI28 CL28 BT30 BW30 BZ30 CC30 CF30 CI30 CL30 BT32 BW32 BZ32 CC32 CF32 CI32 CL32 BT34 BW34 BZ34 CC34 CF34 CI34 CL34 BT36 BW36 BZ36 CC36 CF36 CI36 CL36 BT38 BW38 BZ38 CC38 CF38 CI38 CL38">
+    <cfRule type="expression" dxfId="137" priority="58">
       <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV29 BY29 CB29 CE29 CH29 CK29 CN29 BV31 BY31 CB31 CE31 CH31 CK31 CN31 BV33 BY33 CB33 CE33 CH33 CK33 CN33 BV35 BY35 CB35 CE35 CH35 CK35 CN35 BV37 BY37 CB37 CE37 CH37 CK37 CN37 BV39 BY39 CB39 CE39 CH39 CK39 CN39">
-    <cfRule type="expression" dxfId="132" priority="45">
+  <conditionalFormatting sqref="BU28 BX28 CA28 CD28 CG28 CJ28 CM28 BU30 BX30 CA30 CD30 CG30 CJ30 CM30 BU32 BX32 CA32 CD32 CG32 CJ32 CM32 BU34 BX34 CA34 CD34 CG34 CJ34 CM34 BU36 BX36 CA36 CD36 CG36 CJ36 CM36 BU38 BX38 CA38 CD38 CG38 CJ38 CM38">
+    <cfRule type="expression" dxfId="137" priority="59">
+      <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BV28 BY28 CB28 CE28 CH28 CK28 CN28 BV30 BY30 CB30 CE30 CH30 CK30 CN30 BV32 BY32 CB32 CE32 CH32 CK32 CN32 BV34 BY34 CB34 CE34 CH34 CK34 CN34 BV36 BY36 CB36 CE36 CH36 CK36 CN36 BV38 BY38 CB38 CE38 CH38 CK38 CN38">
+    <cfRule type="expression" dxfId="137" priority="60">
+      <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BW29 BZ29 CC29 CF29 CI29 CL29 CO29 BW31 BZ31 CC31 CF31 CI31 CL31 CO31 BW33 BZ33 CC33 CF33 CI33 CL33 CO33 BW35 BZ35 CC35 CF35 CI35 CL35 CO35 BW37 BZ37 CC37 CF37 CI37 CL37 CO37 BW39 BZ39 CC39 CF39 CI39 CL39 CO39">
+    <cfRule type="expression" dxfId="138" priority="61">
       <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT30 BW30 BZ30 CC30 CF30 CI30 CL30 BT32 BW32 BZ32 CC32 CF32 CI32 CL32 BT34 BW34 BZ34 CC34 CF34 CI34 CL34 BT36 BW36 BZ36 CC36 CF36 CI36 CL36 BT38 BW38 BZ38 CC38 CF38 CI38 CL38 BT40 BW40 BZ40 CC40 CF40 CI40 CL40">
-    <cfRule type="expression" dxfId="133" priority="46">
+    <cfRule type="expression" dxfId="139" priority="62">
       <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU30 BX30 CA30 CD30 CG30 CJ30 CM30 BU32 BX32 CA32 CD32 CG32 CJ32 CM32 BU34 BX34 CA34 CD34 CG34 CJ34 CM34 BU36 BX36 CA36 CD36 CG36 CJ36 CM36 BU38 BX38 CA38 CD38 CG38 CJ38 CM38 BU40 BX40 CA40 CD40 CG40 CJ40 CM40">
-    <cfRule type="expression" dxfId="134" priority="47">
+    <cfRule type="expression" dxfId="140" priority="63">
       <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BV30 BY30 CB30 CE30 CH30 CK30 CN30 BV32 BY32 CB32 CE32 CH32 CK32 CN32 BV34 BY34 CB34 CE34 CH34 CK34 CN34 BV36 BY36 CB36 CE36 CH36 CK36 CN36 BV38 BY38 CB38 CE38 CH38 CK38 CN38 BV40 BY40 CB40 CE40 CH40 CK40 CN40">
-    <cfRule type="expression" dxfId="135" priority="48">
+    <cfRule type="expression" dxfId="141" priority="64">
       <formula>AND(ISNUMBER(BT29),DATE(Planungsjahr,8,BT29)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45 F45 I45 L45 O45 R45 U45 C47 F47 I47 L47 O47 R47 U47 C49 F49 I49 L49 O49 R49 U49 C51 F51 I51 L51 O51 R51 U51 C53 F53 I53 L53 O53 R53 U53 C55 F55 I55 L55 O55 R55 U55">
-    <cfRule type="expression" dxfId="130" priority="49">
+    <cfRule type="expression" dxfId="136" priority="65">
       <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D45 G45 J45 M45 P45 S45 V45 D47 G47 J47 M47 P47 S47 V47 D49 G49 J49 M49 P49 S49 V49 D51 G51 J51 M51 P51 S51 V51 D53 G53 J53 M53 P53 S53 V53 D55 G55 J55 M55 P55 S55 V55">
-    <cfRule type="expression" dxfId="131" priority="50">
+  <conditionalFormatting sqref="C44 F44 I44 L44 O44 R44 U44 C46 F46 I46 L46 O46 R46 U46 C48 F48 I48 L48 O48 R48 U48 C50 F50 I50 L50 O50 R50 U50 C52 F52 I52 L52 O52 R52 U52 C54 F54 I54 L54 O54 R54 U54">
+    <cfRule type="expression" dxfId="137" priority="66">
       <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45 H45 K45 N45 Q45 T45 W45 E47 H47 K47 N47 Q47 T47 W47 E49 H49 K49 N49 Q49 T49 W49 E51 H51 K51 N51 Q51 T51 W51 E53 H53 K53 N53 Q53 T53 W53 E55 H55 K55 N55 Q55 T55 W55">
-    <cfRule type="expression" dxfId="132" priority="51">
+  <conditionalFormatting sqref="D44 G44 J44 M44 P44 S44 V44 D46 G46 J46 M46 P46 S46 V46 D48 G48 J48 M48 P48 S48 V48 D50 G50 J50 M50 P50 S50 V50 D52 G52 J52 M52 P52 S52 V52 D54 G54 J54 M54 P54 S54 V54">
+    <cfRule type="expression" dxfId="137" priority="67">
+      <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E44 H44 K44 N44 Q44 T44 W44 E46 H46 K46 N46 Q46 T46 W46 E48 H48 K48 N48 Q48 T48 W48 E50 H50 K50 N50 Q50 T50 W50 E52 H52 K52 N52 Q52 T52 W52 E54 H54 K54 N54 Q54 T54 W54">
+    <cfRule type="expression" dxfId="137" priority="68">
+      <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F45 I45 L45 O45 R45 U45 X45 F47 I47 L47 O47 R47 U47 X47 F49 I49 L49 O49 R49 U49 X49 F51 I51 L51 O51 R51 U51 X51 F53 I53 L53 O53 R53 U53 X53 F55 I55 L55 O55 R55 U55 X55">
+    <cfRule type="expression" dxfId="138" priority="69">
       <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C46 F46 I46 L46 O46 R46 U46 C48 F48 I48 L48 O48 R48 U48 C50 F50 I50 L50 O50 R50 U50 C52 F52 I52 L52 O52 R52 U52 C54 F54 I54 L54 O54 R54 U54 C56 F56 I56 L56 O56 R56 U56">
-    <cfRule type="expression" dxfId="133" priority="52">
+    <cfRule type="expression" dxfId="139" priority="70">
       <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46 G46 J46 M46 P46 S46 V46 D48 G48 J48 M48 P48 S48 V48 D50 G50 J50 M50 P50 S50 V50 D52 G52 J52 M52 P52 S52 V52 D54 G54 J54 M54 P54 S54 V54 D56 G56 J56 M56 P56 S56 V56">
-    <cfRule type="expression" dxfId="134" priority="53">
+    <cfRule type="expression" dxfId="140" priority="71">
       <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46 H46 K46 N46 Q46 T46 W46 E48 H48 K48 N48 Q48 T48 W48 E50 H50 K50 N50 Q50 T50 W50 E52 H52 K52 N52 Q52 T52 W52 E54 H54 K54 N54 Q54 T54 W54 E56 H56 K56 N56 Q56 T56 W56">
-    <cfRule type="expression" dxfId="135" priority="54">
+    <cfRule type="expression" dxfId="141" priority="72">
       <formula>AND(ISNUMBER(C45),DATE(Planungsjahr,9,C45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z45 AC45 AF45 AI45 AL45 AO45 AR45 Z47 AC47 AF47 AI47 AL47 AO47 AR47 Z49 AC49 AF49 AI49 AL49 AO49 AR49 Z51 AC51 AF51 AI51 AL51 AO51 AR51 Z53 AC53 AF53 AI53 AL53 AO53 AR53 Z55 AC55 AF55 AI55 AL55 AO55 AR55">
-    <cfRule type="expression" dxfId="130" priority="55">
+    <cfRule type="expression" dxfId="136" priority="73">
       <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA45 AD45 AG45 AJ45 AM45 AP45 AS45 AA47 AD47 AG47 AJ47 AM47 AP47 AS47 AA49 AD49 AG49 AJ49 AM49 AP49 AS49 AA51 AD51 AG51 AJ51 AM51 AP51 AS51 AA53 AD53 AG53 AJ53 AM53 AP53 AS53 AA55 AD55 AG55 AJ55 AM55 AP55 AS55">
-    <cfRule type="expression" dxfId="131" priority="56">
+  <conditionalFormatting sqref="Z44 AC44 AF44 AI44 AL44 AO44 AR44 Z46 AC46 AF46 AI46 AL46 AO46 AR46 Z48 AC48 AF48 AI48 AL48 AO48 AR48 Z50 AC50 AF50 AI50 AL50 AO50 AR50 Z52 AC52 AF52 AI52 AL52 AO52 AR52 Z54 AC54 AF54 AI54 AL54 AO54 AR54">
+    <cfRule type="expression" dxfId="137" priority="74">
       <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB45 AE45 AH45 AK45 AN45 AQ45 AT45 AB47 AE47 AH47 AK47 AN47 AQ47 AT47 AB49 AE49 AH49 AK49 AN49 AQ49 AT49 AB51 AE51 AH51 AK51 AN51 AQ51 AT51 AB53 AE53 AH53 AK53 AN53 AQ53 AT53 AB55 AE55 AH55 AK55 AN55 AQ55 AT55">
-    <cfRule type="expression" dxfId="132" priority="57">
+  <conditionalFormatting sqref="AA44 AD44 AG44 AJ44 AM44 AP44 AS44 AA46 AD46 AG46 AJ46 AM46 AP46 AS46 AA48 AD48 AG48 AJ48 AM48 AP48 AS48 AA50 AD50 AG50 AJ50 AM50 AP50 AS50 AA52 AD52 AG52 AJ52 AM52 AP52 AS52 AA54 AD54 AG54 AJ54 AM54 AP54 AS54">
+    <cfRule type="expression" dxfId="137" priority="75">
+      <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB44 AE44 AH44 AK44 AN44 AQ44 AT44 AB46 AE46 AH46 AK46 AN46 AQ46 AT46 AB48 AE48 AH48 AK48 AN48 AQ48 AT48 AB50 AE50 AH50 AK50 AN50 AQ50 AT50 AB52 AE52 AH52 AK52 AN52 AQ52 AT52 AB54 AE54 AH54 AK54 AN54 AQ54 AT54">
+    <cfRule type="expression" dxfId="137" priority="76">
+      <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC45 AF45 AI45 AL45 AO45 AR45 AU45 AC47 AF47 AI47 AL47 AO47 AR47 AU47 AC49 AF49 AI49 AL49 AO49 AR49 AU49 AC51 AF51 AI51 AL51 AO51 AR51 AU51 AC53 AF53 AI53 AL53 AO53 AR53 AU53 AC55 AF55 AI55 AL55 AO55 AR55 AU55">
+    <cfRule type="expression" dxfId="138" priority="77">
       <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z46 AC46 AF46 AI46 AL46 AO46 AR46 Z48 AC48 AF48 AI48 AL48 AO48 AR48 Z50 AC50 AF50 AI50 AL50 AO50 AR50 Z52 AC52 AF52 AI52 AL52 AO52 AR52 Z54 AC54 AF54 AI54 AL54 AO54 AR54 Z56 AC56 AF56 AI56 AL56 AO56 AR56">
-    <cfRule type="expression" dxfId="133" priority="58">
+    <cfRule type="expression" dxfId="139" priority="78">
       <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA46 AD46 AG46 AJ46 AM46 AP46 AS46 AA48 AD48 AG48 AJ48 AM48 AP48 AS48 AA50 AD50 AG50 AJ50 AM50 AP50 AS50 AA52 AD52 AG52 AJ52 AM52 AP52 AS52 AA54 AD54 AG54 AJ54 AM54 AP54 AS54 AA56 AD56 AG56 AJ56 AM56 AP56 AS56">
-    <cfRule type="expression" dxfId="134" priority="59">
+    <cfRule type="expression" dxfId="140" priority="79">
       <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB46 AE46 AH46 AK46 AN46 AQ46 AT46 AB48 AE48 AH48 AK48 AN48 AQ48 AT48 AB50 AE50 AH50 AK50 AN50 AQ50 AT50 AB52 AE52 AH52 AK52 AN52 AQ52 AT52 AB54 AE54 AH54 AK54 AN54 AQ54 AT54 AB56 AE56 AH56 AK56 AN56 AQ56 AT56">
-    <cfRule type="expression" dxfId="135" priority="60">
+    <cfRule type="expression" dxfId="141" priority="80">
       <formula>AND(ISNUMBER(Z45),DATE(Planungsjahr,10,Z45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW45 AZ45 BC45 BF45 BI45 BL45 BO45 AW47 AZ47 BC47 BF47 BI47 BL47 BO47 AW49 AZ49 BC49 BF49 BI49 BL49 BO49 AW51 AZ51 BC51 BF51 BI51 BL51 BO51 AW53 AZ53 BC53 BF53 BI53 BL53 BO53 AW55 AZ55 BC55 BF55 BI55 BL55 BO55">
-    <cfRule type="expression" dxfId="130" priority="61">
+    <cfRule type="expression" dxfId="136" priority="81">
       <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AX45 BA45 BD45 BG45 BJ45 BM45 BP45 AX47 BA47 BD47 BG47 BJ47 BM47 BP47 AX49 BA49 BD49 BG49 BJ49 BM49 BP49 AX51 BA51 BD51 BG51 BJ51 BM51 BP51 AX53 BA53 BD53 BG53 BJ53 BM53 BP53 AX55 BA55 BD55 BG55 BJ55 BM55 BP55">
-    <cfRule type="expression" dxfId="131" priority="62">
+  <conditionalFormatting sqref="AW44 AZ44 BC44 BF44 BI44 BL44 BO44 AW46 AZ46 BC46 BF46 BI46 BL46 BO46 AW48 AZ48 BC48 BF48 BI48 BL48 BO48 AW50 AZ50 BC50 BF50 BI50 BL50 BO50 AW52 AZ52 BC52 BF52 BI52 BL52 BO52 AW54 AZ54 BC54 BF54 BI54 BL54 BO54">
+    <cfRule type="expression" dxfId="137" priority="82">
       <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY45 BB45 BE45 BH45 BK45 BN45 BQ45 AY47 BB47 BE47 BH47 BK47 BN47 BQ47 AY49 BB49 BE49 BH49 BK49 BN49 BQ49 AY51 BB51 BE51 BH51 BK51 BN51 BQ51 AY53 BB53 BE53 BH53 BK53 BN53 BQ53 AY55 BB55 BE55 BH55 BK55 BN55 BQ55">
-    <cfRule type="expression" dxfId="132" priority="63">
+  <conditionalFormatting sqref="AX44 BA44 BD44 BG44 BJ44 BM44 BP44 AX46 BA46 BD46 BG46 BJ46 BM46 BP46 AX48 BA48 BD48 BG48 BJ48 BM48 BP48 AX50 BA50 BD50 BG50 BJ50 BM50 BP50 AX52 BA52 BD52 BG52 BJ52 BM52 BP52 AX54 BA54 BD54 BG54 BJ54 BM54 BP54">
+    <cfRule type="expression" dxfId="137" priority="83">
+      <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AY44 BB44 BE44 BH44 BK44 BN44 BQ44 AY46 BB46 BE46 BH46 BK46 BN46 BQ46 AY48 BB48 BE48 BH48 BK48 BN48 BQ48 AY50 BB50 BE50 BH50 BK50 BN50 BQ50 AY52 BB52 BE52 BH52 BK52 BN52 BQ52 AY54 BB54 BE54 BH54 BK54 BN54 BQ54">
+    <cfRule type="expression" dxfId="137" priority="84">
+      <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AZ45 BC45 BF45 BI45 BL45 BO45 BR45 AZ47 BC47 BF47 BI47 BL47 BO47 BR47 AZ49 BC49 BF49 BI49 BL49 BO49 BR49 AZ51 BC51 BF51 BI51 BL51 BO51 BR51 AZ53 BC53 BF53 BI53 BL53 BO53 BR53 AZ55 BC55 BF55 BI55 BL55 BO55 BR55">
+    <cfRule type="expression" dxfId="138" priority="85">
       <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW46 AZ46 BC46 BF46 BI46 BL46 BO46 AW48 AZ48 BC48 BF48 BI48 BL48 BO48 AW50 AZ50 BC50 BF50 BI50 BL50 BO50 AW52 AZ52 BC52 BF52 BI52 BL52 BO52 AW54 AZ54 BC54 BF54 BI54 BL54 BO54 AW56 AZ56 BC56 BF56 BI56 BL56 BO56">
-    <cfRule type="expression" dxfId="133" priority="64">
+    <cfRule type="expression" dxfId="139" priority="86">
       <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AX46 BA46 BD46 BG46 BJ46 BM46 BP46 AX48 BA48 BD48 BG48 BJ48 BM48 BP48 AX50 BA50 BD50 BG50 BJ50 BM50 BP50 AX52 BA52 BD52 BG52 BJ52 BM52 BP52 AX54 BA54 BD54 BG54 BJ54 BM54 BP54 AX56 BA56 BD56 BG56 BJ56 BM56 BP56">
-    <cfRule type="expression" dxfId="134" priority="65">
+    <cfRule type="expression" dxfId="140" priority="87">
       <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY46 BB46 BE46 BH46 BK46 BN46 BQ46 AY48 BB48 BE48 BH48 BK48 BN48 BQ48 AY50 BB50 BE50 BH50 BK50 BN50 BQ50 AY52 BB52 BE52 BH52 BK52 BN52 BQ52 AY54 BB54 BE54 BH54 BK54 BN54 BQ54 AY56 BB56 BE56 BH56 BK56 BN56 BQ56">
-    <cfRule type="expression" dxfId="135" priority="66">
+    <cfRule type="expression" dxfId="141" priority="88">
       <formula>AND(ISNUMBER(AW45),DATE(Planungsjahr,11,AW45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT45 BW45 BZ45 CC45 CF45 CI45 CL45 BT47 BW47 BZ47 CC47 CF47 CI47 CL47 BT49 BW49 BZ49 CC49 CF49 CI49 CL49 BT51 BW51 BZ51 CC51 CF51 CI51 CL51 BT53 BW53 BZ53 CC53 CF53 CI53 CL53 BT55 BW55 BZ55 CC55 CF55 CI55 CL55">
-    <cfRule type="expression" dxfId="130" priority="67">
+    <cfRule type="expression" dxfId="136" priority="89">
       <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU45 BX45 CA45 CD45 CG45 CJ45 CM45 BU47 BX47 CA47 CD47 CG47 CJ47 CM47 BU49 BX49 CA49 CD49 CG49 CJ49 CM49 BU51 BX51 CA51 CD51 CG51 CJ51 CM51 BU53 BX53 CA53 CD53 CG53 CJ53 CM53 BU55 BX55 CA55 CD55 CG55 CJ55 CM55">
-    <cfRule type="expression" dxfId="131" priority="68">
+  <conditionalFormatting sqref="BT44 BW44 BZ44 CC44 CF44 CI44 CL44 BT46 BW46 BZ46 CC46 CF46 CI46 CL46 BT48 BW48 BZ48 CC48 CF48 CI48 CL48 BT50 BW50 BZ50 CC50 CF50 CI50 CL50 BT52 BW52 BZ52 CC52 CF52 CI52 CL52 BT54 BW54 BZ54 CC54 CF54 CI54 CL54">
+    <cfRule type="expression" dxfId="137" priority="90">
       <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BV45 BY45 CB45 CE45 CH45 CK45 CN45 BV47 BY47 CB47 CE47 CH47 CK47 CN47 BV49 BY49 CB49 CE49 CH49 CK49 CN49 BV51 BY51 CB51 CE51 CH51 CK51 CN51 BV53 BY53 CB53 CE53 CH53 CK53 CN53 BV55 BY55 CB55 CE55 CH55 CK55 CN55">
-    <cfRule type="expression" dxfId="132" priority="69">
+  <conditionalFormatting sqref="BU44 BX44 CA44 CD44 CG44 CJ44 CM44 BU46 BX46 CA46 CD46 CG46 CJ46 CM46 BU48 BX48 CA48 CD48 CG48 CJ48 CM48 BU50 BX50 CA50 CD50 CG50 CJ50 CM50 BU52 BX52 CA52 CD52 CG52 CJ52 CM52 BU54 BX54 CA54 CD54 CG54 CJ54 CM54">
+    <cfRule type="expression" dxfId="137" priority="91">
+      <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BV44 BY44 CB44 CE44 CH44 CK44 CN44 BV46 BY46 CB46 CE46 CH46 CK46 CN46 BV48 BY48 CB48 CE48 CH48 CK48 CN48 BV50 BY50 CB50 CE50 CH50 CK50 CN50 BV52 BY52 CB52 CE52 CH52 CK52 CN52 BV54 BY54 CB54 CE54 CH54 CK54 CN54">
+    <cfRule type="expression" dxfId="137" priority="92">
+      <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BW45 BZ45 CC45 CF45 CI45 CL45 CO45 BW47 BZ47 CC47 CF47 CI47 CL47 CO47 BW49 BZ49 CC49 CF49 CI49 CL49 CO49 BW51 BZ51 CC51 CF51 CI51 CL51 CO51 BW53 BZ53 CC53 CF53 CI53 CL53 CO53 BW55 BZ55 CC55 CF55 CI55 CL55 CO55">
+    <cfRule type="expression" dxfId="138" priority="93">
       <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT46 BW46 BZ46 CC46 CF46 CI46 CL46 BT48 BW48 BZ48 CC48 CF48 CI48 CL48 BT50 BW50 BZ50 CC50 CF50 CI50 CL50 BT52 BW52 BZ52 CC52 CF52 CI52 CL52 BT54 BW54 BZ54 CC54 CF54 CI54 CL54 BT56 BW56 BZ56 CC56 CF56 CI56 CL56">
-    <cfRule type="expression" dxfId="133" priority="70">
+    <cfRule type="expression" dxfId="139" priority="94">
       <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU46 BX46 CA46 CD46 CG46 CJ46 CM46 BU48 BX48 CA48 CD48 CG48 CJ48 CM48 BU50 BX50 CA50 CD50 CG50 CJ50 CM50 BU52 BX52 CA52 CD52 CG52 CJ52 CM52 BU54 BX54 CA54 CD54 CG54 CJ54 CM54 BU56 BX56 CA56 CD56 CG56 CJ56 CM56">
-    <cfRule type="expression" dxfId="134" priority="71">
+    <cfRule type="expression" dxfId="140" priority="95">
       <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BV46 BY46 CB46 CE46 CH46 CK46 CN46 BV48 BY48 CB48 CE48 CH48 CK48 CN48 BV50 BY50 CB50 CE50 CH50 CK50 CN50 BV52 BY52 CB52 CE52 CH52 CK52 CN52 BV54 BY54 CB54 CE54 CH54 CK54 CN54 BV56 BY56 CB56 CE56 CH56 CK56 CN56">
-    <cfRule type="expression" dxfId="135" priority="72">
+    <cfRule type="expression" dxfId="141" priority="96">
       <formula>AND(ISNUMBER(BT45),DATE(Planungsjahr,12,BT45)=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:W13 C15:W15 C17:W17 C19:W19 C21:W21 C23:W23">
-    <cfRule type="expression" dxfId="101" priority="202" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="702" stopIfTrue="1">
       <formula>AND(ISNUMBER(C13),COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="203" stopIfTrue="1">
+    <cfRule type="expression" dxfId="101" priority="703" stopIfTrue="1">
       <formula>AND(ISNUMBER(C13),WEEKDAY(DATE(Planungsjahr,1,C13),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14:W14 Z14:AT14 AW14:BQ14 BT14:CN14 C16:W16 Z16:AT16 AW16:BQ16 BT16:CN16 C18:W18 Z18:AT18 AW18:BQ18 BT18:CN18 C20:W20 Z20:AT20 AW20:BQ20 BT20:CN20 C22:W22 Z22:AT22 AW22:BQ22 BT22:CN22 C24:W24 Z24:AT24 AW24:BQ24 BT24:CN24 C30:W30 Z30:AT30 AW30:BQ30 BT30:CN30 C32:W32 Z32:AT32 AW32:BQ32 BT32:CN32 C34:W34 Z34:AT34 AW34:BQ34 BT34:CN34 C36:W36 Z36:AT36 AW36:BQ36 BT36:CN36 C38:W38 Z38:AT38 AW38:BQ38 BT38:CN38 C40:W40 Z40:AT40 AW40:BQ40 BT40:CN40 C46:W46 Z46:AT46 AW46:BQ46 BT46:CN46 C48:W48 Z48:AT48 AW48:BQ48 BT48:CN48 C50:W50 Z50:AT50 AW50:BQ50 BT50:CN50 C52:W52 Z52:AT52 AW52:BQ52 BT52:CN52 C54:W54 Z54:AT54 AW54:BQ54 BT54:CN54 C56:W56 Z56:AT56 AW56:BQ56 BT56:CN56">
-    <cfRule type="cellIs" dxfId="100" priority="230" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="730" stopIfTrue="1" operator="equal">
       <formula>"w"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="229" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="729" stopIfTrue="1" operator="equal">
       <formula>"h"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="228" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="728" stopIfTrue="1" operator="equal">
       <formula>"P"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="227" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="727" stopIfTrue="1" operator="equal">
       <formula>"I"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="226" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="726" stopIfTrue="1" operator="equal">
       <formula>"S"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:W29 C31:W31 C33:W33 C35:W35 C37:W37 C39:W39">
-    <cfRule type="expression" dxfId="94" priority="210" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="710" stopIfTrue="1">
       <formula>AND(ISNUMBER(C29),COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="211" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="711" stopIfTrue="1">
       <formula>AND(ISNUMBER(C29),WEEKDAY(DATE(Planungsjahr,5,C29),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45:W45 C47:W47 C49:W49 C51:W51 C53:W53 C55:W55">
-    <cfRule type="expression" dxfId="92" priority="218" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="718" stopIfTrue="1">
       <formula>AND(ISNUMBER(C45),COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="219" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="719" stopIfTrue="1">
       <formula>AND(ISNUMBER(C45),WEEKDAY(DATE(Planungsjahr,9,C45),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z62:Z81">
-    <cfRule type="expression" dxfId="0" priority="231">
+    <cfRule type="expression" dxfId="0" priority="731">
       <formula>AND(ISNUMBER(Z62),YEAR(Z62)&lt;&gt;Planungsjahr)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z13:AT13 Z15:AT15 Z17:AT17 Z19:AT19 Z21:AT21 Z23:AT23">
-    <cfRule type="expression" dxfId="90" priority="204" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="704" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z13),COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="205" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="705" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z13),WEEKDAY(DATE(Planungsjahr,2,Z13),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z29:AT29 Z31:AT31 Z33:AT33 Z35:AT35 Z37:AT37 Z39:AT39">
-    <cfRule type="expression" dxfId="88" priority="212" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="712" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z29),COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="213" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="713" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z29),WEEKDAY(DATE(Planungsjahr,6,Z29),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z45:AT45 Z47:AT47 Z49:AT49 Z51:AT51 Z53:AT53 Z55:AT55">
-    <cfRule type="expression" dxfId="87" priority="221" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="721" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z45),WEEKDAY(DATE(Planungsjahr,10,Z45),2)&gt;5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="220" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="720" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z45),COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE7 AX7">
-    <cfRule type="expression" dxfId="85" priority="201">
-      <formula>LEFT(AE7,1)="⚠"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AP62:AP81">
-    <cfRule type="expression" dxfId="84" priority="232">
+    <cfRule type="expression" dxfId="84" priority="732">
       <formula>AND(ISNUMBER(AP62),YEAR(AP62)&lt;&gt;Planungsjahr)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW13:BQ13 AW15:BQ15 AW17:BQ17 AW19:BQ19 AW21:BQ21 AW23:BQ23">
-    <cfRule type="expression" dxfId="83" priority="207" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="707" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW13),WEEKDAY(DATE(Planungsjahr,3,AW13),2)&gt;5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="206" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="706" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW13),COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW29:BQ29 AW31:BQ31 AW33:BQ33 AW35:BQ35 AW37:BQ37 AW39:BQ39">
-    <cfRule type="expression" dxfId="81" priority="215" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="715" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW29),WEEKDAY(DATE(Planungsjahr,7,AW29),2)&gt;5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="214" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="714" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW29),COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW45:BQ45 AW47:BQ47 AW49:BQ49 AW51:BQ51 AW53:BQ53 AW55:BQ55">
-    <cfRule type="expression" dxfId="78" priority="222" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="722" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW45),COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="223" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="723" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW45),WEEKDAY(DATE(Planungsjahr,11,AW45),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD62:BD81">
-    <cfRule type="expression" dxfId="77" priority="233">
+    <cfRule type="expression" dxfId="77" priority="733">
       <formula>AND(ISNUMBER(BD62),YEAR(BD62)&lt;&gt;Planungsjahr)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="234">
+    <cfRule type="expression" dxfId="76" priority="734">
       <formula>AND(ISNUMBER(BD62),ISNUMBER(SEARCH("prüfen",$BU62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BD63:BD81">
-    <cfRule type="expression" dxfId="75" priority="235">
+    <cfRule type="expression" dxfId="75" priority="735">
       <formula>AND(ISNUMBER(BD63),ISNUMBER(BD62),BD63&lt;BD62)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT13:CN13 BT15:CN15 BT17:CN17 BT19:CN19 BT21:CN21 BT23:CN23">
-    <cfRule type="expression" dxfId="74" priority="209" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="709" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT13),WEEKDAY(DATE(Planungsjahr,4,BT13),2)&gt;5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="208" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="708" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT13),COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT29:CN29 BT31:CN31 BT33:CN33 BT35:CN35 BT37:CN37 BT39:CN39">
-    <cfRule type="expression" dxfId="71" priority="216" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="716" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT29),COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="217" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="717" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT29),WEEKDAY(DATE(Planungsjahr,8,BT29),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT45:CN45 BT47:CN47 BT49:CN49 BT51:CN51 BT53:CN53 BT55:CN55">
-    <cfRule type="expression" dxfId="69" priority="224" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="724" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT45),COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="725" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT45),WEEKDAY(DATE(Planungsjahr,12,BT45),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Art der Bitte" prompt="Bitte auswählen: aktiv, passiv oder nein" sqref="BM62:BM81" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"aktiv,passiv,nein"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="PAL" error="Bitte ein Datum eingeben." promptTitle="PAL" prompt="Geplanter Eingang bei der Zielgruppe (Briefkasten-Termin), z. B. 26.11.2027" sqref="BD62:BD81" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>36526</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vorlauf Selektion" error="Bitte eine ganze Zahl ≥ 0 eingeben." promptTitle="Vorlauf Selektion" prompt="Tage vor PAL. Vorbelegt mit dem Standardwert oben – bei Bedarf einfach mit eigener Zahl überschreiben." sqref="AI62:AI81" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vorlauf Selektion" error="Bitte eine ganze Zahl ≥ 0 eingeben." promptTitle="Vorlauf Selektion" prompt="Tage vor PAL. Sommer- und Weihnachtsmailing: automatisch aus dem Gantt (Blatt 2/3), bitte nicht überschreiben. Alle anderen Maßnahmen: hier eintragen." sqref="AI62:AI81" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vorlauf Inhalt" error="Bitte eine ganze Zahl ≥ 0 eingeben." promptTitle="Vorlauf Inhalt" prompt="Tage vor PAL. Vorbelegt mit dem Standardwert oben – bei Bedarf einfach mit eigener Zahl überschreiben." sqref="AW62:AW81" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vorlauf Inhalt" error="Bitte eine ganze Zahl ≥ 0 eingeben." promptTitle="Vorlauf Inhalt" prompt="Tage vor PAL. Sommer- und Weihnachtsmailing: automatisch aus dem Gantt (Blatt 2/3), bitte nicht überschreiben. Alle anderen Maßnahmen: hier eintragen." sqref="AW62:AW81" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Auflage" error="Bitte eine ganze Zahl eingeben." promptTitle="Auflage" prompt="Geplante Auflage (optional, Hinweisfeld)" sqref="V62:V81" xr:uid="{00000000-0002-0000-0000-000004000000}">
@@ -19968,12 +19929,6 @@
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Planungsjahr" error="Bitte ein Jahr zwischen 2000 und 2100 eingeben." promptTitle="Planungsjahr" prompt="Jahr ändern: Kalender und Feiertage passen sich automatisch an." sqref="W4" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>2000</formula1>
       <formula2>2100</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vorlauf Selektion" error="Bitte eine ganze Zahl ≥ 0 eingeben." promptTitle="Vorlauf Selektion" prompt="Gantt: Selektion einleiten 2 + Freigabe 5 + Selektion erstellen 52 + Produktion &amp; Versand 17 = 76 Tage. Gilt für alle Zeilen ohne eigenen Wert." sqref="W5" xr:uid="{00000000-0002-0000-0000-000006000000}">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vorlauf Inhalt" error="Bitte eine ganze Zahl ≥ 0 eingeben." promptTitle="Vorlauf Inhalt" prompt="Gantt: Thema 1 + Texte 7 + Gestaltung 14 + Korrektur 5 + Freigaben 14 + Produktion &amp; Versand 17 = 58 Tage. Gilt für alle Zeilen ohne eigenen Wert." sqref="W6" xr:uid="{00000000-0002-0000-0000-000007000000}">
-      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -19986,7 +19941,7 @@
     <brk id="58" max="16383" man="1"/>
   </rowBreaks>
   <ignoredErrors>
-    <ignoredError sqref="B11:CN57" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1"/>
+    <ignoredError sqref="B11:CO57" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1"/>
   </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -20908,14 +20863,15 @@
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="70">
-        <f>INDEX(JP_StartSel,MATCH($E$4,JP_Massnahme,0))</f>
+        <f>Plan_Sommer[[#This Row],[Ende]]-Plan_Sommer[[#This Row],[Dauer
+in Tage]]</f>
         <v>46481</v>
       </c>
       <c r="G11" s="71">
         <v>2</v>
       </c>
       <c r="H11" s="72">
-        <f>F11+G11</f>
+        <f>F13</f>
         <v>46483</v>
       </c>
       <c r="I11" s="44" t="str">
@@ -21231,14 +21187,15 @@
       <c r="D13" s="56"/>
       <c r="E13" s="57"/>
       <c r="F13" s="70">
-        <f>H11</f>
+        <f>Plan_Sommer[[#This Row],[Ende]]-Plan_Sommer[[#This Row],[Dauer
+in Tage]]</f>
         <v>46483</v>
       </c>
       <c r="G13" s="71">
         <v>5</v>
       </c>
       <c r="H13" s="72">
-        <f>F13+G13</f>
+        <f>F14</f>
         <v>46488</v>
       </c>
       <c r="I13" s="44" t="str">
@@ -21478,11 +21435,11 @@
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="70">
-        <f>H13</f>
+        <f>Plan_Sommer[[#This Row],[Ende]]-Plan_Sommer[[#This Row],[Dauer
+in Tage]]</f>
         <v>46488</v>
       </c>
       <c r="G14" s="71">
-        <f>H14-F14</f>
         <v>52</v>
       </c>
       <c r="H14" s="72">
@@ -22205,11 +22162,11 @@
       <c r="D17" s="63"/>
       <c r="E17" s="57"/>
       <c r="F17" s="70">
-        <f>INDEX(JP_StartInhalt,MATCH($E$4,JP_Massnahme,0))</f>
+        <f>Plan_Sommer[[#This Row],[Ende]]-Plan_Sommer[[#This Row],[Dauer
+in Tage]]</f>
         <v>46499</v>
       </c>
       <c r="G17" s="71">
-        <f>H17-F17</f>
         <v>1</v>
       </c>
       <c r="H17" s="72">
@@ -29285,11 +29242,6 @@
       <formula>AND(TODAY()&gt;=F$7,TODAY()&lt;G$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14 G17">
-    <cfRule type="cellIs" dxfId="47" priority="3000" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
     <cfRule type="expression" dxfId="46" priority="54">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
@@ -29342,7 +29294,7 @@
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10" xr:uid="{E87210D7-3045-41D8-B549-D8254C353C87}">
       <formula1>"Ziel,Meilenstein,Im Plan, Geringes Risiko, Mittleres Risiko, Hohes Risiko"</formula1>
     </dataValidation>
@@ -29357,12 +29309,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C45" xr:uid="{2B59BEAD-9C8D-422A-A3A2-A5C66751BF48}">
       <formula1>$C$5:$H$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Verknüpfung" prompt="Name der Maßnahme auf Blatt „Jahresplanung“. Von hier kommen PAL, Start Selektion und Start inhaltliche Arbeit." sqref="E4" xr:uid="{00000000-0002-0000-0100-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Verknüpfung" prompt="Name der Maßnahme auf Blatt „Jahresplanung“. Von hier kommt der PAL (Briefkasten-Datum). Der Vorlauf wird aus diesem Gantt nach Blatt 1 übertragen." sqref="E4" xr:uid="{00000000-0002-0000-0100-000008000000}">
       <formula1>JP_Massnahme</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Briefkasten-Datum (PAL)" prompt="Wird aus Blatt „Jahresplanung“ übernommen – bitte dort ändern." sqref="C4" xr:uid="{00000000-0002-0000-0100-000009000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Start Selektion" prompt="Kommt aus Blatt „Jahresplanung“ (PAL − Vorlauf Selektion). „Selektion erstellen“ füllt die Zeit bis zur Übergabe an den Lettershop." sqref="F11" xr:uid="{00000000-0002-0000-0100-00000A000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Start inhaltliche Arbeit" prompt="Kommt aus Blatt „Jahresplanung“ (PAL − Vorlauf Inhalt). „Thema definieren“ dauert bis zum Beginn der Texterstellung." sqref="F17" xr:uid="{00000000-0002-0000-0100-00000B000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -30381,14 +30331,15 @@
       </c>
       <c r="E11" s="57"/>
       <c r="F11" s="70">
-        <f>INDEX(JP_StartSel,MATCH($E$4,JP_Massnahme,0))</f>
+        <f>Plan_Weihnachten[[#This Row],[Ende]]-Plan_Weihnachten[[#This Row],[Dauer
+in Tage]]</f>
         <v>46641</v>
       </c>
       <c r="G11" s="71">
         <v>2</v>
       </c>
       <c r="H11" s="72">
-        <f>F11+G11</f>
+        <f>F13</f>
         <v>46643</v>
       </c>
       <c r="I11" s="44" t="str">
@@ -30704,14 +30655,15 @@
       <c r="D13" s="56"/>
       <c r="E13" s="57"/>
       <c r="F13" s="70">
-        <f>H11</f>
+        <f>Plan_Weihnachten[[#This Row],[Ende]]-Plan_Weihnachten[[#This Row],[Dauer
+in Tage]]</f>
         <v>46643</v>
       </c>
       <c r="G13" s="71">
         <v>5</v>
       </c>
       <c r="H13" s="72">
-        <f>F13+G13</f>
+        <f>F14</f>
         <v>46648</v>
       </c>
       <c r="I13" s="44" t="str">
@@ -30951,11 +30903,11 @@
       </c>
       <c r="E14" s="57"/>
       <c r="F14" s="70">
-        <f>H13</f>
+        <f>Plan_Weihnachten[[#This Row],[Ende]]-Plan_Weihnachten[[#This Row],[Dauer
+in Tage]]</f>
         <v>46648</v>
       </c>
       <c r="G14" s="71">
-        <f>H14-F14</f>
         <v>52</v>
       </c>
       <c r="H14" s="72">
@@ -31678,11 +31630,11 @@
       <c r="D17" s="63"/>
       <c r="E17" s="57"/>
       <c r="F17" s="70">
-        <f>INDEX(JP_StartInhalt,MATCH($E$4,JP_Massnahme,0))</f>
+        <f>Plan_Weihnachten[[#This Row],[Ende]]-Plan_Weihnachten[[#This Row],[Dauer
+in Tage]]</f>
         <v>46659</v>
       </c>
       <c r="G17" s="71">
-        <f>H17-F17</f>
         <v>1</v>
       </c>
       <c r="H17" s="72">
@@ -38758,11 +38710,6 @@
       <formula>AND(TODAY()&gt;=F$7,TODAY()&lt;G$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14 G17">
-    <cfRule type="cellIs" dxfId="13" priority="3000" operator="lessThan">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
     <cfRule type="expression" dxfId="12" priority="54">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
@@ -38815,7 +38762,7 @@
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10" xr:uid="{AE36670D-A762-476F-A998-26F2E53DA15E}">
       <formula1>"Ziel,Meilenstein,Im Plan, Geringes Risiko, Mittleres Risiko, Hohes Risiko"</formula1>
     </dataValidation>
@@ -38830,12 +38777,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C45" xr:uid="{1FA86119-1C0F-4FE6-BDF6-8944579FCF85}">
       <formula1>$C$5:$H$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Verknüpfung" prompt="Name der Maßnahme auf Blatt „Jahresplanung“. Von hier kommen PAL, Start Selektion und Start inhaltliche Arbeit." sqref="E4" xr:uid="{00000000-0002-0000-0200-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Verknüpfung" prompt="Name der Maßnahme auf Blatt „Jahresplanung“. Von hier kommt der PAL (Briefkasten-Datum). Der Vorlauf wird aus diesem Gantt nach Blatt 1 übertragen." sqref="E4" xr:uid="{00000000-0002-0000-0200-000008000000}">
       <formula1>JP_Massnahme</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Briefkasten-Datum (PAL)" prompt="Wird aus Blatt „Jahresplanung“ übernommen – bitte dort ändern." sqref="C4" xr:uid="{00000000-0002-0000-0200-000009000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Start Selektion" prompt="Kommt aus Blatt „Jahresplanung“ (PAL − Vorlauf Selektion). „Selektion erstellen“ füllt die Zeit bis zur Übergabe an den Lettershop." sqref="F11" xr:uid="{00000000-0002-0000-0200-00000A000000}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Start inhaltliche Arbeit" prompt="Kommt aus Blatt „Jahresplanung“ (PAL − Vorlauf Inhalt). „Thema definieren“ dauert bis zum Beginn der Texterstellung." sqref="F17" xr:uid="{00000000-0002-0000-0200-00000B000000}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
+++ b/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Feiertage NRW" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Jahresplanung!$A$1:$CN$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Jahresplanung!$A$1:$CN$88</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Sommermailing!$6:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">Weihnachtsmailing!$6:$9</definedName>
     <definedName name="Feiertage">'Feiertage NRW'!$B$7:$B$17</definedName>
@@ -24,6 +24,9 @@
     <definedName name="JP_Auflage">Jahresplanung!$V$62:$V$81</definedName>
     <definedName name="JP_Massnahme">Jahresplanung!$B$62:$B$81</definedName>
     <definedName name="JP_PAL">Jahresplanung!$BD$62:$BD$81</definedName>
+    <definedName name="JP_ShowInhalt">Jahresplanung!$R$62:$R$81</definedName>
+    <definedName name="JP_ShowPAL">Jahresplanung!$T$62:$T$81</definedName>
+    <definedName name="JP_ShowSel">Jahresplanung!$P$62:$P$81</definedName>
     <definedName name="JP_StartInhalt">Jahresplanung!$AP$62:$AP$81</definedName>
     <definedName name="JP_StartSel">Jahresplanung!$Z$62:$Z$81</definedName>
     <definedName name="JP_VorlaufInhalt">Jahresplanung!$AW$62:$AW$81</definedName>
@@ -55,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="158">
   <si>
     <t xml:space="preserve">Erstellen eines Gantt-Diagramms
 Geben Sie den Titel dieses Projekts in Zelle B2 ein.
@@ -589,6 +592,18 @@
   <si>
     <t xml:space="preserve">• Sommer- und Weihnachtsmailing: Der PAL hier steuert die gleichnamigen Detailblätter. Dauern der Arbeitsschritte im Gantt ändern = Vorlauf und Starttermine hier ändern sich mit. Verknüpfung über den Namen in Spalte „Maßnahme“.</t>
   </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Häkchen S · I · P neben der Maßnahme: legt fest, ob Start Selektion, Start inhaltliche Arbeit und PAL im Kalender erscheinen. Häkchen entfernen blendet nur den Marker aus.</t>
+  </si>
 </sst>
 </file>
 
@@ -603,7 +618,7 @@
     <numFmt numFmtId="169" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="170" formatCode="[$-407]dddd"/>
   </numFmts>
-  <fonts count="67" x14ac:knownFonts="1">
+  <fonts count="70" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1096,6 +1111,27 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE30714"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1891,7 +1927,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2463,6 +2499,30 @@
     </xf>
     <xf numFmtId="1" fontId="66" fillId="20" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -4361,6 +4421,23 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2ACA8EBD-BA36-409E-8FDC-8847FB450D69}" name="Plan_Sommer" displayName="Plan_Sommer" ref="B9:H46" totalsRowShown="0" headerRowDxfId="116">
   <tableColumns count="7">
@@ -4675,7 +4752,7 @@
   <sheetPr>
     <tabColor rgb="FFE30714"/>
   </sheetPr>
-  <dimension ref="B1:CN87"/>
+  <dimension ref="B1:CN88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.42578125" customWidth="1"/>
@@ -5641,342 +5718,342 @@
     <row r="14" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="167"/>
       <c r="C14" s="159" t="str">
-        <f>IF(ISNUMBER(C13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,C13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D14" s="159" t="str">
-        <f>IF(ISNUMBER(C13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,C13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E14" s="159" t="str">
-        <f>IF(ISNUMBER(C13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,C13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F14" s="159" t="str">
-        <f>IF(ISNUMBER(F13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,F13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G14" s="159" t="str">
-        <f>IF(ISNUMBER(F13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,F13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H14" s="159" t="str">
-        <f>IF(ISNUMBER(F13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,F13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I14" s="159" t="str">
-        <f>IF(ISNUMBER(I13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,I13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J14" s="159" t="str">
-        <f>IF(ISNUMBER(I13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,I13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K14" s="159" t="str">
-        <f>IF(ISNUMBER(I13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,I13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L14" s="159" t="str">
-        <f>IF(ISNUMBER(L13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,L13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M14" s="159" t="str">
-        <f>IF(ISNUMBER(L13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,L13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N14" s="159" t="str">
-        <f>IF(ISNUMBER(L13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,L13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O14" s="159" t="str">
-        <f>IF(ISNUMBER(O13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,O13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="P14" s="159" t="str">
-        <f>IF(ISNUMBER(O13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,O13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="Q14" s="159" t="str">
-        <f>IF(ISNUMBER(O13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,O13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="R14" s="159" t="str">
-        <f>IF(ISNUMBER(R13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,R13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S14" s="159" t="str">
-        <f>IF(ISNUMBER(R13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,R13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T14" s="159" t="str">
-        <f>IF(ISNUMBER(R13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,R13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U14" s="159" t="str">
-        <f>IF(ISNUMBER(U13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,U13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V14" s="159" t="str">
-        <f>IF(ISNUMBER(U13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,U13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W14" s="168" t="str">
-        <f>IF(ISNUMBER(U13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,U13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y14" s="179"/>
       <c r="Z14" s="159" t="str">
-        <f>IF(ISNUMBER(Z13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,Z13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA14" s="159" t="str">
-        <f>IF(ISNUMBER(Z13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,Z13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB14" s="159" t="str">
-        <f>IF(ISNUMBER(Z13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,Z13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC14" s="159" t="str">
-        <f>IF(ISNUMBER(AC13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AC13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD14" s="159" t="str">
-        <f>IF(ISNUMBER(AC13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AC13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE14" s="159" t="str">
-        <f>IF(ISNUMBER(AC13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AC13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF14" s="159" t="str">
-        <f>IF(ISNUMBER(AF13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AF13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG14" s="159" t="str">
-        <f>IF(ISNUMBER(AF13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AF13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH14" s="159" t="str">
-        <f>IF(ISNUMBER(AF13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AF13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI14" s="159" t="str">
-        <f>IF(ISNUMBER(AI13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AI13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ14" s="159" t="str">
-        <f>IF(ISNUMBER(AI13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AI13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK14" s="159" t="str">
-        <f>IF(ISNUMBER(AI13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AI13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL14" s="159" t="str">
-        <f>IF(ISNUMBER(AL13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AL13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM14" s="159" t="str">
-        <f>IF(ISNUMBER(AL13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AL13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN14" s="159" t="str">
-        <f>IF(ISNUMBER(AL13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AL13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO14" s="159" t="str">
-        <f>IF(ISNUMBER(AO13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AO13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="AP14" s="159" t="str">
-        <f>IF(ISNUMBER(AO13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AO13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ14" s="159" t="str">
-        <f>IF(ISNUMBER(AO13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AO13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR14" s="159" t="str">
-        <f>IF(ISNUMBER(AR13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AR13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS14" s="159" t="str">
-        <f>IF(ISNUMBER(AR13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AR13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT14" s="180" t="str">
-        <f>IF(ISNUMBER(AR13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AR13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV14" s="179"/>
       <c r="AW14" s="159" t="str">
-        <f>IF(ISNUMBER(AW13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AW13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX14" s="159" t="str">
-        <f>IF(ISNUMBER(AW13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AW13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY14" s="159" t="str">
-        <f>IF(ISNUMBER(AW13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AW13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ14" s="159" t="str">
-        <f>IF(ISNUMBER(AZ13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AZ13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA14" s="159" t="str">
-        <f>IF(ISNUMBER(AZ13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AZ13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB14" s="159" t="str">
-        <f>IF(ISNUMBER(AZ13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AZ13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC14" s="159" t="str">
-        <f>IF(ISNUMBER(BC13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BC13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD14" s="159" t="str">
-        <f>IF(ISNUMBER(BC13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BC13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE14" s="159" t="str">
-        <f>IF(ISNUMBER(BC13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BC13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF14" s="159" t="str">
-        <f>IF(ISNUMBER(BF13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BF13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG14" s="159" t="str">
-        <f>IF(ISNUMBER(BF13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BF13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH14" s="159" t="str">
-        <f>IF(ISNUMBER(BF13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BF13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI14" s="159" t="str">
-        <f>IF(ISNUMBER(BI13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BI13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ14" s="159" t="str">
-        <f>IF(ISNUMBER(BI13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BI13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK14" s="159" t="str">
-        <f>IF(ISNUMBER(BI13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BI13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL14" s="159" t="str">
-        <f>IF(ISNUMBER(BL13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BL13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM14" s="159" t="str">
-        <f>IF(ISNUMBER(BL13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BL13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN14" s="159" t="str">
-        <f>IF(ISNUMBER(BL13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BL13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO14" s="159" t="str">
-        <f>IF(ISNUMBER(BO13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BO13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP14" s="159" t="str">
-        <f>IF(ISNUMBER(BO13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BO13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ14" s="180" t="str">
-        <f>IF(ISNUMBER(BO13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BO13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS14" s="179"/>
       <c r="BT14" s="159" t="str">
-        <f>IF(ISNUMBER(BT13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BT13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU14" s="159" t="str">
-        <f>IF(ISNUMBER(BT13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BT13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV14" s="159" t="str">
-        <f>IF(ISNUMBER(BT13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BT13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW14" s="159" t="str">
-        <f>IF(ISNUMBER(BW13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BW13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX14" s="159" t="str">
-        <f>IF(ISNUMBER(BW13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BW13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY14" s="159" t="str">
-        <f>IF(ISNUMBER(BW13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BW13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ14" s="159" t="str">
-        <f>IF(ISNUMBER(BZ13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BZ13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA14" s="159" t="str">
-        <f>IF(ISNUMBER(BZ13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BZ13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB14" s="159" t="str">
-        <f>IF(ISNUMBER(BZ13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BZ13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC14" s="159" t="str">
-        <f>IF(ISNUMBER(CC13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CC13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD14" s="159" t="str">
-        <f>IF(ISNUMBER(CC13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CC13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE14" s="159" t="str">
-        <f>IF(ISNUMBER(CC13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CC13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF14" s="159" t="str">
-        <f>IF(ISNUMBER(CF13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CF13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG14" s="159" t="str">
-        <f>IF(ISNUMBER(CF13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CF13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH14" s="159" t="str">
-        <f>IF(ISNUMBER(CF13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CF13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI14" s="159" t="str">
-        <f>IF(ISNUMBER(CI13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CI13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ14" s="159" t="str">
-        <f>IF(ISNUMBER(CI13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CI13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK14" s="159" t="str">
-        <f>IF(ISNUMBER(CI13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CI13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL14" s="159" t="str">
-        <f>IF(ISNUMBER(CL13),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CL13))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="CM14" s="159" t="str">
-        <f>IF(ISNUMBER(CL13),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CL13))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN14" s="180" t="str">
-        <f>IF(ISNUMBER(CL13),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CL13))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -6169,342 +6246,342 @@
     <row r="16" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="167"/>
       <c r="C16" s="159" t="str">
-        <f>IF(ISNUMBER(C15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,C15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D16" s="159" t="str">
-        <f>IF(ISNUMBER(C15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,C15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E16" s="159" t="str">
-        <f>IF(ISNUMBER(C15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,C15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F16" s="159" t="str">
-        <f>IF(ISNUMBER(F15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,F15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G16" s="159" t="str">
-        <f>IF(ISNUMBER(F15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,F15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H16" s="159" t="str">
-        <f>IF(ISNUMBER(F15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,F15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I16" s="159" t="str">
-        <f>IF(ISNUMBER(I15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,I15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J16" s="159" t="str">
-        <f>IF(ISNUMBER(I15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,I15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K16" s="159" t="str">
-        <f>IF(ISNUMBER(I15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,I15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L16" s="159" t="str">
-        <f>IF(ISNUMBER(L15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,L15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M16" s="159" t="str">
-        <f>IF(ISNUMBER(L15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,L15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N16" s="159" t="str">
-        <f>IF(ISNUMBER(L15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,L15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O16" s="159" t="str">
-        <f>IF(ISNUMBER(O15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,O15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P16" s="159" t="str">
-        <f>IF(ISNUMBER(O15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,O15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q16" s="159" t="str">
-        <f>IF(ISNUMBER(O15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,O15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R16" s="159" t="str">
-        <f>IF(ISNUMBER(R15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,R15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S16" s="159" t="str">
-        <f>IF(ISNUMBER(R15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,R15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T16" s="159" t="str">
-        <f>IF(ISNUMBER(R15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,R15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U16" s="159" t="str">
-        <f>IF(ISNUMBER(U15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,U15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V16" s="159" t="str">
-        <f>IF(ISNUMBER(U15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,U15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W16" s="168" t="str">
-        <f>IF(ISNUMBER(U15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,U15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y16" s="179"/>
       <c r="Z16" s="159" t="str">
-        <f>IF(ISNUMBER(Z15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,Z15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA16" s="159" t="str">
-        <f>IF(ISNUMBER(Z15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,Z15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB16" s="159" t="str">
-        <f>IF(ISNUMBER(Z15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,Z15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC16" s="159" t="str">
-        <f>IF(ISNUMBER(AC15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AC15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD16" s="159" t="str">
-        <f>IF(ISNUMBER(AC15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AC15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE16" s="159" t="str">
-        <f>IF(ISNUMBER(AC15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AC15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF16" s="159" t="str">
-        <f>IF(ISNUMBER(AF15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AF15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG16" s="159" t="str">
-        <f>IF(ISNUMBER(AF15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AF15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH16" s="159" t="str">
-        <f>IF(ISNUMBER(AF15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AF15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI16" s="159" t="str">
-        <f>IF(ISNUMBER(AI15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AI15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ16" s="159" t="str">
-        <f>IF(ISNUMBER(AI15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AI15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK16" s="159" t="str">
-        <f>IF(ISNUMBER(AI15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AI15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL16" s="159" t="str">
-        <f>IF(ISNUMBER(AL15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AL15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM16" s="159" t="str">
-        <f>IF(ISNUMBER(AL15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AL15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AN16" s="159" t="str">
-        <f>IF(ISNUMBER(AL15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AL15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO16" s="159" t="str">
-        <f>IF(ISNUMBER(AO15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AO15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP16" s="159" t="str">
-        <f>IF(ISNUMBER(AO15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AO15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ16" s="159" t="str">
-        <f>IF(ISNUMBER(AO15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AO15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR16" s="159" t="str">
-        <f>IF(ISNUMBER(AR15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AR15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS16" s="159" t="str">
-        <f>IF(ISNUMBER(AR15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AR15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT16" s="180" t="str">
-        <f>IF(ISNUMBER(AR15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AR15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV16" s="179"/>
       <c r="AW16" s="159" t="str">
-        <f>IF(ISNUMBER(AW15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AW15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX16" s="159" t="str">
-        <f>IF(ISNUMBER(AW15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AW15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY16" s="159" t="str">
-        <f>IF(ISNUMBER(AW15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AW15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ16" s="159" t="str">
-        <f>IF(ISNUMBER(AZ15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AZ15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA16" s="159" t="str">
-        <f>IF(ISNUMBER(AZ15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AZ15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB16" s="159" t="str">
-        <f>IF(ISNUMBER(AZ15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AZ15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC16" s="159" t="str">
-        <f>IF(ISNUMBER(BC15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BC15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD16" s="159" t="str">
-        <f>IF(ISNUMBER(BC15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BC15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE16" s="159" t="str">
-        <f>IF(ISNUMBER(BC15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BC15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF16" s="159" t="str">
-        <f>IF(ISNUMBER(BF15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BF15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG16" s="159" t="str">
-        <f>IF(ISNUMBER(BF15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BF15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH16" s="159" t="str">
-        <f>IF(ISNUMBER(BF15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BF15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI16" s="159" t="str">
-        <f>IF(ISNUMBER(BI15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BI15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ16" s="159" t="str">
-        <f>IF(ISNUMBER(BI15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BI15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK16" s="159" t="str">
-        <f>IF(ISNUMBER(BI15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BI15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL16" s="159" t="str">
-        <f>IF(ISNUMBER(BL15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BL15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM16" s="159" t="str">
-        <f>IF(ISNUMBER(BL15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BL15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN16" s="159" t="str">
-        <f>IF(ISNUMBER(BL15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BL15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO16" s="159" t="str">
-        <f>IF(ISNUMBER(BO15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BO15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP16" s="159" t="str">
-        <f>IF(ISNUMBER(BO15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BO15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ16" s="180" t="str">
-        <f>IF(ISNUMBER(BO15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BO15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS16" s="179"/>
       <c r="BT16" s="159" t="str">
-        <f>IF(ISNUMBER(BT15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BT15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU16" s="159" t="str">
-        <f>IF(ISNUMBER(BT15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BT15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV16" s="159" t="str">
-        <f>IF(ISNUMBER(BT15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BT15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW16" s="159" t="str">
-        <f>IF(ISNUMBER(BW15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BW15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX16" s="159" t="str">
-        <f>IF(ISNUMBER(BW15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BW15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY16" s="159" t="str">
-        <f>IF(ISNUMBER(BW15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BW15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ16" s="159" t="str">
-        <f>IF(ISNUMBER(BZ15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BZ15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA16" s="159" t="str">
-        <f>IF(ISNUMBER(BZ15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BZ15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB16" s="159" t="str">
-        <f>IF(ISNUMBER(BZ15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BZ15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC16" s="159" t="str">
-        <f>IF(ISNUMBER(CC15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CC15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD16" s="159" t="str">
-        <f>IF(ISNUMBER(CC15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CC15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE16" s="159" t="str">
-        <f>IF(ISNUMBER(CC15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CC15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF16" s="159" t="str">
-        <f>IF(ISNUMBER(CF15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CF15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG16" s="159" t="str">
-        <f>IF(ISNUMBER(CF15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CF15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH16" s="159" t="str">
-        <f>IF(ISNUMBER(CF15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CF15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI16" s="159" t="str">
-        <f>IF(ISNUMBER(CI15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CI15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ16" s="159" t="str">
-        <f>IF(ISNUMBER(CI15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CI15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK16" s="159" t="str">
-        <f>IF(ISNUMBER(CI15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CI15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL16" s="159" t="str">
-        <f>IF(ISNUMBER(CL15),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CL15))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM16" s="159" t="str">
-        <f>IF(ISNUMBER(CL15),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CL15))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN16" s="180" t="str">
-        <f>IF(ISNUMBER(CL15),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CL15))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -6697,342 +6774,342 @@
     <row r="18" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="167"/>
       <c r="C18" s="159" t="str">
-        <f>IF(ISNUMBER(C17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,C17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D18" s="159" t="str">
-        <f>IF(ISNUMBER(C17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,C17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E18" s="159" t="str">
-        <f>IF(ISNUMBER(C17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,C17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F18" s="159" t="str">
-        <f>IF(ISNUMBER(F17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,F17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G18" s="159" t="str">
-        <f>IF(ISNUMBER(F17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,F17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H18" s="159" t="str">
-        <f>IF(ISNUMBER(F17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,F17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I18" s="159" t="str">
-        <f>IF(ISNUMBER(I17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,I17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J18" s="159" t="str">
-        <f>IF(ISNUMBER(I17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,I17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K18" s="159" t="str">
-        <f>IF(ISNUMBER(I17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,I17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L18" s="159" t="str">
-        <f>IF(ISNUMBER(L17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,L17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M18" s="159" t="str">
-        <f>IF(ISNUMBER(L17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,L17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N18" s="159" t="str">
-        <f>IF(ISNUMBER(L17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,L17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O18" s="159" t="str">
-        <f>IF(ISNUMBER(O17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,O17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P18" s="159" t="str">
-        <f>IF(ISNUMBER(O17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,O17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q18" s="159" t="str">
-        <f>IF(ISNUMBER(O17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,O17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R18" s="159" t="str">
-        <f>IF(ISNUMBER(R17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,R17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S18" s="159" t="str">
-        <f>IF(ISNUMBER(R17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,R17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T18" s="159" t="str">
-        <f>IF(ISNUMBER(R17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,R17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U18" s="159" t="str">
-        <f>IF(ISNUMBER(U17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,U17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V18" s="159" t="str">
-        <f>IF(ISNUMBER(U17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,U17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W18" s="168" t="str">
-        <f>IF(ISNUMBER(U17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,U17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y18" s="179"/>
       <c r="Z18" s="159" t="str">
-        <f>IF(ISNUMBER(Z17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,Z17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA18" s="159" t="str">
-        <f>IF(ISNUMBER(Z17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,Z17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB18" s="159" t="str">
-        <f>IF(ISNUMBER(Z17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,Z17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC18" s="159" t="str">
-        <f>IF(ISNUMBER(AC17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AC17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD18" s="159" t="str">
-        <f>IF(ISNUMBER(AC17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AC17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE18" s="159" t="str">
-        <f>IF(ISNUMBER(AC17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AC17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF18" s="159" t="str">
-        <f>IF(ISNUMBER(AF17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AF17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG18" s="159" t="str">
-        <f>IF(ISNUMBER(AF17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AF17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH18" s="159" t="str">
-        <f>IF(ISNUMBER(AF17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AF17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI18" s="159" t="str">
-        <f>IF(ISNUMBER(AI17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AI17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ18" s="159" t="str">
-        <f>IF(ISNUMBER(AI17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AI17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK18" s="159" t="str">
-        <f>IF(ISNUMBER(AI17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AI17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL18" s="159" t="str">
-        <f>IF(ISNUMBER(AL17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AL17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM18" s="159" t="str">
-        <f>IF(ISNUMBER(AL17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AL17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN18" s="159" t="str">
-        <f>IF(ISNUMBER(AL17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AL17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="AO18" s="159" t="str">
-        <f>IF(ISNUMBER(AO17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AO17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP18" s="159" t="str">
-        <f>IF(ISNUMBER(AO17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AO17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ18" s="159" t="str">
-        <f>IF(ISNUMBER(AO17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AO17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR18" s="159" t="str">
-        <f>IF(ISNUMBER(AR17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AR17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS18" s="159" t="str">
-        <f>IF(ISNUMBER(AR17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AR17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT18" s="180" t="str">
-        <f>IF(ISNUMBER(AR17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AR17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV18" s="179"/>
       <c r="AW18" s="159" t="str">
-        <f>IF(ISNUMBER(AW17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AW17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX18" s="159" t="str">
-        <f>IF(ISNUMBER(AW17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AW17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY18" s="159" t="str">
-        <f>IF(ISNUMBER(AW17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AW17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ18" s="159" t="str">
-        <f>IF(ISNUMBER(AZ17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AZ17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA18" s="159" t="str">
-        <f>IF(ISNUMBER(AZ17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AZ17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB18" s="159" t="str">
-        <f>IF(ISNUMBER(AZ17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AZ17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC18" s="159" t="str">
-        <f>IF(ISNUMBER(BC17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BC17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD18" s="159" t="str">
-        <f>IF(ISNUMBER(BC17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BC17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE18" s="159" t="str">
-        <f>IF(ISNUMBER(BC17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BC17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF18" s="159" t="str">
-        <f>IF(ISNUMBER(BF17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BF17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG18" s="159" t="str">
-        <f>IF(ISNUMBER(BF17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BF17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH18" s="159" t="str">
-        <f>IF(ISNUMBER(BF17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BF17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI18" s="159" t="str">
-        <f>IF(ISNUMBER(BI17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BI17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ18" s="159" t="str">
-        <f>IF(ISNUMBER(BI17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BI17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK18" s="159" t="str">
-        <f>IF(ISNUMBER(BI17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BI17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL18" s="159" t="str">
-        <f>IF(ISNUMBER(BL17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BL17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM18" s="159" t="str">
-        <f>IF(ISNUMBER(BL17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BL17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN18" s="159" t="str">
-        <f>IF(ISNUMBER(BL17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BL17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO18" s="159" t="str">
-        <f>IF(ISNUMBER(BO17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BO17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP18" s="159" t="str">
-        <f>IF(ISNUMBER(BO17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BO17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ18" s="180" t="str">
-        <f>IF(ISNUMBER(BO17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BO17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS18" s="179"/>
       <c r="BT18" s="159" t="str">
-        <f>IF(ISNUMBER(BT17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BT17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU18" s="159" t="str">
-        <f>IF(ISNUMBER(BT17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BT17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV18" s="159" t="str">
-        <f>IF(ISNUMBER(BT17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BT17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW18" s="159" t="str">
-        <f>IF(ISNUMBER(BW17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BW17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX18" s="159" t="str">
-        <f>IF(ISNUMBER(BW17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BW17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY18" s="159" t="str">
-        <f>IF(ISNUMBER(BW17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BW17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ18" s="159" t="str">
-        <f>IF(ISNUMBER(BZ17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BZ17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA18" s="159" t="str">
-        <f>IF(ISNUMBER(BZ17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BZ17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB18" s="159" t="str">
-        <f>IF(ISNUMBER(BZ17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BZ17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC18" s="159" t="str">
-        <f>IF(ISNUMBER(CC17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CC17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD18" s="159" t="str">
-        <f>IF(ISNUMBER(CC17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CC17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE18" s="159" t="str">
-        <f>IF(ISNUMBER(CC17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CC17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF18" s="159" t="str">
-        <f>IF(ISNUMBER(CF17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CF17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG18" s="159" t="str">
-        <f>IF(ISNUMBER(CF17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CF17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH18" s="159" t="str">
-        <f>IF(ISNUMBER(CF17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CF17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI18" s="159" t="str">
-        <f>IF(ISNUMBER(CI17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CI17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ18" s="159" t="str">
-        <f>IF(ISNUMBER(CI17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CI17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK18" s="159" t="str">
-        <f>IF(ISNUMBER(CI17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CI17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL18" s="159" t="str">
-        <f>IF(ISNUMBER(CL17),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CL17))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM18" s="159" t="str">
-        <f>IF(ISNUMBER(CL17),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CL17))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN18" s="180" t="str">
-        <f>IF(ISNUMBER(CL17),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CL17))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -7225,342 +7302,342 @@
     <row r="20" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="167"/>
       <c r="C20" s="159" t="str">
-        <f>IF(ISNUMBER(C19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,C19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D20" s="159" t="str">
-        <f>IF(ISNUMBER(C19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,C19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E20" s="159" t="str">
-        <f>IF(ISNUMBER(C19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,C19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F20" s="159" t="str">
-        <f>IF(ISNUMBER(F19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,F19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G20" s="159" t="str">
-        <f>IF(ISNUMBER(F19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,F19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H20" s="159" t="str">
-        <f>IF(ISNUMBER(F19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,F19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I20" s="159" t="str">
-        <f>IF(ISNUMBER(I19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,I19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J20" s="159" t="str">
-        <f>IF(ISNUMBER(I19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,I19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K20" s="159" t="str">
-        <f>IF(ISNUMBER(I19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,I19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L20" s="159" t="str">
-        <f>IF(ISNUMBER(L19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,L19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M20" s="159" t="str">
-        <f>IF(ISNUMBER(L19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,L19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N20" s="159" t="str">
-        <f>IF(ISNUMBER(L19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,L19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O20" s="159" t="str">
-        <f>IF(ISNUMBER(O19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,O19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P20" s="159" t="str">
-        <f>IF(ISNUMBER(O19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,O19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q20" s="159" t="str">
-        <f>IF(ISNUMBER(O19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,O19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R20" s="159" t="str">
-        <f>IF(ISNUMBER(R19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,R19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S20" s="159" t="str">
-        <f>IF(ISNUMBER(R19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,R19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T20" s="159" t="str">
-        <f>IF(ISNUMBER(R19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,R19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U20" s="159" t="str">
-        <f>IF(ISNUMBER(U19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,U19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V20" s="159" t="str">
-        <f>IF(ISNUMBER(U19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,U19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W20" s="168" t="str">
-        <f>IF(ISNUMBER(U19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,U19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y20" s="179"/>
       <c r="Z20" s="159" t="str">
-        <f>IF(ISNUMBER(Z19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,Z19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA20" s="159" t="str">
-        <f>IF(ISNUMBER(Z19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,Z19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB20" s="159" t="str">
-        <f>IF(ISNUMBER(Z19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,Z19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC20" s="159" t="str">
-        <f>IF(ISNUMBER(AC19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AC19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD20" s="159" t="str">
-        <f>IF(ISNUMBER(AC19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AC19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE20" s="159" t="str">
-        <f>IF(ISNUMBER(AC19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AC19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF20" s="159" t="str">
-        <f>IF(ISNUMBER(AF19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AF19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG20" s="159" t="str">
-        <f>IF(ISNUMBER(AF19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AF19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AH20" s="159" t="str">
-        <f>IF(ISNUMBER(AF19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AF19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI20" s="159" t="str">
-        <f>IF(ISNUMBER(AI19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AI19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ20" s="159" t="str">
-        <f>IF(ISNUMBER(AI19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AI19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK20" s="159" t="str">
-        <f>IF(ISNUMBER(AI19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AI19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL20" s="159" t="str">
-        <f>IF(ISNUMBER(AL19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AL19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM20" s="159" t="str">
-        <f>IF(ISNUMBER(AL19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AL19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN20" s="159" t="str">
-        <f>IF(ISNUMBER(AL19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AL19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO20" s="159" t="str">
-        <f>IF(ISNUMBER(AO19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AO19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP20" s="159" t="str">
-        <f>IF(ISNUMBER(AO19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AO19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ20" s="159" t="str">
-        <f>IF(ISNUMBER(AO19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AO19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR20" s="159" t="str">
-        <f>IF(ISNUMBER(AR19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AR19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS20" s="159" t="str">
-        <f>IF(ISNUMBER(AR19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AR19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT20" s="180" t="str">
-        <f>IF(ISNUMBER(AR19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AR19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV20" s="179"/>
       <c r="AW20" s="159" t="str">
-        <f>IF(ISNUMBER(AW19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AW19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX20" s="159" t="str">
-        <f>IF(ISNUMBER(AW19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AW19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY20" s="159" t="str">
-        <f>IF(ISNUMBER(AW19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AW19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ20" s="159" t="str">
-        <f>IF(ISNUMBER(AZ19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AZ19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA20" s="159" t="str">
-        <f>IF(ISNUMBER(AZ19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AZ19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB20" s="159" t="str">
-        <f>IF(ISNUMBER(AZ19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AZ19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC20" s="159" t="str">
-        <f>IF(ISNUMBER(BC19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BC19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD20" s="159" t="str">
-        <f>IF(ISNUMBER(BC19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BC19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE20" s="159" t="str">
-        <f>IF(ISNUMBER(BC19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BC19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF20" s="159" t="str">
-        <f>IF(ISNUMBER(BF19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BF19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG20" s="159" t="str">
-        <f>IF(ISNUMBER(BF19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BF19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH20" s="159" t="str">
-        <f>IF(ISNUMBER(BF19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BF19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI20" s="159" t="str">
-        <f>IF(ISNUMBER(BI19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BI19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="BJ20" s="159" t="str">
-        <f>IF(ISNUMBER(BI19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BI19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="BK20" s="159" t="str">
-        <f>IF(ISNUMBER(BI19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BI19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="BL20" s="159" t="str">
-        <f>IF(ISNUMBER(BL19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BL19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM20" s="159" t="str">
-        <f>IF(ISNUMBER(BL19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BL19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN20" s="159" t="str">
-        <f>IF(ISNUMBER(BL19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BL19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO20" s="159" t="str">
-        <f>IF(ISNUMBER(BO19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BO19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP20" s="159" t="str">
-        <f>IF(ISNUMBER(BO19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BO19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ20" s="180" t="str">
-        <f>IF(ISNUMBER(BO19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BO19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS20" s="179"/>
       <c r="BT20" s="159" t="str">
-        <f>IF(ISNUMBER(BT19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BT19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU20" s="159" t="str">
-        <f>IF(ISNUMBER(BT19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BT19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV20" s="159" t="str">
-        <f>IF(ISNUMBER(BT19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BT19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW20" s="159" t="str">
-        <f>IF(ISNUMBER(BW19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BW19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX20" s="159" t="str">
-        <f>IF(ISNUMBER(BW19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BW19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY20" s="159" t="str">
-        <f>IF(ISNUMBER(BW19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BW19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ20" s="159" t="str">
-        <f>IF(ISNUMBER(BZ19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BZ19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA20" s="159" t="str">
-        <f>IF(ISNUMBER(BZ19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BZ19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB20" s="159" t="str">
-        <f>IF(ISNUMBER(BZ19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BZ19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC20" s="159" t="str">
-        <f>IF(ISNUMBER(CC19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CC19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD20" s="159" t="str">
-        <f>IF(ISNUMBER(CC19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CC19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="CE20" s="159" t="str">
-        <f>IF(ISNUMBER(CC19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CC19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF20" s="159" t="str">
-        <f>IF(ISNUMBER(CF19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CF19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG20" s="159" t="str">
-        <f>IF(ISNUMBER(CF19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CF19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH20" s="159" t="str">
-        <f>IF(ISNUMBER(CF19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CF19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="CI20" s="159" t="str">
-        <f>IF(ISNUMBER(CI19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CI19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ20" s="159" t="str">
-        <f>IF(ISNUMBER(CI19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CI19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK20" s="159" t="str">
-        <f>IF(ISNUMBER(CI19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CI19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL20" s="159" t="str">
-        <f>IF(ISNUMBER(CL19),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CL19))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM20" s="159" t="str">
-        <f>IF(ISNUMBER(CL19),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CL19))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN20" s="180" t="str">
-        <f>IF(ISNUMBER(CL19),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CL19))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -7753,342 +7830,342 @@
     <row r="22" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="167"/>
       <c r="C22" s="159" t="str">
-        <f>IF(ISNUMBER(C21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,C21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D22" s="159" t="str">
-        <f>IF(ISNUMBER(C21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,C21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E22" s="159" t="str">
-        <f>IF(ISNUMBER(C21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,C21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F22" s="159" t="str">
-        <f>IF(ISNUMBER(F21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,F21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G22" s="159" t="str">
-        <f>IF(ISNUMBER(F21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,F21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H22" s="159" t="str">
-        <f>IF(ISNUMBER(F21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,F21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I22" s="159" t="str">
-        <f>IF(ISNUMBER(I21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,I21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J22" s="159" t="str">
-        <f>IF(ISNUMBER(I21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,I21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K22" s="159" t="str">
-        <f>IF(ISNUMBER(I21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,I21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L22" s="159" t="str">
-        <f>IF(ISNUMBER(L21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,L21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M22" s="159" t="str">
-        <f>IF(ISNUMBER(L21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,L21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N22" s="159" t="str">
-        <f>IF(ISNUMBER(L21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,L21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O22" s="159" t="str">
-        <f>IF(ISNUMBER(O21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,O21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
         <v>S</v>
       </c>
       <c r="P22" s="159" t="str">
-        <f>IF(ISNUMBER(O21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,O21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q22" s="159" t="str">
-        <f>IF(ISNUMBER(O21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,O21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="R22" s="159" t="str">
-        <f>IF(ISNUMBER(R21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,R21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S22" s="159" t="str">
-        <f>IF(ISNUMBER(R21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,R21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T22" s="159" t="str">
-        <f>IF(ISNUMBER(R21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,R21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U22" s="159" t="str">
-        <f>IF(ISNUMBER(U21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,U21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V22" s="159" t="str">
-        <f>IF(ISNUMBER(U21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,U21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W22" s="168" t="str">
-        <f>IF(ISNUMBER(U21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,U21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y22" s="179"/>
       <c r="Z22" s="159" t="str">
-        <f>IF(ISNUMBER(Z21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,Z21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA22" s="159" t="str">
-        <f>IF(ISNUMBER(Z21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,Z21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB22" s="159" t="str">
-        <f>IF(ISNUMBER(Z21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,Z21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC22" s="159" t="str">
-        <f>IF(ISNUMBER(AC21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AC21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD22" s="159" t="str">
-        <f>IF(ISNUMBER(AC21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AC21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE22" s="159" t="str">
-        <f>IF(ISNUMBER(AC21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AC21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF22" s="159" t="str">
-        <f>IF(ISNUMBER(AF21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AF21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG22" s="159" t="str">
-        <f>IF(ISNUMBER(AF21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AF21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH22" s="159" t="str">
-        <f>IF(ISNUMBER(AF21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AF21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI22" s="159" t="str">
-        <f>IF(ISNUMBER(AI21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AI21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ22" s="159" t="str">
-        <f>IF(ISNUMBER(AI21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AI21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK22" s="159" t="str">
-        <f>IF(ISNUMBER(AI21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AI21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL22" s="159" t="str">
-        <f>IF(ISNUMBER(AL21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AL21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM22" s="159" t="str">
-        <f>IF(ISNUMBER(AL21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AL21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN22" s="159" t="str">
-        <f>IF(ISNUMBER(AL21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AL21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO22" s="159" t="str">
-        <f>IF(ISNUMBER(AO21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AO21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP22" s="159" t="str">
-        <f>IF(ISNUMBER(AO21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AO21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ22" s="159" t="str">
-        <f>IF(ISNUMBER(AO21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AO21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR22" s="159" t="str">
-        <f>IF(ISNUMBER(AR21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AR21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS22" s="159" t="str">
-        <f>IF(ISNUMBER(AR21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AR21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT22" s="180" t="str">
-        <f>IF(ISNUMBER(AR21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AR21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV22" s="179"/>
       <c r="AW22" s="159" t="str">
-        <f>IF(ISNUMBER(AW21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AW21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AX22" s="159" t="str">
-        <f>IF(ISNUMBER(AW21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AW21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AY22" s="159" t="str">
-        <f>IF(ISNUMBER(AW21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AW21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AZ22" s="159" t="str">
-        <f>IF(ISNUMBER(AZ21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AZ21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA22" s="159" t="str">
-        <f>IF(ISNUMBER(AZ21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AZ21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB22" s="159" t="str">
-        <f>IF(ISNUMBER(AZ21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AZ21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC22" s="159" t="str">
-        <f>IF(ISNUMBER(BC21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BC21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD22" s="159" t="str">
-        <f>IF(ISNUMBER(BC21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BC21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE22" s="159" t="str">
-        <f>IF(ISNUMBER(BC21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BC21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF22" s="159" t="str">
-        <f>IF(ISNUMBER(BF21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BF21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG22" s="159" t="str">
-        <f>IF(ISNUMBER(BF21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BF21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH22" s="159" t="str">
-        <f>IF(ISNUMBER(BF21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BF21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI22" s="159" t="str">
-        <f>IF(ISNUMBER(BI21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BI21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ22" s="159" t="str">
-        <f>IF(ISNUMBER(BI21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BI21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK22" s="159" t="str">
-        <f>IF(ISNUMBER(BI21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BI21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL22" s="159" t="str">
-        <f>IF(ISNUMBER(BL21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BL21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM22" s="159" t="str">
-        <f>IF(ISNUMBER(BL21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BL21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN22" s="159" t="str">
-        <f>IF(ISNUMBER(BL21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BL21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO22" s="159" t="str">
-        <f>IF(ISNUMBER(BO21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BO21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP22" s="159" t="str">
-        <f>IF(ISNUMBER(BO21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BO21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ22" s="180" t="str">
-        <f>IF(ISNUMBER(BO21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BO21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS22" s="179"/>
       <c r="BT22" s="159" t="str">
-        <f>IF(ISNUMBER(BT21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BT21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU22" s="159" t="str">
-        <f>IF(ISNUMBER(BT21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BT21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV22" s="159" t="str">
-        <f>IF(ISNUMBER(BT21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BT21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW22" s="159" t="str">
-        <f>IF(ISNUMBER(BW21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BW21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX22" s="159" t="str">
-        <f>IF(ISNUMBER(BW21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BW21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY22" s="159" t="str">
-        <f>IF(ISNUMBER(BW21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BW21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ22" s="159" t="str">
-        <f>IF(ISNUMBER(BZ21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BZ21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA22" s="159" t="str">
-        <f>IF(ISNUMBER(BZ21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BZ21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB22" s="159" t="str">
-        <f>IF(ISNUMBER(BZ21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BZ21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC22" s="159" t="str">
-        <f>IF(ISNUMBER(CC21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CC21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD22" s="159" t="str">
-        <f>IF(ISNUMBER(CC21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CC21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE22" s="159" t="str">
-        <f>IF(ISNUMBER(CC21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CC21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF22" s="159" t="str">
-        <f>IF(ISNUMBER(CF21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CF21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG22" s="159" t="str">
-        <f>IF(ISNUMBER(CF21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CF21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH22" s="159" t="str">
-        <f>IF(ISNUMBER(CF21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CF21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI22" s="159" t="str">
-        <f>IF(ISNUMBER(CI21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CI21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ22" s="159" t="str">
-        <f>IF(ISNUMBER(CI21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CI21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK22" s="159" t="str">
-        <f>IF(ISNUMBER(CI21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CI21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL22" s="159" t="str">
-        <f>IF(ISNUMBER(CL21),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CL21))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM22" s="159" t="str">
-        <f>IF(ISNUMBER(CL21),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CL21))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN22" s="180" t="str">
-        <f>IF(ISNUMBER(CL21),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CL21))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -8281,342 +8358,342 @@
     <row r="24" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="169"/>
       <c r="C24" s="170" t="str">
-        <f>IF(ISNUMBER(C23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,C23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D24" s="170" t="str">
-        <f>IF(ISNUMBER(C23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,C23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E24" s="170" t="str">
-        <f>IF(ISNUMBER(C23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,C23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F24" s="170" t="str">
-        <f>IF(ISNUMBER(F23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,F23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G24" s="170" t="str">
-        <f>IF(ISNUMBER(F23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,F23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H24" s="170" t="str">
-        <f>IF(ISNUMBER(F23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,F23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I24" s="170" t="str">
-        <f>IF(ISNUMBER(I23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,I23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J24" s="170" t="str">
-        <f>IF(ISNUMBER(I23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,I23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K24" s="170" t="str">
-        <f>IF(ISNUMBER(I23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,I23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L24" s="170" t="str">
-        <f>IF(ISNUMBER(L23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,L23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M24" s="170" t="str">
-        <f>IF(ISNUMBER(L23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,L23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N24" s="170" t="str">
-        <f>IF(ISNUMBER(L23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,L23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O24" s="170" t="str">
-        <f>IF(ISNUMBER(O23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,O23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P24" s="170" t="str">
-        <f>IF(ISNUMBER(O23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,O23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q24" s="170" t="str">
-        <f>IF(ISNUMBER(O23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,O23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R24" s="170" t="str">
-        <f>IF(ISNUMBER(R23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,R23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S24" s="170" t="str">
-        <f>IF(ISNUMBER(R23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,R23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T24" s="170" t="str">
-        <f>IF(ISNUMBER(R23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,R23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U24" s="170" t="str">
-        <f>IF(ISNUMBER(U23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,1,U23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V24" s="170" t="str">
-        <f>IF(ISNUMBER(U23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,1,U23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W24" s="171" t="str">
-        <f>IF(ISNUMBER(U23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,1,U23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y24" s="181"/>
       <c r="Z24" s="182" t="str">
-        <f>IF(ISNUMBER(Z23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,Z23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA24" s="182" t="str">
-        <f>IF(ISNUMBER(Z23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,Z23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB24" s="182" t="str">
-        <f>IF(ISNUMBER(Z23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,Z23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC24" s="182" t="str">
-        <f>IF(ISNUMBER(AC23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AC23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD24" s="182" t="str">
-        <f>IF(ISNUMBER(AC23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AC23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE24" s="182" t="str">
-        <f>IF(ISNUMBER(AC23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AC23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF24" s="182" t="str">
-        <f>IF(ISNUMBER(AF23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AF23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG24" s="182" t="str">
-        <f>IF(ISNUMBER(AF23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AF23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH24" s="182" t="str">
-        <f>IF(ISNUMBER(AF23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AF23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI24" s="182" t="str">
-        <f>IF(ISNUMBER(AI23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AI23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ24" s="182" t="str">
-        <f>IF(ISNUMBER(AI23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AI23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK24" s="182" t="str">
-        <f>IF(ISNUMBER(AI23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AI23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL24" s="182" t="str">
-        <f>IF(ISNUMBER(AL23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AL23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM24" s="182" t="str">
-        <f>IF(ISNUMBER(AL23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AL23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN24" s="182" t="str">
-        <f>IF(ISNUMBER(AL23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AL23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO24" s="182" t="str">
-        <f>IF(ISNUMBER(AO23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AO23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP24" s="182" t="str">
-        <f>IF(ISNUMBER(AO23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AO23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ24" s="182" t="str">
-        <f>IF(ISNUMBER(AO23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AO23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR24" s="182" t="str">
-        <f>IF(ISNUMBER(AR23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,2,AR23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS24" s="182" t="str">
-        <f>IF(ISNUMBER(AR23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,2,AR23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT24" s="183" t="str">
-        <f>IF(ISNUMBER(AR23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,2,AR23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV24" s="181"/>
       <c r="AW24" s="182" t="str">
-        <f>IF(ISNUMBER(AW23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AW23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX24" s="182" t="str">
-        <f>IF(ISNUMBER(AW23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AW23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY24" s="182" t="str">
-        <f>IF(ISNUMBER(AW23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AW23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ24" s="182" t="str">
-        <f>IF(ISNUMBER(AZ23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,AZ23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA24" s="182" t="str">
-        <f>IF(ISNUMBER(AZ23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,AZ23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB24" s="182" t="str">
-        <f>IF(ISNUMBER(AZ23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,AZ23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC24" s="182" t="str">
-        <f>IF(ISNUMBER(BC23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BC23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD24" s="182" t="str">
-        <f>IF(ISNUMBER(BC23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BC23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE24" s="182" t="str">
-        <f>IF(ISNUMBER(BC23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BC23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF24" s="182" t="str">
-        <f>IF(ISNUMBER(BF23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BF23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG24" s="182" t="str">
-        <f>IF(ISNUMBER(BF23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BF23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH24" s="182" t="str">
-        <f>IF(ISNUMBER(BF23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BF23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI24" s="182" t="str">
-        <f>IF(ISNUMBER(BI23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BI23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ24" s="182" t="str">
-        <f>IF(ISNUMBER(BI23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BI23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK24" s="182" t="str">
-        <f>IF(ISNUMBER(BI23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BI23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL24" s="182" t="str">
-        <f>IF(ISNUMBER(BL23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BL23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM24" s="182" t="str">
-        <f>IF(ISNUMBER(BL23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BL23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN24" s="182" t="str">
-        <f>IF(ISNUMBER(BL23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BL23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO24" s="182" t="str">
-        <f>IF(ISNUMBER(BO23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,3,BO23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP24" s="182" t="str">
-        <f>IF(ISNUMBER(BO23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,3,BO23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ24" s="183" t="str">
-        <f>IF(ISNUMBER(BO23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,3,BO23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS24" s="181"/>
       <c r="BT24" s="182" t="str">
-        <f>IF(ISNUMBER(BT23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BT23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU24" s="182" t="str">
-        <f>IF(ISNUMBER(BT23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BT23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV24" s="182" t="str">
-        <f>IF(ISNUMBER(BT23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BT23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW24" s="182" t="str">
-        <f>IF(ISNUMBER(BW23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BW23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX24" s="182" t="str">
-        <f>IF(ISNUMBER(BW23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BW23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY24" s="182" t="str">
-        <f>IF(ISNUMBER(BW23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BW23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ24" s="182" t="str">
-        <f>IF(ISNUMBER(BZ23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,BZ23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA24" s="182" t="str">
-        <f>IF(ISNUMBER(BZ23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,BZ23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB24" s="182" t="str">
-        <f>IF(ISNUMBER(BZ23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,BZ23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC24" s="182" t="str">
-        <f>IF(ISNUMBER(CC23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CC23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD24" s="182" t="str">
-        <f>IF(ISNUMBER(CC23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CC23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE24" s="182" t="str">
-        <f>IF(ISNUMBER(CC23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CC23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF24" s="182" t="str">
-        <f>IF(ISNUMBER(CF23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CF23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG24" s="182" t="str">
-        <f>IF(ISNUMBER(CF23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CF23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH24" s="182" t="str">
-        <f>IF(ISNUMBER(CF23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CF23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI24" s="182" t="str">
-        <f>IF(ISNUMBER(CI23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CI23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ24" s="182" t="str">
-        <f>IF(ISNUMBER(CI23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CI23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK24" s="182" t="str">
-        <f>IF(ISNUMBER(CI23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CI23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL24" s="182" t="str">
-        <f>IF(ISNUMBER(CL23),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,4,CL23))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM24" s="182" t="str">
-        <f>IF(ISNUMBER(CL23),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,4,CL23))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN24" s="183" t="str">
-        <f>IF(ISNUMBER(CL23),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,4,CL23))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -9168,342 +9245,342 @@
     <row r="30" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="179"/>
       <c r="C30" s="159" t="str">
-        <f>IF(ISNUMBER(C29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,C29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D30" s="159" t="str">
-        <f>IF(ISNUMBER(C29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,C29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E30" s="159" t="str">
-        <f>IF(ISNUMBER(C29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,C29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F30" s="159" t="str">
-        <f>IF(ISNUMBER(F29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,F29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G30" s="159" t="str">
-        <f>IF(ISNUMBER(F29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,F29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H30" s="159" t="str">
-        <f>IF(ISNUMBER(F29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,F29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I30" s="159" t="str">
-        <f>IF(ISNUMBER(I29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,I29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J30" s="159" t="str">
-        <f>IF(ISNUMBER(I29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,I29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K30" s="159" t="str">
-        <f>IF(ISNUMBER(I29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,I29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L30" s="159" t="str">
-        <f>IF(ISNUMBER(L29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,L29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M30" s="159" t="str">
-        <f>IF(ISNUMBER(L29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,L29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N30" s="159" t="str">
-        <f>IF(ISNUMBER(L29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,L29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O30" s="159" t="str">
-        <f>IF(ISNUMBER(O29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,O29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P30" s="159" t="str">
-        <f>IF(ISNUMBER(O29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,O29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q30" s="159" t="str">
-        <f>IF(ISNUMBER(O29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,O29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R30" s="159" t="str">
-        <f>IF(ISNUMBER(R29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,R29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="S30" s="159" t="str">
-        <f>IF(ISNUMBER(R29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,R29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="T30" s="159" t="str">
-        <f>IF(ISNUMBER(R29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,R29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="U30" s="159" t="str">
-        <f>IF(ISNUMBER(U29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,U29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V30" s="159" t="str">
-        <f>IF(ISNUMBER(U29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,U29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W30" s="180" t="str">
-        <f>IF(ISNUMBER(U29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,U29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y30" s="179"/>
       <c r="Z30" s="159" t="str">
-        <f>IF(ISNUMBER(Z29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,Z29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA30" s="159" t="str">
-        <f>IF(ISNUMBER(Z29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,Z29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB30" s="159" t="str">
-        <f>IF(ISNUMBER(Z29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,Z29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC30" s="159" t="str">
-        <f>IF(ISNUMBER(AC29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AC29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD30" s="159" t="str">
-        <f>IF(ISNUMBER(AC29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AC29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE30" s="159" t="str">
-        <f>IF(ISNUMBER(AC29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AC29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF30" s="159" t="str">
-        <f>IF(ISNUMBER(AF29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AF29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG30" s="159" t="str">
-        <f>IF(ISNUMBER(AF29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AF29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH30" s="159" t="str">
-        <f>IF(ISNUMBER(AF29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AF29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI30" s="159" t="str">
-        <f>IF(ISNUMBER(AI29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AI29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ30" s="159" t="str">
-        <f>IF(ISNUMBER(AI29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AI29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK30" s="159" t="str">
-        <f>IF(ISNUMBER(AI29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AI29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL30" s="159" t="str">
-        <f>IF(ISNUMBER(AL29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AL29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM30" s="159" t="str">
-        <f>IF(ISNUMBER(AL29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AL29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN30" s="159" t="str">
-        <f>IF(ISNUMBER(AL29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AL29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO30" s="159" t="str">
-        <f>IF(ISNUMBER(AO29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AO29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP30" s="159" t="str">
-        <f>IF(ISNUMBER(AO29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AO29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ30" s="159" t="str">
-        <f>IF(ISNUMBER(AO29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AO29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR30" s="159" t="str">
-        <f>IF(ISNUMBER(AR29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AR29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS30" s="159" t="str">
-        <f>IF(ISNUMBER(AR29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AR29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT30" s="180" t="str">
-        <f>IF(ISNUMBER(AR29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AR29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV30" s="179"/>
       <c r="AW30" s="159" t="str">
-        <f>IF(ISNUMBER(AW29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AW29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX30" s="159" t="str">
-        <f>IF(ISNUMBER(AW29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AW29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY30" s="159" t="str">
-        <f>IF(ISNUMBER(AW29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AW29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ30" s="159" t="str">
-        <f>IF(ISNUMBER(AZ29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AZ29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA30" s="159" t="str">
-        <f>IF(ISNUMBER(AZ29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AZ29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB30" s="159" t="str">
-        <f>IF(ISNUMBER(AZ29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AZ29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC30" s="159" t="str">
-        <f>IF(ISNUMBER(BC29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BC29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD30" s="159" t="str">
-        <f>IF(ISNUMBER(BC29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BC29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE30" s="159" t="str">
-        <f>IF(ISNUMBER(BC29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BC29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF30" s="159" t="str">
-        <f>IF(ISNUMBER(BF29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BF29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG30" s="159" t="str">
-        <f>IF(ISNUMBER(BF29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BF29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH30" s="159" t="str">
-        <f>IF(ISNUMBER(BF29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BF29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI30" s="159" t="str">
-        <f>IF(ISNUMBER(BI29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BI29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ30" s="159" t="str">
-        <f>IF(ISNUMBER(BI29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BI29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK30" s="159" t="str">
-        <f>IF(ISNUMBER(BI29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BI29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL30" s="159" t="str">
-        <f>IF(ISNUMBER(BL29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BL29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM30" s="159" t="str">
-        <f>IF(ISNUMBER(BL29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BL29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN30" s="159" t="str">
-        <f>IF(ISNUMBER(BL29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BL29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO30" s="159" t="str">
-        <f>IF(ISNUMBER(BO29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BO29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP30" s="159" t="str">
-        <f>IF(ISNUMBER(BO29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BO29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ30" s="180" t="str">
-        <f>IF(ISNUMBER(BO29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BO29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS30" s="179"/>
       <c r="BT30" s="159" t="str">
-        <f>IF(ISNUMBER(BT29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BT29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU30" s="159" t="str">
-        <f>IF(ISNUMBER(BT29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BT29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV30" s="159" t="str">
-        <f>IF(ISNUMBER(BT29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BT29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW30" s="159" t="str">
-        <f>IF(ISNUMBER(BW29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BW29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX30" s="159" t="str">
-        <f>IF(ISNUMBER(BW29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BW29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY30" s="159" t="str">
-        <f>IF(ISNUMBER(BW29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BW29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ30" s="159" t="str">
-        <f>IF(ISNUMBER(BZ29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BZ29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA30" s="159" t="str">
-        <f>IF(ISNUMBER(BZ29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BZ29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB30" s="159" t="str">
-        <f>IF(ISNUMBER(BZ29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BZ29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC30" s="159" t="str">
-        <f>IF(ISNUMBER(CC29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CC29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD30" s="159" t="str">
-        <f>IF(ISNUMBER(CC29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CC29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE30" s="159" t="str">
-        <f>IF(ISNUMBER(CC29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CC29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF30" s="159" t="str">
-        <f>IF(ISNUMBER(CF29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CF29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG30" s="159" t="str">
-        <f>IF(ISNUMBER(CF29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CF29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH30" s="159" t="str">
-        <f>IF(ISNUMBER(CF29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CF29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI30" s="159" t="str">
-        <f>IF(ISNUMBER(CI29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CI29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ30" s="159" t="str">
-        <f>IF(ISNUMBER(CI29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CI29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK30" s="159" t="str">
-        <f>IF(ISNUMBER(CI29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CI29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL30" s="159" t="str">
-        <f>IF(ISNUMBER(CL29),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CL29))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM30" s="159" t="str">
-        <f>IF(ISNUMBER(CL29),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CL29))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN30" s="180" t="str">
-        <f>IF(ISNUMBER(CL29),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CL29))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -9696,342 +9773,342 @@
     <row r="32" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="179"/>
       <c r="C32" s="159" t="str">
-        <f>IF(ISNUMBER(C31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,C31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D32" s="159" t="str">
-        <f>IF(ISNUMBER(C31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,C31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E32" s="159" t="str">
-        <f>IF(ISNUMBER(C31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,C31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F32" s="159" t="str">
-        <f>IF(ISNUMBER(F31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,F31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G32" s="159" t="str">
-        <f>IF(ISNUMBER(F31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,F31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H32" s="159" t="str">
-        <f>IF(ISNUMBER(F31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,F31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I32" s="159" t="str">
-        <f>IF(ISNUMBER(I31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,I31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J32" s="159" t="str">
-        <f>IF(ISNUMBER(I31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,I31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K32" s="159" t="str">
-        <f>IF(ISNUMBER(I31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,I31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L32" s="159" t="str">
-        <f>IF(ISNUMBER(L31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,L31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="M32" s="159" t="str">
-        <f>IF(ISNUMBER(L31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,L31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="N32" s="159" t="str">
-        <f>IF(ISNUMBER(L31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,L31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="O32" s="159" t="str">
-        <f>IF(ISNUMBER(O31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,O31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P32" s="159" t="str">
-        <f>IF(ISNUMBER(O31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,O31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q32" s="159" t="str">
-        <f>IF(ISNUMBER(O31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,O31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R32" s="159" t="str">
-        <f>IF(ISNUMBER(R31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,R31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S32" s="159" t="str">
-        <f>IF(ISNUMBER(R31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,R31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T32" s="159" t="str">
-        <f>IF(ISNUMBER(R31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,R31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U32" s="159" t="str">
-        <f>IF(ISNUMBER(U31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,U31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V32" s="159" t="str">
-        <f>IF(ISNUMBER(U31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,U31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W32" s="180" t="str">
-        <f>IF(ISNUMBER(U31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,U31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y32" s="179"/>
       <c r="Z32" s="159" t="str">
-        <f>IF(ISNUMBER(Z31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,Z31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA32" s="159" t="str">
-        <f>IF(ISNUMBER(Z31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,Z31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB32" s="159" t="str">
-        <f>IF(ISNUMBER(Z31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,Z31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC32" s="159" t="str">
-        <f>IF(ISNUMBER(AC31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AC31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD32" s="159" t="str">
-        <f>IF(ISNUMBER(AC31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AC31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE32" s="159" t="str">
-        <f>IF(ISNUMBER(AC31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AC31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF32" s="159" t="str">
-        <f>IF(ISNUMBER(AF31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AF31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG32" s="159" t="str">
-        <f>IF(ISNUMBER(AF31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AF31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH32" s="159" t="str">
-        <f>IF(ISNUMBER(AF31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AF31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI32" s="159" t="str">
-        <f>IF(ISNUMBER(AI31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AI31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ32" s="159" t="str">
-        <f>IF(ISNUMBER(AI31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AI31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK32" s="159" t="str">
-        <f>IF(ISNUMBER(AI31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AI31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL32" s="159" t="str">
-        <f>IF(ISNUMBER(AL31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AL31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM32" s="159" t="str">
-        <f>IF(ISNUMBER(AL31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AL31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN32" s="159" t="str">
-        <f>IF(ISNUMBER(AL31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AL31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO32" s="159" t="str">
-        <f>IF(ISNUMBER(AO31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AO31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="AP32" s="159" t="str">
-        <f>IF(ISNUMBER(AO31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AO31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ32" s="159" t="str">
-        <f>IF(ISNUMBER(AO31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AO31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR32" s="159" t="str">
-        <f>IF(ISNUMBER(AR31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AR31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS32" s="159" t="str">
-        <f>IF(ISNUMBER(AR31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AR31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT32" s="180" t="str">
-        <f>IF(ISNUMBER(AR31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AR31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV32" s="179"/>
       <c r="AW32" s="159" t="str">
-        <f>IF(ISNUMBER(AW31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AW31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX32" s="159" t="str">
-        <f>IF(ISNUMBER(AW31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AW31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY32" s="159" t="str">
-        <f>IF(ISNUMBER(AW31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AW31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ32" s="159" t="str">
-        <f>IF(ISNUMBER(AZ31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AZ31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA32" s="159" t="str">
-        <f>IF(ISNUMBER(AZ31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AZ31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB32" s="159" t="str">
-        <f>IF(ISNUMBER(AZ31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AZ31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC32" s="159" t="str">
-        <f>IF(ISNUMBER(BC31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BC31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD32" s="159" t="str">
-        <f>IF(ISNUMBER(BC31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BC31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE32" s="159" t="str">
-        <f>IF(ISNUMBER(BC31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BC31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF32" s="159" t="str">
-        <f>IF(ISNUMBER(BF31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BF31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG32" s="159" t="str">
-        <f>IF(ISNUMBER(BF31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BF31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH32" s="159" t="str">
-        <f>IF(ISNUMBER(BF31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BF31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI32" s="159" t="str">
-        <f>IF(ISNUMBER(BI31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BI31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ32" s="159" t="str">
-        <f>IF(ISNUMBER(BI31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BI31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK32" s="159" t="str">
-        <f>IF(ISNUMBER(BI31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BI31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL32" s="159" t="str">
-        <f>IF(ISNUMBER(BL31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BL31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="BM32" s="159" t="str">
-        <f>IF(ISNUMBER(BL31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BL31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN32" s="159" t="str">
-        <f>IF(ISNUMBER(BL31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BL31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO32" s="159" t="str">
-        <f>IF(ISNUMBER(BO31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BO31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP32" s="159" t="str">
-        <f>IF(ISNUMBER(BO31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BO31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ32" s="180" t="str">
-        <f>IF(ISNUMBER(BO31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BO31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS32" s="179"/>
       <c r="BT32" s="159" t="str">
-        <f>IF(ISNUMBER(BT31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BT31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU32" s="159" t="str">
-        <f>IF(ISNUMBER(BT31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BT31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV32" s="159" t="str">
-        <f>IF(ISNUMBER(BT31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BT31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW32" s="159" t="str">
-        <f>IF(ISNUMBER(BW31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BW31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX32" s="159" t="str">
-        <f>IF(ISNUMBER(BW31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BW31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY32" s="159" t="str">
-        <f>IF(ISNUMBER(BW31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BW31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ32" s="159" t="str">
-        <f>IF(ISNUMBER(BZ31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BZ31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA32" s="159" t="str">
-        <f>IF(ISNUMBER(BZ31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BZ31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB32" s="159" t="str">
-        <f>IF(ISNUMBER(BZ31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BZ31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC32" s="159" t="str">
-        <f>IF(ISNUMBER(CC31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CC31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD32" s="159" t="str">
-        <f>IF(ISNUMBER(CC31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CC31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE32" s="159" t="str">
-        <f>IF(ISNUMBER(CC31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CC31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF32" s="159" t="str">
-        <f>IF(ISNUMBER(CF31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CF31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG32" s="159" t="str">
-        <f>IF(ISNUMBER(CF31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CF31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH32" s="159" t="str">
-        <f>IF(ISNUMBER(CF31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CF31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI32" s="159" t="str">
-        <f>IF(ISNUMBER(CI31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CI31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="CJ32" s="159" t="str">
-        <f>IF(ISNUMBER(CI31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CI31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK32" s="159" t="str">
-        <f>IF(ISNUMBER(CI31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CI31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL32" s="159" t="str">
-        <f>IF(ISNUMBER(CL31),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CL31))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM32" s="159" t="str">
-        <f>IF(ISNUMBER(CL31),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CL31))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN32" s="180" t="str">
-        <f>IF(ISNUMBER(CL31),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CL31))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -10224,342 +10301,342 @@
     <row r="34" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="179"/>
       <c r="C34" s="159" t="str">
-        <f>IF(ISNUMBER(C33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,C33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D34" s="159" t="str">
-        <f>IF(ISNUMBER(C33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,C33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E34" s="159" t="str">
-        <f>IF(ISNUMBER(C33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,C33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F34" s="159" t="str">
-        <f>IF(ISNUMBER(F33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,F33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G34" s="159" t="str">
-        <f>IF(ISNUMBER(F33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,F33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H34" s="159" t="str">
-        <f>IF(ISNUMBER(F33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,F33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I34" s="159" t="str">
-        <f>IF(ISNUMBER(I33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,I33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J34" s="159" t="str">
-        <f>IF(ISNUMBER(I33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,I33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K34" s="159" t="str">
-        <f>IF(ISNUMBER(I33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,I33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L34" s="159" t="str">
-        <f>IF(ISNUMBER(L33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,L33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M34" s="159" t="str">
-        <f>IF(ISNUMBER(L33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,L33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N34" s="159" t="str">
-        <f>IF(ISNUMBER(L33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,L33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O34" s="159" t="str">
-        <f>IF(ISNUMBER(O33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,O33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P34" s="159" t="str">
-        <f>IF(ISNUMBER(O33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,O33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q34" s="159" t="str">
-        <f>IF(ISNUMBER(O33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,O33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R34" s="159" t="str">
-        <f>IF(ISNUMBER(R33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,R33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S34" s="159" t="str">
-        <f>IF(ISNUMBER(R33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,R33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T34" s="159" t="str">
-        <f>IF(ISNUMBER(R33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,R33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U34" s="159" t="str">
-        <f>IF(ISNUMBER(U33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,U33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V34" s="159" t="str">
-        <f>IF(ISNUMBER(U33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,U33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W34" s="180" t="str">
-        <f>IF(ISNUMBER(U33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,U33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y34" s="179"/>
       <c r="Z34" s="159" t="str">
-        <f>IF(ISNUMBER(Z33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,Z33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA34" s="159" t="str">
-        <f>IF(ISNUMBER(Z33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,Z33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB34" s="159" t="str">
-        <f>IF(ISNUMBER(Z33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,Z33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC34" s="159" t="str">
-        <f>IF(ISNUMBER(AC33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AC33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD34" s="159" t="str">
-        <f>IF(ISNUMBER(AC33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AC33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE34" s="159" t="str">
-        <f>IF(ISNUMBER(AC33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AC33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF34" s="159" t="str">
-        <f>IF(ISNUMBER(AF33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AF33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG34" s="159" t="str">
-        <f>IF(ISNUMBER(AF33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AF33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH34" s="159" t="str">
-        <f>IF(ISNUMBER(AF33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AF33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI34" s="159" t="str">
-        <f>IF(ISNUMBER(AI33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AI33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ34" s="159" t="str">
-        <f>IF(ISNUMBER(AI33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AI33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK34" s="159" t="str">
-        <f>IF(ISNUMBER(AI33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AI33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL34" s="159" t="str">
-        <f>IF(ISNUMBER(AL33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AL33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM34" s="159" t="str">
-        <f>IF(ISNUMBER(AL33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AL33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN34" s="159" t="str">
-        <f>IF(ISNUMBER(AL33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AL33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO34" s="159" t="str">
-        <f>IF(ISNUMBER(AO33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AO33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP34" s="159" t="str">
-        <f>IF(ISNUMBER(AO33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AO33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ34" s="159" t="str">
-        <f>IF(ISNUMBER(AO33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AO33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
         <v>P</v>
       </c>
       <c r="AR34" s="159" t="str">
-        <f>IF(ISNUMBER(AR33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AR33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS34" s="159" t="str">
-        <f>IF(ISNUMBER(AR33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AR33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT34" s="180" t="str">
-        <f>IF(ISNUMBER(AR33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AR33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV34" s="179"/>
       <c r="AW34" s="159" t="str">
-        <f>IF(ISNUMBER(AW33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AW33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX34" s="159" t="str">
-        <f>IF(ISNUMBER(AW33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AW33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY34" s="159" t="str">
-        <f>IF(ISNUMBER(AW33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AW33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ34" s="159" t="str">
-        <f>IF(ISNUMBER(AZ33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AZ33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA34" s="159" t="str">
-        <f>IF(ISNUMBER(AZ33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AZ33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB34" s="159" t="str">
-        <f>IF(ISNUMBER(AZ33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AZ33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC34" s="159" t="str">
-        <f>IF(ISNUMBER(BC33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BC33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD34" s="159" t="str">
-        <f>IF(ISNUMBER(BC33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BC33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE34" s="159" t="str">
-        <f>IF(ISNUMBER(BC33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BC33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF34" s="159" t="str">
-        <f>IF(ISNUMBER(BF33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BF33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG34" s="159" t="str">
-        <f>IF(ISNUMBER(BF33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BF33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH34" s="159" t="str">
-        <f>IF(ISNUMBER(BF33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BF33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI34" s="159" t="str">
-        <f>IF(ISNUMBER(BI33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BI33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ34" s="159" t="str">
-        <f>IF(ISNUMBER(BI33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BI33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK34" s="159" t="str">
-        <f>IF(ISNUMBER(BI33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BI33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL34" s="159" t="str">
-        <f>IF(ISNUMBER(BL33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BL33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM34" s="159" t="str">
-        <f>IF(ISNUMBER(BL33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BL33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN34" s="159" t="str">
-        <f>IF(ISNUMBER(BL33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BL33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO34" s="159" t="str">
-        <f>IF(ISNUMBER(BO33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BO33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP34" s="159" t="str">
-        <f>IF(ISNUMBER(BO33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BO33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ34" s="180" t="str">
-        <f>IF(ISNUMBER(BO33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BO33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS34" s="179"/>
       <c r="BT34" s="159" t="str">
-        <f>IF(ISNUMBER(BT33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BT33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU34" s="159" t="str">
-        <f>IF(ISNUMBER(BT33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BT33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV34" s="159" t="str">
-        <f>IF(ISNUMBER(BT33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BT33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW34" s="159" t="str">
-        <f>IF(ISNUMBER(BW33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BW33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX34" s="159" t="str">
-        <f>IF(ISNUMBER(BW33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BW33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY34" s="159" t="str">
-        <f>IF(ISNUMBER(BW33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BW33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ34" s="159" t="str">
-        <f>IF(ISNUMBER(BZ33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BZ33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA34" s="159" t="str">
-        <f>IF(ISNUMBER(BZ33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BZ33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="CB34" s="159" t="str">
-        <f>IF(ISNUMBER(BZ33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BZ33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC34" s="159" t="str">
-        <f>IF(ISNUMBER(CC33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CC33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD34" s="159" t="str">
-        <f>IF(ISNUMBER(CC33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CC33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE34" s="159" t="str">
-        <f>IF(ISNUMBER(CC33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CC33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF34" s="159" t="str">
-        <f>IF(ISNUMBER(CF33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CF33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG34" s="159" t="str">
-        <f>IF(ISNUMBER(CF33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CF33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH34" s="159" t="str">
-        <f>IF(ISNUMBER(CF33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CF33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI34" s="159" t="str">
-        <f>IF(ISNUMBER(CI33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CI33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ34" s="159" t="str">
-        <f>IF(ISNUMBER(CI33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CI33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK34" s="159" t="str">
-        <f>IF(ISNUMBER(CI33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CI33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL34" s="159" t="str">
-        <f>IF(ISNUMBER(CL33),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CL33))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM34" s="159" t="str">
-        <f>IF(ISNUMBER(CL33),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CL33))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN34" s="180" t="str">
-        <f>IF(ISNUMBER(CL33),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CL33))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -10752,342 +10829,342 @@
     <row r="36" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="179"/>
       <c r="C36" s="159" t="str">
-        <f>IF(ISNUMBER(C35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,C35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="D36" s="159" t="str">
-        <f>IF(ISNUMBER(C35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,C35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="E36" s="159" t="str">
-        <f>IF(ISNUMBER(C35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,C35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="F36" s="159" t="str">
-        <f>IF(ISNUMBER(F35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,F35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G36" s="159" t="str">
-        <f>IF(ISNUMBER(F35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,F35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H36" s="159" t="str">
-        <f>IF(ISNUMBER(F35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,F35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I36" s="159" t="str">
-        <f>IF(ISNUMBER(I35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,I35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J36" s="159" t="str">
-        <f>IF(ISNUMBER(I35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,I35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K36" s="159" t="str">
-        <f>IF(ISNUMBER(I35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,I35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L36" s="159" t="str">
-        <f>IF(ISNUMBER(L35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,L35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M36" s="159" t="str">
-        <f>IF(ISNUMBER(L35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,L35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N36" s="159" t="str">
-        <f>IF(ISNUMBER(L35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,L35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O36" s="159" t="str">
-        <f>IF(ISNUMBER(O35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,O35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P36" s="159" t="str">
-        <f>IF(ISNUMBER(O35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,O35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q36" s="159" t="str">
-        <f>IF(ISNUMBER(O35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,O35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R36" s="159" t="str">
-        <f>IF(ISNUMBER(R35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,R35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S36" s="159" t="str">
-        <f>IF(ISNUMBER(R35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,R35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T36" s="159" t="str">
-        <f>IF(ISNUMBER(R35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,R35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U36" s="159" t="str">
-        <f>IF(ISNUMBER(U35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,U35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V36" s="159" t="str">
-        <f>IF(ISNUMBER(U35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,U35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W36" s="180" t="str">
-        <f>IF(ISNUMBER(U35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,U35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y36" s="179"/>
       <c r="Z36" s="159" t="str">
-        <f>IF(ISNUMBER(Z35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,Z35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA36" s="159" t="str">
-        <f>IF(ISNUMBER(Z35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,Z35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB36" s="159" t="str">
-        <f>IF(ISNUMBER(Z35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,Z35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC36" s="159" t="str">
-        <f>IF(ISNUMBER(AC35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AC35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD36" s="159" t="str">
-        <f>IF(ISNUMBER(AC35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AC35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE36" s="159" t="str">
-        <f>IF(ISNUMBER(AC35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AC35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF36" s="159" t="str">
-        <f>IF(ISNUMBER(AF35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AF35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG36" s="159" t="str">
-        <f>IF(ISNUMBER(AF35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AF35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH36" s="159" t="str">
-        <f>IF(ISNUMBER(AF35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AF35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI36" s="159" t="str">
-        <f>IF(ISNUMBER(AI35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AI35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ36" s="159" t="str">
-        <f>IF(ISNUMBER(AI35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AI35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK36" s="159" t="str">
-        <f>IF(ISNUMBER(AI35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AI35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL36" s="159" t="str">
-        <f>IF(ISNUMBER(AL35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AL35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM36" s="159" t="str">
-        <f>IF(ISNUMBER(AL35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AL35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN36" s="159" t="str">
-        <f>IF(ISNUMBER(AL35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AL35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO36" s="159" t="str">
-        <f>IF(ISNUMBER(AO35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AO35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP36" s="159" t="str">
-        <f>IF(ISNUMBER(AO35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AO35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ36" s="159" t="str">
-        <f>IF(ISNUMBER(AO35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AO35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR36" s="159" t="str">
-        <f>IF(ISNUMBER(AR35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AR35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS36" s="159" t="str">
-        <f>IF(ISNUMBER(AR35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AR35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT36" s="180" t="str">
-        <f>IF(ISNUMBER(AR35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AR35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV36" s="179"/>
       <c r="AW36" s="159" t="str">
-        <f>IF(ISNUMBER(AW35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AW35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX36" s="159" t="str">
-        <f>IF(ISNUMBER(AW35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AW35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY36" s="159" t="str">
-        <f>IF(ISNUMBER(AW35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AW35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ36" s="159" t="str">
-        <f>IF(ISNUMBER(AZ35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AZ35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA36" s="159" t="str">
-        <f>IF(ISNUMBER(AZ35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AZ35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB36" s="159" t="str">
-        <f>IF(ISNUMBER(AZ35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AZ35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC36" s="159" t="str">
-        <f>IF(ISNUMBER(BC35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BC35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD36" s="159" t="str">
-        <f>IF(ISNUMBER(BC35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BC35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE36" s="159" t="str">
-        <f>IF(ISNUMBER(BC35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BC35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF36" s="159" t="str">
-        <f>IF(ISNUMBER(BF35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BF35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG36" s="159" t="str">
-        <f>IF(ISNUMBER(BF35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BF35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH36" s="159" t="str">
-        <f>IF(ISNUMBER(BF35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BF35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI36" s="159" t="str">
-        <f>IF(ISNUMBER(BI35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BI35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ36" s="159" t="str">
-        <f>IF(ISNUMBER(BI35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BI35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK36" s="159" t="str">
-        <f>IF(ISNUMBER(BI35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BI35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL36" s="159" t="str">
-        <f>IF(ISNUMBER(BL35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BL35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="BM36" s="159" t="str">
-        <f>IF(ISNUMBER(BL35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BL35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN36" s="159" t="str">
-        <f>IF(ISNUMBER(BL35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BL35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO36" s="159" t="str">
-        <f>IF(ISNUMBER(BO35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BO35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP36" s="159" t="str">
-        <f>IF(ISNUMBER(BO35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BO35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ36" s="180" t="str">
-        <f>IF(ISNUMBER(BO35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BO35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS36" s="179"/>
       <c r="BT36" s="159" t="str">
-        <f>IF(ISNUMBER(BT35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BT35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU36" s="159" t="str">
-        <f>IF(ISNUMBER(BT35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BT35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV36" s="159" t="str">
-        <f>IF(ISNUMBER(BT35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BT35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW36" s="159" t="str">
-        <f>IF(ISNUMBER(BW35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BW35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX36" s="159" t="str">
-        <f>IF(ISNUMBER(BW35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BW35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY36" s="159" t="str">
-        <f>IF(ISNUMBER(BW35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BW35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ36" s="159" t="str">
-        <f>IF(ISNUMBER(BZ35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BZ35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA36" s="159" t="str">
-        <f>IF(ISNUMBER(BZ35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BZ35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB36" s="159" t="str">
-        <f>IF(ISNUMBER(BZ35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BZ35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC36" s="159" t="str">
-        <f>IF(ISNUMBER(CC35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CC35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD36" s="159" t="str">
-        <f>IF(ISNUMBER(CC35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CC35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE36" s="159" t="str">
-        <f>IF(ISNUMBER(CC35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CC35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF36" s="159" t="str">
-        <f>IF(ISNUMBER(CF35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CF35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG36" s="159" t="str">
-        <f>IF(ISNUMBER(CF35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CF35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH36" s="159" t="str">
-        <f>IF(ISNUMBER(CF35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CF35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI36" s="159" t="str">
-        <f>IF(ISNUMBER(CI35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CI35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ36" s="159" t="str">
-        <f>IF(ISNUMBER(CI35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CI35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK36" s="159" t="str">
-        <f>IF(ISNUMBER(CI35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CI35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL36" s="159" t="str">
-        <f>IF(ISNUMBER(CL35),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CL35))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM36" s="159" t="str">
-        <f>IF(ISNUMBER(CL35),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CL35))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN36" s="180" t="str">
-        <f>IF(ISNUMBER(CL35),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CL35))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -11280,342 +11357,342 @@
     <row r="38" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="179"/>
       <c r="C38" s="159" t="str">
-        <f>IF(ISNUMBER(C37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,C37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D38" s="159" t="str">
-        <f>IF(ISNUMBER(C37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,C37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E38" s="159" t="str">
-        <f>IF(ISNUMBER(C37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,C37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F38" s="159" t="str">
-        <f>IF(ISNUMBER(F37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,F37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G38" s="159" t="str">
-        <f>IF(ISNUMBER(F37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,F37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H38" s="159" t="str">
-        <f>IF(ISNUMBER(F37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,F37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I38" s="159" t="str">
-        <f>IF(ISNUMBER(I37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,I37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J38" s="159" t="str">
-        <f>IF(ISNUMBER(I37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,I37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K38" s="159" t="str">
-        <f>IF(ISNUMBER(I37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,I37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L38" s="159" t="str">
-        <f>IF(ISNUMBER(L37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,L37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="M38" s="159" t="str">
-        <f>IF(ISNUMBER(L37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,L37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="N38" s="159" t="str">
-        <f>IF(ISNUMBER(L37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,L37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="O38" s="159" t="str">
-        <f>IF(ISNUMBER(O37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,O37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P38" s="159" t="str">
-        <f>IF(ISNUMBER(O37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,O37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q38" s="159" t="str">
-        <f>IF(ISNUMBER(O37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,O37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R38" s="159" t="str">
-        <f>IF(ISNUMBER(R37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,R37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S38" s="159" t="str">
-        <f>IF(ISNUMBER(R37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,R37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T38" s="159" t="str">
-        <f>IF(ISNUMBER(R37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,R37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U38" s="159" t="str">
-        <f>IF(ISNUMBER(U37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,U37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V38" s="159" t="str">
-        <f>IF(ISNUMBER(U37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,U37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W38" s="180" t="str">
-        <f>IF(ISNUMBER(U37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,U37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y38" s="179"/>
       <c r="Z38" s="159" t="str">
-        <f>IF(ISNUMBER(Z37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,Z37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA38" s="159" t="str">
-        <f>IF(ISNUMBER(Z37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,Z37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB38" s="159" t="str">
-        <f>IF(ISNUMBER(Z37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,Z37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC38" s="159" t="str">
-        <f>IF(ISNUMBER(AC37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AC37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD38" s="159" t="str">
-        <f>IF(ISNUMBER(AC37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AC37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE38" s="159" t="str">
-        <f>IF(ISNUMBER(AC37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AC37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF38" s="159" t="str">
-        <f>IF(ISNUMBER(AF37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AF37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG38" s="159" t="str">
-        <f>IF(ISNUMBER(AF37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AF37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AH38" s="159" t="str">
-        <f>IF(ISNUMBER(AF37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AF37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI38" s="159" t="str">
-        <f>IF(ISNUMBER(AI37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AI37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ38" s="159" t="str">
-        <f>IF(ISNUMBER(AI37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AI37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK38" s="159" t="str">
-        <f>IF(ISNUMBER(AI37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AI37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL38" s="159" t="str">
-        <f>IF(ISNUMBER(AL37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AL37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM38" s="159" t="str">
-        <f>IF(ISNUMBER(AL37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AL37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN38" s="159" t="str">
-        <f>IF(ISNUMBER(AL37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AL37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO38" s="159" t="str">
-        <f>IF(ISNUMBER(AO37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AO37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP38" s="159" t="str">
-        <f>IF(ISNUMBER(AO37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AO37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ38" s="159" t="str">
-        <f>IF(ISNUMBER(AO37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AO37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR38" s="159" t="str">
-        <f>IF(ISNUMBER(AR37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AR37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS38" s="159" t="str">
-        <f>IF(ISNUMBER(AR37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AR37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT38" s="180" t="str">
-        <f>IF(ISNUMBER(AR37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AR37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV38" s="179"/>
       <c r="AW38" s="159" t="str">
-        <f>IF(ISNUMBER(AW37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AW37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX38" s="159" t="str">
-        <f>IF(ISNUMBER(AW37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AW37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY38" s="159" t="str">
-        <f>IF(ISNUMBER(AW37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AW37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ38" s="159" t="str">
-        <f>IF(ISNUMBER(AZ37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AZ37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA38" s="159" t="str">
-        <f>IF(ISNUMBER(AZ37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AZ37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB38" s="159" t="str">
-        <f>IF(ISNUMBER(AZ37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AZ37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC38" s="159" t="str">
-        <f>IF(ISNUMBER(BC37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BC37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD38" s="159" t="str">
-        <f>IF(ISNUMBER(BC37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BC37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="BE38" s="159" t="str">
-        <f>IF(ISNUMBER(BC37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BC37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF38" s="159" t="str">
-        <f>IF(ISNUMBER(BF37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BF37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG38" s="159" t="str">
-        <f>IF(ISNUMBER(BF37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BF37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH38" s="159" t="str">
-        <f>IF(ISNUMBER(BF37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BF37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI38" s="159" t="str">
-        <f>IF(ISNUMBER(BI37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BI37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ38" s="159" t="str">
-        <f>IF(ISNUMBER(BI37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BI37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK38" s="159" t="str">
-        <f>IF(ISNUMBER(BI37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BI37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL38" s="159" t="str">
-        <f>IF(ISNUMBER(BL37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BL37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM38" s="159" t="str">
-        <f>IF(ISNUMBER(BL37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BL37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN38" s="159" t="str">
-        <f>IF(ISNUMBER(BL37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BL37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO38" s="159" t="str">
-        <f>IF(ISNUMBER(BO37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BO37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP38" s="159" t="str">
-        <f>IF(ISNUMBER(BO37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BO37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ38" s="180" t="str">
-        <f>IF(ISNUMBER(BO37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BO37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS38" s="179"/>
       <c r="BT38" s="159" t="str">
-        <f>IF(ISNUMBER(BT37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BT37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU38" s="159" t="str">
-        <f>IF(ISNUMBER(BT37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BT37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV38" s="159" t="str">
-        <f>IF(ISNUMBER(BT37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BT37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW38" s="159" t="str">
-        <f>IF(ISNUMBER(BW37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BW37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX38" s="159" t="str">
-        <f>IF(ISNUMBER(BW37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BW37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY38" s="159" t="str">
-        <f>IF(ISNUMBER(BW37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BW37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ38" s="159" t="str">
-        <f>IF(ISNUMBER(BZ37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BZ37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA38" s="159" t="str">
-        <f>IF(ISNUMBER(BZ37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BZ37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="CB38" s="159" t="str">
-        <f>IF(ISNUMBER(BZ37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BZ37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC38" s="159" t="str">
-        <f>IF(ISNUMBER(CC37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CC37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD38" s="159" t="str">
-        <f>IF(ISNUMBER(CC37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CC37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE38" s="159" t="str">
-        <f>IF(ISNUMBER(CC37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CC37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF38" s="159" t="str">
-        <f>IF(ISNUMBER(CF37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CF37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG38" s="159" t="str">
-        <f>IF(ISNUMBER(CF37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CF37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH38" s="159" t="str">
-        <f>IF(ISNUMBER(CF37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CF37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="CI38" s="159" t="str">
-        <f>IF(ISNUMBER(CI37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CI37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ38" s="159" t="str">
-        <f>IF(ISNUMBER(CI37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CI37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK38" s="159" t="str">
-        <f>IF(ISNUMBER(CI37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CI37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL38" s="159" t="str">
-        <f>IF(ISNUMBER(CL37),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CL37))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM38" s="159" t="str">
-        <f>IF(ISNUMBER(CL37),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CL37))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN38" s="180" t="str">
-        <f>IF(ISNUMBER(CL37),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CL37))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -11808,342 +11885,342 @@
     <row r="40" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="181"/>
       <c r="C40" s="182" t="str">
-        <f>IF(ISNUMBER(C39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,C39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D40" s="182" t="str">
-        <f>IF(ISNUMBER(C39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,C39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E40" s="182" t="str">
-        <f>IF(ISNUMBER(C39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,C39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F40" s="182" t="str">
-        <f>IF(ISNUMBER(F39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,F39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G40" s="182" t="str">
-        <f>IF(ISNUMBER(F39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,F39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H40" s="182" t="str">
-        <f>IF(ISNUMBER(F39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,F39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I40" s="182" t="str">
-        <f>IF(ISNUMBER(I39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,I39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J40" s="182" t="str">
-        <f>IF(ISNUMBER(I39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,I39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K40" s="182" t="str">
-        <f>IF(ISNUMBER(I39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,I39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L40" s="182" t="str">
-        <f>IF(ISNUMBER(L39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,L39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M40" s="182" t="str">
-        <f>IF(ISNUMBER(L39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,L39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N40" s="182" t="str">
-        <f>IF(ISNUMBER(L39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,L39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O40" s="182" t="str">
-        <f>IF(ISNUMBER(O39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,O39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P40" s="182" t="str">
-        <f>IF(ISNUMBER(O39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,O39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q40" s="182" t="str">
-        <f>IF(ISNUMBER(O39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,O39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R40" s="182" t="str">
-        <f>IF(ISNUMBER(R39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,R39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S40" s="182" t="str">
-        <f>IF(ISNUMBER(R39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,R39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T40" s="182" t="str">
-        <f>IF(ISNUMBER(R39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,R39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U40" s="182" t="str">
-        <f>IF(ISNUMBER(U39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,5,U39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V40" s="182" t="str">
-        <f>IF(ISNUMBER(U39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,5,U39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W40" s="183" t="str">
-        <f>IF(ISNUMBER(U39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,5,U39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y40" s="181"/>
       <c r="Z40" s="182" t="str">
-        <f>IF(ISNUMBER(Z39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,Z39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA40" s="182" t="str">
-        <f>IF(ISNUMBER(Z39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,Z39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB40" s="182" t="str">
-        <f>IF(ISNUMBER(Z39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,Z39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC40" s="182" t="str">
-        <f>IF(ISNUMBER(AC39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AC39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD40" s="182" t="str">
-        <f>IF(ISNUMBER(AC39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AC39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE40" s="182" t="str">
-        <f>IF(ISNUMBER(AC39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AC39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF40" s="182" t="str">
-        <f>IF(ISNUMBER(AF39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AF39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG40" s="182" t="str">
-        <f>IF(ISNUMBER(AF39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AF39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH40" s="182" t="str">
-        <f>IF(ISNUMBER(AF39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AF39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI40" s="182" t="str">
-        <f>IF(ISNUMBER(AI39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AI39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ40" s="182" t="str">
-        <f>IF(ISNUMBER(AI39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AI39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK40" s="182" t="str">
-        <f>IF(ISNUMBER(AI39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AI39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL40" s="182" t="str">
-        <f>IF(ISNUMBER(AL39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AL39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM40" s="182" t="str">
-        <f>IF(ISNUMBER(AL39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AL39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN40" s="182" t="str">
-        <f>IF(ISNUMBER(AL39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AL39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO40" s="182" t="str">
-        <f>IF(ISNUMBER(AO39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AO39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP40" s="182" t="str">
-        <f>IF(ISNUMBER(AO39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AO39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ40" s="182" t="str">
-        <f>IF(ISNUMBER(AO39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AO39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR40" s="182" t="str">
-        <f>IF(ISNUMBER(AR39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,6,AR39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS40" s="182" t="str">
-        <f>IF(ISNUMBER(AR39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,6,AR39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT40" s="183" t="str">
-        <f>IF(ISNUMBER(AR39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,6,AR39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV40" s="181"/>
       <c r="AW40" s="182" t="str">
-        <f>IF(ISNUMBER(AW39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AW39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX40" s="182" t="str">
-        <f>IF(ISNUMBER(AW39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AW39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY40" s="182" t="str">
-        <f>IF(ISNUMBER(AW39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AW39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ40" s="182" t="str">
-        <f>IF(ISNUMBER(AZ39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,AZ39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA40" s="182" t="str">
-        <f>IF(ISNUMBER(AZ39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,AZ39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB40" s="182" t="str">
-        <f>IF(ISNUMBER(AZ39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,AZ39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC40" s="182" t="str">
-        <f>IF(ISNUMBER(BC39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BC39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD40" s="182" t="str">
-        <f>IF(ISNUMBER(BC39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BC39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE40" s="182" t="str">
-        <f>IF(ISNUMBER(BC39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BC39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF40" s="182" t="str">
-        <f>IF(ISNUMBER(BF39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BF39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG40" s="182" t="str">
-        <f>IF(ISNUMBER(BF39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BF39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH40" s="182" t="str">
-        <f>IF(ISNUMBER(BF39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BF39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI40" s="182" t="str">
-        <f>IF(ISNUMBER(BI39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BI39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ40" s="182" t="str">
-        <f>IF(ISNUMBER(BI39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BI39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK40" s="182" t="str">
-        <f>IF(ISNUMBER(BI39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BI39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL40" s="182" t="str">
-        <f>IF(ISNUMBER(BL39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BL39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM40" s="182" t="str">
-        <f>IF(ISNUMBER(BL39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BL39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN40" s="182" t="str">
-        <f>IF(ISNUMBER(BL39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BL39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO40" s="182" t="str">
-        <f>IF(ISNUMBER(BO39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,7,BO39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP40" s="182" t="str">
-        <f>IF(ISNUMBER(BO39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,7,BO39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ40" s="183" t="str">
-        <f>IF(ISNUMBER(BO39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,7,BO39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS40" s="181"/>
       <c r="BT40" s="182" t="str">
-        <f>IF(ISNUMBER(BT39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BT39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU40" s="182" t="str">
-        <f>IF(ISNUMBER(BT39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BT39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV40" s="182" t="str">
-        <f>IF(ISNUMBER(BT39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BT39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW40" s="182" t="str">
-        <f>IF(ISNUMBER(BW39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BW39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX40" s="182" t="str">
-        <f>IF(ISNUMBER(BW39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BW39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY40" s="182" t="str">
-        <f>IF(ISNUMBER(BW39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BW39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ40" s="182" t="str">
-        <f>IF(ISNUMBER(BZ39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,BZ39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA40" s="182" t="str">
-        <f>IF(ISNUMBER(BZ39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,BZ39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB40" s="182" t="str">
-        <f>IF(ISNUMBER(BZ39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,BZ39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC40" s="182" t="str">
-        <f>IF(ISNUMBER(CC39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CC39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD40" s="182" t="str">
-        <f>IF(ISNUMBER(CC39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CC39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE40" s="182" t="str">
-        <f>IF(ISNUMBER(CC39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CC39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF40" s="182" t="str">
-        <f>IF(ISNUMBER(CF39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CF39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG40" s="182" t="str">
-        <f>IF(ISNUMBER(CF39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CF39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH40" s="182" t="str">
-        <f>IF(ISNUMBER(CF39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CF39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI40" s="182" t="str">
-        <f>IF(ISNUMBER(CI39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CI39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ40" s="182" t="str">
-        <f>IF(ISNUMBER(CI39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CI39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK40" s="182" t="str">
-        <f>IF(ISNUMBER(CI39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CI39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL40" s="182" t="str">
-        <f>IF(ISNUMBER(CL39),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,8,CL39))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM40" s="182" t="str">
-        <f>IF(ISNUMBER(CL39),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,8,CL39))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN40" s="183" t="str">
-        <f>IF(ISNUMBER(CL39),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,8,CL39))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -12695,342 +12772,342 @@
     <row r="46" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="179"/>
       <c r="C46" s="159" t="str">
-        <f>IF(ISNUMBER(C45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,C45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D46" s="159" t="str">
-        <f>IF(ISNUMBER(C45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,C45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E46" s="159" t="str">
-        <f>IF(ISNUMBER(C45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,C45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F46" s="159" t="str">
-        <f>IF(ISNUMBER(F45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,F45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G46" s="159" t="str">
-        <f>IF(ISNUMBER(F45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,F45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H46" s="159" t="str">
-        <f>IF(ISNUMBER(F45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,F45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I46" s="159" t="str">
-        <f>IF(ISNUMBER(I45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,I45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J46" s="159" t="str">
-        <f>IF(ISNUMBER(I45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,I45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K46" s="159" t="str">
-        <f>IF(ISNUMBER(I45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,I45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L46" s="159" t="str">
-        <f>IF(ISNUMBER(L45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,L45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M46" s="159" t="str">
-        <f>IF(ISNUMBER(L45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,L45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N46" s="159" t="str">
-        <f>IF(ISNUMBER(L45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,L45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O46" s="159" t="str">
-        <f>IF(ISNUMBER(O45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,O45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P46" s="159" t="str">
-        <f>IF(ISNUMBER(O45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,O45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q46" s="159" t="str">
-        <f>IF(ISNUMBER(O45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,O45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R46" s="159" t="str">
-        <f>IF(ISNUMBER(R45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,R45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S46" s="159" t="str">
-        <f>IF(ISNUMBER(R45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,R45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T46" s="159" t="str">
-        <f>IF(ISNUMBER(R45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,R45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U46" s="159" t="str">
-        <f>IF(ISNUMBER(U45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,U45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V46" s="159" t="str">
-        <f>IF(ISNUMBER(U45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,U45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W46" s="180" t="str">
-        <f>IF(ISNUMBER(U45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,U45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y46" s="179"/>
       <c r="Z46" s="159" t="str">
-        <f>IF(ISNUMBER(Z45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,Z45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA46" s="159" t="str">
-        <f>IF(ISNUMBER(Z45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,Z45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB46" s="159" t="str">
-        <f>IF(ISNUMBER(Z45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,Z45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC46" s="159" t="str">
-        <f>IF(ISNUMBER(AC45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AC45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD46" s="159" t="str">
-        <f>IF(ISNUMBER(AC45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AC45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE46" s="159" t="str">
-        <f>IF(ISNUMBER(AC45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AC45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF46" s="159" t="str">
-        <f>IF(ISNUMBER(AF45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AF45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG46" s="159" t="str">
-        <f>IF(ISNUMBER(AF45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AF45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH46" s="159" t="str">
-        <f>IF(ISNUMBER(AF45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AF45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI46" s="159" t="str">
-        <f>IF(ISNUMBER(AI45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AI45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ46" s="159" t="str">
-        <f>IF(ISNUMBER(AI45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AI45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK46" s="159" t="str">
-        <f>IF(ISNUMBER(AI45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AI45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL46" s="159" t="str">
-        <f>IF(ISNUMBER(AL45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AL45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM46" s="159" t="str">
-        <f>IF(ISNUMBER(AL45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AL45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN46" s="159" t="str">
-        <f>IF(ISNUMBER(AL45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AL45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO46" s="159" t="str">
-        <f>IF(ISNUMBER(AO45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AO45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP46" s="159" t="str">
-        <f>IF(ISNUMBER(AO45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AO45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ46" s="159" t="str">
-        <f>IF(ISNUMBER(AO45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AO45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR46" s="159" t="str">
-        <f>IF(ISNUMBER(AR45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AR45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="AS46" s="159" t="str">
-        <f>IF(ISNUMBER(AR45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AR45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="AT46" s="180" t="str">
-        <f>IF(ISNUMBER(AR45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AR45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="AV46" s="179"/>
       <c r="AW46" s="159" t="str">
-        <f>IF(ISNUMBER(AW45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AW45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AX46" s="159" t="str">
-        <f>IF(ISNUMBER(AW45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AW45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AY46" s="159" t="str">
-        <f>IF(ISNUMBER(AW45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AW45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AZ46" s="159" t="str">
-        <f>IF(ISNUMBER(AZ45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AZ45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA46" s="159" t="str">
-        <f>IF(ISNUMBER(AZ45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AZ45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB46" s="159" t="str">
-        <f>IF(ISNUMBER(AZ45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AZ45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC46" s="159" t="str">
-        <f>IF(ISNUMBER(BC45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BC45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD46" s="159" t="str">
-        <f>IF(ISNUMBER(BC45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BC45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE46" s="159" t="str">
-        <f>IF(ISNUMBER(BC45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BC45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF46" s="159" t="str">
-        <f>IF(ISNUMBER(BF45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BF45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG46" s="159" t="str">
-        <f>IF(ISNUMBER(BF45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BF45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH46" s="159" t="str">
-        <f>IF(ISNUMBER(BF45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BF45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI46" s="159" t="str">
-        <f>IF(ISNUMBER(BI45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BI45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ46" s="159" t="str">
-        <f>IF(ISNUMBER(BI45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BI45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK46" s="159" t="str">
-        <f>IF(ISNUMBER(BI45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BI45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL46" s="159" t="str">
-        <f>IF(ISNUMBER(BL45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BL45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM46" s="159" t="str">
-        <f>IF(ISNUMBER(BL45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BL45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN46" s="159" t="str">
-        <f>IF(ISNUMBER(BL45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BL45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO46" s="159" t="str">
-        <f>IF(ISNUMBER(BO45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BO45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP46" s="159" t="str">
-        <f>IF(ISNUMBER(BO45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BO45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ46" s="180" t="str">
-        <f>IF(ISNUMBER(BO45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BO45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS46" s="179"/>
       <c r="BT46" s="159" t="str">
-        <f>IF(ISNUMBER(BT45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BT45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU46" s="159" t="str">
-        <f>IF(ISNUMBER(BT45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BT45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV46" s="159" t="str">
-        <f>IF(ISNUMBER(BT45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BT45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW46" s="159" t="str">
-        <f>IF(ISNUMBER(BW45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BW45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX46" s="159" t="str">
-        <f>IF(ISNUMBER(BW45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BW45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY46" s="159" t="str">
-        <f>IF(ISNUMBER(BW45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BW45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ46" s="159" t="str">
-        <f>IF(ISNUMBER(BZ45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BZ45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA46" s="159" t="str">
-        <f>IF(ISNUMBER(BZ45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BZ45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB46" s="159" t="str">
-        <f>IF(ISNUMBER(BZ45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BZ45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC46" s="159" t="str">
-        <f>IF(ISNUMBER(CC45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CC45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD46" s="159" t="str">
-        <f>IF(ISNUMBER(CC45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CC45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE46" s="159" t="str">
-        <f>IF(ISNUMBER(CC45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CC45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF46" s="159" t="str">
-        <f>IF(ISNUMBER(CF45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CF45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG46" s="159" t="str">
-        <f>IF(ISNUMBER(CF45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CF45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH46" s="159" t="str">
-        <f>IF(ISNUMBER(CF45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CF45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI46" s="159" t="str">
-        <f>IF(ISNUMBER(CI45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CI45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ46" s="159" t="str">
-        <f>IF(ISNUMBER(CI45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CI45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK46" s="159" t="str">
-        <f>IF(ISNUMBER(CI45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CI45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL46" s="159" t="str">
-        <f>IF(ISNUMBER(CL45),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CL45))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM46" s="159" t="str">
-        <f>IF(ISNUMBER(CL45),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CL45))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN46" s="180" t="str">
-        <f>IF(ISNUMBER(CL45),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CL45))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -13223,342 +13300,342 @@
     <row r="48" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="179"/>
       <c r="C48" s="159" t="str">
-        <f>IF(ISNUMBER(C47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,C47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D48" s="159" t="str">
-        <f>IF(ISNUMBER(C47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,C47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E48" s="159" t="str">
-        <f>IF(ISNUMBER(C47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,C47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F48" s="159" t="str">
-        <f>IF(ISNUMBER(F47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,F47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G48" s="159" t="str">
-        <f>IF(ISNUMBER(F47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,F47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H48" s="159" t="str">
-        <f>IF(ISNUMBER(F47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,F47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I48" s="159" t="str">
-        <f>IF(ISNUMBER(I47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,I47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J48" s="159" t="str">
-        <f>IF(ISNUMBER(I47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,I47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K48" s="159" t="str">
-        <f>IF(ISNUMBER(I47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,I47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L48" s="159" t="str">
-        <f>IF(ISNUMBER(L47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,L47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M48" s="159" t="str">
-        <f>IF(ISNUMBER(L47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,L47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N48" s="159" t="str">
-        <f>IF(ISNUMBER(L47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,L47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O48" s="159" t="str">
-        <f>IF(ISNUMBER(O47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,O47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P48" s="159" t="str">
-        <f>IF(ISNUMBER(O47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,O47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q48" s="159" t="str">
-        <f>IF(ISNUMBER(O47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,O47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R48" s="159" t="str">
-        <f>IF(ISNUMBER(R47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,R47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="S48" s="159" t="str">
-        <f>IF(ISNUMBER(R47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,R47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T48" s="159" t="str">
-        <f>IF(ISNUMBER(R47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,R47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U48" s="159" t="str">
-        <f>IF(ISNUMBER(U47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,U47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V48" s="159" t="str">
-        <f>IF(ISNUMBER(U47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,U47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W48" s="180" t="str">
-        <f>IF(ISNUMBER(U47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,U47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y48" s="179"/>
       <c r="Z48" s="159" t="str">
-        <f>IF(ISNUMBER(Z47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,Z47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA48" s="159" t="str">
-        <f>IF(ISNUMBER(Z47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,Z47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB48" s="159" t="str">
-        <f>IF(ISNUMBER(Z47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,Z47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC48" s="159" t="str">
-        <f>IF(ISNUMBER(AC47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AC47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD48" s="159" t="str">
-        <f>IF(ISNUMBER(AC47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AC47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE48" s="159" t="str">
-        <f>IF(ISNUMBER(AC47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AC47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF48" s="159" t="str">
-        <f>IF(ISNUMBER(AF47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AF47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG48" s="159" t="str">
-        <f>IF(ISNUMBER(AF47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AF47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH48" s="159" t="str">
-        <f>IF(ISNUMBER(AF47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AF47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI48" s="159" t="str">
-        <f>IF(ISNUMBER(AI47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AI47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ48" s="159" t="str">
-        <f>IF(ISNUMBER(AI47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AI47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK48" s="159" t="str">
-        <f>IF(ISNUMBER(AI47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AI47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL48" s="159" t="str">
-        <f>IF(ISNUMBER(AL47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AL47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM48" s="159" t="str">
-        <f>IF(ISNUMBER(AL47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AL47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN48" s="159" t="str">
-        <f>IF(ISNUMBER(AL47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AL47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="AO48" s="159" t="str">
-        <f>IF(ISNUMBER(AO47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AO47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP48" s="159" t="str">
-        <f>IF(ISNUMBER(AO47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AO47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ48" s="159" t="str">
-        <f>IF(ISNUMBER(AO47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AO47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR48" s="159" t="str">
-        <f>IF(ISNUMBER(AR47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AR47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS48" s="159" t="str">
-        <f>IF(ISNUMBER(AR47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AR47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT48" s="180" t="str">
-        <f>IF(ISNUMBER(AR47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AR47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV48" s="179"/>
       <c r="AW48" s="159" t="str">
-        <f>IF(ISNUMBER(AW47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AW47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX48" s="159" t="str">
-        <f>IF(ISNUMBER(AW47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AW47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY48" s="159" t="str">
-        <f>IF(ISNUMBER(AW47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AW47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ48" s="159" t="str">
-        <f>IF(ISNUMBER(AZ47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AZ47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA48" s="159" t="str">
-        <f>IF(ISNUMBER(AZ47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AZ47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB48" s="159" t="str">
-        <f>IF(ISNUMBER(AZ47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AZ47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC48" s="159" t="str">
-        <f>IF(ISNUMBER(BC47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BC47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD48" s="159" t="str">
-        <f>IF(ISNUMBER(BC47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BC47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE48" s="159" t="str">
-        <f>IF(ISNUMBER(BC47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BC47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF48" s="159" t="str">
-        <f>IF(ISNUMBER(BF47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BF47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG48" s="159" t="str">
-        <f>IF(ISNUMBER(BF47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BF47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH48" s="159" t="str">
-        <f>IF(ISNUMBER(BF47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BF47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI48" s="159" t="str">
-        <f>IF(ISNUMBER(BI47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BI47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ48" s="159" t="str">
-        <f>IF(ISNUMBER(BI47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BI47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK48" s="159" t="str">
-        <f>IF(ISNUMBER(BI47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BI47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL48" s="159" t="str">
-        <f>IF(ISNUMBER(BL47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BL47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM48" s="159" t="str">
-        <f>IF(ISNUMBER(BL47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BL47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN48" s="159" t="str">
-        <f>IF(ISNUMBER(BL47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BL47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO48" s="159" t="str">
-        <f>IF(ISNUMBER(BO47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BO47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP48" s="159" t="str">
-        <f>IF(ISNUMBER(BO47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BO47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ48" s="180" t="str">
-        <f>IF(ISNUMBER(BO47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BO47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS48" s="179"/>
       <c r="BT48" s="159" t="str">
-        <f>IF(ISNUMBER(BT47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BT47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU48" s="159" t="str">
-        <f>IF(ISNUMBER(BT47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BT47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV48" s="159" t="str">
-        <f>IF(ISNUMBER(BT47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BT47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW48" s="159" t="str">
-        <f>IF(ISNUMBER(BW47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BW47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX48" s="159" t="str">
-        <f>IF(ISNUMBER(BW47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BW47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY48" s="159" t="str">
-        <f>IF(ISNUMBER(BW47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BW47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ48" s="159" t="str">
-        <f>IF(ISNUMBER(BZ47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BZ47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA48" s="159" t="str">
-        <f>IF(ISNUMBER(BZ47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BZ47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB48" s="159" t="str">
-        <f>IF(ISNUMBER(BZ47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BZ47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC48" s="159" t="str">
-        <f>IF(ISNUMBER(CC47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CC47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD48" s="159" t="str">
-        <f>IF(ISNUMBER(CC47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CC47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE48" s="159" t="str">
-        <f>IF(ISNUMBER(CC47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CC47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF48" s="159" t="str">
-        <f>IF(ISNUMBER(CF47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CF47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG48" s="159" t="str">
-        <f>IF(ISNUMBER(CF47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CF47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH48" s="159" t="str">
-        <f>IF(ISNUMBER(CF47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CF47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="CI48" s="159" t="str">
-        <f>IF(ISNUMBER(CI47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CI47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ48" s="159" t="str">
-        <f>IF(ISNUMBER(CI47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CI47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK48" s="159" t="str">
-        <f>IF(ISNUMBER(CI47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CI47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL48" s="159" t="str">
-        <f>IF(ISNUMBER(CL47),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CL47))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM48" s="159" t="str">
-        <f>IF(ISNUMBER(CL47),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CL47))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN48" s="180" t="str">
-        <f>IF(ISNUMBER(CL47),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CL47))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -13751,342 +13828,342 @@
     <row r="50" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="179"/>
       <c r="C50" s="159" t="str">
-        <f>IF(ISNUMBER(C49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,C49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D50" s="159" t="str">
-        <f>IF(ISNUMBER(C49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,C49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E50" s="159" t="str">
-        <f>IF(ISNUMBER(C49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,C49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F50" s="159" t="str">
-        <f>IF(ISNUMBER(F49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,F49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G50" s="159" t="str">
-        <f>IF(ISNUMBER(F49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,F49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H50" s="159" t="str">
-        <f>IF(ISNUMBER(F49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,F49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I50" s="159" t="str">
-        <f>IF(ISNUMBER(I49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,I49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J50" s="159" t="str">
-        <f>IF(ISNUMBER(I49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,I49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K50" s="159" t="str">
-        <f>IF(ISNUMBER(I49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,I49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L50" s="159" t="str">
-        <f>IF(ISNUMBER(L49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,L49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M50" s="159" t="str">
-        <f>IF(ISNUMBER(L49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,L49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N50" s="159" t="str">
-        <f>IF(ISNUMBER(L49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,L49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O50" s="159" t="str">
-        <f>IF(ISNUMBER(O49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,O49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P50" s="159" t="str">
-        <f>IF(ISNUMBER(O49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,O49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q50" s="159" t="str">
-        <f>IF(ISNUMBER(O49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,O49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R50" s="159" t="str">
-        <f>IF(ISNUMBER(R49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,R49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S50" s="159" t="str">
-        <f>IF(ISNUMBER(R49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,R49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T50" s="159" t="str">
-        <f>IF(ISNUMBER(R49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,R49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U50" s="159" t="str">
-        <f>IF(ISNUMBER(U49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,U49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V50" s="159" t="str">
-        <f>IF(ISNUMBER(U49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,U49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W50" s="180" t="str">
-        <f>IF(ISNUMBER(U49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,U49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y50" s="179"/>
       <c r="Z50" s="159" t="str">
-        <f>IF(ISNUMBER(Z49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,Z49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA50" s="159" t="str">
-        <f>IF(ISNUMBER(Z49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,Z49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB50" s="159" t="str">
-        <f>IF(ISNUMBER(Z49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,Z49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC50" s="159" t="str">
-        <f>IF(ISNUMBER(AC49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AC49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD50" s="159" t="str">
-        <f>IF(ISNUMBER(AC49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AC49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE50" s="159" t="str">
-        <f>IF(ISNUMBER(AC49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AC49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF50" s="159" t="str">
-        <f>IF(ISNUMBER(AF49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AF49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG50" s="159" t="str">
-        <f>IF(ISNUMBER(AF49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AF49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AH50" s="159" t="str">
-        <f>IF(ISNUMBER(AF49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AF49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI50" s="159" t="str">
-        <f>IF(ISNUMBER(AI49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AI49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ50" s="159" t="str">
-        <f>IF(ISNUMBER(AI49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AI49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK50" s="159" t="str">
-        <f>IF(ISNUMBER(AI49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AI49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL50" s="159" t="str">
-        <f>IF(ISNUMBER(AL49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AL49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM50" s="159" t="str">
-        <f>IF(ISNUMBER(AL49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AL49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN50" s="159" t="str">
-        <f>IF(ISNUMBER(AL49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AL49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO50" s="159" t="str">
-        <f>IF(ISNUMBER(AO49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AO49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP50" s="159" t="str">
-        <f>IF(ISNUMBER(AO49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AO49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ50" s="159" t="str">
-        <f>IF(ISNUMBER(AO49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AO49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR50" s="159" t="str">
-        <f>IF(ISNUMBER(AR49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AR49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS50" s="159" t="str">
-        <f>IF(ISNUMBER(AR49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AR49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT50" s="180" t="str">
-        <f>IF(ISNUMBER(AR49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AR49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV50" s="179"/>
       <c r="AW50" s="159" t="str">
-        <f>IF(ISNUMBER(AW49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AW49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX50" s="159" t="str">
-        <f>IF(ISNUMBER(AW49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AW49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY50" s="159" t="str">
-        <f>IF(ISNUMBER(AW49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AW49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ50" s="159" t="str">
-        <f>IF(ISNUMBER(AZ49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AZ49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA50" s="159" t="str">
-        <f>IF(ISNUMBER(AZ49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AZ49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB50" s="159" t="str">
-        <f>IF(ISNUMBER(AZ49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AZ49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC50" s="159" t="str">
-        <f>IF(ISNUMBER(BC49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BC49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD50" s="159" t="str">
-        <f>IF(ISNUMBER(BC49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BC49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE50" s="159" t="str">
-        <f>IF(ISNUMBER(BC49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BC49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF50" s="159" t="str">
-        <f>IF(ISNUMBER(BF49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BF49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG50" s="159" t="str">
-        <f>IF(ISNUMBER(BF49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BF49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH50" s="159" t="str">
-        <f>IF(ISNUMBER(BF49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BF49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI50" s="159" t="str">
-        <f>IF(ISNUMBER(BI49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BI49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ50" s="159" t="str">
-        <f>IF(ISNUMBER(BI49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BI49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK50" s="159" t="str">
-        <f>IF(ISNUMBER(BI49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BI49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL50" s="159" t="str">
-        <f>IF(ISNUMBER(BL49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BL49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM50" s="159" t="str">
-        <f>IF(ISNUMBER(BL49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BL49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN50" s="159" t="str">
-        <f>IF(ISNUMBER(BL49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BL49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO50" s="159" t="str">
-        <f>IF(ISNUMBER(BO49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BO49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP50" s="159" t="str">
-        <f>IF(ISNUMBER(BO49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BO49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ50" s="180" t="str">
-        <f>IF(ISNUMBER(BO49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BO49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS50" s="179"/>
       <c r="BT50" s="159" t="str">
-        <f>IF(ISNUMBER(BT49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BT49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU50" s="159" t="str">
-        <f>IF(ISNUMBER(BT49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BT49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV50" s="159" t="str">
-        <f>IF(ISNUMBER(BT49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BT49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW50" s="159" t="str">
-        <f>IF(ISNUMBER(BW49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BW49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX50" s="159" t="str">
-        <f>IF(ISNUMBER(BW49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BW49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY50" s="159" t="str">
-        <f>IF(ISNUMBER(BW49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BW49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ50" s="159" t="str">
-        <f>IF(ISNUMBER(BZ49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BZ49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA50" s="159" t="str">
-        <f>IF(ISNUMBER(BZ49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BZ49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB50" s="159" t="str">
-        <f>IF(ISNUMBER(BZ49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BZ49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC50" s="159" t="str">
-        <f>IF(ISNUMBER(CC49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CC49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD50" s="159" t="str">
-        <f>IF(ISNUMBER(CC49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CC49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE50" s="159" t="str">
-        <f>IF(ISNUMBER(CC49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CC49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF50" s="159" t="str">
-        <f>IF(ISNUMBER(CF49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CF49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG50" s="159" t="str">
-        <f>IF(ISNUMBER(CF49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CF49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH50" s="159" t="str">
-        <f>IF(ISNUMBER(CF49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CF49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI50" s="159" t="str">
-        <f>IF(ISNUMBER(CI49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CI49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ50" s="159" t="str">
-        <f>IF(ISNUMBER(CI49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CI49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK50" s="159" t="str">
-        <f>IF(ISNUMBER(CI49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CI49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL50" s="159" t="str">
-        <f>IF(ISNUMBER(CL49),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CL49))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM50" s="159" t="str">
-        <f>IF(ISNUMBER(CL49),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CL49))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN50" s="180" t="str">
-        <f>IF(ISNUMBER(CL49),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CL49))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -14279,342 +14356,342 @@
     <row r="52" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="179"/>
       <c r="C52" s="159" t="str">
-        <f>IF(ISNUMBER(C51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,C51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D52" s="159" t="str">
-        <f>IF(ISNUMBER(C51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,C51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E52" s="159" t="str">
-        <f>IF(ISNUMBER(C51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,C51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F52" s="159" t="str">
-        <f>IF(ISNUMBER(F51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,F51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G52" s="159" t="str">
-        <f>IF(ISNUMBER(F51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,F51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H52" s="159" t="str">
-        <f>IF(ISNUMBER(F51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,F51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I52" s="159" t="str">
-        <f>IF(ISNUMBER(I51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,I51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J52" s="159" t="str">
-        <f>IF(ISNUMBER(I51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,I51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K52" s="159" t="str">
-        <f>IF(ISNUMBER(I51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,I51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L52" s="159" t="str">
-        <f>IF(ISNUMBER(L51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,L51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M52" s="159" t="str">
-        <f>IF(ISNUMBER(L51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,L51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N52" s="159" t="str">
-        <f>IF(ISNUMBER(L51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,L51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O52" s="159" t="str">
-        <f>IF(ISNUMBER(O51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,O51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P52" s="159" t="str">
-        <f>IF(ISNUMBER(O51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,O51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q52" s="159" t="str">
-        <f>IF(ISNUMBER(O51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,O51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="R52" s="159" t="str">
-        <f>IF(ISNUMBER(R51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,R51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="S52" s="159" t="str">
-        <f>IF(ISNUMBER(R51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,R51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T52" s="159" t="str">
-        <f>IF(ISNUMBER(R51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,R51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U52" s="159" t="str">
-        <f>IF(ISNUMBER(U51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,U51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V52" s="159" t="str">
-        <f>IF(ISNUMBER(U51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,U51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W52" s="180" t="str">
-        <f>IF(ISNUMBER(U51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,U51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y52" s="179"/>
       <c r="Z52" s="159" t="str">
-        <f>IF(ISNUMBER(Z51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,Z51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA52" s="159" t="str">
-        <f>IF(ISNUMBER(Z51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,Z51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB52" s="159" t="str">
-        <f>IF(ISNUMBER(Z51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,Z51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC52" s="159" t="str">
-        <f>IF(ISNUMBER(AC51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AC51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD52" s="159" t="str">
-        <f>IF(ISNUMBER(AC51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AC51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE52" s="159" t="str">
-        <f>IF(ISNUMBER(AC51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AC51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF52" s="159" t="str">
-        <f>IF(ISNUMBER(AF51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AF51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG52" s="159" t="str">
-        <f>IF(ISNUMBER(AF51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AF51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH52" s="159" t="str">
-        <f>IF(ISNUMBER(AF51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AF51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI52" s="159" t="str">
-        <f>IF(ISNUMBER(AI51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AI51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ52" s="159" t="str">
-        <f>IF(ISNUMBER(AI51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AI51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK52" s="159" t="str">
-        <f>IF(ISNUMBER(AI51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AI51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL52" s="159" t="str">
-        <f>IF(ISNUMBER(AL51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AL51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM52" s="159" t="str">
-        <f>IF(ISNUMBER(AL51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AL51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN52" s="159" t="str">
-        <f>IF(ISNUMBER(AL51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AL51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="AO52" s="159" t="str">
-        <f>IF(ISNUMBER(AO51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AO51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP52" s="159" t="str">
-        <f>IF(ISNUMBER(AO51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AO51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ52" s="159" t="str">
-        <f>IF(ISNUMBER(AO51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AO51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR52" s="159" t="str">
-        <f>IF(ISNUMBER(AR51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AR51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS52" s="159" t="str">
-        <f>IF(ISNUMBER(AR51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AR51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT52" s="180" t="str">
-        <f>IF(ISNUMBER(AR51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AR51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV52" s="179"/>
       <c r="AW52" s="159" t="str">
-        <f>IF(ISNUMBER(AW51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AW51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX52" s="159" t="str">
-        <f>IF(ISNUMBER(AW51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AW51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY52" s="159" t="str">
-        <f>IF(ISNUMBER(AW51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AW51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ52" s="159" t="str">
-        <f>IF(ISNUMBER(AZ51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AZ51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA52" s="159" t="str">
-        <f>IF(ISNUMBER(AZ51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AZ51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB52" s="159" t="str">
-        <f>IF(ISNUMBER(AZ51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AZ51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC52" s="159" t="str">
-        <f>IF(ISNUMBER(BC51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BC51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD52" s="159" t="str">
-        <f>IF(ISNUMBER(BC51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BC51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE52" s="159" t="str">
-        <f>IF(ISNUMBER(BC51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BC51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF52" s="159" t="str">
-        <f>IF(ISNUMBER(BF51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BF51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG52" s="159" t="str">
-        <f>IF(ISNUMBER(BF51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BF51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH52" s="159" t="str">
-        <f>IF(ISNUMBER(BF51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BF51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI52" s="159" t="str">
-        <f>IF(ISNUMBER(BI51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BI51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ52" s="159" t="str">
-        <f>IF(ISNUMBER(BI51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BI51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK52" s="159" t="str">
-        <f>IF(ISNUMBER(BI51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BI51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="BL52" s="159" t="str">
-        <f>IF(ISNUMBER(BL51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BL51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM52" s="159" t="str">
-        <f>IF(ISNUMBER(BL51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BL51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN52" s="159" t="str">
-        <f>IF(ISNUMBER(BL51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BL51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO52" s="159" t="str">
-        <f>IF(ISNUMBER(BO51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BO51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP52" s="159" t="str">
-        <f>IF(ISNUMBER(BO51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BO51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ52" s="180" t="str">
-        <f>IF(ISNUMBER(BO51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BO51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS52" s="179"/>
       <c r="BT52" s="159" t="str">
-        <f>IF(ISNUMBER(BT51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BT51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU52" s="159" t="str">
-        <f>IF(ISNUMBER(BT51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BT51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV52" s="159" t="str">
-        <f>IF(ISNUMBER(BT51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BT51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW52" s="159" t="str">
-        <f>IF(ISNUMBER(BW51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BW51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX52" s="159" t="str">
-        <f>IF(ISNUMBER(BW51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BW51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY52" s="159" t="str">
-        <f>IF(ISNUMBER(BW51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BW51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ52" s="159" t="str">
-        <f>IF(ISNUMBER(BZ51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BZ51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA52" s="159" t="str">
-        <f>IF(ISNUMBER(BZ51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BZ51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB52" s="159" t="str">
-        <f>IF(ISNUMBER(BZ51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BZ51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC52" s="159" t="str">
-        <f>IF(ISNUMBER(CC51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CC51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD52" s="159" t="str">
-        <f>IF(ISNUMBER(CC51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CC51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE52" s="159" t="str">
-        <f>IF(ISNUMBER(CC51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CC51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF52" s="159" t="str">
-        <f>IF(ISNUMBER(CF51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CF51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG52" s="159" t="str">
-        <f>IF(ISNUMBER(CF51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CF51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH52" s="159" t="str">
-        <f>IF(ISNUMBER(CF51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CF51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI52" s="159" t="str">
-        <f>IF(ISNUMBER(CI51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CI51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CJ52" s="159" t="str">
-        <f>IF(ISNUMBER(CI51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CI51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CK52" s="159" t="str">
-        <f>IF(ISNUMBER(CI51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CI51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CL52" s="159" t="str">
-        <f>IF(ISNUMBER(CL51),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CL51))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CM52" s="159" t="str">
-        <f>IF(ISNUMBER(CL51),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CL51))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CN52" s="180" t="str">
-        <f>IF(ISNUMBER(CL51),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CL51))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
     </row>
@@ -14807,342 +14884,342 @@
     <row r="54" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="179"/>
       <c r="C54" s="159" t="str">
-        <f>IF(ISNUMBER(C53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,C53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D54" s="159" t="str">
-        <f>IF(ISNUMBER(C53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,C53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E54" s="159" t="str">
-        <f>IF(ISNUMBER(C53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,C53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F54" s="159" t="str">
-        <f>IF(ISNUMBER(F53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,F53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G54" s="159" t="str">
-        <f>IF(ISNUMBER(F53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,F53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H54" s="159" t="str">
-        <f>IF(ISNUMBER(F53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,F53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I54" s="159" t="str">
-        <f>IF(ISNUMBER(I53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,I53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J54" s="159" t="str">
-        <f>IF(ISNUMBER(I53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,I53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="K54" s="159" t="str">
-        <f>IF(ISNUMBER(I53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,I53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L54" s="159" t="str">
-        <f>IF(ISNUMBER(L53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,L53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M54" s="159" t="str">
-        <f>IF(ISNUMBER(L53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,L53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N54" s="159" t="str">
-        <f>IF(ISNUMBER(L53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,L53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O54" s="159" t="str">
-        <f>IF(ISNUMBER(O53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,O53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P54" s="159" t="str">
-        <f>IF(ISNUMBER(O53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,O53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q54" s="159" t="str">
-        <f>IF(ISNUMBER(O53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,O53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R54" s="159" t="str">
-        <f>IF(ISNUMBER(R53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,R53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S54" s="159" t="str">
-        <f>IF(ISNUMBER(R53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,R53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T54" s="159" t="str">
-        <f>IF(ISNUMBER(R53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,R53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U54" s="159" t="str">
-        <f>IF(ISNUMBER(U53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,U53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V54" s="159" t="str">
-        <f>IF(ISNUMBER(U53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,U53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W54" s="180" t="str">
-        <f>IF(ISNUMBER(U53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,U53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y54" s="179"/>
       <c r="Z54" s="159" t="str">
-        <f>IF(ISNUMBER(Z53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,Z53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA54" s="159" t="str">
-        <f>IF(ISNUMBER(Z53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,Z53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB54" s="159" t="str">
-        <f>IF(ISNUMBER(Z53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,Z53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC54" s="159" t="str">
-        <f>IF(ISNUMBER(AC53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AC53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD54" s="159" t="str">
-        <f>IF(ISNUMBER(AC53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AC53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE54" s="159" t="str">
-        <f>IF(ISNUMBER(AC53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AC53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF54" s="159" t="str">
-        <f>IF(ISNUMBER(AF53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AF53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG54" s="159" t="str">
-        <f>IF(ISNUMBER(AF53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AF53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH54" s="159" t="str">
-        <f>IF(ISNUMBER(AF53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AF53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI54" s="159" t="str">
-        <f>IF(ISNUMBER(AI53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AI53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ54" s="159" t="str">
-        <f>IF(ISNUMBER(AI53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AI53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK54" s="159" t="str">
-        <f>IF(ISNUMBER(AI53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AI53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL54" s="159" t="str">
-        <f>IF(ISNUMBER(AL53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AL53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM54" s="159" t="str">
-        <f>IF(ISNUMBER(AL53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AL53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN54" s="159" t="str">
-        <f>IF(ISNUMBER(AL53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AL53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO54" s="159" t="str">
-        <f>IF(ISNUMBER(AO53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AO53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP54" s="159" t="str">
-        <f>IF(ISNUMBER(AO53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AO53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ54" s="159" t="str">
-        <f>IF(ISNUMBER(AO53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AO53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR54" s="159" t="str">
-        <f>IF(ISNUMBER(AR53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AR53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS54" s="159" t="str">
-        <f>IF(ISNUMBER(AR53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AR53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT54" s="180" t="str">
-        <f>IF(ISNUMBER(AR53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AR53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV54" s="179"/>
       <c r="AW54" s="159" t="str">
-        <f>IF(ISNUMBER(AW53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AW53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX54" s="159" t="str">
-        <f>IF(ISNUMBER(AW53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AW53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY54" s="159" t="str">
-        <f>IF(ISNUMBER(AW53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AW53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ54" s="159" t="str">
-        <f>IF(ISNUMBER(AZ53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AZ53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA54" s="159" t="str">
-        <f>IF(ISNUMBER(AZ53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AZ53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB54" s="159" t="str">
-        <f>IF(ISNUMBER(AZ53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AZ53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC54" s="159" t="str">
-        <f>IF(ISNUMBER(BC53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BC53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD54" s="159" t="str">
-        <f>IF(ISNUMBER(BC53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BC53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE54" s="159" t="str">
-        <f>IF(ISNUMBER(BC53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BC53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF54" s="159" t="str">
-        <f>IF(ISNUMBER(BF53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BF53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG54" s="159" t="str">
-        <f>IF(ISNUMBER(BF53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BF53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH54" s="159" t="str">
-        <f>IF(ISNUMBER(BF53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BF53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI54" s="159" t="str">
-        <f>IF(ISNUMBER(BI53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BI53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ54" s="159" t="str">
-        <f>IF(ISNUMBER(BI53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BI53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK54" s="159" t="str">
-        <f>IF(ISNUMBER(BI53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BI53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL54" s="159" t="str">
-        <f>IF(ISNUMBER(BL53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BL53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM54" s="159" t="str">
-        <f>IF(ISNUMBER(BL53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BL53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN54" s="159" t="str">
-        <f>IF(ISNUMBER(BL53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BL53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO54" s="159" t="str">
-        <f>IF(ISNUMBER(BO53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BO53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP54" s="159" t="str">
-        <f>IF(ISNUMBER(BO53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BO53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ54" s="180" t="str">
-        <f>IF(ISNUMBER(BO53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BO53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS54" s="179"/>
       <c r="BT54" s="159" t="str">
-        <f>IF(ISNUMBER(BT53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BT53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU54" s="159" t="str">
-        <f>IF(ISNUMBER(BT53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BT53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV54" s="159" t="str">
-        <f>IF(ISNUMBER(BT53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BT53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW54" s="159" t="str">
-        <f>IF(ISNUMBER(BW53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BW53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX54" s="159" t="str">
-        <f>IF(ISNUMBER(BW53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BW53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY54" s="159" t="str">
-        <f>IF(ISNUMBER(BW53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BW53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ54" s="159" t="str">
-        <f>IF(ISNUMBER(BZ53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BZ53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA54" s="159" t="str">
-        <f>IF(ISNUMBER(BZ53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BZ53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB54" s="159" t="str">
-        <f>IF(ISNUMBER(BZ53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BZ53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC54" s="159" t="str">
-        <f>IF(ISNUMBER(CC53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CC53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD54" s="159" t="str">
-        <f>IF(ISNUMBER(CC53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CC53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE54" s="159" t="str">
-        <f>IF(ISNUMBER(CC53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CC53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF54" s="159" t="str">
-        <f>IF(ISNUMBER(CF53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CF53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG54" s="159" t="str">
-        <f>IF(ISNUMBER(CF53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CF53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH54" s="159" t="str">
-        <f>IF(ISNUMBER(CF53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CF53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI54" s="159" t="str">
-        <f>IF(ISNUMBER(CI53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CI53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ54" s="159" t="str">
-        <f>IF(ISNUMBER(CI53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CI53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK54" s="159" t="str">
-        <f>IF(ISNUMBER(CI53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CI53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL54" s="159" t="str">
-        <f>IF(ISNUMBER(CL53),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CL53))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM54" s="159" t="str">
-        <f>IF(ISNUMBER(CL53),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CL53))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN54" s="180" t="str">
-        <f>IF(ISNUMBER(CL53),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CL53))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -15335,342 +15412,342 @@
     <row r="56" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="181"/>
       <c r="C56" s="182" t="str">
-        <f>IF(ISNUMBER(C55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,C55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D56" s="182" t="str">
-        <f>IF(ISNUMBER(C55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,C55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E56" s="182" t="str">
-        <f>IF(ISNUMBER(C55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,C55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F56" s="182" t="str">
-        <f>IF(ISNUMBER(F55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,F55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G56" s="182" t="str">
-        <f>IF(ISNUMBER(F55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,F55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H56" s="182" t="str">
-        <f>IF(ISNUMBER(F55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,F55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I56" s="182" t="str">
-        <f>IF(ISNUMBER(I55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,I55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J56" s="182" t="str">
-        <f>IF(ISNUMBER(I55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,I55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K56" s="182" t="str">
-        <f>IF(ISNUMBER(I55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,I55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L56" s="182" t="str">
-        <f>IF(ISNUMBER(L55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,L55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M56" s="182" t="str">
-        <f>IF(ISNUMBER(L55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,L55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N56" s="182" t="str">
-        <f>IF(ISNUMBER(L55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,L55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O56" s="182" t="str">
-        <f>IF(ISNUMBER(O55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,O55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P56" s="182" t="str">
-        <f>IF(ISNUMBER(O55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,O55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q56" s="182" t="str">
-        <f>IF(ISNUMBER(O55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,O55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R56" s="182" t="str">
-        <f>IF(ISNUMBER(R55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,R55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S56" s="182" t="str">
-        <f>IF(ISNUMBER(R55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,R55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T56" s="182" t="str">
-        <f>IF(ISNUMBER(R55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,R55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U56" s="182" t="str">
-        <f>IF(ISNUMBER(U55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,9,U55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V56" s="182" t="str">
-        <f>IF(ISNUMBER(U55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,9,U55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W56" s="183" t="str">
-        <f>IF(ISNUMBER(U55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,9,U55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y56" s="181"/>
       <c r="Z56" s="182" t="str">
-        <f>IF(ISNUMBER(Z55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,Z55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA56" s="182" t="str">
-        <f>IF(ISNUMBER(Z55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,Z55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB56" s="182" t="str">
-        <f>IF(ISNUMBER(Z55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,Z55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC56" s="182" t="str">
-        <f>IF(ISNUMBER(AC55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AC55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD56" s="182" t="str">
-        <f>IF(ISNUMBER(AC55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AC55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE56" s="182" t="str">
-        <f>IF(ISNUMBER(AC55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AC55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF56" s="182" t="str">
-        <f>IF(ISNUMBER(AF55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AF55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG56" s="182" t="str">
-        <f>IF(ISNUMBER(AF55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AF55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH56" s="182" t="str">
-        <f>IF(ISNUMBER(AF55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AF55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI56" s="182" t="str">
-        <f>IF(ISNUMBER(AI55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AI55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ56" s="182" t="str">
-        <f>IF(ISNUMBER(AI55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AI55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK56" s="182" t="str">
-        <f>IF(ISNUMBER(AI55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AI55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL56" s="182" t="str">
-        <f>IF(ISNUMBER(AL55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AL55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM56" s="182" t="str">
-        <f>IF(ISNUMBER(AL55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AL55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN56" s="182" t="str">
-        <f>IF(ISNUMBER(AL55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AL55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO56" s="182" t="str">
-        <f>IF(ISNUMBER(AO55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AO55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP56" s="182" t="str">
-        <f>IF(ISNUMBER(AO55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AO55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ56" s="182" t="str">
-        <f>IF(ISNUMBER(AO55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AO55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR56" s="182" t="str">
-        <f>IF(ISNUMBER(AR55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,10,AR55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS56" s="182" t="str">
-        <f>IF(ISNUMBER(AR55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,10,AR55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT56" s="183" t="str">
-        <f>IF(ISNUMBER(AR55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,10,AR55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV56" s="181"/>
       <c r="AW56" s="182" t="str">
-        <f>IF(ISNUMBER(AW55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AW55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX56" s="182" t="str">
-        <f>IF(ISNUMBER(AW55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AW55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY56" s="182" t="str">
-        <f>IF(ISNUMBER(AW55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AW55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ56" s="182" t="str">
-        <f>IF(ISNUMBER(AZ55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,AZ55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA56" s="182" t="str">
-        <f>IF(ISNUMBER(AZ55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,AZ55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB56" s="182" t="str">
-        <f>IF(ISNUMBER(AZ55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,AZ55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC56" s="182" t="str">
-        <f>IF(ISNUMBER(BC55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BC55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD56" s="182" t="str">
-        <f>IF(ISNUMBER(BC55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BC55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE56" s="182" t="str">
-        <f>IF(ISNUMBER(BC55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BC55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF56" s="182" t="str">
-        <f>IF(ISNUMBER(BF55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BF55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG56" s="182" t="str">
-        <f>IF(ISNUMBER(BF55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BF55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH56" s="182" t="str">
-        <f>IF(ISNUMBER(BF55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BF55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI56" s="182" t="str">
-        <f>IF(ISNUMBER(BI55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BI55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ56" s="182" t="str">
-        <f>IF(ISNUMBER(BI55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BI55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK56" s="182" t="str">
-        <f>IF(ISNUMBER(BI55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BI55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL56" s="182" t="str">
-        <f>IF(ISNUMBER(BL55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BL55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM56" s="182" t="str">
-        <f>IF(ISNUMBER(BL55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BL55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN56" s="182" t="str">
-        <f>IF(ISNUMBER(BL55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BL55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO56" s="182" t="str">
-        <f>IF(ISNUMBER(BO55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,11,BO55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP56" s="182" t="str">
-        <f>IF(ISNUMBER(BO55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,11,BO55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ56" s="183" t="str">
-        <f>IF(ISNUMBER(BO55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,11,BO55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS56" s="181"/>
       <c r="BT56" s="182" t="str">
-        <f>IF(ISNUMBER(BT55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BT55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU56" s="182" t="str">
-        <f>IF(ISNUMBER(BT55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BT55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV56" s="182" t="str">
-        <f>IF(ISNUMBER(BT55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BT55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW56" s="182" t="str">
-        <f>IF(ISNUMBER(BW55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BW55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX56" s="182" t="str">
-        <f>IF(ISNUMBER(BW55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BW55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY56" s="182" t="str">
-        <f>IF(ISNUMBER(BW55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BW55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ56" s="182" t="str">
-        <f>IF(ISNUMBER(BZ55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,BZ55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA56" s="182" t="str">
-        <f>IF(ISNUMBER(BZ55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,BZ55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB56" s="182" t="str">
-        <f>IF(ISNUMBER(BZ55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,BZ55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC56" s="182" t="str">
-        <f>IF(ISNUMBER(CC55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CC55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD56" s="182" t="str">
-        <f>IF(ISNUMBER(CC55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CC55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE56" s="182" t="str">
-        <f>IF(ISNUMBER(CC55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CC55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF56" s="182" t="str">
-        <f>IF(ISNUMBER(CF55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CF55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG56" s="182" t="str">
-        <f>IF(ISNUMBER(CF55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CF55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH56" s="182" t="str">
-        <f>IF(ISNUMBER(CF55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CF55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI56" s="182" t="str">
-        <f>IF(ISNUMBER(CI55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CI55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ56" s="182" t="str">
-        <f>IF(ISNUMBER(CI55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CI55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK56" s="182" t="str">
-        <f>IF(ISNUMBER(CI55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CI55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL56" s="182" t="str">
-        <f>IF(ISNUMBER(CL55),IF(COUNTIF(JP_StartSel,DATE(Planungsjahr,12,CL55))&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM56" s="182" t="str">
-        <f>IF(ISNUMBER(CL55),IF(COUNTIF(JP_StartInhalt,DATE(Planungsjahr,12,CL55))&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN56" s="183" t="str">
-        <f>IF(ISNUMBER(CL55),IF(COUNTIF(JP_PAL,DATE(Planungsjahr,12,CL55))&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -15893,12 +15970,18 @@
       <c r="M61" s="127"/>
       <c r="N61" s="127"/>
       <c r="O61" s="127"/>
-      <c r="P61" s="127"/>
-      <c r="Q61" s="127"/>
-      <c r="R61" s="127"/>
-      <c r="S61" s="127"/>
-      <c r="T61" s="127"/>
-      <c r="U61" s="127"/>
+      <c r="P61" s="129" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q61" s="129"/>
+      <c r="R61" s="131" t="s">
+        <v>155</v>
+      </c>
+      <c r="S61" s="131"/>
+      <c r="T61" s="133" t="s">
+        <v>156</v>
+      </c>
+      <c r="U61" s="133"/>
       <c r="V61" s="128" t="s">
         <v>82</v>
       </c>
@@ -16004,12 +16087,18 @@
       <c r="M62" s="134"/>
       <c r="N62" s="134"/>
       <c r="O62" s="134"/>
-      <c r="P62" s="134"/>
-      <c r="Q62" s="134"/>
-      <c r="R62" s="134"/>
-      <c r="S62" s="134"/>
-      <c r="T62" s="134"/>
-      <c r="U62" s="134"/>
+      <c r="P62" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="139"/>
+      <c r="R62" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S62" s="139"/>
+      <c r="T62" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U62" s="139"/>
       <c r="V62" s="135"/>
       <c r="W62" s="135"/>
       <c r="X62" s="135"/>
@@ -16113,12 +16202,18 @@
       <c r="M63" s="134"/>
       <c r="N63" s="134"/>
       <c r="O63" s="134"/>
-      <c r="P63" s="134"/>
-      <c r="Q63" s="134"/>
-      <c r="R63" s="134"/>
-      <c r="S63" s="134"/>
-      <c r="T63" s="134"/>
-      <c r="U63" s="134"/>
+      <c r="P63" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="139"/>
+      <c r="R63" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S63" s="139"/>
+      <c r="T63" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U63" s="139"/>
       <c r="V63" s="135"/>
       <c r="W63" s="135"/>
       <c r="X63" s="135"/>
@@ -16222,12 +16317,18 @@
       <c r="M64" s="134"/>
       <c r="N64" s="134"/>
       <c r="O64" s="134"/>
-      <c r="P64" s="134"/>
-      <c r="Q64" s="134"/>
-      <c r="R64" s="134"/>
-      <c r="S64" s="134"/>
-      <c r="T64" s="134"/>
-      <c r="U64" s="134"/>
+      <c r="P64" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="139"/>
+      <c r="R64" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S64" s="139"/>
+      <c r="T64" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U64" s="139"/>
       <c r="V64" s="135"/>
       <c r="W64" s="135"/>
       <c r="X64" s="135"/>
@@ -16331,12 +16432,18 @@
       <c r="M65" s="134"/>
       <c r="N65" s="134"/>
       <c r="O65" s="134"/>
-      <c r="P65" s="134"/>
-      <c r="Q65" s="134"/>
-      <c r="R65" s="134"/>
-      <c r="S65" s="134"/>
-      <c r="T65" s="134"/>
-      <c r="U65" s="134"/>
+      <c r="P65" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="139"/>
+      <c r="R65" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S65" s="139"/>
+      <c r="T65" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U65" s="139"/>
       <c r="V65" s="135"/>
       <c r="W65" s="135"/>
       <c r="X65" s="135"/>
@@ -16444,12 +16551,18 @@
       <c r="M66" s="134"/>
       <c r="N66" s="134"/>
       <c r="O66" s="134"/>
-      <c r="P66" s="134"/>
-      <c r="Q66" s="134"/>
-      <c r="R66" s="134"/>
-      <c r="S66" s="134"/>
-      <c r="T66" s="134"/>
-      <c r="U66" s="134"/>
+      <c r="P66" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="139"/>
+      <c r="R66" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S66" s="139"/>
+      <c r="T66" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U66" s="139"/>
       <c r="V66" s="135"/>
       <c r="W66" s="135"/>
       <c r="X66" s="135"/>
@@ -16553,12 +16666,18 @@
       <c r="M67" s="134"/>
       <c r="N67" s="134"/>
       <c r="O67" s="134"/>
-      <c r="P67" s="134"/>
-      <c r="Q67" s="134"/>
-      <c r="R67" s="134"/>
-      <c r="S67" s="134"/>
-      <c r="T67" s="134"/>
-      <c r="U67" s="134"/>
+      <c r="P67" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="139"/>
+      <c r="R67" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S67" s="139"/>
+      <c r="T67" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U67" s="139"/>
       <c r="V67" s="135"/>
       <c r="W67" s="135"/>
       <c r="X67" s="135"/>
@@ -16662,12 +16781,18 @@
       <c r="M68" s="134"/>
       <c r="N68" s="134"/>
       <c r="O68" s="134"/>
-      <c r="P68" s="134"/>
-      <c r="Q68" s="134"/>
-      <c r="R68" s="134"/>
-      <c r="S68" s="134"/>
-      <c r="T68" s="134"/>
-      <c r="U68" s="134"/>
+      <c r="P68" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="139"/>
+      <c r="R68" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S68" s="139"/>
+      <c r="T68" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U68" s="139"/>
       <c r="V68" s="135"/>
       <c r="W68" s="135"/>
       <c r="X68" s="135"/>
@@ -16773,12 +16898,18 @@
       <c r="M69" s="134"/>
       <c r="N69" s="134"/>
       <c r="O69" s="134"/>
-      <c r="P69" s="134"/>
-      <c r="Q69" s="134"/>
-      <c r="R69" s="134"/>
-      <c r="S69" s="134"/>
-      <c r="T69" s="134"/>
-      <c r="U69" s="134"/>
+      <c r="P69" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="139"/>
+      <c r="R69" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S69" s="139"/>
+      <c r="T69" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U69" s="139"/>
       <c r="V69" s="135"/>
       <c r="W69" s="135"/>
       <c r="X69" s="135"/>
@@ -16882,12 +17013,18 @@
       <c r="M70" s="134"/>
       <c r="N70" s="134"/>
       <c r="O70" s="134"/>
-      <c r="P70" s="134"/>
-      <c r="Q70" s="134"/>
-      <c r="R70" s="134"/>
-      <c r="S70" s="134"/>
-      <c r="T70" s="134"/>
-      <c r="U70" s="134"/>
+      <c r="P70" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q70" s="139"/>
+      <c r="R70" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S70" s="139"/>
+      <c r="T70" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U70" s="139"/>
       <c r="V70" s="135"/>
       <c r="W70" s="135"/>
       <c r="X70" s="135"/>
@@ -16995,12 +17132,18 @@
       <c r="M71" s="134"/>
       <c r="N71" s="134"/>
       <c r="O71" s="134"/>
-      <c r="P71" s="134"/>
-      <c r="Q71" s="134"/>
-      <c r="R71" s="134"/>
-      <c r="S71" s="134"/>
-      <c r="T71" s="134"/>
-      <c r="U71" s="134"/>
+      <c r="P71" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="139"/>
+      <c r="R71" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S71" s="139"/>
+      <c r="T71" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U71" s="139"/>
       <c r="V71" s="135"/>
       <c r="W71" s="135"/>
       <c r="X71" s="135"/>
@@ -17102,12 +17245,18 @@
       <c r="M72" s="134"/>
       <c r="N72" s="134"/>
       <c r="O72" s="134"/>
-      <c r="P72" s="134"/>
-      <c r="Q72" s="134"/>
-      <c r="R72" s="134"/>
-      <c r="S72" s="134"/>
-      <c r="T72" s="134"/>
-      <c r="U72" s="134"/>
+      <c r="P72" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="139"/>
+      <c r="R72" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S72" s="139"/>
+      <c r="T72" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U72" s="139"/>
       <c r="V72" s="135"/>
       <c r="W72" s="135"/>
       <c r="X72" s="135"/>
@@ -17201,12 +17350,18 @@
       <c r="M73" s="134"/>
       <c r="N73" s="134"/>
       <c r="O73" s="134"/>
-      <c r="P73" s="134"/>
-      <c r="Q73" s="134"/>
-      <c r="R73" s="134"/>
-      <c r="S73" s="134"/>
-      <c r="T73" s="134"/>
-      <c r="U73" s="134"/>
+      <c r="P73" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="139"/>
+      <c r="R73" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S73" s="139"/>
+      <c r="T73" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U73" s="139"/>
       <c r="V73" s="135"/>
       <c r="W73" s="135"/>
       <c r="X73" s="135"/>
@@ -17300,12 +17455,18 @@
       <c r="M74" s="134"/>
       <c r="N74" s="134"/>
       <c r="O74" s="134"/>
-      <c r="P74" s="134"/>
-      <c r="Q74" s="134"/>
-      <c r="R74" s="134"/>
-      <c r="S74" s="134"/>
-      <c r="T74" s="134"/>
-      <c r="U74" s="134"/>
+      <c r="P74" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="139"/>
+      <c r="R74" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S74" s="139"/>
+      <c r="T74" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U74" s="139"/>
       <c r="V74" s="135"/>
       <c r="W74" s="135"/>
       <c r="X74" s="135"/>
@@ -17399,12 +17560,18 @@
       <c r="M75" s="134"/>
       <c r="N75" s="134"/>
       <c r="O75" s="134"/>
-      <c r="P75" s="134"/>
-      <c r="Q75" s="134"/>
-      <c r="R75" s="134"/>
-      <c r="S75" s="134"/>
-      <c r="T75" s="134"/>
-      <c r="U75" s="134"/>
+      <c r="P75" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="139"/>
+      <c r="R75" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S75" s="139"/>
+      <c r="T75" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U75" s="139"/>
       <c r="V75" s="135"/>
       <c r="W75" s="135"/>
       <c r="X75" s="135"/>
@@ -17498,12 +17665,18 @@
       <c r="M76" s="134"/>
       <c r="N76" s="134"/>
       <c r="O76" s="134"/>
-      <c r="P76" s="134"/>
-      <c r="Q76" s="134"/>
-      <c r="R76" s="134"/>
-      <c r="S76" s="134"/>
-      <c r="T76" s="134"/>
-      <c r="U76" s="134"/>
+      <c r="P76" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="139"/>
+      <c r="R76" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S76" s="139"/>
+      <c r="T76" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U76" s="139"/>
       <c r="V76" s="135"/>
       <c r="W76" s="135"/>
       <c r="X76" s="135"/>
@@ -17597,12 +17770,18 @@
       <c r="M77" s="134"/>
       <c r="N77" s="134"/>
       <c r="O77" s="134"/>
-      <c r="P77" s="134"/>
-      <c r="Q77" s="134"/>
-      <c r="R77" s="134"/>
-      <c r="S77" s="134"/>
-      <c r="T77" s="134"/>
-      <c r="U77" s="134"/>
+      <c r="P77" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="139"/>
+      <c r="R77" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S77" s="139"/>
+      <c r="T77" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U77" s="139"/>
       <c r="V77" s="135"/>
       <c r="W77" s="135"/>
       <c r="X77" s="135"/>
@@ -17696,12 +17875,18 @@
       <c r="M78" s="134"/>
       <c r="N78" s="134"/>
       <c r="O78" s="134"/>
-      <c r="P78" s="134"/>
-      <c r="Q78" s="134"/>
-      <c r="R78" s="134"/>
-      <c r="S78" s="134"/>
-      <c r="T78" s="134"/>
-      <c r="U78" s="134"/>
+      <c r="P78" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="139"/>
+      <c r="R78" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S78" s="139"/>
+      <c r="T78" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U78" s="139"/>
       <c r="V78" s="135"/>
       <c r="W78" s="135"/>
       <c r="X78" s="135"/>
@@ -17795,12 +17980,18 @@
       <c r="M79" s="134"/>
       <c r="N79" s="134"/>
       <c r="O79" s="134"/>
-      <c r="P79" s="134"/>
-      <c r="Q79" s="134"/>
-      <c r="R79" s="134"/>
-      <c r="S79" s="134"/>
-      <c r="T79" s="134"/>
-      <c r="U79" s="134"/>
+      <c r="P79" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="139"/>
+      <c r="R79" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S79" s="139"/>
+      <c r="T79" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U79" s="139"/>
       <c r="V79" s="135"/>
       <c r="W79" s="135"/>
       <c r="X79" s="135"/>
@@ -17894,12 +18085,18 @@
       <c r="M80" s="134"/>
       <c r="N80" s="134"/>
       <c r="O80" s="134"/>
-      <c r="P80" s="134"/>
-      <c r="Q80" s="134"/>
-      <c r="R80" s="134"/>
-      <c r="S80" s="134"/>
-      <c r="T80" s="134"/>
-      <c r="U80" s="134"/>
+      <c r="P80" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q80" s="139"/>
+      <c r="R80" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S80" s="139"/>
+      <c r="T80" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U80" s="139"/>
       <c r="V80" s="135"/>
       <c r="W80" s="135"/>
       <c r="X80" s="135"/>
@@ -17993,12 +18190,18 @@
       <c r="M81" s="134"/>
       <c r="N81" s="134"/>
       <c r="O81" s="134"/>
-      <c r="P81" s="134"/>
-      <c r="Q81" s="134"/>
-      <c r="R81" s="134"/>
-      <c r="S81" s="134"/>
-      <c r="T81" s="134"/>
-      <c r="U81" s="134"/>
+      <c r="P81" s="198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q81" s="139"/>
+      <c r="R81" s="199" t="b">
+        <v>1</v>
+      </c>
+      <c r="S81" s="139"/>
+      <c r="T81" s="200" t="b">
+        <v>1</v>
+      </c>
+      <c r="U81" s="139"/>
       <c r="V81" s="135"/>
       <c r="W81" s="135"/>
       <c r="X81" s="135"/>
@@ -18552,14 +18755,23 @@
       <c r="CM87" s="142"/>
       <c r="CN87" s="142"/>
     </row>
+    <row r="88" spans="2:92" ht="15" customHeight="1">
+      <c r="B88" s="142" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="739">
+  <mergeCells count="803">
     <mergeCell ref="B83:CN83"/>
     <mergeCell ref="B84:CN84"/>
     <mergeCell ref="B85:CN85"/>
     <mergeCell ref="B86:CN86"/>
     <mergeCell ref="B87:CN87"/>
-    <mergeCell ref="B81:U81"/>
+    <mergeCell ref="B88:CN88"/>
+    <mergeCell ref="B81:O81"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="R81:S81"/>
+    <mergeCell ref="T81:U81"/>
     <mergeCell ref="V81:Y81"/>
     <mergeCell ref="Z81:AH81"/>
     <mergeCell ref="AI81:AO81"/>
@@ -18568,7 +18780,10 @@
     <mergeCell ref="BD81:BL81"/>
     <mergeCell ref="BM81:BT81"/>
     <mergeCell ref="BU81:CN81"/>
-    <mergeCell ref="B80:U80"/>
+    <mergeCell ref="B80:O80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="R80:S80"/>
+    <mergeCell ref="T80:U80"/>
     <mergeCell ref="V80:Y80"/>
     <mergeCell ref="Z80:AH80"/>
     <mergeCell ref="AI80:AO80"/>
@@ -18577,7 +18792,10 @@
     <mergeCell ref="BD80:BL80"/>
     <mergeCell ref="BM80:BT80"/>
     <mergeCell ref="BU80:CN80"/>
-    <mergeCell ref="B79:U79"/>
+    <mergeCell ref="B79:O79"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="R79:S79"/>
+    <mergeCell ref="T79:U79"/>
     <mergeCell ref="V79:Y79"/>
     <mergeCell ref="Z79:AH79"/>
     <mergeCell ref="AI79:AO79"/>
@@ -18586,7 +18804,10 @@
     <mergeCell ref="BD79:BL79"/>
     <mergeCell ref="BM79:BT79"/>
     <mergeCell ref="BU79:CN79"/>
-    <mergeCell ref="B78:U78"/>
+    <mergeCell ref="B78:O78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="R78:S78"/>
+    <mergeCell ref="T78:U78"/>
     <mergeCell ref="V78:Y78"/>
     <mergeCell ref="Z78:AH78"/>
     <mergeCell ref="AI78:AO78"/>
@@ -18595,7 +18816,10 @@
     <mergeCell ref="BD78:BL78"/>
     <mergeCell ref="BM78:BT78"/>
     <mergeCell ref="BU78:CN78"/>
-    <mergeCell ref="B77:U77"/>
+    <mergeCell ref="B77:O77"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="R77:S77"/>
+    <mergeCell ref="T77:U77"/>
     <mergeCell ref="V77:Y77"/>
     <mergeCell ref="Z77:AH77"/>
     <mergeCell ref="AI77:AO77"/>
@@ -18604,7 +18828,10 @@
     <mergeCell ref="BD77:BL77"/>
     <mergeCell ref="BM77:BT77"/>
     <mergeCell ref="BU77:CN77"/>
-    <mergeCell ref="B76:U76"/>
+    <mergeCell ref="B76:O76"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="R76:S76"/>
+    <mergeCell ref="T76:U76"/>
     <mergeCell ref="V76:Y76"/>
     <mergeCell ref="Z76:AH76"/>
     <mergeCell ref="AI76:AO76"/>
@@ -18613,7 +18840,10 @@
     <mergeCell ref="BD76:BL76"/>
     <mergeCell ref="BM76:BT76"/>
     <mergeCell ref="BU76:CN76"/>
-    <mergeCell ref="B75:U75"/>
+    <mergeCell ref="B75:O75"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="T75:U75"/>
     <mergeCell ref="V75:Y75"/>
     <mergeCell ref="Z75:AH75"/>
     <mergeCell ref="AI75:AO75"/>
@@ -18622,7 +18852,10 @@
     <mergeCell ref="BD75:BL75"/>
     <mergeCell ref="BM75:BT75"/>
     <mergeCell ref="BU75:CN75"/>
-    <mergeCell ref="B74:U74"/>
+    <mergeCell ref="B74:O74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="T74:U74"/>
     <mergeCell ref="V74:Y74"/>
     <mergeCell ref="Z74:AH74"/>
     <mergeCell ref="AI74:AO74"/>
@@ -18631,7 +18864,10 @@
     <mergeCell ref="BD74:BL74"/>
     <mergeCell ref="BM74:BT74"/>
     <mergeCell ref="BU74:CN74"/>
-    <mergeCell ref="B73:U73"/>
+    <mergeCell ref="B73:O73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="T73:U73"/>
     <mergeCell ref="V73:Y73"/>
     <mergeCell ref="Z73:AH73"/>
     <mergeCell ref="AI73:AO73"/>
@@ -18640,7 +18876,10 @@
     <mergeCell ref="BD73:BL73"/>
     <mergeCell ref="BM73:BT73"/>
     <mergeCell ref="BU73:CN73"/>
-    <mergeCell ref="B72:U72"/>
+    <mergeCell ref="B72:O72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T72:U72"/>
     <mergeCell ref="V72:Y72"/>
     <mergeCell ref="Z72:AH72"/>
     <mergeCell ref="AI72:AO72"/>
@@ -18649,7 +18888,10 @@
     <mergeCell ref="BD72:BL72"/>
     <mergeCell ref="BM72:BT72"/>
     <mergeCell ref="BU72:CN72"/>
-    <mergeCell ref="B71:U71"/>
+    <mergeCell ref="B71:O71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="T71:U71"/>
     <mergeCell ref="V71:Y71"/>
     <mergeCell ref="Z71:AH71"/>
     <mergeCell ref="AI71:AO71"/>
@@ -18658,7 +18900,10 @@
     <mergeCell ref="BD71:BL71"/>
     <mergeCell ref="BM71:BT71"/>
     <mergeCell ref="BU71:CN71"/>
-    <mergeCell ref="B70:U70"/>
+    <mergeCell ref="B70:O70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="R70:S70"/>
+    <mergeCell ref="T70:U70"/>
     <mergeCell ref="V70:Y70"/>
     <mergeCell ref="Z70:AH70"/>
     <mergeCell ref="AI70:AO70"/>
@@ -18667,7 +18912,10 @@
     <mergeCell ref="BD70:BL70"/>
     <mergeCell ref="BM70:BT70"/>
     <mergeCell ref="BU70:CN70"/>
-    <mergeCell ref="B69:U69"/>
+    <mergeCell ref="B69:O69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="R69:S69"/>
+    <mergeCell ref="T69:U69"/>
     <mergeCell ref="V69:Y69"/>
     <mergeCell ref="Z69:AH69"/>
     <mergeCell ref="AI69:AO69"/>
@@ -18676,7 +18924,10 @@
     <mergeCell ref="BD69:BL69"/>
     <mergeCell ref="BM69:BT69"/>
     <mergeCell ref="BU69:CN69"/>
-    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B68:O68"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="R68:S68"/>
+    <mergeCell ref="T68:U68"/>
     <mergeCell ref="V68:Y68"/>
     <mergeCell ref="Z68:AH68"/>
     <mergeCell ref="AI68:AO68"/>
@@ -18685,7 +18936,10 @@
     <mergeCell ref="BD68:BL68"/>
     <mergeCell ref="BM68:BT68"/>
     <mergeCell ref="BU68:CN68"/>
-    <mergeCell ref="B67:U67"/>
+    <mergeCell ref="B67:O67"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="T67:U67"/>
     <mergeCell ref="V67:Y67"/>
     <mergeCell ref="Z67:AH67"/>
     <mergeCell ref="AI67:AO67"/>
@@ -18694,7 +18948,10 @@
     <mergeCell ref="BD67:BL67"/>
     <mergeCell ref="BM67:BT67"/>
     <mergeCell ref="BU67:CN67"/>
-    <mergeCell ref="B66:U66"/>
+    <mergeCell ref="B66:O66"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="R66:S66"/>
+    <mergeCell ref="T66:U66"/>
     <mergeCell ref="V66:Y66"/>
     <mergeCell ref="Z66:AH66"/>
     <mergeCell ref="AI66:AO66"/>
@@ -18703,7 +18960,10 @@
     <mergeCell ref="BD66:BL66"/>
     <mergeCell ref="BM66:BT66"/>
     <mergeCell ref="BU66:CN66"/>
-    <mergeCell ref="B65:U65"/>
+    <mergeCell ref="B65:O65"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="R65:S65"/>
+    <mergeCell ref="T65:U65"/>
     <mergeCell ref="V65:Y65"/>
     <mergeCell ref="Z65:AH65"/>
     <mergeCell ref="AI65:AO65"/>
@@ -18712,7 +18972,10 @@
     <mergeCell ref="BD65:BL65"/>
     <mergeCell ref="BM65:BT65"/>
     <mergeCell ref="BU65:CN65"/>
-    <mergeCell ref="B64:U64"/>
+    <mergeCell ref="B64:O64"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="R64:S64"/>
+    <mergeCell ref="T64:U64"/>
     <mergeCell ref="V64:Y64"/>
     <mergeCell ref="Z64:AH64"/>
     <mergeCell ref="AI64:AO64"/>
@@ -18721,7 +18984,10 @@
     <mergeCell ref="BD64:BL64"/>
     <mergeCell ref="BM64:BT64"/>
     <mergeCell ref="BU64:CN64"/>
-    <mergeCell ref="B63:U63"/>
+    <mergeCell ref="B63:O63"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="T63:U63"/>
     <mergeCell ref="V63:Y63"/>
     <mergeCell ref="Z63:AH63"/>
     <mergeCell ref="AI63:AO63"/>
@@ -18730,7 +18996,10 @@
     <mergeCell ref="BD63:BL63"/>
     <mergeCell ref="BM63:BT63"/>
     <mergeCell ref="BU63:CN63"/>
-    <mergeCell ref="B62:U62"/>
+    <mergeCell ref="B62:O62"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="T62:U62"/>
     <mergeCell ref="V62:Y62"/>
     <mergeCell ref="Z62:AH62"/>
     <mergeCell ref="AI62:AO62"/>
@@ -18742,7 +19011,10 @@
     <mergeCell ref="BS57:CN57"/>
     <mergeCell ref="B60:AJ60"/>
     <mergeCell ref="AK60:CN60"/>
-    <mergeCell ref="B61:U61"/>
+    <mergeCell ref="B61:O61"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="T61:U61"/>
     <mergeCell ref="V61:Y61"/>
     <mergeCell ref="Z61:AH61"/>
     <mergeCell ref="AI61:AO61"/>
@@ -19910,7 +20182,7 @@
       <formula>AND(ISNUMBER(BT45),WEEKDAY(DATE(Planungsjahr,12,BT45),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Art der Bitte" prompt="Bitte auswählen: aktiv, passiv oder nein" sqref="BM62:BM81" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"aktiv,passiv,nein"</formula1>
     </dataValidation>
@@ -19930,6 +20202,9 @@
       <formula1>2000</formula1>
       <formula2>2100</formula2>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (S)" prompt="Häkchen = Start Selektion dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="P62:P81"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (I)" prompt="Häkchen = Start inhaltliche Arbeit dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="R62:R81"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (P)" prompt="Häkchen = PAL dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="T62:T81"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
+++ b/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
@@ -24,9 +24,9 @@
     <definedName name="JP_Auflage">Jahresplanung!$V$62:$V$81</definedName>
     <definedName name="JP_Massnahme">Jahresplanung!$B$62:$B$81</definedName>
     <definedName name="JP_PAL">Jahresplanung!$BD$62:$BD$81</definedName>
-    <definedName name="JP_ShowInhalt">Jahresplanung!$R$62:$R$81</definedName>
-    <definedName name="JP_ShowPAL">Jahresplanung!$T$62:$T$81</definedName>
-    <definedName name="JP_ShowSel">Jahresplanung!$P$62:$P$81</definedName>
+    <definedName name="JP_ShowInhalt">Jahresplanung!$T$62:$T$81</definedName>
+    <definedName name="JP_ShowPAL">Jahresplanung!$U$62:$U$81</definedName>
+    <definedName name="JP_ShowSel">Jahresplanung!$S$62:$S$81</definedName>
     <definedName name="JP_StartInhalt">Jahresplanung!$AP$62:$AP$81</definedName>
     <definedName name="JP_StartSel">Jahresplanung!$Z$62:$Z$81</definedName>
     <definedName name="JP_VorlaufInhalt">Jahresplanung!$AW$62:$AW$81</definedName>
@@ -618,7 +618,7 @@
     <numFmt numFmtId="169" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="170" formatCode="[$-407]dddd"/>
   </numFmts>
-  <fonts count="70" x14ac:knownFonts="1">
+  <fonts count="74" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1136,8 +1136,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFE30714"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1255,6 +1284,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="lightUp">
+        <fgColor rgb="FFA6A6A6"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1927,7 +1962,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2524,6 +2559,33 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Akzent3" xfId="11" builtinId="37"/>
@@ -2539,7 +2601,7 @@
     <cellStyle name="Überschrift 3" xfId="8" builtinId="18" customBuiltin="1"/>
     <cellStyle name="zAusgeblText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="142">
+  <dxfs count="144">
     <dxf>
       <font>
         <i/>
@@ -4048,6 +4110,27 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF404040"/>
+      </font>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor rgb="FFA6A6A6"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="200" formatCode=";;;"/>
+      <fill>
+        <patternFill patternType="lightUp">
+          <fgColor rgb="FFA6A6A6"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Gantt-Tabellenformat" pivot="0" count="4" xr9:uid="{4904D139-63E4-4221-B7C9-C6C5B7A50FAF}">
@@ -5160,10 +5243,10 @@
       <c r="BZ7" s="121"/>
       <c r="CA7" s="121"/>
       <c r="CB7" s="121"/>
-      <c r="CD7" s="122" t="s">
+      <c r="CD7" s="204" t="s">
         <v>68</v>
       </c>
-      <c r="CE7" s="122"/>
+      <c r="CE7" s="204"/>
       <c r="CF7" s="121" t="s">
         <v>70</v>
       </c>
@@ -15970,18 +16053,18 @@
       <c r="M61" s="127"/>
       <c r="N61" s="127"/>
       <c r="O61" s="127"/>
-      <c r="P61" s="129" t="s">
+      <c r="P61" s="127"/>
+      <c r="Q61" s="127"/>
+      <c r="R61" s="127"/>
+      <c r="S61" s="129" t="s">
         <v>154</v>
       </c>
-      <c r="Q61" s="129"/>
-      <c r="R61" s="131" t="s">
+      <c r="T61" s="131" t="s">
         <v>155</v>
       </c>
-      <c r="S61" s="131"/>
-      <c r="T61" s="133" t="s">
+      <c r="U61" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="U61" s="133"/>
       <c r="V61" s="128" t="s">
         <v>82</v>
       </c>
@@ -16087,18 +16170,18 @@
       <c r="M62" s="134"/>
       <c r="N62" s="134"/>
       <c r="O62" s="134"/>
-      <c r="P62" s="198" t="b">
+      <c r="P62" s="134"/>
+      <c r="Q62" s="134"/>
+      <c r="R62" s="134"/>
+      <c r="S62" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q62" s="139"/>
-      <c r="R62" s="199" t="b">
+      <c r="T62" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S62" s="139"/>
-      <c r="T62" s="200" t="b">
+      <c r="U62" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U62" s="139"/>
       <c r="V62" s="135"/>
       <c r="W62" s="135"/>
       <c r="X62" s="135"/>
@@ -16202,18 +16285,18 @@
       <c r="M63" s="134"/>
       <c r="N63" s="134"/>
       <c r="O63" s="134"/>
-      <c r="P63" s="198" t="b">
+      <c r="P63" s="134"/>
+      <c r="Q63" s="134"/>
+      <c r="R63" s="134"/>
+      <c r="S63" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q63" s="139"/>
-      <c r="R63" s="199" t="b">
+      <c r="T63" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S63" s="139"/>
-      <c r="T63" s="200" t="b">
+      <c r="U63" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U63" s="139"/>
       <c r="V63" s="135"/>
       <c r="W63" s="135"/>
       <c r="X63" s="135"/>
@@ -16317,18 +16400,18 @@
       <c r="M64" s="134"/>
       <c r="N64" s="134"/>
       <c r="O64" s="134"/>
-      <c r="P64" s="198" t="b">
+      <c r="P64" s="134"/>
+      <c r="Q64" s="134"/>
+      <c r="R64" s="134"/>
+      <c r="S64" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q64" s="139"/>
-      <c r="R64" s="199" t="b">
+      <c r="T64" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S64" s="139"/>
-      <c r="T64" s="200" t="b">
+      <c r="U64" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U64" s="139"/>
       <c r="V64" s="135"/>
       <c r="W64" s="135"/>
       <c r="X64" s="135"/>
@@ -16432,18 +16515,18 @@
       <c r="M65" s="134"/>
       <c r="N65" s="134"/>
       <c r="O65" s="134"/>
-      <c r="P65" s="198" t="b">
+      <c r="P65" s="134"/>
+      <c r="Q65" s="134"/>
+      <c r="R65" s="134"/>
+      <c r="S65" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q65" s="139"/>
-      <c r="R65" s="199" t="b">
+      <c r="T65" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S65" s="139"/>
-      <c r="T65" s="200" t="b">
+      <c r="U65" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U65" s="139"/>
       <c r="V65" s="135"/>
       <c r="W65" s="135"/>
       <c r="X65" s="135"/>
@@ -16551,18 +16634,18 @@
       <c r="M66" s="134"/>
       <c r="N66" s="134"/>
       <c r="O66" s="134"/>
-      <c r="P66" s="198" t="b">
+      <c r="P66" s="134"/>
+      <c r="Q66" s="134"/>
+      <c r="R66" s="134"/>
+      <c r="S66" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q66" s="139"/>
-      <c r="R66" s="199" t="b">
+      <c r="T66" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S66" s="139"/>
-      <c r="T66" s="200" t="b">
+      <c r="U66" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U66" s="139"/>
       <c r="V66" s="135"/>
       <c r="W66" s="135"/>
       <c r="X66" s="135"/>
@@ -16666,18 +16749,18 @@
       <c r="M67" s="134"/>
       <c r="N67" s="134"/>
       <c r="O67" s="134"/>
-      <c r="P67" s="198" t="b">
+      <c r="P67" s="134"/>
+      <c r="Q67" s="134"/>
+      <c r="R67" s="134"/>
+      <c r="S67" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q67" s="139"/>
-      <c r="R67" s="199" t="b">
+      <c r="T67" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S67" s="139"/>
-      <c r="T67" s="200" t="b">
+      <c r="U67" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U67" s="139"/>
       <c r="V67" s="135"/>
       <c r="W67" s="135"/>
       <c r="X67" s="135"/>
@@ -16781,18 +16864,18 @@
       <c r="M68" s="134"/>
       <c r="N68" s="134"/>
       <c r="O68" s="134"/>
-      <c r="P68" s="198" t="b">
+      <c r="P68" s="134"/>
+      <c r="Q68" s="134"/>
+      <c r="R68" s="134"/>
+      <c r="S68" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q68" s="139"/>
-      <c r="R68" s="199" t="b">
+      <c r="T68" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S68" s="139"/>
-      <c r="T68" s="200" t="b">
+      <c r="U68" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U68" s="139"/>
       <c r="V68" s="135"/>
       <c r="W68" s="135"/>
       <c r="X68" s="135"/>
@@ -16898,18 +16981,18 @@
       <c r="M69" s="134"/>
       <c r="N69" s="134"/>
       <c r="O69" s="134"/>
-      <c r="P69" s="198" t="b">
+      <c r="P69" s="134"/>
+      <c r="Q69" s="134"/>
+      <c r="R69" s="134"/>
+      <c r="S69" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q69" s="139"/>
-      <c r="R69" s="199" t="b">
+      <c r="T69" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S69" s="139"/>
-      <c r="T69" s="200" t="b">
+      <c r="U69" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U69" s="139"/>
       <c r="V69" s="135"/>
       <c r="W69" s="135"/>
       <c r="X69" s="135"/>
@@ -17013,18 +17096,18 @@
       <c r="M70" s="134"/>
       <c r="N70" s="134"/>
       <c r="O70" s="134"/>
-      <c r="P70" s="198" t="b">
+      <c r="P70" s="134"/>
+      <c r="Q70" s="134"/>
+      <c r="R70" s="134"/>
+      <c r="S70" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q70" s="139"/>
-      <c r="R70" s="199" t="b">
+      <c r="T70" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S70" s="139"/>
-      <c r="T70" s="200" t="b">
+      <c r="U70" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U70" s="139"/>
       <c r="V70" s="135"/>
       <c r="W70" s="135"/>
       <c r="X70" s="135"/>
@@ -17132,18 +17215,18 @@
       <c r="M71" s="134"/>
       <c r="N71" s="134"/>
       <c r="O71" s="134"/>
-      <c r="P71" s="198" t="b">
+      <c r="P71" s="134"/>
+      <c r="Q71" s="134"/>
+      <c r="R71" s="134"/>
+      <c r="S71" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q71" s="139"/>
-      <c r="R71" s="199" t="b">
+      <c r="T71" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S71" s="139"/>
-      <c r="T71" s="200" t="b">
+      <c r="U71" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U71" s="139"/>
       <c r="V71" s="135"/>
       <c r="W71" s="135"/>
       <c r="X71" s="135"/>
@@ -17245,18 +17328,18 @@
       <c r="M72" s="134"/>
       <c r="N72" s="134"/>
       <c r="O72" s="134"/>
-      <c r="P72" s="198" t="b">
+      <c r="P72" s="134"/>
+      <c r="Q72" s="134"/>
+      <c r="R72" s="134"/>
+      <c r="S72" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q72" s="139"/>
-      <c r="R72" s="199" t="b">
+      <c r="T72" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S72" s="139"/>
-      <c r="T72" s="200" t="b">
+      <c r="U72" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U72" s="139"/>
       <c r="V72" s="135"/>
       <c r="W72" s="135"/>
       <c r="X72" s="135"/>
@@ -17350,18 +17433,18 @@
       <c r="M73" s="134"/>
       <c r="N73" s="134"/>
       <c r="O73" s="134"/>
-      <c r="P73" s="198" t="b">
+      <c r="P73" s="134"/>
+      <c r="Q73" s="134"/>
+      <c r="R73" s="134"/>
+      <c r="S73" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q73" s="139"/>
-      <c r="R73" s="199" t="b">
+      <c r="T73" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S73" s="139"/>
-      <c r="T73" s="200" t="b">
+      <c r="U73" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U73" s="139"/>
       <c r="V73" s="135"/>
       <c r="W73" s="135"/>
       <c r="X73" s="135"/>
@@ -17455,18 +17538,18 @@
       <c r="M74" s="134"/>
       <c r="N74" s="134"/>
       <c r="O74" s="134"/>
-      <c r="P74" s="198" t="b">
+      <c r="P74" s="134"/>
+      <c r="Q74" s="134"/>
+      <c r="R74" s="134"/>
+      <c r="S74" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q74" s="139"/>
-      <c r="R74" s="199" t="b">
+      <c r="T74" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S74" s="139"/>
-      <c r="T74" s="200" t="b">
+      <c r="U74" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U74" s="139"/>
       <c r="V74" s="135"/>
       <c r="W74" s="135"/>
       <c r="X74" s="135"/>
@@ -17560,18 +17643,18 @@
       <c r="M75" s="134"/>
       <c r="N75" s="134"/>
       <c r="O75" s="134"/>
-      <c r="P75" s="198" t="b">
+      <c r="P75" s="134"/>
+      <c r="Q75" s="134"/>
+      <c r="R75" s="134"/>
+      <c r="S75" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q75" s="139"/>
-      <c r="R75" s="199" t="b">
+      <c r="T75" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S75" s="139"/>
-      <c r="T75" s="200" t="b">
+      <c r="U75" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U75" s="139"/>
       <c r="V75" s="135"/>
       <c r="W75" s="135"/>
       <c r="X75" s="135"/>
@@ -17665,18 +17748,18 @@
       <c r="M76" s="134"/>
       <c r="N76" s="134"/>
       <c r="O76" s="134"/>
-      <c r="P76" s="198" t="b">
+      <c r="P76" s="134"/>
+      <c r="Q76" s="134"/>
+      <c r="R76" s="134"/>
+      <c r="S76" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q76" s="139"/>
-      <c r="R76" s="199" t="b">
+      <c r="T76" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S76" s="139"/>
-      <c r="T76" s="200" t="b">
+      <c r="U76" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U76" s="139"/>
       <c r="V76" s="135"/>
       <c r="W76" s="135"/>
       <c r="X76" s="135"/>
@@ -17770,18 +17853,18 @@
       <c r="M77" s="134"/>
       <c r="N77" s="134"/>
       <c r="O77" s="134"/>
-      <c r="P77" s="198" t="b">
+      <c r="P77" s="134"/>
+      <c r="Q77" s="134"/>
+      <c r="R77" s="134"/>
+      <c r="S77" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q77" s="139"/>
-      <c r="R77" s="199" t="b">
+      <c r="T77" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S77" s="139"/>
-      <c r="T77" s="200" t="b">
+      <c r="U77" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U77" s="139"/>
       <c r="V77" s="135"/>
       <c r="W77" s="135"/>
       <c r="X77" s="135"/>
@@ -17875,18 +17958,18 @@
       <c r="M78" s="134"/>
       <c r="N78" s="134"/>
       <c r="O78" s="134"/>
-      <c r="P78" s="198" t="b">
+      <c r="P78" s="134"/>
+      <c r="Q78" s="134"/>
+      <c r="R78" s="134"/>
+      <c r="S78" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q78" s="139"/>
-      <c r="R78" s="199" t="b">
+      <c r="T78" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S78" s="139"/>
-      <c r="T78" s="200" t="b">
+      <c r="U78" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U78" s="139"/>
       <c r="V78" s="135"/>
       <c r="W78" s="135"/>
       <c r="X78" s="135"/>
@@ -17980,18 +18063,18 @@
       <c r="M79" s="134"/>
       <c r="N79" s="134"/>
       <c r="O79" s="134"/>
-      <c r="P79" s="198" t="b">
+      <c r="P79" s="134"/>
+      <c r="Q79" s="134"/>
+      <c r="R79" s="134"/>
+      <c r="S79" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q79" s="139"/>
-      <c r="R79" s="199" t="b">
+      <c r="T79" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S79" s="139"/>
-      <c r="T79" s="200" t="b">
+      <c r="U79" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U79" s="139"/>
       <c r="V79" s="135"/>
       <c r="W79" s="135"/>
       <c r="X79" s="135"/>
@@ -18085,18 +18168,18 @@
       <c r="M80" s="134"/>
       <c r="N80" s="134"/>
       <c r="O80" s="134"/>
-      <c r="P80" s="198" t="b">
+      <c r="P80" s="134"/>
+      <c r="Q80" s="134"/>
+      <c r="R80" s="134"/>
+      <c r="S80" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q80" s="139"/>
-      <c r="R80" s="199" t="b">
+      <c r="T80" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S80" s="139"/>
-      <c r="T80" s="200" t="b">
+      <c r="U80" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U80" s="139"/>
       <c r="V80" s="135"/>
       <c r="W80" s="135"/>
       <c r="X80" s="135"/>
@@ -18190,18 +18273,18 @@
       <c r="M81" s="134"/>
       <c r="N81" s="134"/>
       <c r="O81" s="134"/>
-      <c r="P81" s="198" t="b">
+      <c r="P81" s="134"/>
+      <c r="Q81" s="134"/>
+      <c r="R81" s="134"/>
+      <c r="S81" s="201" t="b">
         <v>1</v>
       </c>
-      <c r="Q81" s="139"/>
-      <c r="R81" s="199" t="b">
+      <c r="T81" s="202" t="b">
         <v>1</v>
       </c>
-      <c r="S81" s="139"/>
-      <c r="T81" s="200" t="b">
+      <c r="U81" s="203" t="b">
         <v>1</v>
       </c>
-      <c r="U81" s="139"/>
       <c r="V81" s="135"/>
       <c r="W81" s="135"/>
       <c r="X81" s="135"/>
@@ -18761,17 +18844,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="803">
+  <mergeCells count="740">
     <mergeCell ref="B83:CN83"/>
     <mergeCell ref="B84:CN84"/>
     <mergeCell ref="B85:CN85"/>
     <mergeCell ref="B86:CN86"/>
     <mergeCell ref="B87:CN87"/>
     <mergeCell ref="B88:CN88"/>
-    <mergeCell ref="B81:O81"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="R81:S81"/>
-    <mergeCell ref="T81:U81"/>
     <mergeCell ref="V81:Y81"/>
     <mergeCell ref="Z81:AH81"/>
     <mergeCell ref="AI81:AO81"/>
@@ -18780,10 +18859,6 @@
     <mergeCell ref="BD81:BL81"/>
     <mergeCell ref="BM81:BT81"/>
     <mergeCell ref="BU81:CN81"/>
-    <mergeCell ref="B80:O80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="R80:S80"/>
-    <mergeCell ref="T80:U80"/>
     <mergeCell ref="V80:Y80"/>
     <mergeCell ref="Z80:AH80"/>
     <mergeCell ref="AI80:AO80"/>
@@ -18792,10 +18867,6 @@
     <mergeCell ref="BD80:BL80"/>
     <mergeCell ref="BM80:BT80"/>
     <mergeCell ref="BU80:CN80"/>
-    <mergeCell ref="B79:O79"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="R79:S79"/>
-    <mergeCell ref="T79:U79"/>
     <mergeCell ref="V79:Y79"/>
     <mergeCell ref="Z79:AH79"/>
     <mergeCell ref="AI79:AO79"/>
@@ -18804,10 +18875,6 @@
     <mergeCell ref="BD79:BL79"/>
     <mergeCell ref="BM79:BT79"/>
     <mergeCell ref="BU79:CN79"/>
-    <mergeCell ref="B78:O78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="R78:S78"/>
-    <mergeCell ref="T78:U78"/>
     <mergeCell ref="V78:Y78"/>
     <mergeCell ref="Z78:AH78"/>
     <mergeCell ref="AI78:AO78"/>
@@ -18816,10 +18883,6 @@
     <mergeCell ref="BD78:BL78"/>
     <mergeCell ref="BM78:BT78"/>
     <mergeCell ref="BU78:CN78"/>
-    <mergeCell ref="B77:O77"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="R77:S77"/>
-    <mergeCell ref="T77:U77"/>
     <mergeCell ref="V77:Y77"/>
     <mergeCell ref="Z77:AH77"/>
     <mergeCell ref="AI77:AO77"/>
@@ -18828,10 +18891,6 @@
     <mergeCell ref="BD77:BL77"/>
     <mergeCell ref="BM77:BT77"/>
     <mergeCell ref="BU77:CN77"/>
-    <mergeCell ref="B76:O76"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="T76:U76"/>
     <mergeCell ref="V76:Y76"/>
     <mergeCell ref="Z76:AH76"/>
     <mergeCell ref="AI76:AO76"/>
@@ -18840,10 +18899,6 @@
     <mergeCell ref="BD76:BL76"/>
     <mergeCell ref="BM76:BT76"/>
     <mergeCell ref="BU76:CN76"/>
-    <mergeCell ref="B75:O75"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="T75:U75"/>
     <mergeCell ref="V75:Y75"/>
     <mergeCell ref="Z75:AH75"/>
     <mergeCell ref="AI75:AO75"/>
@@ -18852,10 +18907,6 @@
     <mergeCell ref="BD75:BL75"/>
     <mergeCell ref="BM75:BT75"/>
     <mergeCell ref="BU75:CN75"/>
-    <mergeCell ref="B74:O74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="R74:S74"/>
-    <mergeCell ref="T74:U74"/>
     <mergeCell ref="V74:Y74"/>
     <mergeCell ref="Z74:AH74"/>
     <mergeCell ref="AI74:AO74"/>
@@ -18864,10 +18915,6 @@
     <mergeCell ref="BD74:BL74"/>
     <mergeCell ref="BM74:BT74"/>
     <mergeCell ref="BU74:CN74"/>
-    <mergeCell ref="B73:O73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="T73:U73"/>
     <mergeCell ref="V73:Y73"/>
     <mergeCell ref="Z73:AH73"/>
     <mergeCell ref="AI73:AO73"/>
@@ -18876,10 +18923,6 @@
     <mergeCell ref="BD73:BL73"/>
     <mergeCell ref="BM73:BT73"/>
     <mergeCell ref="BU73:CN73"/>
-    <mergeCell ref="B72:O72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T72:U72"/>
     <mergeCell ref="V72:Y72"/>
     <mergeCell ref="Z72:AH72"/>
     <mergeCell ref="AI72:AO72"/>
@@ -18888,10 +18931,6 @@
     <mergeCell ref="BD72:BL72"/>
     <mergeCell ref="BM72:BT72"/>
     <mergeCell ref="BU72:CN72"/>
-    <mergeCell ref="B71:O71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="T71:U71"/>
     <mergeCell ref="V71:Y71"/>
     <mergeCell ref="Z71:AH71"/>
     <mergeCell ref="AI71:AO71"/>
@@ -18900,10 +18939,6 @@
     <mergeCell ref="BD71:BL71"/>
     <mergeCell ref="BM71:BT71"/>
     <mergeCell ref="BU71:CN71"/>
-    <mergeCell ref="B70:O70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="R70:S70"/>
-    <mergeCell ref="T70:U70"/>
     <mergeCell ref="V70:Y70"/>
     <mergeCell ref="Z70:AH70"/>
     <mergeCell ref="AI70:AO70"/>
@@ -18912,10 +18947,6 @@
     <mergeCell ref="BD70:BL70"/>
     <mergeCell ref="BM70:BT70"/>
     <mergeCell ref="BU70:CN70"/>
-    <mergeCell ref="B69:O69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="R69:S69"/>
-    <mergeCell ref="T69:U69"/>
     <mergeCell ref="V69:Y69"/>
     <mergeCell ref="Z69:AH69"/>
     <mergeCell ref="AI69:AO69"/>
@@ -18924,10 +18955,6 @@
     <mergeCell ref="BD69:BL69"/>
     <mergeCell ref="BM69:BT69"/>
     <mergeCell ref="BU69:CN69"/>
-    <mergeCell ref="B68:O68"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="R68:S68"/>
-    <mergeCell ref="T68:U68"/>
     <mergeCell ref="V68:Y68"/>
     <mergeCell ref="Z68:AH68"/>
     <mergeCell ref="AI68:AO68"/>
@@ -18936,10 +18963,6 @@
     <mergeCell ref="BD68:BL68"/>
     <mergeCell ref="BM68:BT68"/>
     <mergeCell ref="BU68:CN68"/>
-    <mergeCell ref="B67:O67"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="T67:U67"/>
     <mergeCell ref="V67:Y67"/>
     <mergeCell ref="Z67:AH67"/>
     <mergeCell ref="AI67:AO67"/>
@@ -18948,10 +18971,6 @@
     <mergeCell ref="BD67:BL67"/>
     <mergeCell ref="BM67:BT67"/>
     <mergeCell ref="BU67:CN67"/>
-    <mergeCell ref="B66:O66"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="R66:S66"/>
-    <mergeCell ref="T66:U66"/>
     <mergeCell ref="V66:Y66"/>
     <mergeCell ref="Z66:AH66"/>
     <mergeCell ref="AI66:AO66"/>
@@ -18960,10 +18979,6 @@
     <mergeCell ref="BD66:BL66"/>
     <mergeCell ref="BM66:BT66"/>
     <mergeCell ref="BU66:CN66"/>
-    <mergeCell ref="B65:O65"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="R65:S65"/>
-    <mergeCell ref="T65:U65"/>
     <mergeCell ref="V65:Y65"/>
     <mergeCell ref="Z65:AH65"/>
     <mergeCell ref="AI65:AO65"/>
@@ -18972,10 +18987,6 @@
     <mergeCell ref="BD65:BL65"/>
     <mergeCell ref="BM65:BT65"/>
     <mergeCell ref="BU65:CN65"/>
-    <mergeCell ref="B64:O64"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="R64:S64"/>
-    <mergeCell ref="T64:U64"/>
     <mergeCell ref="V64:Y64"/>
     <mergeCell ref="Z64:AH64"/>
     <mergeCell ref="AI64:AO64"/>
@@ -18984,10 +18995,6 @@
     <mergeCell ref="BD64:BL64"/>
     <mergeCell ref="BM64:BT64"/>
     <mergeCell ref="BU64:CN64"/>
-    <mergeCell ref="B63:O63"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="T63:U63"/>
     <mergeCell ref="V63:Y63"/>
     <mergeCell ref="Z63:AH63"/>
     <mergeCell ref="AI63:AO63"/>
@@ -18996,10 +19003,6 @@
     <mergeCell ref="BD63:BL63"/>
     <mergeCell ref="BM63:BT63"/>
     <mergeCell ref="BU63:CN63"/>
-    <mergeCell ref="B62:O62"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="T62:U62"/>
     <mergeCell ref="V62:Y62"/>
     <mergeCell ref="Z62:AH62"/>
     <mergeCell ref="AI62:AO62"/>
@@ -19011,10 +19014,6 @@
     <mergeCell ref="BS57:CN57"/>
     <mergeCell ref="B60:AJ60"/>
     <mergeCell ref="AK60:CN60"/>
-    <mergeCell ref="B61:O61"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="T61:U61"/>
     <mergeCell ref="V61:Y61"/>
     <mergeCell ref="Z61:AH61"/>
     <mergeCell ref="AI61:AO61"/>
@@ -19565,6 +19564,27 @@
     <mergeCell ref="BV7:CB7"/>
     <mergeCell ref="CD7:CE7"/>
     <mergeCell ref="CF7:CN7"/>
+    <mergeCell ref="B61:R61"/>
+    <mergeCell ref="B62:R62"/>
+    <mergeCell ref="B63:R63"/>
+    <mergeCell ref="B64:R64"/>
+    <mergeCell ref="B65:R65"/>
+    <mergeCell ref="B66:R66"/>
+    <mergeCell ref="B67:R67"/>
+    <mergeCell ref="B68:R68"/>
+    <mergeCell ref="B69:R69"/>
+    <mergeCell ref="B70:R70"/>
+    <mergeCell ref="B71:R71"/>
+    <mergeCell ref="B72:R72"/>
+    <mergeCell ref="B73:R73"/>
+    <mergeCell ref="B74:R74"/>
+    <mergeCell ref="B75:R75"/>
+    <mergeCell ref="B76:R76"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B78:R78"/>
+    <mergeCell ref="B79:R79"/>
+    <mergeCell ref="B80:R80"/>
+    <mergeCell ref="B81:R81"/>
   </mergeCells>
   <conditionalFormatting sqref="C13 F13 I13 L13 O13 R13 U13 C15 F15 I15 L15 O15 R15 U15 C17 F17 I17 L17 O17 R17 U17 C19 F19 I19 L19 O19 R19 U19 C21 F21 I21 L21 O21 R21 U21 C23 F23 I23 L23 O23 R23 U23">
     <cfRule type="expression" dxfId="136" priority="1">
@@ -20047,7 +20067,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:W13 C15:W15 C17:W17 C19:W19 C21:W21 C23:W23">
-    <cfRule type="expression" dxfId="101" priority="702" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="702" stopIfTrue="1">
       <formula>AND(ISNUMBER(C13),COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="101" priority="703" stopIfTrue="1">
@@ -20058,7 +20078,7 @@
     <cfRule type="cellIs" dxfId="100" priority="730" stopIfTrue="1" operator="equal">
       <formula>"w"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="729" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="729" stopIfTrue="1" operator="equal">
       <formula>"h"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="98" priority="728" stopIfTrue="1" operator="equal">
@@ -20072,7 +20092,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:W29 C31:W31 C33:W33 C35:W35 C37:W37 C39:W39">
-    <cfRule type="expression" dxfId="94" priority="710" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="710" stopIfTrue="1">
       <formula>AND(ISNUMBER(C29),COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="94" priority="711" stopIfTrue="1">
@@ -20080,7 +20100,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C45:W45 C47:W47 C49:W49 C51:W51 C53:W53 C55:W55">
-    <cfRule type="expression" dxfId="92" priority="718" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="718" stopIfTrue="1">
       <formula>AND(ISNUMBER(C45),COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="92" priority="719" stopIfTrue="1">
@@ -20093,7 +20113,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z13:AT13 Z15:AT15 Z17:AT17 Z19:AT19 Z21:AT21 Z23:AT23">
-    <cfRule type="expression" dxfId="90" priority="704" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="704" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z13),COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="90" priority="705" stopIfTrue="1">
@@ -20101,7 +20121,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z29:AT29 Z31:AT31 Z33:AT33 Z35:AT35 Z37:AT37 Z39:AT39">
-    <cfRule type="expression" dxfId="88" priority="712" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="712" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z29),COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="88" priority="713" stopIfTrue="1">
@@ -20109,11 +20129,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z45:AT45 Z47:AT47 Z49:AT49 Z51:AT51 Z53:AT53 Z55:AT55">
+    <cfRule type="expression" dxfId="142" priority="720" stopIfTrue="1">
+      <formula>AND(ISNUMBER(Z45),COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0)</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="87" priority="721" stopIfTrue="1">
       <formula>AND(ISNUMBER(Z45),WEEKDAY(DATE(Planungsjahr,10,Z45),2)&gt;5)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="720" stopIfTrue="1">
-      <formula>AND(ISNUMBER(Z45),COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AP62:AP81">
@@ -20122,23 +20142,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW13:BQ13 AW15:BQ15 AW17:BQ17 AW19:BQ19 AW21:BQ21 AW23:BQ23">
+    <cfRule type="expression" dxfId="142" priority="706" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AW13),COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0)</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="83" priority="707" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW13),WEEKDAY(DATE(Planungsjahr,3,AW13),2)&gt;5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="706" stopIfTrue="1">
-      <formula>AND(ISNUMBER(AW13),COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0)</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW29:BQ29 AW31:BQ31 AW33:BQ33 AW35:BQ35 AW37:BQ37 AW39:BQ39">
+    <cfRule type="expression" dxfId="142" priority="714" stopIfTrue="1">
+      <formula>AND(ISNUMBER(AW29),COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0)</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="81" priority="715" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW29),WEEKDAY(DATE(Planungsjahr,7,AW29),2)&gt;5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="714" stopIfTrue="1">
-      <formula>AND(ISNUMBER(AW29),COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0)</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW45:BQ45 AW47:BQ47 AW49:BQ49 AW51:BQ51 AW53:BQ53 AW55:BQ55">
-    <cfRule type="expression" dxfId="78" priority="722" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="722" stopIfTrue="1">
       <formula>AND(ISNUMBER(AW45),COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="78" priority="723" stopIfTrue="1">
@@ -20159,15 +20179,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT13:CN13 BT15:CN15 BT17:CN17 BT19:CN19 BT21:CN21 BT23:CN23">
+    <cfRule type="expression" dxfId="142" priority="708" stopIfTrue="1">
+      <formula>AND(ISNUMBER(BT13),COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0)</formula>
+    </cfRule>
     <cfRule type="expression" dxfId="74" priority="709" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT13),WEEKDAY(DATE(Planungsjahr,4,BT13),2)&gt;5)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="708" stopIfTrue="1">
-      <formula>AND(ISNUMBER(BT13),COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0)</formula>
-    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT29:CN29 BT31:CN31 BT33:CN33 BT35:CN35 BT37:CN37 BT39:CN39">
-    <cfRule type="expression" dxfId="71" priority="716" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="716" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT29),COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="71" priority="717" stopIfTrue="1">
@@ -20175,7 +20195,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BT45:CN45 BT47:CN47 BT49:CN49 BT51:CN51 BT53:CN53 BT55:CN55">
-    <cfRule type="expression" dxfId="69" priority="724" stopIfTrue="1">
+    <cfRule type="expression" dxfId="142" priority="724" stopIfTrue="1">
       <formula>AND(ISNUMBER(BT45),COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="69" priority="725" stopIfTrue="1">
@@ -20202,9 +20222,9 @@
       <formula1>2000</formula1>
       <formula2>2100</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (S)" prompt="Häkchen = Start Selektion dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="P62:P81"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (I)" prompt="Häkchen = Start inhaltliche Arbeit dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="R62:R81"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (P)" prompt="Häkchen = PAL dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="T62:T81"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (S)" prompt="Häkchen = Start Selektion dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="S62:S81"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (I)" prompt="Häkchen = Start inhaltliche Arbeit dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="T62:T81"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (P)" prompt="Häkchen = PAL dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="U62:U81"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
+++ b/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
@@ -17,16 +17,17 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Jahresplanung!$A$1:$CN$88</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Sommermailing!$6:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">Weihnachtsmailing!$6:$9</definedName>
+    <definedName name="Anzeige_I">Jahresplanung!$BS$5</definedName>
+    <definedName name="Anzeige_P">Jahresplanung!$BS$6</definedName>
+    <definedName name="Anzeige_S">Jahresplanung!$BS$4</definedName>
     <definedName name="Feiertage">'Feiertage NRW'!$B$7:$B$17</definedName>
     <definedName name="Feiertage_Name">'Feiertage NRW'!$D$7:$D$17</definedName>
     <definedName name="Heute" localSheetId="1">TODAY()</definedName>
     <definedName name="Heute" localSheetId="2">TODAY()</definedName>
+    <definedName name="JP_Anzeige">Jahresplanung!$A$62:$A$81</definedName>
     <definedName name="JP_Auflage">Jahresplanung!$V$62:$V$81</definedName>
     <definedName name="JP_Massnahme">Jahresplanung!$B$62:$B$81</definedName>
     <definedName name="JP_PAL">Jahresplanung!$BD$62:$BD$81</definedName>
-    <definedName name="JP_ShowInhalt">Jahresplanung!$T$62:$T$81</definedName>
-    <definedName name="JP_ShowPAL">Jahresplanung!$U$62:$U$81</definedName>
-    <definedName name="JP_ShowSel">Jahresplanung!$S$62:$S$81</definedName>
     <definedName name="JP_StartInhalt">Jahresplanung!$AP$62:$AP$81</definedName>
     <definedName name="JP_StartSel">Jahresplanung!$Z$62:$Z$81</definedName>
     <definedName name="JP_VorlaufInhalt">Jahresplanung!$AW$62:$AW$81</definedName>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="159">
   <si>
     <t xml:space="preserve">Erstellen eines Gantt-Diagramms
 Geben Sie den Titel dieses Projekts in Zelle B2 ein.
@@ -604,6 +605,9 @@
   <si>
     <t xml:space="preserve">• Häkchen S · I · P neben der Maßnahme: legt fest, ob Start Selektion, Start inhaltliche Arbeit und PAL im Kalender erscheinen. Häkchen entfernen blendet nur den Marker aus.</t>
   </si>
+  <si>
+    <t xml:space="preserve">• Kontrollkästchen: Oben rechts neben S · I · P blendet die jeweilige Markerart für alle Maßnahmen ein oder aus. Das Kästchen links neben einer Maßnahme blendet alle ihre Marker ein oder aus.</t>
+  </si>
 </sst>
 </file>
 
@@ -618,7 +622,7 @@
     <numFmt numFmtId="169" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="170" formatCode="[$-407]dddd"/>
   </numFmts>
-  <fonts count="74" x14ac:knownFonts="1">
+  <fonts count="78" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1161,6 +1165,34 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF548235"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFE30714"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1962,7 +1994,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2585,6 +2617,38 @@
     </xf>
     <xf numFmtId="0" fontId="73" fillId="21" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -4932,7 +4996,7 @@
       <c r="CN2" s="114"/>
     </row>
     <row r="3" spans="2:92" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="115" t="s">
         <v>56</v>
       </c>
@@ -5004,6 +5068,9 @@
       <c r="BO4" s="116"/>
       <c r="BP4" s="116"/>
       <c r="BQ4" s="116"/>
+      <c r="BS4" s="206" t="b">
+        <v>1</v>
+      </c>
       <c r="BT4" s="99" t="s">
         <v>58</v>
       </c>
@@ -5029,7 +5096,7 @@
       <c r="CM4" s="121"/>
       <c r="CN4" s="121"/>
     </row>
-    <row r="5" spans="2:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AE5" s="116" t="s">
         <v>61</v>
       </c>
@@ -5071,6 +5138,9 @@
       <c r="BO5" s="116"/>
       <c r="BP5" s="116"/>
       <c r="BQ5" s="116"/>
+      <c r="BS5" s="207" t="b">
+        <v>1</v>
+      </c>
       <c r="BT5" s="100" t="s">
         <v>62</v>
       </c>
@@ -5096,7 +5166,7 @@
       <c r="CM5" s="121"/>
       <c r="CN5" s="121"/>
     </row>
-    <row r="6" spans="2:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AE6" s="116" t="s">
         <v>65</v>
       </c>
@@ -5138,6 +5208,9 @@
       <c r="BO6" s="116"/>
       <c r="BP6" s="116"/>
       <c r="BQ6" s="116"/>
+      <c r="BS6" s="208" t="b">
+        <v>1</v>
+      </c>
       <c r="BT6" s="101" t="s">
         <v>66</v>
       </c>
@@ -5801,342 +5874,342 @@
     <row r="14" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="167"/>
       <c r="C14" s="159" t="str">
-        <f>IF(ISNUMBER(C13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D14" s="159" t="str">
-        <f>IF(ISNUMBER(C13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E14" s="159" t="str">
-        <f>IF(ISNUMBER(C13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F14" s="159" t="str">
-        <f>IF(ISNUMBER(F13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G14" s="159" t="str">
-        <f>IF(ISNUMBER(F13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H14" s="159" t="str">
-        <f>IF(ISNUMBER(F13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I14" s="159" t="str">
-        <f>IF(ISNUMBER(I13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J14" s="159" t="str">
-        <f>IF(ISNUMBER(I13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K14" s="159" t="str">
-        <f>IF(ISNUMBER(I13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L14" s="159" t="str">
-        <f>IF(ISNUMBER(L13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M14" s="159" t="str">
-        <f>IF(ISNUMBER(L13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N14" s="159" t="str">
-        <f>IF(ISNUMBER(L13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O14" s="159" t="str">
-        <f>IF(ISNUMBER(O13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="P14" s="159" t="str">
-        <f>IF(ISNUMBER(O13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="Q14" s="159" t="str">
-        <f>IF(ISNUMBER(O13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O13))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="R14" s="159" t="str">
-        <f>IF(ISNUMBER(R13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S14" s="159" t="str">
-        <f>IF(ISNUMBER(R13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T14" s="159" t="str">
-        <f>IF(ISNUMBER(R13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U14" s="159" t="str">
-        <f>IF(ISNUMBER(U13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V14" s="159" t="str">
-        <f>IF(ISNUMBER(U13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W14" s="168" t="str">
-        <f>IF(ISNUMBER(U13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y14" s="179"/>
       <c r="Z14" s="159" t="str">
-        <f>IF(ISNUMBER(Z13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA14" s="159" t="str">
-        <f>IF(ISNUMBER(Z13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB14" s="159" t="str">
-        <f>IF(ISNUMBER(Z13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC14" s="159" t="str">
-        <f>IF(ISNUMBER(AC13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD14" s="159" t="str">
-        <f>IF(ISNUMBER(AC13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE14" s="159" t="str">
-        <f>IF(ISNUMBER(AC13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF14" s="159" t="str">
-        <f>IF(ISNUMBER(AF13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG14" s="159" t="str">
-        <f>IF(ISNUMBER(AF13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH14" s="159" t="str">
-        <f>IF(ISNUMBER(AF13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI14" s="159" t="str">
-        <f>IF(ISNUMBER(AI13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ14" s="159" t="str">
-        <f>IF(ISNUMBER(AI13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK14" s="159" t="str">
-        <f>IF(ISNUMBER(AI13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL14" s="159" t="str">
-        <f>IF(ISNUMBER(AL13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM14" s="159" t="str">
-        <f>IF(ISNUMBER(AL13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN14" s="159" t="str">
-        <f>IF(ISNUMBER(AL13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO14" s="159" t="str">
-        <f>IF(ISNUMBER(AO13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="AP14" s="159" t="str">
-        <f>IF(ISNUMBER(AO13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ14" s="159" t="str">
-        <f>IF(ISNUMBER(AO13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR14" s="159" t="str">
-        <f>IF(ISNUMBER(AR13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS14" s="159" t="str">
-        <f>IF(ISNUMBER(AR13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT14" s="180" t="str">
-        <f>IF(ISNUMBER(AR13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV14" s="179"/>
       <c r="AW14" s="159" t="str">
-        <f>IF(ISNUMBER(AW13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX14" s="159" t="str">
-        <f>IF(ISNUMBER(AW13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY14" s="159" t="str">
-        <f>IF(ISNUMBER(AW13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ14" s="159" t="str">
-        <f>IF(ISNUMBER(AZ13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA14" s="159" t="str">
-        <f>IF(ISNUMBER(AZ13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB14" s="159" t="str">
-        <f>IF(ISNUMBER(AZ13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC14" s="159" t="str">
-        <f>IF(ISNUMBER(BC13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD14" s="159" t="str">
-        <f>IF(ISNUMBER(BC13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE14" s="159" t="str">
-        <f>IF(ISNUMBER(BC13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF14" s="159" t="str">
-        <f>IF(ISNUMBER(BF13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG14" s="159" t="str">
-        <f>IF(ISNUMBER(BF13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH14" s="159" t="str">
-        <f>IF(ISNUMBER(BF13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI14" s="159" t="str">
-        <f>IF(ISNUMBER(BI13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ14" s="159" t="str">
-        <f>IF(ISNUMBER(BI13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK14" s="159" t="str">
-        <f>IF(ISNUMBER(BI13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL14" s="159" t="str">
-        <f>IF(ISNUMBER(BL13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM14" s="159" t="str">
-        <f>IF(ISNUMBER(BL13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN14" s="159" t="str">
-        <f>IF(ISNUMBER(BL13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO14" s="159" t="str">
-        <f>IF(ISNUMBER(BO13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP14" s="159" t="str">
-        <f>IF(ISNUMBER(BO13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ14" s="180" t="str">
-        <f>IF(ISNUMBER(BO13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS14" s="179"/>
       <c r="BT14" s="159" t="str">
-        <f>IF(ISNUMBER(BT13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU14" s="159" t="str">
-        <f>IF(ISNUMBER(BT13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV14" s="159" t="str">
-        <f>IF(ISNUMBER(BT13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW14" s="159" t="str">
-        <f>IF(ISNUMBER(BW13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX14" s="159" t="str">
-        <f>IF(ISNUMBER(BW13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY14" s="159" t="str">
-        <f>IF(ISNUMBER(BW13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ14" s="159" t="str">
-        <f>IF(ISNUMBER(BZ13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA14" s="159" t="str">
-        <f>IF(ISNUMBER(BZ13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB14" s="159" t="str">
-        <f>IF(ISNUMBER(BZ13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC14" s="159" t="str">
-        <f>IF(ISNUMBER(CC13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD14" s="159" t="str">
-        <f>IF(ISNUMBER(CC13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE14" s="159" t="str">
-        <f>IF(ISNUMBER(CC13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF14" s="159" t="str">
-        <f>IF(ISNUMBER(CF13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG14" s="159" t="str">
-        <f>IF(ISNUMBER(CF13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH14" s="159" t="str">
-        <f>IF(ISNUMBER(CF13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF13))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI14" s="159" t="str">
-        <f>IF(ISNUMBER(CI13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ14" s="159" t="str">
-        <f>IF(ISNUMBER(CI13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK14" s="159" t="str">
-        <f>IF(ISNUMBER(CI13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL14" s="159" t="str">
-        <f>IF(ISNUMBER(CL13),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL13),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL13),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL13),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="CM14" s="159" t="str">
-        <f>IF(ISNUMBER(CL13),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL13),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL13),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL13),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN14" s="180" t="str">
-        <f>IF(ISNUMBER(CL13),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL13),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL13),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL13),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL13))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -6329,342 +6402,342 @@
     <row r="16" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="167"/>
       <c r="C16" s="159" t="str">
-        <f>IF(ISNUMBER(C15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D16" s="159" t="str">
-        <f>IF(ISNUMBER(C15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E16" s="159" t="str">
-        <f>IF(ISNUMBER(C15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F16" s="159" t="str">
-        <f>IF(ISNUMBER(F15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G16" s="159" t="str">
-        <f>IF(ISNUMBER(F15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H16" s="159" t="str">
-        <f>IF(ISNUMBER(F15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I16" s="159" t="str">
-        <f>IF(ISNUMBER(I15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J16" s="159" t="str">
-        <f>IF(ISNUMBER(I15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K16" s="159" t="str">
-        <f>IF(ISNUMBER(I15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L16" s="159" t="str">
-        <f>IF(ISNUMBER(L15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M16" s="159" t="str">
-        <f>IF(ISNUMBER(L15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N16" s="159" t="str">
-        <f>IF(ISNUMBER(L15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O16" s="159" t="str">
-        <f>IF(ISNUMBER(O15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P16" s="159" t="str">
-        <f>IF(ISNUMBER(O15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q16" s="159" t="str">
-        <f>IF(ISNUMBER(O15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R16" s="159" t="str">
-        <f>IF(ISNUMBER(R15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S16" s="159" t="str">
-        <f>IF(ISNUMBER(R15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T16" s="159" t="str">
-        <f>IF(ISNUMBER(R15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U16" s="159" t="str">
-        <f>IF(ISNUMBER(U15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V16" s="159" t="str">
-        <f>IF(ISNUMBER(U15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W16" s="168" t="str">
-        <f>IF(ISNUMBER(U15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y16" s="179"/>
       <c r="Z16" s="159" t="str">
-        <f>IF(ISNUMBER(Z15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA16" s="159" t="str">
-        <f>IF(ISNUMBER(Z15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB16" s="159" t="str">
-        <f>IF(ISNUMBER(Z15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC16" s="159" t="str">
-        <f>IF(ISNUMBER(AC15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD16" s="159" t="str">
-        <f>IF(ISNUMBER(AC15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE16" s="159" t="str">
-        <f>IF(ISNUMBER(AC15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF16" s="159" t="str">
-        <f>IF(ISNUMBER(AF15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG16" s="159" t="str">
-        <f>IF(ISNUMBER(AF15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH16" s="159" t="str">
-        <f>IF(ISNUMBER(AF15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI16" s="159" t="str">
-        <f>IF(ISNUMBER(AI15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ16" s="159" t="str">
-        <f>IF(ISNUMBER(AI15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK16" s="159" t="str">
-        <f>IF(ISNUMBER(AI15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL16" s="159" t="str">
-        <f>IF(ISNUMBER(AL15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM16" s="159" t="str">
-        <f>IF(ISNUMBER(AL15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AN16" s="159" t="str">
-        <f>IF(ISNUMBER(AL15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO16" s="159" t="str">
-        <f>IF(ISNUMBER(AO15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP16" s="159" t="str">
-        <f>IF(ISNUMBER(AO15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ16" s="159" t="str">
-        <f>IF(ISNUMBER(AO15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR16" s="159" t="str">
-        <f>IF(ISNUMBER(AR15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS16" s="159" t="str">
-        <f>IF(ISNUMBER(AR15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT16" s="180" t="str">
-        <f>IF(ISNUMBER(AR15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV16" s="179"/>
       <c r="AW16" s="159" t="str">
-        <f>IF(ISNUMBER(AW15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX16" s="159" t="str">
-        <f>IF(ISNUMBER(AW15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY16" s="159" t="str">
-        <f>IF(ISNUMBER(AW15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ16" s="159" t="str">
-        <f>IF(ISNUMBER(AZ15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA16" s="159" t="str">
-        <f>IF(ISNUMBER(AZ15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB16" s="159" t="str">
-        <f>IF(ISNUMBER(AZ15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC16" s="159" t="str">
-        <f>IF(ISNUMBER(BC15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD16" s="159" t="str">
-        <f>IF(ISNUMBER(BC15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE16" s="159" t="str">
-        <f>IF(ISNUMBER(BC15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF16" s="159" t="str">
-        <f>IF(ISNUMBER(BF15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG16" s="159" t="str">
-        <f>IF(ISNUMBER(BF15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH16" s="159" t="str">
-        <f>IF(ISNUMBER(BF15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI16" s="159" t="str">
-        <f>IF(ISNUMBER(BI15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ16" s="159" t="str">
-        <f>IF(ISNUMBER(BI15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK16" s="159" t="str">
-        <f>IF(ISNUMBER(BI15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL16" s="159" t="str">
-        <f>IF(ISNUMBER(BL15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM16" s="159" t="str">
-        <f>IF(ISNUMBER(BL15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN16" s="159" t="str">
-        <f>IF(ISNUMBER(BL15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO16" s="159" t="str">
-        <f>IF(ISNUMBER(BO15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP16" s="159" t="str">
-        <f>IF(ISNUMBER(BO15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ16" s="180" t="str">
-        <f>IF(ISNUMBER(BO15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS16" s="179"/>
       <c r="BT16" s="159" t="str">
-        <f>IF(ISNUMBER(BT15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU16" s="159" t="str">
-        <f>IF(ISNUMBER(BT15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV16" s="159" t="str">
-        <f>IF(ISNUMBER(BT15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW16" s="159" t="str">
-        <f>IF(ISNUMBER(BW15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX16" s="159" t="str">
-        <f>IF(ISNUMBER(BW15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY16" s="159" t="str">
-        <f>IF(ISNUMBER(BW15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ16" s="159" t="str">
-        <f>IF(ISNUMBER(BZ15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA16" s="159" t="str">
-        <f>IF(ISNUMBER(BZ15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB16" s="159" t="str">
-        <f>IF(ISNUMBER(BZ15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC16" s="159" t="str">
-        <f>IF(ISNUMBER(CC15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD16" s="159" t="str">
-        <f>IF(ISNUMBER(CC15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE16" s="159" t="str">
-        <f>IF(ISNUMBER(CC15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF16" s="159" t="str">
-        <f>IF(ISNUMBER(CF15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG16" s="159" t="str">
-        <f>IF(ISNUMBER(CF15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH16" s="159" t="str">
-        <f>IF(ISNUMBER(CF15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF15))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI16" s="159" t="str">
-        <f>IF(ISNUMBER(CI15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ16" s="159" t="str">
-        <f>IF(ISNUMBER(CI15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK16" s="159" t="str">
-        <f>IF(ISNUMBER(CI15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL16" s="159" t="str">
-        <f>IF(ISNUMBER(CL15),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL15),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL15),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL15),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM16" s="159" t="str">
-        <f>IF(ISNUMBER(CL15),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL15),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL15),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL15),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN16" s="180" t="str">
-        <f>IF(ISNUMBER(CL15),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL15),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL15),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL15),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL15))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -6857,342 +6930,342 @@
     <row r="18" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="167"/>
       <c r="C18" s="159" t="str">
-        <f>IF(ISNUMBER(C17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D18" s="159" t="str">
-        <f>IF(ISNUMBER(C17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E18" s="159" t="str">
-        <f>IF(ISNUMBER(C17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F18" s="159" t="str">
-        <f>IF(ISNUMBER(F17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G18" s="159" t="str">
-        <f>IF(ISNUMBER(F17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H18" s="159" t="str">
-        <f>IF(ISNUMBER(F17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I18" s="159" t="str">
-        <f>IF(ISNUMBER(I17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J18" s="159" t="str">
-        <f>IF(ISNUMBER(I17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K18" s="159" t="str">
-        <f>IF(ISNUMBER(I17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L18" s="159" t="str">
-        <f>IF(ISNUMBER(L17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M18" s="159" t="str">
-        <f>IF(ISNUMBER(L17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N18" s="159" t="str">
-        <f>IF(ISNUMBER(L17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O18" s="159" t="str">
-        <f>IF(ISNUMBER(O17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P18" s="159" t="str">
-        <f>IF(ISNUMBER(O17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q18" s="159" t="str">
-        <f>IF(ISNUMBER(O17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R18" s="159" t="str">
-        <f>IF(ISNUMBER(R17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S18" s="159" t="str">
-        <f>IF(ISNUMBER(R17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T18" s="159" t="str">
-        <f>IF(ISNUMBER(R17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U18" s="159" t="str">
-        <f>IF(ISNUMBER(U17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V18" s="159" t="str">
-        <f>IF(ISNUMBER(U17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W18" s="168" t="str">
-        <f>IF(ISNUMBER(U17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y18" s="179"/>
       <c r="Z18" s="159" t="str">
-        <f>IF(ISNUMBER(Z17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA18" s="159" t="str">
-        <f>IF(ISNUMBER(Z17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB18" s="159" t="str">
-        <f>IF(ISNUMBER(Z17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC18" s="159" t="str">
-        <f>IF(ISNUMBER(AC17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD18" s="159" t="str">
-        <f>IF(ISNUMBER(AC17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE18" s="159" t="str">
-        <f>IF(ISNUMBER(AC17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF18" s="159" t="str">
-        <f>IF(ISNUMBER(AF17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG18" s="159" t="str">
-        <f>IF(ISNUMBER(AF17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH18" s="159" t="str">
-        <f>IF(ISNUMBER(AF17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI18" s="159" t="str">
-        <f>IF(ISNUMBER(AI17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ18" s="159" t="str">
-        <f>IF(ISNUMBER(AI17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK18" s="159" t="str">
-        <f>IF(ISNUMBER(AI17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL18" s="159" t="str">
-        <f>IF(ISNUMBER(AL17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM18" s="159" t="str">
-        <f>IF(ISNUMBER(AL17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN18" s="159" t="str">
-        <f>IF(ISNUMBER(AL17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL17))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="AO18" s="159" t="str">
-        <f>IF(ISNUMBER(AO17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP18" s="159" t="str">
-        <f>IF(ISNUMBER(AO17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ18" s="159" t="str">
-        <f>IF(ISNUMBER(AO17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR18" s="159" t="str">
-        <f>IF(ISNUMBER(AR17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS18" s="159" t="str">
-        <f>IF(ISNUMBER(AR17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT18" s="180" t="str">
-        <f>IF(ISNUMBER(AR17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV18" s="179"/>
       <c r="AW18" s="159" t="str">
-        <f>IF(ISNUMBER(AW17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX18" s="159" t="str">
-        <f>IF(ISNUMBER(AW17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY18" s="159" t="str">
-        <f>IF(ISNUMBER(AW17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ18" s="159" t="str">
-        <f>IF(ISNUMBER(AZ17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA18" s="159" t="str">
-        <f>IF(ISNUMBER(AZ17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB18" s="159" t="str">
-        <f>IF(ISNUMBER(AZ17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC18" s="159" t="str">
-        <f>IF(ISNUMBER(BC17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD18" s="159" t="str">
-        <f>IF(ISNUMBER(BC17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE18" s="159" t="str">
-        <f>IF(ISNUMBER(BC17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF18" s="159" t="str">
-        <f>IF(ISNUMBER(BF17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG18" s="159" t="str">
-        <f>IF(ISNUMBER(BF17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH18" s="159" t="str">
-        <f>IF(ISNUMBER(BF17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI18" s="159" t="str">
-        <f>IF(ISNUMBER(BI17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ18" s="159" t="str">
-        <f>IF(ISNUMBER(BI17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK18" s="159" t="str">
-        <f>IF(ISNUMBER(BI17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL18" s="159" t="str">
-        <f>IF(ISNUMBER(BL17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM18" s="159" t="str">
-        <f>IF(ISNUMBER(BL17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN18" s="159" t="str">
-        <f>IF(ISNUMBER(BL17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO18" s="159" t="str">
-        <f>IF(ISNUMBER(BO17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP18" s="159" t="str">
-        <f>IF(ISNUMBER(BO17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ18" s="180" t="str">
-        <f>IF(ISNUMBER(BO17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS18" s="179"/>
       <c r="BT18" s="159" t="str">
-        <f>IF(ISNUMBER(BT17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU18" s="159" t="str">
-        <f>IF(ISNUMBER(BT17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV18" s="159" t="str">
-        <f>IF(ISNUMBER(BT17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW18" s="159" t="str">
-        <f>IF(ISNUMBER(BW17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX18" s="159" t="str">
-        <f>IF(ISNUMBER(BW17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY18" s="159" t="str">
-        <f>IF(ISNUMBER(BW17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ18" s="159" t="str">
-        <f>IF(ISNUMBER(BZ17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA18" s="159" t="str">
-        <f>IF(ISNUMBER(BZ17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB18" s="159" t="str">
-        <f>IF(ISNUMBER(BZ17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC18" s="159" t="str">
-        <f>IF(ISNUMBER(CC17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD18" s="159" t="str">
-        <f>IF(ISNUMBER(CC17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE18" s="159" t="str">
-        <f>IF(ISNUMBER(CC17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF18" s="159" t="str">
-        <f>IF(ISNUMBER(CF17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG18" s="159" t="str">
-        <f>IF(ISNUMBER(CF17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH18" s="159" t="str">
-        <f>IF(ISNUMBER(CF17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF17))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI18" s="159" t="str">
-        <f>IF(ISNUMBER(CI17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ18" s="159" t="str">
-        <f>IF(ISNUMBER(CI17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK18" s="159" t="str">
-        <f>IF(ISNUMBER(CI17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL18" s="159" t="str">
-        <f>IF(ISNUMBER(CL17),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL17),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL17),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL17),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM18" s="159" t="str">
-        <f>IF(ISNUMBER(CL17),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL17),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL17),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL17),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN18" s="180" t="str">
-        <f>IF(ISNUMBER(CL17),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL17),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL17),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL17),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL17))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -7385,342 +7458,342 @@
     <row r="20" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="167"/>
       <c r="C20" s="159" t="str">
-        <f>IF(ISNUMBER(C19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D20" s="159" t="str">
-        <f>IF(ISNUMBER(C19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E20" s="159" t="str">
-        <f>IF(ISNUMBER(C19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F20" s="159" t="str">
-        <f>IF(ISNUMBER(F19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G20" s="159" t="str">
-        <f>IF(ISNUMBER(F19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H20" s="159" t="str">
-        <f>IF(ISNUMBER(F19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I20" s="159" t="str">
-        <f>IF(ISNUMBER(I19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J20" s="159" t="str">
-        <f>IF(ISNUMBER(I19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K20" s="159" t="str">
-        <f>IF(ISNUMBER(I19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L20" s="159" t="str">
-        <f>IF(ISNUMBER(L19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M20" s="159" t="str">
-        <f>IF(ISNUMBER(L19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N20" s="159" t="str">
-        <f>IF(ISNUMBER(L19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O20" s="159" t="str">
-        <f>IF(ISNUMBER(O19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P20" s="159" t="str">
-        <f>IF(ISNUMBER(O19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q20" s="159" t="str">
-        <f>IF(ISNUMBER(O19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R20" s="159" t="str">
-        <f>IF(ISNUMBER(R19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S20" s="159" t="str">
-        <f>IF(ISNUMBER(R19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T20" s="159" t="str">
-        <f>IF(ISNUMBER(R19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U20" s="159" t="str">
-        <f>IF(ISNUMBER(U19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V20" s="159" t="str">
-        <f>IF(ISNUMBER(U19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W20" s="168" t="str">
-        <f>IF(ISNUMBER(U19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y20" s="179"/>
       <c r="Z20" s="159" t="str">
-        <f>IF(ISNUMBER(Z19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA20" s="159" t="str">
-        <f>IF(ISNUMBER(Z19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB20" s="159" t="str">
-        <f>IF(ISNUMBER(Z19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC20" s="159" t="str">
-        <f>IF(ISNUMBER(AC19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD20" s="159" t="str">
-        <f>IF(ISNUMBER(AC19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE20" s="159" t="str">
-        <f>IF(ISNUMBER(AC19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF20" s="159" t="str">
-        <f>IF(ISNUMBER(AF19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG20" s="159" t="str">
-        <f>IF(ISNUMBER(AF19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AH20" s="159" t="str">
-        <f>IF(ISNUMBER(AF19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI20" s="159" t="str">
-        <f>IF(ISNUMBER(AI19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ20" s="159" t="str">
-        <f>IF(ISNUMBER(AI19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK20" s="159" t="str">
-        <f>IF(ISNUMBER(AI19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL20" s="159" t="str">
-        <f>IF(ISNUMBER(AL19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM20" s="159" t="str">
-        <f>IF(ISNUMBER(AL19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN20" s="159" t="str">
-        <f>IF(ISNUMBER(AL19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO20" s="159" t="str">
-        <f>IF(ISNUMBER(AO19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP20" s="159" t="str">
-        <f>IF(ISNUMBER(AO19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ20" s="159" t="str">
-        <f>IF(ISNUMBER(AO19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR20" s="159" t="str">
-        <f>IF(ISNUMBER(AR19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS20" s="159" t="str">
-        <f>IF(ISNUMBER(AR19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT20" s="180" t="str">
-        <f>IF(ISNUMBER(AR19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV20" s="179"/>
       <c r="AW20" s="159" t="str">
-        <f>IF(ISNUMBER(AW19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX20" s="159" t="str">
-        <f>IF(ISNUMBER(AW19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY20" s="159" t="str">
-        <f>IF(ISNUMBER(AW19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ20" s="159" t="str">
-        <f>IF(ISNUMBER(AZ19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA20" s="159" t="str">
-        <f>IF(ISNUMBER(AZ19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB20" s="159" t="str">
-        <f>IF(ISNUMBER(AZ19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC20" s="159" t="str">
-        <f>IF(ISNUMBER(BC19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD20" s="159" t="str">
-        <f>IF(ISNUMBER(BC19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE20" s="159" t="str">
-        <f>IF(ISNUMBER(BC19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF20" s="159" t="str">
-        <f>IF(ISNUMBER(BF19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG20" s="159" t="str">
-        <f>IF(ISNUMBER(BF19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH20" s="159" t="str">
-        <f>IF(ISNUMBER(BF19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI20" s="159" t="str">
-        <f>IF(ISNUMBER(BI19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="BJ20" s="159" t="str">
-        <f>IF(ISNUMBER(BI19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="BK20" s="159" t="str">
-        <f>IF(ISNUMBER(BI19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI19))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="BL20" s="159" t="str">
-        <f>IF(ISNUMBER(BL19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM20" s="159" t="str">
-        <f>IF(ISNUMBER(BL19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN20" s="159" t="str">
-        <f>IF(ISNUMBER(BL19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO20" s="159" t="str">
-        <f>IF(ISNUMBER(BO19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP20" s="159" t="str">
-        <f>IF(ISNUMBER(BO19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ20" s="180" t="str">
-        <f>IF(ISNUMBER(BO19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS20" s="179"/>
       <c r="BT20" s="159" t="str">
-        <f>IF(ISNUMBER(BT19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU20" s="159" t="str">
-        <f>IF(ISNUMBER(BT19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV20" s="159" t="str">
-        <f>IF(ISNUMBER(BT19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW20" s="159" t="str">
-        <f>IF(ISNUMBER(BW19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX20" s="159" t="str">
-        <f>IF(ISNUMBER(BW19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY20" s="159" t="str">
-        <f>IF(ISNUMBER(BW19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ20" s="159" t="str">
-        <f>IF(ISNUMBER(BZ19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA20" s="159" t="str">
-        <f>IF(ISNUMBER(BZ19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB20" s="159" t="str">
-        <f>IF(ISNUMBER(BZ19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC20" s="159" t="str">
-        <f>IF(ISNUMBER(CC19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD20" s="159" t="str">
-        <f>IF(ISNUMBER(CC19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="CE20" s="159" t="str">
-        <f>IF(ISNUMBER(CC19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF20" s="159" t="str">
-        <f>IF(ISNUMBER(CF19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG20" s="159" t="str">
-        <f>IF(ISNUMBER(CF19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH20" s="159" t="str">
-        <f>IF(ISNUMBER(CF19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF19))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="CI20" s="159" t="str">
-        <f>IF(ISNUMBER(CI19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ20" s="159" t="str">
-        <f>IF(ISNUMBER(CI19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK20" s="159" t="str">
-        <f>IF(ISNUMBER(CI19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL20" s="159" t="str">
-        <f>IF(ISNUMBER(CL19),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL19),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL19),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL19),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM20" s="159" t="str">
-        <f>IF(ISNUMBER(CL19),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL19),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL19),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL19),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN20" s="180" t="str">
-        <f>IF(ISNUMBER(CL19),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL19),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL19),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL19),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL19))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -7913,342 +7986,342 @@
     <row r="22" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="167"/>
       <c r="C22" s="159" t="str">
-        <f>IF(ISNUMBER(C21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D22" s="159" t="str">
-        <f>IF(ISNUMBER(C21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E22" s="159" t="str">
-        <f>IF(ISNUMBER(C21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F22" s="159" t="str">
-        <f>IF(ISNUMBER(F21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G22" s="159" t="str">
-        <f>IF(ISNUMBER(F21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H22" s="159" t="str">
-        <f>IF(ISNUMBER(F21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I22" s="159" t="str">
-        <f>IF(ISNUMBER(I21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J22" s="159" t="str">
-        <f>IF(ISNUMBER(I21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K22" s="159" t="str">
-        <f>IF(ISNUMBER(I21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L22" s="159" t="str">
-        <f>IF(ISNUMBER(L21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M22" s="159" t="str">
-        <f>IF(ISNUMBER(L21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N22" s="159" t="str">
-        <f>IF(ISNUMBER(L21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O22" s="159" t="str">
-        <f>IF(ISNUMBER(O21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
         <v>S</v>
       </c>
       <c r="P22" s="159" t="str">
-        <f>IF(ISNUMBER(O21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q22" s="159" t="str">
-        <f>IF(ISNUMBER(O21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O21))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="R22" s="159" t="str">
-        <f>IF(ISNUMBER(R21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S22" s="159" t="str">
-        <f>IF(ISNUMBER(R21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T22" s="159" t="str">
-        <f>IF(ISNUMBER(R21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U22" s="159" t="str">
-        <f>IF(ISNUMBER(U21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V22" s="159" t="str">
-        <f>IF(ISNUMBER(U21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W22" s="168" t="str">
-        <f>IF(ISNUMBER(U21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U21))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y22" s="179"/>
       <c r="Z22" s="159" t="str">
-        <f>IF(ISNUMBER(Z21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA22" s="159" t="str">
-        <f>IF(ISNUMBER(Z21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB22" s="159" t="str">
-        <f>IF(ISNUMBER(Z21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC22" s="159" t="str">
-        <f>IF(ISNUMBER(AC21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD22" s="159" t="str">
-        <f>IF(ISNUMBER(AC21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE22" s="159" t="str">
-        <f>IF(ISNUMBER(AC21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF22" s="159" t="str">
-        <f>IF(ISNUMBER(AF21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG22" s="159" t="str">
-        <f>IF(ISNUMBER(AF21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH22" s="159" t="str">
-        <f>IF(ISNUMBER(AF21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI22" s="159" t="str">
-        <f>IF(ISNUMBER(AI21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ22" s="159" t="str">
-        <f>IF(ISNUMBER(AI21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK22" s="159" t="str">
-        <f>IF(ISNUMBER(AI21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL22" s="159" t="str">
-        <f>IF(ISNUMBER(AL21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM22" s="159" t="str">
-        <f>IF(ISNUMBER(AL21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN22" s="159" t="str">
-        <f>IF(ISNUMBER(AL21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO22" s="159" t="str">
-        <f>IF(ISNUMBER(AO21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP22" s="159" t="str">
-        <f>IF(ISNUMBER(AO21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ22" s="159" t="str">
-        <f>IF(ISNUMBER(AO21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR22" s="159" t="str">
-        <f>IF(ISNUMBER(AR21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS22" s="159" t="str">
-        <f>IF(ISNUMBER(AR21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT22" s="180" t="str">
-        <f>IF(ISNUMBER(AR21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV22" s="179"/>
       <c r="AW22" s="159" t="str">
-        <f>IF(ISNUMBER(AW21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AX22" s="159" t="str">
-        <f>IF(ISNUMBER(AW21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AY22" s="159" t="str">
-        <f>IF(ISNUMBER(AW21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW21))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AZ22" s="159" t="str">
-        <f>IF(ISNUMBER(AZ21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA22" s="159" t="str">
-        <f>IF(ISNUMBER(AZ21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB22" s="159" t="str">
-        <f>IF(ISNUMBER(AZ21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC22" s="159" t="str">
-        <f>IF(ISNUMBER(BC21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD22" s="159" t="str">
-        <f>IF(ISNUMBER(BC21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE22" s="159" t="str">
-        <f>IF(ISNUMBER(BC21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF22" s="159" t="str">
-        <f>IF(ISNUMBER(BF21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG22" s="159" t="str">
-        <f>IF(ISNUMBER(BF21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH22" s="159" t="str">
-        <f>IF(ISNUMBER(BF21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI22" s="159" t="str">
-        <f>IF(ISNUMBER(BI21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ22" s="159" t="str">
-        <f>IF(ISNUMBER(BI21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK22" s="159" t="str">
-        <f>IF(ISNUMBER(BI21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL22" s="159" t="str">
-        <f>IF(ISNUMBER(BL21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM22" s="159" t="str">
-        <f>IF(ISNUMBER(BL21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN22" s="159" t="str">
-        <f>IF(ISNUMBER(BL21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO22" s="159" t="str">
-        <f>IF(ISNUMBER(BO21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP22" s="159" t="str">
-        <f>IF(ISNUMBER(BO21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ22" s="180" t="str">
-        <f>IF(ISNUMBER(BO21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS22" s="179"/>
       <c r="BT22" s="159" t="str">
-        <f>IF(ISNUMBER(BT21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU22" s="159" t="str">
-        <f>IF(ISNUMBER(BT21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV22" s="159" t="str">
-        <f>IF(ISNUMBER(BT21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW22" s="159" t="str">
-        <f>IF(ISNUMBER(BW21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX22" s="159" t="str">
-        <f>IF(ISNUMBER(BW21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY22" s="159" t="str">
-        <f>IF(ISNUMBER(BW21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ22" s="159" t="str">
-        <f>IF(ISNUMBER(BZ21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA22" s="159" t="str">
-        <f>IF(ISNUMBER(BZ21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB22" s="159" t="str">
-        <f>IF(ISNUMBER(BZ21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC22" s="159" t="str">
-        <f>IF(ISNUMBER(CC21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD22" s="159" t="str">
-        <f>IF(ISNUMBER(CC21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE22" s="159" t="str">
-        <f>IF(ISNUMBER(CC21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF22" s="159" t="str">
-        <f>IF(ISNUMBER(CF21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG22" s="159" t="str">
-        <f>IF(ISNUMBER(CF21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH22" s="159" t="str">
-        <f>IF(ISNUMBER(CF21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF21))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI22" s="159" t="str">
-        <f>IF(ISNUMBER(CI21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ22" s="159" t="str">
-        <f>IF(ISNUMBER(CI21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK22" s="159" t="str">
-        <f>IF(ISNUMBER(CI21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL22" s="159" t="str">
-        <f>IF(ISNUMBER(CL21),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL21),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL21),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL21),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM22" s="159" t="str">
-        <f>IF(ISNUMBER(CL21),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL21),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL21),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL21),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN22" s="180" t="str">
-        <f>IF(ISNUMBER(CL21),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL21),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL21),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL21),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL21))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -8441,342 +8514,342 @@
     <row r="24" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="169"/>
       <c r="C24" s="170" t="str">
-        <f>IF(ISNUMBER(C23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,C23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D24" s="170" t="str">
-        <f>IF(ISNUMBER(C23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,C23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E24" s="170" t="str">
-        <f>IF(ISNUMBER(C23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,C23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F24" s="170" t="str">
-        <f>IF(ISNUMBER(F23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,F23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G24" s="170" t="str">
-        <f>IF(ISNUMBER(F23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,F23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H24" s="170" t="str">
-        <f>IF(ISNUMBER(F23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,F23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I24" s="170" t="str">
-        <f>IF(ISNUMBER(I23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,I23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J24" s="170" t="str">
-        <f>IF(ISNUMBER(I23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,I23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K24" s="170" t="str">
-        <f>IF(ISNUMBER(I23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,I23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L24" s="170" t="str">
-        <f>IF(ISNUMBER(L23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,L23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M24" s="170" t="str">
-        <f>IF(ISNUMBER(L23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,L23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N24" s="170" t="str">
-        <f>IF(ISNUMBER(L23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,L23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O24" s="170" t="str">
-        <f>IF(ISNUMBER(O23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,O23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P24" s="170" t="str">
-        <f>IF(ISNUMBER(O23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,O23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q24" s="170" t="str">
-        <f>IF(ISNUMBER(O23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,O23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R24" s="170" t="str">
-        <f>IF(ISNUMBER(R23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,R23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S24" s="170" t="str">
-        <f>IF(ISNUMBER(R23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,R23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T24" s="170" t="str">
-        <f>IF(ISNUMBER(R23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,R23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U24" s="170" t="str">
-        <f>IF(ISNUMBER(U23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,1,U23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V24" s="170" t="str">
-        <f>IF(ISNUMBER(U23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,1,U23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W24" s="171" t="str">
-        <f>IF(ISNUMBER(U23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,1,U23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y24" s="181"/>
       <c r="Z24" s="182" t="str">
-        <f>IF(ISNUMBER(Z23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,Z23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA24" s="182" t="str">
-        <f>IF(ISNUMBER(Z23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,Z23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB24" s="182" t="str">
-        <f>IF(ISNUMBER(Z23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,Z23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC24" s="182" t="str">
-        <f>IF(ISNUMBER(AC23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AC23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD24" s="182" t="str">
-        <f>IF(ISNUMBER(AC23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AC23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE24" s="182" t="str">
-        <f>IF(ISNUMBER(AC23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AC23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF24" s="182" t="str">
-        <f>IF(ISNUMBER(AF23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AF23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG24" s="182" t="str">
-        <f>IF(ISNUMBER(AF23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AF23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH24" s="182" t="str">
-        <f>IF(ISNUMBER(AF23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AF23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI24" s="182" t="str">
-        <f>IF(ISNUMBER(AI23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AI23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ24" s="182" t="str">
-        <f>IF(ISNUMBER(AI23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AI23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK24" s="182" t="str">
-        <f>IF(ISNUMBER(AI23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AI23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL24" s="182" t="str">
-        <f>IF(ISNUMBER(AL23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AL23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM24" s="182" t="str">
-        <f>IF(ISNUMBER(AL23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AL23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN24" s="182" t="str">
-        <f>IF(ISNUMBER(AL23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AL23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO24" s="182" t="str">
-        <f>IF(ISNUMBER(AO23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AO23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP24" s="182" t="str">
-        <f>IF(ISNUMBER(AO23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AO23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ24" s="182" t="str">
-        <f>IF(ISNUMBER(AO23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AO23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR24" s="182" t="str">
-        <f>IF(ISNUMBER(AR23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,2,AR23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS24" s="182" t="str">
-        <f>IF(ISNUMBER(AR23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,2,AR23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT24" s="183" t="str">
-        <f>IF(ISNUMBER(AR23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,2,AR23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV24" s="181"/>
       <c r="AW24" s="182" t="str">
-        <f>IF(ISNUMBER(AW23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AW23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX24" s="182" t="str">
-        <f>IF(ISNUMBER(AW23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AW23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY24" s="182" t="str">
-        <f>IF(ISNUMBER(AW23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AW23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ24" s="182" t="str">
-        <f>IF(ISNUMBER(AZ23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,AZ23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA24" s="182" t="str">
-        <f>IF(ISNUMBER(AZ23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,AZ23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB24" s="182" t="str">
-        <f>IF(ISNUMBER(AZ23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,AZ23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC24" s="182" t="str">
-        <f>IF(ISNUMBER(BC23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BC23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD24" s="182" t="str">
-        <f>IF(ISNUMBER(BC23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BC23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE24" s="182" t="str">
-        <f>IF(ISNUMBER(BC23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BC23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF24" s="182" t="str">
-        <f>IF(ISNUMBER(BF23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BF23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG24" s="182" t="str">
-        <f>IF(ISNUMBER(BF23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BF23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH24" s="182" t="str">
-        <f>IF(ISNUMBER(BF23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BF23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI24" s="182" t="str">
-        <f>IF(ISNUMBER(BI23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BI23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ24" s="182" t="str">
-        <f>IF(ISNUMBER(BI23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BI23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK24" s="182" t="str">
-        <f>IF(ISNUMBER(BI23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BI23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL24" s="182" t="str">
-        <f>IF(ISNUMBER(BL23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BL23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM24" s="182" t="str">
-        <f>IF(ISNUMBER(BL23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BL23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN24" s="182" t="str">
-        <f>IF(ISNUMBER(BL23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BL23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO24" s="182" t="str">
-        <f>IF(ISNUMBER(BO23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,3,BO23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP24" s="182" t="str">
-        <f>IF(ISNUMBER(BO23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,3,BO23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ24" s="183" t="str">
-        <f>IF(ISNUMBER(BO23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,3,BO23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS24" s="181"/>
       <c r="BT24" s="182" t="str">
-        <f>IF(ISNUMBER(BT23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BT23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU24" s="182" t="str">
-        <f>IF(ISNUMBER(BT23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BT23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV24" s="182" t="str">
-        <f>IF(ISNUMBER(BT23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BT23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW24" s="182" t="str">
-        <f>IF(ISNUMBER(BW23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BW23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX24" s="182" t="str">
-        <f>IF(ISNUMBER(BW23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BW23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY24" s="182" t="str">
-        <f>IF(ISNUMBER(BW23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BW23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ24" s="182" t="str">
-        <f>IF(ISNUMBER(BZ23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,BZ23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA24" s="182" t="str">
-        <f>IF(ISNUMBER(BZ23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,BZ23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB24" s="182" t="str">
-        <f>IF(ISNUMBER(BZ23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,BZ23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC24" s="182" t="str">
-        <f>IF(ISNUMBER(CC23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CC23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD24" s="182" t="str">
-        <f>IF(ISNUMBER(CC23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CC23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE24" s="182" t="str">
-        <f>IF(ISNUMBER(CC23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CC23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF24" s="182" t="str">
-        <f>IF(ISNUMBER(CF23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CF23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG24" s="182" t="str">
-        <f>IF(ISNUMBER(CF23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CF23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH24" s="182" t="str">
-        <f>IF(ISNUMBER(CF23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CF23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF23))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI24" s="182" t="str">
-        <f>IF(ISNUMBER(CI23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CI23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ24" s="182" t="str">
-        <f>IF(ISNUMBER(CI23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CI23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK24" s="182" t="str">
-        <f>IF(ISNUMBER(CI23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CI23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL24" s="182" t="str">
-        <f>IF(ISNUMBER(CL23),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL23),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL23),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,4,CL23),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM24" s="182" t="str">
-        <f>IF(ISNUMBER(CL23),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL23),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL23),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,4,CL23),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN24" s="183" t="str">
-        <f>IF(ISNUMBER(CL23),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL23),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL23),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,4,CL23),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL23))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -9328,342 +9401,342 @@
     <row r="30" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="179"/>
       <c r="C30" s="159" t="str">
-        <f>IF(ISNUMBER(C29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D30" s="159" t="str">
-        <f>IF(ISNUMBER(C29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E30" s="159" t="str">
-        <f>IF(ISNUMBER(C29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F30" s="159" t="str">
-        <f>IF(ISNUMBER(F29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G30" s="159" t="str">
-        <f>IF(ISNUMBER(F29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H30" s="159" t="str">
-        <f>IF(ISNUMBER(F29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I30" s="159" t="str">
-        <f>IF(ISNUMBER(I29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J30" s="159" t="str">
-        <f>IF(ISNUMBER(I29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K30" s="159" t="str">
-        <f>IF(ISNUMBER(I29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L30" s="159" t="str">
-        <f>IF(ISNUMBER(L29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M30" s="159" t="str">
-        <f>IF(ISNUMBER(L29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N30" s="159" t="str">
-        <f>IF(ISNUMBER(L29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O30" s="159" t="str">
-        <f>IF(ISNUMBER(O29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P30" s="159" t="str">
-        <f>IF(ISNUMBER(O29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q30" s="159" t="str">
-        <f>IF(ISNUMBER(O29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R30" s="159" t="str">
-        <f>IF(ISNUMBER(R29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="S30" s="159" t="str">
-        <f>IF(ISNUMBER(R29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="T30" s="159" t="str">
-        <f>IF(ISNUMBER(R29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R29))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="U30" s="159" t="str">
-        <f>IF(ISNUMBER(U29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V30" s="159" t="str">
-        <f>IF(ISNUMBER(U29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W30" s="180" t="str">
-        <f>IF(ISNUMBER(U29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y30" s="179"/>
       <c r="Z30" s="159" t="str">
-        <f>IF(ISNUMBER(Z29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA30" s="159" t="str">
-        <f>IF(ISNUMBER(Z29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB30" s="159" t="str">
-        <f>IF(ISNUMBER(Z29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC30" s="159" t="str">
-        <f>IF(ISNUMBER(AC29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD30" s="159" t="str">
-        <f>IF(ISNUMBER(AC29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE30" s="159" t="str">
-        <f>IF(ISNUMBER(AC29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF30" s="159" t="str">
-        <f>IF(ISNUMBER(AF29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG30" s="159" t="str">
-        <f>IF(ISNUMBER(AF29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH30" s="159" t="str">
-        <f>IF(ISNUMBER(AF29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI30" s="159" t="str">
-        <f>IF(ISNUMBER(AI29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ30" s="159" t="str">
-        <f>IF(ISNUMBER(AI29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK30" s="159" t="str">
-        <f>IF(ISNUMBER(AI29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL30" s="159" t="str">
-        <f>IF(ISNUMBER(AL29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM30" s="159" t="str">
-        <f>IF(ISNUMBER(AL29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN30" s="159" t="str">
-        <f>IF(ISNUMBER(AL29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO30" s="159" t="str">
-        <f>IF(ISNUMBER(AO29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP30" s="159" t="str">
-        <f>IF(ISNUMBER(AO29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ30" s="159" t="str">
-        <f>IF(ISNUMBER(AO29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR30" s="159" t="str">
-        <f>IF(ISNUMBER(AR29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS30" s="159" t="str">
-        <f>IF(ISNUMBER(AR29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT30" s="180" t="str">
-        <f>IF(ISNUMBER(AR29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV30" s="179"/>
       <c r="AW30" s="159" t="str">
-        <f>IF(ISNUMBER(AW29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX30" s="159" t="str">
-        <f>IF(ISNUMBER(AW29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY30" s="159" t="str">
-        <f>IF(ISNUMBER(AW29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ30" s="159" t="str">
-        <f>IF(ISNUMBER(AZ29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA30" s="159" t="str">
-        <f>IF(ISNUMBER(AZ29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB30" s="159" t="str">
-        <f>IF(ISNUMBER(AZ29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC30" s="159" t="str">
-        <f>IF(ISNUMBER(BC29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD30" s="159" t="str">
-        <f>IF(ISNUMBER(BC29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE30" s="159" t="str">
-        <f>IF(ISNUMBER(BC29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF30" s="159" t="str">
-        <f>IF(ISNUMBER(BF29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG30" s="159" t="str">
-        <f>IF(ISNUMBER(BF29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH30" s="159" t="str">
-        <f>IF(ISNUMBER(BF29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI30" s="159" t="str">
-        <f>IF(ISNUMBER(BI29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ30" s="159" t="str">
-        <f>IF(ISNUMBER(BI29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK30" s="159" t="str">
-        <f>IF(ISNUMBER(BI29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL30" s="159" t="str">
-        <f>IF(ISNUMBER(BL29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM30" s="159" t="str">
-        <f>IF(ISNUMBER(BL29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN30" s="159" t="str">
-        <f>IF(ISNUMBER(BL29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO30" s="159" t="str">
-        <f>IF(ISNUMBER(BO29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP30" s="159" t="str">
-        <f>IF(ISNUMBER(BO29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ30" s="180" t="str">
-        <f>IF(ISNUMBER(BO29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS30" s="179"/>
       <c r="BT30" s="159" t="str">
-        <f>IF(ISNUMBER(BT29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU30" s="159" t="str">
-        <f>IF(ISNUMBER(BT29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV30" s="159" t="str">
-        <f>IF(ISNUMBER(BT29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW30" s="159" t="str">
-        <f>IF(ISNUMBER(BW29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX30" s="159" t="str">
-        <f>IF(ISNUMBER(BW29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY30" s="159" t="str">
-        <f>IF(ISNUMBER(BW29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ30" s="159" t="str">
-        <f>IF(ISNUMBER(BZ29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA30" s="159" t="str">
-        <f>IF(ISNUMBER(BZ29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB30" s="159" t="str">
-        <f>IF(ISNUMBER(BZ29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC30" s="159" t="str">
-        <f>IF(ISNUMBER(CC29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD30" s="159" t="str">
-        <f>IF(ISNUMBER(CC29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE30" s="159" t="str">
-        <f>IF(ISNUMBER(CC29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF30" s="159" t="str">
-        <f>IF(ISNUMBER(CF29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG30" s="159" t="str">
-        <f>IF(ISNUMBER(CF29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH30" s="159" t="str">
-        <f>IF(ISNUMBER(CF29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF29))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI30" s="159" t="str">
-        <f>IF(ISNUMBER(CI29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ30" s="159" t="str">
-        <f>IF(ISNUMBER(CI29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK30" s="159" t="str">
-        <f>IF(ISNUMBER(CI29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI29))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL30" s="159" t="str">
-        <f>IF(ISNUMBER(CL29),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL29),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL29),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL29),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM30" s="159" t="str">
-        <f>IF(ISNUMBER(CL29),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL29),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL29),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL29),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN30" s="180" t="str">
-        <f>IF(ISNUMBER(CL29),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL29),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL29),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL29),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL29))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -9856,342 +9929,342 @@
     <row r="32" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="179"/>
       <c r="C32" s="159" t="str">
-        <f>IF(ISNUMBER(C31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D32" s="159" t="str">
-        <f>IF(ISNUMBER(C31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E32" s="159" t="str">
-        <f>IF(ISNUMBER(C31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F32" s="159" t="str">
-        <f>IF(ISNUMBER(F31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G32" s="159" t="str">
-        <f>IF(ISNUMBER(F31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H32" s="159" t="str">
-        <f>IF(ISNUMBER(F31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I32" s="159" t="str">
-        <f>IF(ISNUMBER(I31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J32" s="159" t="str">
-        <f>IF(ISNUMBER(I31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K32" s="159" t="str">
-        <f>IF(ISNUMBER(I31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L32" s="159" t="str">
-        <f>IF(ISNUMBER(L31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="M32" s="159" t="str">
-        <f>IF(ISNUMBER(L31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="N32" s="159" t="str">
-        <f>IF(ISNUMBER(L31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L31))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="O32" s="159" t="str">
-        <f>IF(ISNUMBER(O31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P32" s="159" t="str">
-        <f>IF(ISNUMBER(O31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q32" s="159" t="str">
-        <f>IF(ISNUMBER(O31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R32" s="159" t="str">
-        <f>IF(ISNUMBER(R31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S32" s="159" t="str">
-        <f>IF(ISNUMBER(R31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T32" s="159" t="str">
-        <f>IF(ISNUMBER(R31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U32" s="159" t="str">
-        <f>IF(ISNUMBER(U31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V32" s="159" t="str">
-        <f>IF(ISNUMBER(U31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W32" s="180" t="str">
-        <f>IF(ISNUMBER(U31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y32" s="179"/>
       <c r="Z32" s="159" t="str">
-        <f>IF(ISNUMBER(Z31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA32" s="159" t="str">
-        <f>IF(ISNUMBER(Z31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB32" s="159" t="str">
-        <f>IF(ISNUMBER(Z31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC32" s="159" t="str">
-        <f>IF(ISNUMBER(AC31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD32" s="159" t="str">
-        <f>IF(ISNUMBER(AC31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE32" s="159" t="str">
-        <f>IF(ISNUMBER(AC31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF32" s="159" t="str">
-        <f>IF(ISNUMBER(AF31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG32" s="159" t="str">
-        <f>IF(ISNUMBER(AF31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH32" s="159" t="str">
-        <f>IF(ISNUMBER(AF31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI32" s="159" t="str">
-        <f>IF(ISNUMBER(AI31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ32" s="159" t="str">
-        <f>IF(ISNUMBER(AI31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK32" s="159" t="str">
-        <f>IF(ISNUMBER(AI31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL32" s="159" t="str">
-        <f>IF(ISNUMBER(AL31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM32" s="159" t="str">
-        <f>IF(ISNUMBER(AL31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN32" s="159" t="str">
-        <f>IF(ISNUMBER(AL31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO32" s="159" t="str">
-        <f>IF(ISNUMBER(AO31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="AP32" s="159" t="str">
-        <f>IF(ISNUMBER(AO31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ32" s="159" t="str">
-        <f>IF(ISNUMBER(AO31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR32" s="159" t="str">
-        <f>IF(ISNUMBER(AR31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS32" s="159" t="str">
-        <f>IF(ISNUMBER(AR31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT32" s="180" t="str">
-        <f>IF(ISNUMBER(AR31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV32" s="179"/>
       <c r="AW32" s="159" t="str">
-        <f>IF(ISNUMBER(AW31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX32" s="159" t="str">
-        <f>IF(ISNUMBER(AW31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY32" s="159" t="str">
-        <f>IF(ISNUMBER(AW31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ32" s="159" t="str">
-        <f>IF(ISNUMBER(AZ31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA32" s="159" t="str">
-        <f>IF(ISNUMBER(AZ31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB32" s="159" t="str">
-        <f>IF(ISNUMBER(AZ31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC32" s="159" t="str">
-        <f>IF(ISNUMBER(BC31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD32" s="159" t="str">
-        <f>IF(ISNUMBER(BC31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE32" s="159" t="str">
-        <f>IF(ISNUMBER(BC31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF32" s="159" t="str">
-        <f>IF(ISNUMBER(BF31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG32" s="159" t="str">
-        <f>IF(ISNUMBER(BF31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH32" s="159" t="str">
-        <f>IF(ISNUMBER(BF31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI32" s="159" t="str">
-        <f>IF(ISNUMBER(BI31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ32" s="159" t="str">
-        <f>IF(ISNUMBER(BI31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK32" s="159" t="str">
-        <f>IF(ISNUMBER(BI31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL32" s="159" t="str">
-        <f>IF(ISNUMBER(BL31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="BM32" s="159" t="str">
-        <f>IF(ISNUMBER(BL31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN32" s="159" t="str">
-        <f>IF(ISNUMBER(BL31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO32" s="159" t="str">
-        <f>IF(ISNUMBER(BO31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP32" s="159" t="str">
-        <f>IF(ISNUMBER(BO31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ32" s="180" t="str">
-        <f>IF(ISNUMBER(BO31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS32" s="179"/>
       <c r="BT32" s="159" t="str">
-        <f>IF(ISNUMBER(BT31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU32" s="159" t="str">
-        <f>IF(ISNUMBER(BT31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV32" s="159" t="str">
-        <f>IF(ISNUMBER(BT31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW32" s="159" t="str">
-        <f>IF(ISNUMBER(BW31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX32" s="159" t="str">
-        <f>IF(ISNUMBER(BW31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY32" s="159" t="str">
-        <f>IF(ISNUMBER(BW31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ32" s="159" t="str">
-        <f>IF(ISNUMBER(BZ31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA32" s="159" t="str">
-        <f>IF(ISNUMBER(BZ31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB32" s="159" t="str">
-        <f>IF(ISNUMBER(BZ31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC32" s="159" t="str">
-        <f>IF(ISNUMBER(CC31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD32" s="159" t="str">
-        <f>IF(ISNUMBER(CC31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE32" s="159" t="str">
-        <f>IF(ISNUMBER(CC31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF32" s="159" t="str">
-        <f>IF(ISNUMBER(CF31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG32" s="159" t="str">
-        <f>IF(ISNUMBER(CF31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH32" s="159" t="str">
-        <f>IF(ISNUMBER(CF31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF31))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI32" s="159" t="str">
-        <f>IF(ISNUMBER(CI31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="CJ32" s="159" t="str">
-        <f>IF(ISNUMBER(CI31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK32" s="159" t="str">
-        <f>IF(ISNUMBER(CI31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL32" s="159" t="str">
-        <f>IF(ISNUMBER(CL31),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL31),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL31),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL31),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM32" s="159" t="str">
-        <f>IF(ISNUMBER(CL31),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL31),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL31),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL31),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN32" s="180" t="str">
-        <f>IF(ISNUMBER(CL31),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL31),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL31),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL31),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL31))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -10384,342 +10457,342 @@
     <row r="34" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="179"/>
       <c r="C34" s="159" t="str">
-        <f>IF(ISNUMBER(C33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D34" s="159" t="str">
-        <f>IF(ISNUMBER(C33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E34" s="159" t="str">
-        <f>IF(ISNUMBER(C33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F34" s="159" t="str">
-        <f>IF(ISNUMBER(F33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G34" s="159" t="str">
-        <f>IF(ISNUMBER(F33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H34" s="159" t="str">
-        <f>IF(ISNUMBER(F33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I34" s="159" t="str">
-        <f>IF(ISNUMBER(I33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J34" s="159" t="str">
-        <f>IF(ISNUMBER(I33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K34" s="159" t="str">
-        <f>IF(ISNUMBER(I33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L34" s="159" t="str">
-        <f>IF(ISNUMBER(L33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M34" s="159" t="str">
-        <f>IF(ISNUMBER(L33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N34" s="159" t="str">
-        <f>IF(ISNUMBER(L33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O34" s="159" t="str">
-        <f>IF(ISNUMBER(O33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P34" s="159" t="str">
-        <f>IF(ISNUMBER(O33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q34" s="159" t="str">
-        <f>IF(ISNUMBER(O33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R34" s="159" t="str">
-        <f>IF(ISNUMBER(R33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S34" s="159" t="str">
-        <f>IF(ISNUMBER(R33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T34" s="159" t="str">
-        <f>IF(ISNUMBER(R33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U34" s="159" t="str">
-        <f>IF(ISNUMBER(U33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V34" s="159" t="str">
-        <f>IF(ISNUMBER(U33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W34" s="180" t="str">
-        <f>IF(ISNUMBER(U33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y34" s="179"/>
       <c r="Z34" s="159" t="str">
-        <f>IF(ISNUMBER(Z33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA34" s="159" t="str">
-        <f>IF(ISNUMBER(Z33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB34" s="159" t="str">
-        <f>IF(ISNUMBER(Z33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC34" s="159" t="str">
-        <f>IF(ISNUMBER(AC33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD34" s="159" t="str">
-        <f>IF(ISNUMBER(AC33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE34" s="159" t="str">
-        <f>IF(ISNUMBER(AC33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF34" s="159" t="str">
-        <f>IF(ISNUMBER(AF33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG34" s="159" t="str">
-        <f>IF(ISNUMBER(AF33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH34" s="159" t="str">
-        <f>IF(ISNUMBER(AF33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI34" s="159" t="str">
-        <f>IF(ISNUMBER(AI33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ34" s="159" t="str">
-        <f>IF(ISNUMBER(AI33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK34" s="159" t="str">
-        <f>IF(ISNUMBER(AI33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL34" s="159" t="str">
-        <f>IF(ISNUMBER(AL33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM34" s="159" t="str">
-        <f>IF(ISNUMBER(AL33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN34" s="159" t="str">
-        <f>IF(ISNUMBER(AL33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO34" s="159" t="str">
-        <f>IF(ISNUMBER(AO33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP34" s="159" t="str">
-        <f>IF(ISNUMBER(AO33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ34" s="159" t="str">
-        <f>IF(ISNUMBER(AO33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO33))&gt;0,"h","w")),"")</f>
         <v>P</v>
       </c>
       <c r="AR34" s="159" t="str">
-        <f>IF(ISNUMBER(AR33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS34" s="159" t="str">
-        <f>IF(ISNUMBER(AR33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT34" s="180" t="str">
-        <f>IF(ISNUMBER(AR33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV34" s="179"/>
       <c r="AW34" s="159" t="str">
-        <f>IF(ISNUMBER(AW33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX34" s="159" t="str">
-        <f>IF(ISNUMBER(AW33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY34" s="159" t="str">
-        <f>IF(ISNUMBER(AW33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ34" s="159" t="str">
-        <f>IF(ISNUMBER(AZ33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA34" s="159" t="str">
-        <f>IF(ISNUMBER(AZ33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB34" s="159" t="str">
-        <f>IF(ISNUMBER(AZ33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC34" s="159" t="str">
-        <f>IF(ISNUMBER(BC33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD34" s="159" t="str">
-        <f>IF(ISNUMBER(BC33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE34" s="159" t="str">
-        <f>IF(ISNUMBER(BC33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF34" s="159" t="str">
-        <f>IF(ISNUMBER(BF33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG34" s="159" t="str">
-        <f>IF(ISNUMBER(BF33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH34" s="159" t="str">
-        <f>IF(ISNUMBER(BF33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI34" s="159" t="str">
-        <f>IF(ISNUMBER(BI33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ34" s="159" t="str">
-        <f>IF(ISNUMBER(BI33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK34" s="159" t="str">
-        <f>IF(ISNUMBER(BI33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL34" s="159" t="str">
-        <f>IF(ISNUMBER(BL33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM34" s="159" t="str">
-        <f>IF(ISNUMBER(BL33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN34" s="159" t="str">
-        <f>IF(ISNUMBER(BL33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO34" s="159" t="str">
-        <f>IF(ISNUMBER(BO33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP34" s="159" t="str">
-        <f>IF(ISNUMBER(BO33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ34" s="180" t="str">
-        <f>IF(ISNUMBER(BO33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS34" s="179"/>
       <c r="BT34" s="159" t="str">
-        <f>IF(ISNUMBER(BT33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU34" s="159" t="str">
-        <f>IF(ISNUMBER(BT33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV34" s="159" t="str">
-        <f>IF(ISNUMBER(BT33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW34" s="159" t="str">
-        <f>IF(ISNUMBER(BW33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX34" s="159" t="str">
-        <f>IF(ISNUMBER(BW33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY34" s="159" t="str">
-        <f>IF(ISNUMBER(BW33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ34" s="159" t="str">
-        <f>IF(ISNUMBER(BZ33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA34" s="159" t="str">
-        <f>IF(ISNUMBER(BZ33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="CB34" s="159" t="str">
-        <f>IF(ISNUMBER(BZ33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC34" s="159" t="str">
-        <f>IF(ISNUMBER(CC33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD34" s="159" t="str">
-        <f>IF(ISNUMBER(CC33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE34" s="159" t="str">
-        <f>IF(ISNUMBER(CC33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF34" s="159" t="str">
-        <f>IF(ISNUMBER(CF33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG34" s="159" t="str">
-        <f>IF(ISNUMBER(CF33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH34" s="159" t="str">
-        <f>IF(ISNUMBER(CF33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF33))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI34" s="159" t="str">
-        <f>IF(ISNUMBER(CI33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ34" s="159" t="str">
-        <f>IF(ISNUMBER(CI33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK34" s="159" t="str">
-        <f>IF(ISNUMBER(CI33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL34" s="159" t="str">
-        <f>IF(ISNUMBER(CL33),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL33),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL33),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL33),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM34" s="159" t="str">
-        <f>IF(ISNUMBER(CL33),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL33),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL33),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL33),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN34" s="180" t="str">
-        <f>IF(ISNUMBER(CL33),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL33),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL33),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL33),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL33))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -10912,342 +10985,342 @@
     <row r="36" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="179"/>
       <c r="C36" s="159" t="str">
-        <f>IF(ISNUMBER(C35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="D36" s="159" t="str">
-        <f>IF(ISNUMBER(C35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="E36" s="159" t="str">
-        <f>IF(ISNUMBER(C35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C35))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="F36" s="159" t="str">
-        <f>IF(ISNUMBER(F35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G36" s="159" t="str">
-        <f>IF(ISNUMBER(F35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H36" s="159" t="str">
-        <f>IF(ISNUMBER(F35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I36" s="159" t="str">
-        <f>IF(ISNUMBER(I35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J36" s="159" t="str">
-        <f>IF(ISNUMBER(I35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K36" s="159" t="str">
-        <f>IF(ISNUMBER(I35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L36" s="159" t="str">
-        <f>IF(ISNUMBER(L35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M36" s="159" t="str">
-        <f>IF(ISNUMBER(L35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N36" s="159" t="str">
-        <f>IF(ISNUMBER(L35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O36" s="159" t="str">
-        <f>IF(ISNUMBER(O35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P36" s="159" t="str">
-        <f>IF(ISNUMBER(O35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q36" s="159" t="str">
-        <f>IF(ISNUMBER(O35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R36" s="159" t="str">
-        <f>IF(ISNUMBER(R35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S36" s="159" t="str">
-        <f>IF(ISNUMBER(R35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T36" s="159" t="str">
-        <f>IF(ISNUMBER(R35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U36" s="159" t="str">
-        <f>IF(ISNUMBER(U35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V36" s="159" t="str">
-        <f>IF(ISNUMBER(U35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W36" s="180" t="str">
-        <f>IF(ISNUMBER(U35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y36" s="179"/>
       <c r="Z36" s="159" t="str">
-        <f>IF(ISNUMBER(Z35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA36" s="159" t="str">
-        <f>IF(ISNUMBER(Z35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB36" s="159" t="str">
-        <f>IF(ISNUMBER(Z35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC36" s="159" t="str">
-        <f>IF(ISNUMBER(AC35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD36" s="159" t="str">
-        <f>IF(ISNUMBER(AC35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE36" s="159" t="str">
-        <f>IF(ISNUMBER(AC35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF36" s="159" t="str">
-        <f>IF(ISNUMBER(AF35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG36" s="159" t="str">
-        <f>IF(ISNUMBER(AF35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH36" s="159" t="str">
-        <f>IF(ISNUMBER(AF35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI36" s="159" t="str">
-        <f>IF(ISNUMBER(AI35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ36" s="159" t="str">
-        <f>IF(ISNUMBER(AI35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK36" s="159" t="str">
-        <f>IF(ISNUMBER(AI35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL36" s="159" t="str">
-        <f>IF(ISNUMBER(AL35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM36" s="159" t="str">
-        <f>IF(ISNUMBER(AL35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN36" s="159" t="str">
-        <f>IF(ISNUMBER(AL35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO36" s="159" t="str">
-        <f>IF(ISNUMBER(AO35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP36" s="159" t="str">
-        <f>IF(ISNUMBER(AO35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ36" s="159" t="str">
-        <f>IF(ISNUMBER(AO35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR36" s="159" t="str">
-        <f>IF(ISNUMBER(AR35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS36" s="159" t="str">
-        <f>IF(ISNUMBER(AR35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT36" s="180" t="str">
-        <f>IF(ISNUMBER(AR35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV36" s="179"/>
       <c r="AW36" s="159" t="str">
-        <f>IF(ISNUMBER(AW35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX36" s="159" t="str">
-        <f>IF(ISNUMBER(AW35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY36" s="159" t="str">
-        <f>IF(ISNUMBER(AW35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ36" s="159" t="str">
-        <f>IF(ISNUMBER(AZ35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA36" s="159" t="str">
-        <f>IF(ISNUMBER(AZ35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB36" s="159" t="str">
-        <f>IF(ISNUMBER(AZ35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC36" s="159" t="str">
-        <f>IF(ISNUMBER(BC35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD36" s="159" t="str">
-        <f>IF(ISNUMBER(BC35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE36" s="159" t="str">
-        <f>IF(ISNUMBER(BC35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF36" s="159" t="str">
-        <f>IF(ISNUMBER(BF35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG36" s="159" t="str">
-        <f>IF(ISNUMBER(BF35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH36" s="159" t="str">
-        <f>IF(ISNUMBER(BF35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI36" s="159" t="str">
-        <f>IF(ISNUMBER(BI35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ36" s="159" t="str">
-        <f>IF(ISNUMBER(BI35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK36" s="159" t="str">
-        <f>IF(ISNUMBER(BI35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL36" s="159" t="str">
-        <f>IF(ISNUMBER(BL35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="BM36" s="159" t="str">
-        <f>IF(ISNUMBER(BL35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN36" s="159" t="str">
-        <f>IF(ISNUMBER(BL35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO36" s="159" t="str">
-        <f>IF(ISNUMBER(BO35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP36" s="159" t="str">
-        <f>IF(ISNUMBER(BO35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ36" s="180" t="str">
-        <f>IF(ISNUMBER(BO35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS36" s="179"/>
       <c r="BT36" s="159" t="str">
-        <f>IF(ISNUMBER(BT35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU36" s="159" t="str">
-        <f>IF(ISNUMBER(BT35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV36" s="159" t="str">
-        <f>IF(ISNUMBER(BT35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW36" s="159" t="str">
-        <f>IF(ISNUMBER(BW35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX36" s="159" t="str">
-        <f>IF(ISNUMBER(BW35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY36" s="159" t="str">
-        <f>IF(ISNUMBER(BW35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ36" s="159" t="str">
-        <f>IF(ISNUMBER(BZ35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA36" s="159" t="str">
-        <f>IF(ISNUMBER(BZ35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB36" s="159" t="str">
-        <f>IF(ISNUMBER(BZ35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC36" s="159" t="str">
-        <f>IF(ISNUMBER(CC35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD36" s="159" t="str">
-        <f>IF(ISNUMBER(CC35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE36" s="159" t="str">
-        <f>IF(ISNUMBER(CC35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF36" s="159" t="str">
-        <f>IF(ISNUMBER(CF35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG36" s="159" t="str">
-        <f>IF(ISNUMBER(CF35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH36" s="159" t="str">
-        <f>IF(ISNUMBER(CF35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF35))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI36" s="159" t="str">
-        <f>IF(ISNUMBER(CI35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ36" s="159" t="str">
-        <f>IF(ISNUMBER(CI35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK36" s="159" t="str">
-        <f>IF(ISNUMBER(CI35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL36" s="159" t="str">
-        <f>IF(ISNUMBER(CL35),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL35),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL35),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL35),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM36" s="159" t="str">
-        <f>IF(ISNUMBER(CL35),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL35),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL35),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL35),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN36" s="180" t="str">
-        <f>IF(ISNUMBER(CL35),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL35),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL35),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL35),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL35))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -11440,342 +11513,342 @@
     <row r="38" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="179"/>
       <c r="C38" s="159" t="str">
-        <f>IF(ISNUMBER(C37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D38" s="159" t="str">
-        <f>IF(ISNUMBER(C37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E38" s="159" t="str">
-        <f>IF(ISNUMBER(C37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F38" s="159" t="str">
-        <f>IF(ISNUMBER(F37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G38" s="159" t="str">
-        <f>IF(ISNUMBER(F37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H38" s="159" t="str">
-        <f>IF(ISNUMBER(F37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I38" s="159" t="str">
-        <f>IF(ISNUMBER(I37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J38" s="159" t="str">
-        <f>IF(ISNUMBER(I37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K38" s="159" t="str">
-        <f>IF(ISNUMBER(I37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L38" s="159" t="str">
-        <f>IF(ISNUMBER(L37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="M38" s="159" t="str">
-        <f>IF(ISNUMBER(L37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="N38" s="159" t="str">
-        <f>IF(ISNUMBER(L37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L37))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="O38" s="159" t="str">
-        <f>IF(ISNUMBER(O37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P38" s="159" t="str">
-        <f>IF(ISNUMBER(O37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q38" s="159" t="str">
-        <f>IF(ISNUMBER(O37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R38" s="159" t="str">
-        <f>IF(ISNUMBER(R37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S38" s="159" t="str">
-        <f>IF(ISNUMBER(R37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T38" s="159" t="str">
-        <f>IF(ISNUMBER(R37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U38" s="159" t="str">
-        <f>IF(ISNUMBER(U37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V38" s="159" t="str">
-        <f>IF(ISNUMBER(U37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W38" s="180" t="str">
-        <f>IF(ISNUMBER(U37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y38" s="179"/>
       <c r="Z38" s="159" t="str">
-        <f>IF(ISNUMBER(Z37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA38" s="159" t="str">
-        <f>IF(ISNUMBER(Z37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB38" s="159" t="str">
-        <f>IF(ISNUMBER(Z37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC38" s="159" t="str">
-        <f>IF(ISNUMBER(AC37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD38" s="159" t="str">
-        <f>IF(ISNUMBER(AC37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE38" s="159" t="str">
-        <f>IF(ISNUMBER(AC37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF38" s="159" t="str">
-        <f>IF(ISNUMBER(AF37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG38" s="159" t="str">
-        <f>IF(ISNUMBER(AF37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AH38" s="159" t="str">
-        <f>IF(ISNUMBER(AF37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI38" s="159" t="str">
-        <f>IF(ISNUMBER(AI37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ38" s="159" t="str">
-        <f>IF(ISNUMBER(AI37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK38" s="159" t="str">
-        <f>IF(ISNUMBER(AI37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL38" s="159" t="str">
-        <f>IF(ISNUMBER(AL37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM38" s="159" t="str">
-        <f>IF(ISNUMBER(AL37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN38" s="159" t="str">
-        <f>IF(ISNUMBER(AL37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO38" s="159" t="str">
-        <f>IF(ISNUMBER(AO37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP38" s="159" t="str">
-        <f>IF(ISNUMBER(AO37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ38" s="159" t="str">
-        <f>IF(ISNUMBER(AO37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR38" s="159" t="str">
-        <f>IF(ISNUMBER(AR37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS38" s="159" t="str">
-        <f>IF(ISNUMBER(AR37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT38" s="180" t="str">
-        <f>IF(ISNUMBER(AR37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV38" s="179"/>
       <c r="AW38" s="159" t="str">
-        <f>IF(ISNUMBER(AW37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX38" s="159" t="str">
-        <f>IF(ISNUMBER(AW37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY38" s="159" t="str">
-        <f>IF(ISNUMBER(AW37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ38" s="159" t="str">
-        <f>IF(ISNUMBER(AZ37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA38" s="159" t="str">
-        <f>IF(ISNUMBER(AZ37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB38" s="159" t="str">
-        <f>IF(ISNUMBER(AZ37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC38" s="159" t="str">
-        <f>IF(ISNUMBER(BC37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD38" s="159" t="str">
-        <f>IF(ISNUMBER(BC37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="BE38" s="159" t="str">
-        <f>IF(ISNUMBER(BC37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF38" s="159" t="str">
-        <f>IF(ISNUMBER(BF37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG38" s="159" t="str">
-        <f>IF(ISNUMBER(BF37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH38" s="159" t="str">
-        <f>IF(ISNUMBER(BF37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI38" s="159" t="str">
-        <f>IF(ISNUMBER(BI37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ38" s="159" t="str">
-        <f>IF(ISNUMBER(BI37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK38" s="159" t="str">
-        <f>IF(ISNUMBER(BI37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL38" s="159" t="str">
-        <f>IF(ISNUMBER(BL37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM38" s="159" t="str">
-        <f>IF(ISNUMBER(BL37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN38" s="159" t="str">
-        <f>IF(ISNUMBER(BL37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO38" s="159" t="str">
-        <f>IF(ISNUMBER(BO37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP38" s="159" t="str">
-        <f>IF(ISNUMBER(BO37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ38" s="180" t="str">
-        <f>IF(ISNUMBER(BO37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO37))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS38" s="179"/>
       <c r="BT38" s="159" t="str">
-        <f>IF(ISNUMBER(BT37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU38" s="159" t="str">
-        <f>IF(ISNUMBER(BT37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV38" s="159" t="str">
-        <f>IF(ISNUMBER(BT37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW38" s="159" t="str">
-        <f>IF(ISNUMBER(BW37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX38" s="159" t="str">
-        <f>IF(ISNUMBER(BW37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY38" s="159" t="str">
-        <f>IF(ISNUMBER(BW37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ38" s="159" t="str">
-        <f>IF(ISNUMBER(BZ37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA38" s="159" t="str">
-        <f>IF(ISNUMBER(BZ37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="CB38" s="159" t="str">
-        <f>IF(ISNUMBER(BZ37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC38" s="159" t="str">
-        <f>IF(ISNUMBER(CC37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD38" s="159" t="str">
-        <f>IF(ISNUMBER(CC37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE38" s="159" t="str">
-        <f>IF(ISNUMBER(CC37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF38" s="159" t="str">
-        <f>IF(ISNUMBER(CF37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG38" s="159" t="str">
-        <f>IF(ISNUMBER(CF37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH38" s="159" t="str">
-        <f>IF(ISNUMBER(CF37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF37))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="CI38" s="159" t="str">
-        <f>IF(ISNUMBER(CI37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ38" s="159" t="str">
-        <f>IF(ISNUMBER(CI37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK38" s="159" t="str">
-        <f>IF(ISNUMBER(CI37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL38" s="159" t="str">
-        <f>IF(ISNUMBER(CL37),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL37),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL37),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL37),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM38" s="159" t="str">
-        <f>IF(ISNUMBER(CL37),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL37),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL37),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL37),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN38" s="180" t="str">
-        <f>IF(ISNUMBER(CL37),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL37),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL37),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL37),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL37))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -11968,342 +12041,342 @@
     <row r="40" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="181"/>
       <c r="C40" s="182" t="str">
-        <f>IF(ISNUMBER(C39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,C39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D40" s="182" t="str">
-        <f>IF(ISNUMBER(C39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,C39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E40" s="182" t="str">
-        <f>IF(ISNUMBER(C39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,C39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F40" s="182" t="str">
-        <f>IF(ISNUMBER(F39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,F39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G40" s="182" t="str">
-        <f>IF(ISNUMBER(F39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,F39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H40" s="182" t="str">
-        <f>IF(ISNUMBER(F39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,F39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I40" s="182" t="str">
-        <f>IF(ISNUMBER(I39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,I39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J40" s="182" t="str">
-        <f>IF(ISNUMBER(I39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,I39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K40" s="182" t="str">
-        <f>IF(ISNUMBER(I39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,I39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L40" s="182" t="str">
-        <f>IF(ISNUMBER(L39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,L39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M40" s="182" t="str">
-        <f>IF(ISNUMBER(L39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,L39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N40" s="182" t="str">
-        <f>IF(ISNUMBER(L39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,L39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O40" s="182" t="str">
-        <f>IF(ISNUMBER(O39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,O39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P40" s="182" t="str">
-        <f>IF(ISNUMBER(O39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,O39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q40" s="182" t="str">
-        <f>IF(ISNUMBER(O39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,O39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R40" s="182" t="str">
-        <f>IF(ISNUMBER(R39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,R39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S40" s="182" t="str">
-        <f>IF(ISNUMBER(R39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,R39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T40" s="182" t="str">
-        <f>IF(ISNUMBER(R39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,R39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U40" s="182" t="str">
-        <f>IF(ISNUMBER(U39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,5,U39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V40" s="182" t="str">
-        <f>IF(ISNUMBER(U39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,5,U39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W40" s="183" t="str">
-        <f>IF(ISNUMBER(U39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,5,U39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y40" s="181"/>
       <c r="Z40" s="182" t="str">
-        <f>IF(ISNUMBER(Z39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,Z39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA40" s="182" t="str">
-        <f>IF(ISNUMBER(Z39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,Z39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB40" s="182" t="str">
-        <f>IF(ISNUMBER(Z39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,Z39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC40" s="182" t="str">
-        <f>IF(ISNUMBER(AC39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AC39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD40" s="182" t="str">
-        <f>IF(ISNUMBER(AC39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AC39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE40" s="182" t="str">
-        <f>IF(ISNUMBER(AC39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AC39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF40" s="182" t="str">
-        <f>IF(ISNUMBER(AF39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AF39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG40" s="182" t="str">
-        <f>IF(ISNUMBER(AF39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AF39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH40" s="182" t="str">
-        <f>IF(ISNUMBER(AF39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AF39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI40" s="182" t="str">
-        <f>IF(ISNUMBER(AI39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AI39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ40" s="182" t="str">
-        <f>IF(ISNUMBER(AI39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AI39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK40" s="182" t="str">
-        <f>IF(ISNUMBER(AI39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AI39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL40" s="182" t="str">
-        <f>IF(ISNUMBER(AL39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AL39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM40" s="182" t="str">
-        <f>IF(ISNUMBER(AL39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AL39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN40" s="182" t="str">
-        <f>IF(ISNUMBER(AL39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AL39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO40" s="182" t="str">
-        <f>IF(ISNUMBER(AO39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AO39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP40" s="182" t="str">
-        <f>IF(ISNUMBER(AO39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AO39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ40" s="182" t="str">
-        <f>IF(ISNUMBER(AO39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AO39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR40" s="182" t="str">
-        <f>IF(ISNUMBER(AR39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,6,AR39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS40" s="182" t="str">
-        <f>IF(ISNUMBER(AR39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,6,AR39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT40" s="183" t="str">
-        <f>IF(ISNUMBER(AR39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,6,AR39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV40" s="181"/>
       <c r="AW40" s="182" t="str">
-        <f>IF(ISNUMBER(AW39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AW39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX40" s="182" t="str">
-        <f>IF(ISNUMBER(AW39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AW39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY40" s="182" t="str">
-        <f>IF(ISNUMBER(AW39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AW39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ40" s="182" t="str">
-        <f>IF(ISNUMBER(AZ39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,AZ39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA40" s="182" t="str">
-        <f>IF(ISNUMBER(AZ39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,AZ39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB40" s="182" t="str">
-        <f>IF(ISNUMBER(AZ39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,AZ39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC40" s="182" t="str">
-        <f>IF(ISNUMBER(BC39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BC39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD40" s="182" t="str">
-        <f>IF(ISNUMBER(BC39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BC39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE40" s="182" t="str">
-        <f>IF(ISNUMBER(BC39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BC39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF40" s="182" t="str">
-        <f>IF(ISNUMBER(BF39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BF39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG40" s="182" t="str">
-        <f>IF(ISNUMBER(BF39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BF39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH40" s="182" t="str">
-        <f>IF(ISNUMBER(BF39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BF39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI40" s="182" t="str">
-        <f>IF(ISNUMBER(BI39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BI39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ40" s="182" t="str">
-        <f>IF(ISNUMBER(BI39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BI39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK40" s="182" t="str">
-        <f>IF(ISNUMBER(BI39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BI39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL40" s="182" t="str">
-        <f>IF(ISNUMBER(BL39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BL39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM40" s="182" t="str">
-        <f>IF(ISNUMBER(BL39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BL39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN40" s="182" t="str">
-        <f>IF(ISNUMBER(BL39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BL39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO40" s="182" t="str">
-        <f>IF(ISNUMBER(BO39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,7,BO39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP40" s="182" t="str">
-        <f>IF(ISNUMBER(BO39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,7,BO39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ40" s="183" t="str">
-        <f>IF(ISNUMBER(BO39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,7,BO39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS40" s="181"/>
       <c r="BT40" s="182" t="str">
-        <f>IF(ISNUMBER(BT39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BT39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU40" s="182" t="str">
-        <f>IF(ISNUMBER(BT39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BT39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV40" s="182" t="str">
-        <f>IF(ISNUMBER(BT39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BT39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW40" s="182" t="str">
-        <f>IF(ISNUMBER(BW39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BW39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX40" s="182" t="str">
-        <f>IF(ISNUMBER(BW39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BW39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY40" s="182" t="str">
-        <f>IF(ISNUMBER(BW39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BW39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ40" s="182" t="str">
-        <f>IF(ISNUMBER(BZ39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,BZ39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA40" s="182" t="str">
-        <f>IF(ISNUMBER(BZ39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,BZ39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB40" s="182" t="str">
-        <f>IF(ISNUMBER(BZ39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,BZ39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC40" s="182" t="str">
-        <f>IF(ISNUMBER(CC39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CC39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD40" s="182" t="str">
-        <f>IF(ISNUMBER(CC39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CC39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE40" s="182" t="str">
-        <f>IF(ISNUMBER(CC39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CC39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF40" s="182" t="str">
-        <f>IF(ISNUMBER(CF39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CF39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG40" s="182" t="str">
-        <f>IF(ISNUMBER(CF39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CF39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH40" s="182" t="str">
-        <f>IF(ISNUMBER(CF39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CF39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF39))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI40" s="182" t="str">
-        <f>IF(ISNUMBER(CI39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CI39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ40" s="182" t="str">
-        <f>IF(ISNUMBER(CI39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CI39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK40" s="182" t="str">
-        <f>IF(ISNUMBER(CI39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CI39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL40" s="182" t="str">
-        <f>IF(ISNUMBER(CL39),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL39),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL39),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,8,CL39),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM40" s="182" t="str">
-        <f>IF(ISNUMBER(CL39),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL39),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL39),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,8,CL39),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN40" s="183" t="str">
-        <f>IF(ISNUMBER(CL39),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL39),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL39),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,8,CL39),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL39))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -12855,342 +12928,342 @@
     <row r="46" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="179"/>
       <c r="C46" s="159" t="str">
-        <f>IF(ISNUMBER(C45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D46" s="159" t="str">
-        <f>IF(ISNUMBER(C45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E46" s="159" t="str">
-        <f>IF(ISNUMBER(C45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F46" s="159" t="str">
-        <f>IF(ISNUMBER(F45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G46" s="159" t="str">
-        <f>IF(ISNUMBER(F45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H46" s="159" t="str">
-        <f>IF(ISNUMBER(F45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I46" s="159" t="str">
-        <f>IF(ISNUMBER(I45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J46" s="159" t="str">
-        <f>IF(ISNUMBER(I45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K46" s="159" t="str">
-        <f>IF(ISNUMBER(I45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L46" s="159" t="str">
-        <f>IF(ISNUMBER(L45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M46" s="159" t="str">
-        <f>IF(ISNUMBER(L45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N46" s="159" t="str">
-        <f>IF(ISNUMBER(L45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O46" s="159" t="str">
-        <f>IF(ISNUMBER(O45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P46" s="159" t="str">
-        <f>IF(ISNUMBER(O45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q46" s="159" t="str">
-        <f>IF(ISNUMBER(O45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R46" s="159" t="str">
-        <f>IF(ISNUMBER(R45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S46" s="159" t="str">
-        <f>IF(ISNUMBER(R45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T46" s="159" t="str">
-        <f>IF(ISNUMBER(R45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U46" s="159" t="str">
-        <f>IF(ISNUMBER(U45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V46" s="159" t="str">
-        <f>IF(ISNUMBER(U45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W46" s="180" t="str">
-        <f>IF(ISNUMBER(U45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y46" s="179"/>
       <c r="Z46" s="159" t="str">
-        <f>IF(ISNUMBER(Z45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA46" s="159" t="str">
-        <f>IF(ISNUMBER(Z45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB46" s="159" t="str">
-        <f>IF(ISNUMBER(Z45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC46" s="159" t="str">
-        <f>IF(ISNUMBER(AC45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD46" s="159" t="str">
-        <f>IF(ISNUMBER(AC45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE46" s="159" t="str">
-        <f>IF(ISNUMBER(AC45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF46" s="159" t="str">
-        <f>IF(ISNUMBER(AF45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG46" s="159" t="str">
-        <f>IF(ISNUMBER(AF45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH46" s="159" t="str">
-        <f>IF(ISNUMBER(AF45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI46" s="159" t="str">
-        <f>IF(ISNUMBER(AI45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ46" s="159" t="str">
-        <f>IF(ISNUMBER(AI45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK46" s="159" t="str">
-        <f>IF(ISNUMBER(AI45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL46" s="159" t="str">
-        <f>IF(ISNUMBER(AL45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM46" s="159" t="str">
-        <f>IF(ISNUMBER(AL45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN46" s="159" t="str">
-        <f>IF(ISNUMBER(AL45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO46" s="159" t="str">
-        <f>IF(ISNUMBER(AO45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP46" s="159" t="str">
-        <f>IF(ISNUMBER(AO45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ46" s="159" t="str">
-        <f>IF(ISNUMBER(AO45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR46" s="159" t="str">
-        <f>IF(ISNUMBER(AR45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="AS46" s="159" t="str">
-        <f>IF(ISNUMBER(AR45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="AT46" s="180" t="str">
-        <f>IF(ISNUMBER(AR45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR45))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="AV46" s="179"/>
       <c r="AW46" s="159" t="str">
-        <f>IF(ISNUMBER(AW45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AX46" s="159" t="str">
-        <f>IF(ISNUMBER(AW45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AY46" s="159" t="str">
-        <f>IF(ISNUMBER(AW45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW45))&gt;0,"h","")),"")</f>
         <v>h</v>
       </c>
       <c r="AZ46" s="159" t="str">
-        <f>IF(ISNUMBER(AZ45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA46" s="159" t="str">
-        <f>IF(ISNUMBER(AZ45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB46" s="159" t="str">
-        <f>IF(ISNUMBER(AZ45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC46" s="159" t="str">
-        <f>IF(ISNUMBER(BC45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD46" s="159" t="str">
-        <f>IF(ISNUMBER(BC45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE46" s="159" t="str">
-        <f>IF(ISNUMBER(BC45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF46" s="159" t="str">
-        <f>IF(ISNUMBER(BF45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG46" s="159" t="str">
-        <f>IF(ISNUMBER(BF45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH46" s="159" t="str">
-        <f>IF(ISNUMBER(BF45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI46" s="159" t="str">
-        <f>IF(ISNUMBER(BI45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ46" s="159" t="str">
-        <f>IF(ISNUMBER(BI45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK46" s="159" t="str">
-        <f>IF(ISNUMBER(BI45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL46" s="159" t="str">
-        <f>IF(ISNUMBER(BL45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM46" s="159" t="str">
-        <f>IF(ISNUMBER(BL45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN46" s="159" t="str">
-        <f>IF(ISNUMBER(BL45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO46" s="159" t="str">
-        <f>IF(ISNUMBER(BO45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP46" s="159" t="str">
-        <f>IF(ISNUMBER(BO45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ46" s="180" t="str">
-        <f>IF(ISNUMBER(BO45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS46" s="179"/>
       <c r="BT46" s="159" t="str">
-        <f>IF(ISNUMBER(BT45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU46" s="159" t="str">
-        <f>IF(ISNUMBER(BT45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV46" s="159" t="str">
-        <f>IF(ISNUMBER(BT45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW46" s="159" t="str">
-        <f>IF(ISNUMBER(BW45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX46" s="159" t="str">
-        <f>IF(ISNUMBER(BW45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY46" s="159" t="str">
-        <f>IF(ISNUMBER(BW45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ46" s="159" t="str">
-        <f>IF(ISNUMBER(BZ45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA46" s="159" t="str">
-        <f>IF(ISNUMBER(BZ45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB46" s="159" t="str">
-        <f>IF(ISNUMBER(BZ45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC46" s="159" t="str">
-        <f>IF(ISNUMBER(CC45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD46" s="159" t="str">
-        <f>IF(ISNUMBER(CC45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE46" s="159" t="str">
-        <f>IF(ISNUMBER(CC45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF46" s="159" t="str">
-        <f>IF(ISNUMBER(CF45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG46" s="159" t="str">
-        <f>IF(ISNUMBER(CF45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH46" s="159" t="str">
-        <f>IF(ISNUMBER(CF45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF45))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI46" s="159" t="str">
-        <f>IF(ISNUMBER(CI45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ46" s="159" t="str">
-        <f>IF(ISNUMBER(CI45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK46" s="159" t="str">
-        <f>IF(ISNUMBER(CI45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL46" s="159" t="str">
-        <f>IF(ISNUMBER(CL45),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL45),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL45),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM46" s="159" t="str">
-        <f>IF(ISNUMBER(CL45),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL45),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL45),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN46" s="180" t="str">
-        <f>IF(ISNUMBER(CL45),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL45),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL45),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL45))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -13383,342 +13456,342 @@
     <row r="48" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="179"/>
       <c r="C48" s="159" t="str">
-        <f>IF(ISNUMBER(C47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D48" s="159" t="str">
-        <f>IF(ISNUMBER(C47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E48" s="159" t="str">
-        <f>IF(ISNUMBER(C47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F48" s="159" t="str">
-        <f>IF(ISNUMBER(F47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G48" s="159" t="str">
-        <f>IF(ISNUMBER(F47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H48" s="159" t="str">
-        <f>IF(ISNUMBER(F47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I48" s="159" t="str">
-        <f>IF(ISNUMBER(I47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J48" s="159" t="str">
-        <f>IF(ISNUMBER(I47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K48" s="159" t="str">
-        <f>IF(ISNUMBER(I47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L48" s="159" t="str">
-        <f>IF(ISNUMBER(L47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M48" s="159" t="str">
-        <f>IF(ISNUMBER(L47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N48" s="159" t="str">
-        <f>IF(ISNUMBER(L47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O48" s="159" t="str">
-        <f>IF(ISNUMBER(O47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P48" s="159" t="str">
-        <f>IF(ISNUMBER(O47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q48" s="159" t="str">
-        <f>IF(ISNUMBER(O47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R48" s="159" t="str">
-        <f>IF(ISNUMBER(R47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="S48" s="159" t="str">
-        <f>IF(ISNUMBER(R47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T48" s="159" t="str">
-        <f>IF(ISNUMBER(R47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U48" s="159" t="str">
-        <f>IF(ISNUMBER(U47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V48" s="159" t="str">
-        <f>IF(ISNUMBER(U47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W48" s="180" t="str">
-        <f>IF(ISNUMBER(U47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y48" s="179"/>
       <c r="Z48" s="159" t="str">
-        <f>IF(ISNUMBER(Z47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA48" s="159" t="str">
-        <f>IF(ISNUMBER(Z47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB48" s="159" t="str">
-        <f>IF(ISNUMBER(Z47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC48" s="159" t="str">
-        <f>IF(ISNUMBER(AC47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD48" s="159" t="str">
-        <f>IF(ISNUMBER(AC47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE48" s="159" t="str">
-        <f>IF(ISNUMBER(AC47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF48" s="159" t="str">
-        <f>IF(ISNUMBER(AF47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG48" s="159" t="str">
-        <f>IF(ISNUMBER(AF47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH48" s="159" t="str">
-        <f>IF(ISNUMBER(AF47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI48" s="159" t="str">
-        <f>IF(ISNUMBER(AI47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ48" s="159" t="str">
-        <f>IF(ISNUMBER(AI47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK48" s="159" t="str">
-        <f>IF(ISNUMBER(AI47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL48" s="159" t="str">
-        <f>IF(ISNUMBER(AL47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM48" s="159" t="str">
-        <f>IF(ISNUMBER(AL47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN48" s="159" t="str">
-        <f>IF(ISNUMBER(AL47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL47))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="AO48" s="159" t="str">
-        <f>IF(ISNUMBER(AO47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP48" s="159" t="str">
-        <f>IF(ISNUMBER(AO47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ48" s="159" t="str">
-        <f>IF(ISNUMBER(AO47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR48" s="159" t="str">
-        <f>IF(ISNUMBER(AR47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS48" s="159" t="str">
-        <f>IF(ISNUMBER(AR47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT48" s="180" t="str">
-        <f>IF(ISNUMBER(AR47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV48" s="179"/>
       <c r="AW48" s="159" t="str">
-        <f>IF(ISNUMBER(AW47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX48" s="159" t="str">
-        <f>IF(ISNUMBER(AW47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY48" s="159" t="str">
-        <f>IF(ISNUMBER(AW47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ48" s="159" t="str">
-        <f>IF(ISNUMBER(AZ47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA48" s="159" t="str">
-        <f>IF(ISNUMBER(AZ47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB48" s="159" t="str">
-        <f>IF(ISNUMBER(AZ47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC48" s="159" t="str">
-        <f>IF(ISNUMBER(BC47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD48" s="159" t="str">
-        <f>IF(ISNUMBER(BC47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE48" s="159" t="str">
-        <f>IF(ISNUMBER(BC47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF48" s="159" t="str">
-        <f>IF(ISNUMBER(BF47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG48" s="159" t="str">
-        <f>IF(ISNUMBER(BF47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH48" s="159" t="str">
-        <f>IF(ISNUMBER(BF47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI48" s="159" t="str">
-        <f>IF(ISNUMBER(BI47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ48" s="159" t="str">
-        <f>IF(ISNUMBER(BI47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK48" s="159" t="str">
-        <f>IF(ISNUMBER(BI47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL48" s="159" t="str">
-        <f>IF(ISNUMBER(BL47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM48" s="159" t="str">
-        <f>IF(ISNUMBER(BL47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN48" s="159" t="str">
-        <f>IF(ISNUMBER(BL47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO48" s="159" t="str">
-        <f>IF(ISNUMBER(BO47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP48" s="159" t="str">
-        <f>IF(ISNUMBER(BO47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ48" s="180" t="str">
-        <f>IF(ISNUMBER(BO47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS48" s="179"/>
       <c r="BT48" s="159" t="str">
-        <f>IF(ISNUMBER(BT47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU48" s="159" t="str">
-        <f>IF(ISNUMBER(BT47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV48" s="159" t="str">
-        <f>IF(ISNUMBER(BT47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW48" s="159" t="str">
-        <f>IF(ISNUMBER(BW47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX48" s="159" t="str">
-        <f>IF(ISNUMBER(BW47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY48" s="159" t="str">
-        <f>IF(ISNUMBER(BW47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ48" s="159" t="str">
-        <f>IF(ISNUMBER(BZ47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA48" s="159" t="str">
-        <f>IF(ISNUMBER(BZ47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB48" s="159" t="str">
-        <f>IF(ISNUMBER(BZ47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC48" s="159" t="str">
-        <f>IF(ISNUMBER(CC47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD48" s="159" t="str">
-        <f>IF(ISNUMBER(CC47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE48" s="159" t="str">
-        <f>IF(ISNUMBER(CC47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF48" s="159" t="str">
-        <f>IF(ISNUMBER(CF47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG48" s="159" t="str">
-        <f>IF(ISNUMBER(CF47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH48" s="159" t="str">
-        <f>IF(ISNUMBER(CF47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF47))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="CI48" s="159" t="str">
-        <f>IF(ISNUMBER(CI47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ48" s="159" t="str">
-        <f>IF(ISNUMBER(CI47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK48" s="159" t="str">
-        <f>IF(ISNUMBER(CI47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL48" s="159" t="str">
-        <f>IF(ISNUMBER(CL47),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL47),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL47),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM48" s="159" t="str">
-        <f>IF(ISNUMBER(CL47),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL47),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL47),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN48" s="180" t="str">
-        <f>IF(ISNUMBER(CL47),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL47),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL47),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL47))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -13911,342 +13984,342 @@
     <row r="50" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="179"/>
       <c r="C50" s="159" t="str">
-        <f>IF(ISNUMBER(C49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D50" s="159" t="str">
-        <f>IF(ISNUMBER(C49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E50" s="159" t="str">
-        <f>IF(ISNUMBER(C49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F50" s="159" t="str">
-        <f>IF(ISNUMBER(F49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G50" s="159" t="str">
-        <f>IF(ISNUMBER(F49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H50" s="159" t="str">
-        <f>IF(ISNUMBER(F49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I50" s="159" t="str">
-        <f>IF(ISNUMBER(I49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J50" s="159" t="str">
-        <f>IF(ISNUMBER(I49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K50" s="159" t="str">
-        <f>IF(ISNUMBER(I49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L50" s="159" t="str">
-        <f>IF(ISNUMBER(L49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M50" s="159" t="str">
-        <f>IF(ISNUMBER(L49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N50" s="159" t="str">
-        <f>IF(ISNUMBER(L49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O50" s="159" t="str">
-        <f>IF(ISNUMBER(O49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P50" s="159" t="str">
-        <f>IF(ISNUMBER(O49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q50" s="159" t="str">
-        <f>IF(ISNUMBER(O49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R50" s="159" t="str">
-        <f>IF(ISNUMBER(R49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="S50" s="159" t="str">
-        <f>IF(ISNUMBER(R49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T50" s="159" t="str">
-        <f>IF(ISNUMBER(R49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U50" s="159" t="str">
-        <f>IF(ISNUMBER(U49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V50" s="159" t="str">
-        <f>IF(ISNUMBER(U49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W50" s="180" t="str">
-        <f>IF(ISNUMBER(U49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y50" s="179"/>
       <c r="Z50" s="159" t="str">
-        <f>IF(ISNUMBER(Z49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA50" s="159" t="str">
-        <f>IF(ISNUMBER(Z49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB50" s="159" t="str">
-        <f>IF(ISNUMBER(Z49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC50" s="159" t="str">
-        <f>IF(ISNUMBER(AC49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD50" s="159" t="str">
-        <f>IF(ISNUMBER(AC49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE50" s="159" t="str">
-        <f>IF(ISNUMBER(AC49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF50" s="159" t="str">
-        <f>IF(ISNUMBER(AF49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG50" s="159" t="str">
-        <f>IF(ISNUMBER(AF49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="AH50" s="159" t="str">
-        <f>IF(ISNUMBER(AF49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI50" s="159" t="str">
-        <f>IF(ISNUMBER(AI49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ50" s="159" t="str">
-        <f>IF(ISNUMBER(AI49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK50" s="159" t="str">
-        <f>IF(ISNUMBER(AI49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL50" s="159" t="str">
-        <f>IF(ISNUMBER(AL49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM50" s="159" t="str">
-        <f>IF(ISNUMBER(AL49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN50" s="159" t="str">
-        <f>IF(ISNUMBER(AL49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO50" s="159" t="str">
-        <f>IF(ISNUMBER(AO49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP50" s="159" t="str">
-        <f>IF(ISNUMBER(AO49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ50" s="159" t="str">
-        <f>IF(ISNUMBER(AO49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR50" s="159" t="str">
-        <f>IF(ISNUMBER(AR49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS50" s="159" t="str">
-        <f>IF(ISNUMBER(AR49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT50" s="180" t="str">
-        <f>IF(ISNUMBER(AR49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV50" s="179"/>
       <c r="AW50" s="159" t="str">
-        <f>IF(ISNUMBER(AW49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX50" s="159" t="str">
-        <f>IF(ISNUMBER(AW49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY50" s="159" t="str">
-        <f>IF(ISNUMBER(AW49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ50" s="159" t="str">
-        <f>IF(ISNUMBER(AZ49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA50" s="159" t="str">
-        <f>IF(ISNUMBER(AZ49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB50" s="159" t="str">
-        <f>IF(ISNUMBER(AZ49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC50" s="159" t="str">
-        <f>IF(ISNUMBER(BC49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD50" s="159" t="str">
-        <f>IF(ISNUMBER(BC49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE50" s="159" t="str">
-        <f>IF(ISNUMBER(BC49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF50" s="159" t="str">
-        <f>IF(ISNUMBER(BF49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG50" s="159" t="str">
-        <f>IF(ISNUMBER(BF49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH50" s="159" t="str">
-        <f>IF(ISNUMBER(BF49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI50" s="159" t="str">
-        <f>IF(ISNUMBER(BI49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ50" s="159" t="str">
-        <f>IF(ISNUMBER(BI49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK50" s="159" t="str">
-        <f>IF(ISNUMBER(BI49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL50" s="159" t="str">
-        <f>IF(ISNUMBER(BL49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM50" s="159" t="str">
-        <f>IF(ISNUMBER(BL49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN50" s="159" t="str">
-        <f>IF(ISNUMBER(BL49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO50" s="159" t="str">
-        <f>IF(ISNUMBER(BO49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP50" s="159" t="str">
-        <f>IF(ISNUMBER(BO49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ50" s="180" t="str">
-        <f>IF(ISNUMBER(BO49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS50" s="179"/>
       <c r="BT50" s="159" t="str">
-        <f>IF(ISNUMBER(BT49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU50" s="159" t="str">
-        <f>IF(ISNUMBER(BT49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV50" s="159" t="str">
-        <f>IF(ISNUMBER(BT49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW50" s="159" t="str">
-        <f>IF(ISNUMBER(BW49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX50" s="159" t="str">
-        <f>IF(ISNUMBER(BW49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY50" s="159" t="str">
-        <f>IF(ISNUMBER(BW49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ50" s="159" t="str">
-        <f>IF(ISNUMBER(BZ49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA50" s="159" t="str">
-        <f>IF(ISNUMBER(BZ49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB50" s="159" t="str">
-        <f>IF(ISNUMBER(BZ49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC50" s="159" t="str">
-        <f>IF(ISNUMBER(CC49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD50" s="159" t="str">
-        <f>IF(ISNUMBER(CC49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE50" s="159" t="str">
-        <f>IF(ISNUMBER(CC49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF50" s="159" t="str">
-        <f>IF(ISNUMBER(CF49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG50" s="159" t="str">
-        <f>IF(ISNUMBER(CF49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH50" s="159" t="str">
-        <f>IF(ISNUMBER(CF49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF49))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI50" s="159" t="str">
-        <f>IF(ISNUMBER(CI49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CJ50" s="159" t="str">
-        <f>IF(ISNUMBER(CI49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CK50" s="159" t="str">
-        <f>IF(ISNUMBER(CI49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CL50" s="159" t="str">
-        <f>IF(ISNUMBER(CL49),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL49),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL49),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CM50" s="159" t="str">
-        <f>IF(ISNUMBER(CL49),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL49),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL49),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="CN50" s="180" t="str">
-        <f>IF(ISNUMBER(CL49),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL49),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL49),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL49))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
     </row>
@@ -14439,342 +14512,342 @@
     <row r="52" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="179"/>
       <c r="C52" s="159" t="str">
-        <f>IF(ISNUMBER(C51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D52" s="159" t="str">
-        <f>IF(ISNUMBER(C51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E52" s="159" t="str">
-        <f>IF(ISNUMBER(C51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F52" s="159" t="str">
-        <f>IF(ISNUMBER(F51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G52" s="159" t="str">
-        <f>IF(ISNUMBER(F51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H52" s="159" t="str">
-        <f>IF(ISNUMBER(F51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I52" s="159" t="str">
-        <f>IF(ISNUMBER(I51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J52" s="159" t="str">
-        <f>IF(ISNUMBER(I51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K52" s="159" t="str">
-        <f>IF(ISNUMBER(I51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L52" s="159" t="str">
-        <f>IF(ISNUMBER(L51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M52" s="159" t="str">
-        <f>IF(ISNUMBER(L51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N52" s="159" t="str">
-        <f>IF(ISNUMBER(L51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O52" s="159" t="str">
-        <f>IF(ISNUMBER(O51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P52" s="159" t="str">
-        <f>IF(ISNUMBER(O51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q52" s="159" t="str">
-        <f>IF(ISNUMBER(O51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O51))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="R52" s="159" t="str">
-        <f>IF(ISNUMBER(R51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
         <v>S</v>
       </c>
       <c r="S52" s="159" t="str">
-        <f>IF(ISNUMBER(R51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="T52" s="159" t="str">
-        <f>IF(ISNUMBER(R51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="U52" s="159" t="str">
-        <f>IF(ISNUMBER(U51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="V52" s="159" t="str">
-        <f>IF(ISNUMBER(U51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="W52" s="180" t="str">
-        <f>IF(ISNUMBER(U51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="Y52" s="179"/>
       <c r="Z52" s="159" t="str">
-        <f>IF(ISNUMBER(Z51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA52" s="159" t="str">
-        <f>IF(ISNUMBER(Z51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB52" s="159" t="str">
-        <f>IF(ISNUMBER(Z51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC52" s="159" t="str">
-        <f>IF(ISNUMBER(AC51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD52" s="159" t="str">
-        <f>IF(ISNUMBER(AC51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE52" s="159" t="str">
-        <f>IF(ISNUMBER(AC51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF52" s="159" t="str">
-        <f>IF(ISNUMBER(AF51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG52" s="159" t="str">
-        <f>IF(ISNUMBER(AF51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH52" s="159" t="str">
-        <f>IF(ISNUMBER(AF51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI52" s="159" t="str">
-        <f>IF(ISNUMBER(AI51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ52" s="159" t="str">
-        <f>IF(ISNUMBER(AI51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK52" s="159" t="str">
-        <f>IF(ISNUMBER(AI51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL52" s="159" t="str">
-        <f>IF(ISNUMBER(AL51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM52" s="159" t="str">
-        <f>IF(ISNUMBER(AL51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN52" s="159" t="str">
-        <f>IF(ISNUMBER(AL51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL51))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="AO52" s="159" t="str">
-        <f>IF(ISNUMBER(AO51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP52" s="159" t="str">
-        <f>IF(ISNUMBER(AO51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ52" s="159" t="str">
-        <f>IF(ISNUMBER(AO51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR52" s="159" t="str">
-        <f>IF(ISNUMBER(AR51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS52" s="159" t="str">
-        <f>IF(ISNUMBER(AR51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT52" s="180" t="str">
-        <f>IF(ISNUMBER(AR51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV52" s="179"/>
       <c r="AW52" s="159" t="str">
-        <f>IF(ISNUMBER(AW51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX52" s="159" t="str">
-        <f>IF(ISNUMBER(AW51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY52" s="159" t="str">
-        <f>IF(ISNUMBER(AW51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ52" s="159" t="str">
-        <f>IF(ISNUMBER(AZ51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA52" s="159" t="str">
-        <f>IF(ISNUMBER(AZ51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB52" s="159" t="str">
-        <f>IF(ISNUMBER(AZ51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC52" s="159" t="str">
-        <f>IF(ISNUMBER(BC51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD52" s="159" t="str">
-        <f>IF(ISNUMBER(BC51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE52" s="159" t="str">
-        <f>IF(ISNUMBER(BC51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF52" s="159" t="str">
-        <f>IF(ISNUMBER(BF51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG52" s="159" t="str">
-        <f>IF(ISNUMBER(BF51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH52" s="159" t="str">
-        <f>IF(ISNUMBER(BF51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI52" s="159" t="str">
-        <f>IF(ISNUMBER(BI51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ52" s="159" t="str">
-        <f>IF(ISNUMBER(BI51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK52" s="159" t="str">
-        <f>IF(ISNUMBER(BI51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI51))&gt;0,"h","")),"")</f>
         <v>P</v>
       </c>
       <c r="BL52" s="159" t="str">
-        <f>IF(ISNUMBER(BL51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BM52" s="159" t="str">
-        <f>IF(ISNUMBER(BL51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BN52" s="159" t="str">
-        <f>IF(ISNUMBER(BL51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BO52" s="159" t="str">
-        <f>IF(ISNUMBER(BO51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BP52" s="159" t="str">
-        <f>IF(ISNUMBER(BO51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BQ52" s="180" t="str">
-        <f>IF(ISNUMBER(BO51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO51))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="BS52" s="179"/>
       <c r="BT52" s="159" t="str">
-        <f>IF(ISNUMBER(BT51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU52" s="159" t="str">
-        <f>IF(ISNUMBER(BT51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV52" s="159" t="str">
-        <f>IF(ISNUMBER(BT51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW52" s="159" t="str">
-        <f>IF(ISNUMBER(BW51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX52" s="159" t="str">
-        <f>IF(ISNUMBER(BW51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY52" s="159" t="str">
-        <f>IF(ISNUMBER(BW51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ52" s="159" t="str">
-        <f>IF(ISNUMBER(BZ51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA52" s="159" t="str">
-        <f>IF(ISNUMBER(BZ51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB52" s="159" t="str">
-        <f>IF(ISNUMBER(BZ51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC52" s="159" t="str">
-        <f>IF(ISNUMBER(CC51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD52" s="159" t="str">
-        <f>IF(ISNUMBER(CC51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE52" s="159" t="str">
-        <f>IF(ISNUMBER(CC51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF52" s="159" t="str">
-        <f>IF(ISNUMBER(CF51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG52" s="159" t="str">
-        <f>IF(ISNUMBER(CF51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH52" s="159" t="str">
-        <f>IF(ISNUMBER(CF51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF51))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI52" s="159" t="str">
-        <f>IF(ISNUMBER(CI51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CJ52" s="159" t="str">
-        <f>IF(ISNUMBER(CI51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CK52" s="159" t="str">
-        <f>IF(ISNUMBER(CI51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CL52" s="159" t="str">
-        <f>IF(ISNUMBER(CL51),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL51),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL51),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CM52" s="159" t="str">
-        <f>IF(ISNUMBER(CL51),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL51),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL51),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
       <c r="CN52" s="180" t="str">
-        <f>IF(ISNUMBER(CL51),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL51),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL51),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL51))&gt;0,"h","w")),"")</f>
         <v>h</v>
       </c>
     </row>
@@ -14967,342 +15040,342 @@
     <row r="54" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="179"/>
       <c r="C54" s="159" t="str">
-        <f>IF(ISNUMBER(C53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D54" s="159" t="str">
-        <f>IF(ISNUMBER(C53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E54" s="159" t="str">
-        <f>IF(ISNUMBER(C53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F54" s="159" t="str">
-        <f>IF(ISNUMBER(F53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G54" s="159" t="str">
-        <f>IF(ISNUMBER(F53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H54" s="159" t="str">
-        <f>IF(ISNUMBER(F53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I54" s="159" t="str">
-        <f>IF(ISNUMBER(I53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J54" s="159" t="str">
-        <f>IF(ISNUMBER(I53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
         <v>I</v>
       </c>
       <c r="K54" s="159" t="str">
-        <f>IF(ISNUMBER(I53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L54" s="159" t="str">
-        <f>IF(ISNUMBER(L53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M54" s="159" t="str">
-        <f>IF(ISNUMBER(L53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N54" s="159" t="str">
-        <f>IF(ISNUMBER(L53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O54" s="159" t="str">
-        <f>IF(ISNUMBER(O53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P54" s="159" t="str">
-        <f>IF(ISNUMBER(O53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q54" s="159" t="str">
-        <f>IF(ISNUMBER(O53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R54" s="159" t="str">
-        <f>IF(ISNUMBER(R53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S54" s="159" t="str">
-        <f>IF(ISNUMBER(R53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T54" s="159" t="str">
-        <f>IF(ISNUMBER(R53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U54" s="159" t="str">
-        <f>IF(ISNUMBER(U53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V54" s="159" t="str">
-        <f>IF(ISNUMBER(U53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W54" s="180" t="str">
-        <f>IF(ISNUMBER(U53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y54" s="179"/>
       <c r="Z54" s="159" t="str">
-        <f>IF(ISNUMBER(Z53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA54" s="159" t="str">
-        <f>IF(ISNUMBER(Z53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB54" s="159" t="str">
-        <f>IF(ISNUMBER(Z53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC54" s="159" t="str">
-        <f>IF(ISNUMBER(AC53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD54" s="159" t="str">
-        <f>IF(ISNUMBER(AC53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE54" s="159" t="str">
-        <f>IF(ISNUMBER(AC53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF54" s="159" t="str">
-        <f>IF(ISNUMBER(AF53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG54" s="159" t="str">
-        <f>IF(ISNUMBER(AF53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH54" s="159" t="str">
-        <f>IF(ISNUMBER(AF53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI54" s="159" t="str">
-        <f>IF(ISNUMBER(AI53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ54" s="159" t="str">
-        <f>IF(ISNUMBER(AI53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK54" s="159" t="str">
-        <f>IF(ISNUMBER(AI53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL54" s="159" t="str">
-        <f>IF(ISNUMBER(AL53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM54" s="159" t="str">
-        <f>IF(ISNUMBER(AL53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN54" s="159" t="str">
-        <f>IF(ISNUMBER(AL53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO54" s="159" t="str">
-        <f>IF(ISNUMBER(AO53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AP54" s="159" t="str">
-        <f>IF(ISNUMBER(AO53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AQ54" s="159" t="str">
-        <f>IF(ISNUMBER(AO53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AR54" s="159" t="str">
-        <f>IF(ISNUMBER(AR53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AS54" s="159" t="str">
-        <f>IF(ISNUMBER(AR53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AT54" s="180" t="str">
-        <f>IF(ISNUMBER(AR53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR53))&gt;0,"h","w")),"")</f>
         <v>w</v>
       </c>
       <c r="AV54" s="179"/>
       <c r="AW54" s="159" t="str">
-        <f>IF(ISNUMBER(AW53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX54" s="159" t="str">
-        <f>IF(ISNUMBER(AW53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY54" s="159" t="str">
-        <f>IF(ISNUMBER(AW53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ54" s="159" t="str">
-        <f>IF(ISNUMBER(AZ53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA54" s="159" t="str">
-        <f>IF(ISNUMBER(AZ53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB54" s="159" t="str">
-        <f>IF(ISNUMBER(AZ53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC54" s="159" t="str">
-        <f>IF(ISNUMBER(BC53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD54" s="159" t="str">
-        <f>IF(ISNUMBER(BC53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE54" s="159" t="str">
-        <f>IF(ISNUMBER(BC53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF54" s="159" t="str">
-        <f>IF(ISNUMBER(BF53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG54" s="159" t="str">
-        <f>IF(ISNUMBER(BF53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH54" s="159" t="str">
-        <f>IF(ISNUMBER(BF53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI54" s="159" t="str">
-        <f>IF(ISNUMBER(BI53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ54" s="159" t="str">
-        <f>IF(ISNUMBER(BI53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK54" s="159" t="str">
-        <f>IF(ISNUMBER(BI53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL54" s="159" t="str">
-        <f>IF(ISNUMBER(BL53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM54" s="159" t="str">
-        <f>IF(ISNUMBER(BL53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN54" s="159" t="str">
-        <f>IF(ISNUMBER(BL53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO54" s="159" t="str">
-        <f>IF(ISNUMBER(BO53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP54" s="159" t="str">
-        <f>IF(ISNUMBER(BO53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ54" s="180" t="str">
-        <f>IF(ISNUMBER(BO53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS54" s="179"/>
       <c r="BT54" s="159" t="str">
-        <f>IF(ISNUMBER(BT53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU54" s="159" t="str">
-        <f>IF(ISNUMBER(BT53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV54" s="159" t="str">
-        <f>IF(ISNUMBER(BT53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW54" s="159" t="str">
-        <f>IF(ISNUMBER(BW53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX54" s="159" t="str">
-        <f>IF(ISNUMBER(BW53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY54" s="159" t="str">
-        <f>IF(ISNUMBER(BW53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ54" s="159" t="str">
-        <f>IF(ISNUMBER(BZ53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA54" s="159" t="str">
-        <f>IF(ISNUMBER(BZ53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB54" s="159" t="str">
-        <f>IF(ISNUMBER(BZ53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC54" s="159" t="str">
-        <f>IF(ISNUMBER(CC53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD54" s="159" t="str">
-        <f>IF(ISNUMBER(CC53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE54" s="159" t="str">
-        <f>IF(ISNUMBER(CC53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF54" s="159" t="str">
-        <f>IF(ISNUMBER(CF53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG54" s="159" t="str">
-        <f>IF(ISNUMBER(CF53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH54" s="159" t="str">
-        <f>IF(ISNUMBER(CF53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF53))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI54" s="159" t="str">
-        <f>IF(ISNUMBER(CI53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ54" s="159" t="str">
-        <f>IF(ISNUMBER(CI53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK54" s="159" t="str">
-        <f>IF(ISNUMBER(CI53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL54" s="159" t="str">
-        <f>IF(ISNUMBER(CL53),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL53),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL53),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM54" s="159" t="str">
-        <f>IF(ISNUMBER(CL53),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL53),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL53),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN54" s="180" t="str">
-        <f>IF(ISNUMBER(CL53),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL53),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL53),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL53))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -15495,342 +15568,342 @@
     <row r="56" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="181"/>
       <c r="C56" s="182" t="str">
-        <f>IF(ISNUMBER(C55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,C55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="D56" s="182" t="str">
-        <f>IF(ISNUMBER(C55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,C55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="E56" s="182" t="str">
-        <f>IF(ISNUMBER(C55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(C55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,C55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,C55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="F56" s="182" t="str">
-        <f>IF(ISNUMBER(F55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,F55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="G56" s="182" t="str">
-        <f>IF(ISNUMBER(F55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,F55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="H56" s="182" t="str">
-        <f>IF(ISNUMBER(F55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(F55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,F55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,F55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="I56" s="182" t="str">
-        <f>IF(ISNUMBER(I55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,I55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="J56" s="182" t="str">
-        <f>IF(ISNUMBER(I55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,I55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="K56" s="182" t="str">
-        <f>IF(ISNUMBER(I55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(I55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,I55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,I55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="L56" s="182" t="str">
-        <f>IF(ISNUMBER(L55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,L55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="M56" s="182" t="str">
-        <f>IF(ISNUMBER(L55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,L55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="N56" s="182" t="str">
-        <f>IF(ISNUMBER(L55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(L55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,L55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,L55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="O56" s="182" t="str">
-        <f>IF(ISNUMBER(O55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,O55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="P56" s="182" t="str">
-        <f>IF(ISNUMBER(O55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,O55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="Q56" s="182" t="str">
-        <f>IF(ISNUMBER(O55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(O55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,O55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,O55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="R56" s="182" t="str">
-        <f>IF(ISNUMBER(R55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,R55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="S56" s="182" t="str">
-        <f>IF(ISNUMBER(R55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,R55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="T56" s="182" t="str">
-        <f>IF(ISNUMBER(R55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,R55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,R55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="U56" s="182" t="str">
-        <f>IF(ISNUMBER(U55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,9,U55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="V56" s="182" t="str">
-        <f>IF(ISNUMBER(U55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,9,U55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="W56" s="183" t="str">
-        <f>IF(ISNUMBER(U55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,9,U55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,9,U55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="Y56" s="181"/>
       <c r="Z56" s="182" t="str">
-        <f>IF(ISNUMBER(Z55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,Z55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AA56" s="182" t="str">
-        <f>IF(ISNUMBER(Z55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,Z55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AB56" s="182" t="str">
-        <f>IF(ISNUMBER(Z55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(Z55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,Z55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,Z55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AC56" s="182" t="str">
-        <f>IF(ISNUMBER(AC55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AC55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AD56" s="182" t="str">
-        <f>IF(ISNUMBER(AC55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AC55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AE56" s="182" t="str">
-        <f>IF(ISNUMBER(AC55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AC55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AC55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AF56" s="182" t="str">
-        <f>IF(ISNUMBER(AF55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AF55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AG56" s="182" t="str">
-        <f>IF(ISNUMBER(AF55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AF55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AH56" s="182" t="str">
-        <f>IF(ISNUMBER(AF55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AF55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AF55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AI56" s="182" t="str">
-        <f>IF(ISNUMBER(AI55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AI55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AJ56" s="182" t="str">
-        <f>IF(ISNUMBER(AI55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AI55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AK56" s="182" t="str">
-        <f>IF(ISNUMBER(AI55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AI55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AI55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AL56" s="182" t="str">
-        <f>IF(ISNUMBER(AL55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AL55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AM56" s="182" t="str">
-        <f>IF(ISNUMBER(AL55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AL55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AN56" s="182" t="str">
-        <f>IF(ISNUMBER(AL55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AL55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AL55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AL55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AO56" s="182" t="str">
-        <f>IF(ISNUMBER(AO55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AO55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AP56" s="182" t="str">
-        <f>IF(ISNUMBER(AO55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AO55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AQ56" s="182" t="str">
-        <f>IF(ISNUMBER(AO55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AO55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AR56" s="182" t="str">
-        <f>IF(ISNUMBER(AR55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,10,AR55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AS56" s="182" t="str">
-        <f>IF(ISNUMBER(AR55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,10,AR55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AT56" s="183" t="str">
-        <f>IF(ISNUMBER(AR55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,10,AR55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,10,AR55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="AV56" s="181"/>
       <c r="AW56" s="182" t="str">
-        <f>IF(ISNUMBER(AW55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AW55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AX56" s="182" t="str">
-        <f>IF(ISNUMBER(AW55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AW55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AY56" s="182" t="str">
-        <f>IF(ISNUMBER(AW55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AW55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AW55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="AZ56" s="182" t="str">
-        <f>IF(ISNUMBER(AZ55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,AZ55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BA56" s="182" t="str">
-        <f>IF(ISNUMBER(AZ55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,AZ55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BB56" s="182" t="str">
-        <f>IF(ISNUMBER(AZ55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(AZ55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,AZ55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,AZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BC56" s="182" t="str">
-        <f>IF(ISNUMBER(BC55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BC55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BD56" s="182" t="str">
-        <f>IF(ISNUMBER(BC55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BC55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BE56" s="182" t="str">
-        <f>IF(ISNUMBER(BC55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BC55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BC55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BF56" s="182" t="str">
-        <f>IF(ISNUMBER(BF55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BF55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BG56" s="182" t="str">
-        <f>IF(ISNUMBER(BF55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BF55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BH56" s="182" t="str">
-        <f>IF(ISNUMBER(BF55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BF55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BF55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BI56" s="182" t="str">
-        <f>IF(ISNUMBER(BI55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BI55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BJ56" s="182" t="str">
-        <f>IF(ISNUMBER(BI55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BI55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BK56" s="182" t="str">
-        <f>IF(ISNUMBER(BI55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BI55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BI55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BI55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BL56" s="182" t="str">
-        <f>IF(ISNUMBER(BL55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BL55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BM56" s="182" t="str">
-        <f>IF(ISNUMBER(BL55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BL55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BN56" s="182" t="str">
-        <f>IF(ISNUMBER(BL55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BL55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BO56" s="182" t="str">
-        <f>IF(ISNUMBER(BO55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,11,BO55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BP56" s="182" t="str">
-        <f>IF(ISNUMBER(BO55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,11,BO55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BQ56" s="183" t="str">
-        <f>IF(ISNUMBER(BO55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,11,BO55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,11,BO55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="BS56" s="181"/>
       <c r="BT56" s="182" t="str">
-        <f>IF(ISNUMBER(BT55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BT55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BU56" s="182" t="str">
-        <f>IF(ISNUMBER(BT55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BT55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BV56" s="182" t="str">
-        <f>IF(ISNUMBER(BT55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BT55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BT55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BT55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BW56" s="182" t="str">
-        <f>IF(ISNUMBER(BW55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BW55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BX56" s="182" t="str">
-        <f>IF(ISNUMBER(BW55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BW55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BY56" s="182" t="str">
-        <f>IF(ISNUMBER(BW55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BW55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BW55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BW55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="BZ56" s="182" t="str">
-        <f>IF(ISNUMBER(BZ55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,BZ55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CA56" s="182" t="str">
-        <f>IF(ISNUMBER(BZ55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,BZ55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CB56" s="182" t="str">
-        <f>IF(ISNUMBER(BZ55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(BZ55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,BZ55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,BZ55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CC56" s="182" t="str">
-        <f>IF(ISNUMBER(CC55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CC55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CD56" s="182" t="str">
-        <f>IF(ISNUMBER(CC55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CC55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CE56" s="182" t="str">
-        <f>IF(ISNUMBER(CC55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CC55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CC55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CC55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CF56" s="182" t="str">
-        <f>IF(ISNUMBER(CF55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CF55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CG56" s="182" t="str">
-        <f>IF(ISNUMBER(CF55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CF55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CH56" s="182" t="str">
-        <f>IF(ISNUMBER(CF55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
+        <f>IF(ISNUMBER(CF55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CF55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CF55))&gt;0,"h","")),"")</f>
         <v/>
       </c>
       <c r="CI56" s="182" t="str">
-        <f>IF(ISNUMBER(CI55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CI55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CJ56" s="182" t="str">
-        <f>IF(ISNUMBER(CI55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CI55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CK56" s="182" t="str">
-        <f>IF(ISNUMBER(CI55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CI55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CI55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CL56" s="182" t="str">
-        <f>IF(ISNUMBER(CL55),IF(COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL55),JP_ShowSel,TRUE)&gt;0,"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL55),IF(AND(Anzeige_S,COUNTIFS(JP_StartSel,DATE(Planungsjahr,12,CL55),JP_Anzeige,TRUE)&gt;0),"S",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CM56" s="182" t="str">
-        <f>IF(ISNUMBER(CL55),IF(COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL55),JP_ShowInhalt,TRUE)&gt;0,"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL55),IF(AND(Anzeige_I,COUNTIFS(JP_StartInhalt,DATE(Planungsjahr,12,CL55),JP_Anzeige,TRUE)&gt;0),"I",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
       <c r="CN56" s="183" t="str">
-        <f>IF(ISNUMBER(CL55),IF(COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL55),JP_ShowPAL,TRUE)&gt;0,"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL55),IF(AND(Anzeige_P,COUNTIFS(JP_PAL,DATE(Planungsjahr,12,CL55),JP_Anzeige,TRUE)&gt;0),"P",IF(COUNTIF(Feiertage,DATE(Planungsjahr,12,CL55))&gt;0,"h","w")),"")</f>
         <v/>
       </c>
     </row>
@@ -16056,15 +16129,9 @@
       <c r="P61" s="127"/>
       <c r="Q61" s="127"/>
       <c r="R61" s="127"/>
-      <c r="S61" s="129" t="s">
-        <v>154</v>
-      </c>
-      <c r="T61" s="131" t="s">
-        <v>155</v>
-      </c>
-      <c r="U61" s="133" t="s">
-        <v>156</v>
-      </c>
+      <c r="S61" s="127"/>
+      <c r="T61" s="127"/>
+      <c r="U61" s="127"/>
       <c r="V61" s="128" t="s">
         <v>82</v>
       </c>
@@ -16153,7 +16220,10 @@
       <c r="CM61" s="127"/>
       <c r="CN61" s="127"/>
     </row>
-    <row r="62" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B62" s="134" t="s">
         <v>86</v>
       </c>
@@ -16173,15 +16243,9 @@
       <c r="P62" s="134"/>
       <c r="Q62" s="134"/>
       <c r="R62" s="134"/>
-      <c r="S62" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T62" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U62" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S62" s="134"/>
+      <c r="T62" s="134"/>
+      <c r="U62" s="134"/>
       <c r="V62" s="135"/>
       <c r="W62" s="135"/>
       <c r="X62" s="135"/>
@@ -16268,7 +16332,10 @@
       <c r="CM62" s="140"/>
       <c r="CN62" s="140"/>
     </row>
-    <row r="63" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B63" s="134" t="s">
         <v>88</v>
       </c>
@@ -16288,15 +16355,9 @@
       <c r="P63" s="134"/>
       <c r="Q63" s="134"/>
       <c r="R63" s="134"/>
-      <c r="S63" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T63" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U63" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S63" s="134"/>
+      <c r="T63" s="134"/>
+      <c r="U63" s="134"/>
       <c r="V63" s="135"/>
       <c r="W63" s="135"/>
       <c r="X63" s="135"/>
@@ -16383,7 +16444,10 @@
       <c r="CM63" s="140"/>
       <c r="CN63" s="140"/>
     </row>
-    <row r="64" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B64" s="134" t="s">
         <v>89</v>
       </c>
@@ -16403,15 +16467,9 @@
       <c r="P64" s="134"/>
       <c r="Q64" s="134"/>
       <c r="R64" s="134"/>
-      <c r="S64" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T64" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U64" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S64" s="134"/>
+      <c r="T64" s="134"/>
+      <c r="U64" s="134"/>
       <c r="V64" s="135"/>
       <c r="W64" s="135"/>
       <c r="X64" s="135"/>
@@ -16498,7 +16556,10 @@
       <c r="CM64" s="140"/>
       <c r="CN64" s="140"/>
     </row>
-    <row r="65" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B65" s="134" t="s">
         <v>54</v>
       </c>
@@ -16518,15 +16579,9 @@
       <c r="P65" s="134"/>
       <c r="Q65" s="134"/>
       <c r="R65" s="134"/>
-      <c r="S65" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T65" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U65" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S65" s="134"/>
+      <c r="T65" s="134"/>
+      <c r="U65" s="134"/>
       <c r="V65" s="135"/>
       <c r="W65" s="135"/>
       <c r="X65" s="135"/>
@@ -16617,7 +16672,10 @@
       <c r="CM65" s="140"/>
       <c r="CN65" s="140"/>
     </row>
-    <row r="66" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B66" s="134" t="s">
         <v>92</v>
       </c>
@@ -16637,15 +16695,9 @@
       <c r="P66" s="134"/>
       <c r="Q66" s="134"/>
       <c r="R66" s="134"/>
-      <c r="S66" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T66" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U66" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S66" s="134"/>
+      <c r="T66" s="134"/>
+      <c r="U66" s="134"/>
       <c r="V66" s="135"/>
       <c r="W66" s="135"/>
       <c r="X66" s="135"/>
@@ -16732,7 +16784,10 @@
       <c r="CM66" s="140"/>
       <c r="CN66" s="140"/>
     </row>
-    <row r="67" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B67" s="134" t="s">
         <v>93</v>
       </c>
@@ -16752,15 +16807,9 @@
       <c r="P67" s="134"/>
       <c r="Q67" s="134"/>
       <c r="R67" s="134"/>
-      <c r="S67" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T67" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U67" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S67" s="134"/>
+      <c r="T67" s="134"/>
+      <c r="U67" s="134"/>
       <c r="V67" s="135"/>
       <c r="W67" s="135"/>
       <c r="X67" s="135"/>
@@ -16847,7 +16896,10 @@
       <c r="CM67" s="140"/>
       <c r="CN67" s="140"/>
     </row>
-    <row r="68" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B68" s="134" t="s">
         <v>150</v>
       </c>
@@ -16867,15 +16919,9 @@
       <c r="P68" s="134"/>
       <c r="Q68" s="134"/>
       <c r="R68" s="134"/>
-      <c r="S68" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T68" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U68" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S68" s="134"/>
+      <c r="T68" s="134"/>
+      <c r="U68" s="134"/>
       <c r="V68" s="135"/>
       <c r="W68" s="135"/>
       <c r="X68" s="135"/>
@@ -16964,7 +17010,10 @@
       <c r="CM68" s="140"/>
       <c r="CN68" s="140"/>
     </row>
-    <row r="69" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B69" s="134" t="s">
         <v>151</v>
       </c>
@@ -16984,15 +17033,9 @@
       <c r="P69" s="134"/>
       <c r="Q69" s="134"/>
       <c r="R69" s="134"/>
-      <c r="S69" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T69" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U69" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S69" s="134"/>
+      <c r="T69" s="134"/>
+      <c r="U69" s="134"/>
       <c r="V69" s="135"/>
       <c r="W69" s="135"/>
       <c r="X69" s="135"/>
@@ -17079,7 +17122,10 @@
       <c r="CM69" s="140"/>
       <c r="CN69" s="140"/>
     </row>
-    <row r="70" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B70" s="134" t="s">
         <v>55</v>
       </c>
@@ -17099,15 +17145,9 @@
       <c r="P70" s="134"/>
       <c r="Q70" s="134"/>
       <c r="R70" s="134"/>
-      <c r="S70" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T70" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U70" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S70" s="134"/>
+      <c r="T70" s="134"/>
+      <c r="U70" s="134"/>
       <c r="V70" s="135"/>
       <c r="W70" s="135"/>
       <c r="X70" s="135"/>
@@ -17198,7 +17238,10 @@
       <c r="CM70" s="140"/>
       <c r="CN70" s="140"/>
     </row>
-    <row r="71" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B71" s="134" t="s">
         <v>96</v>
       </c>
@@ -17218,15 +17261,9 @@
       <c r="P71" s="134"/>
       <c r="Q71" s="134"/>
       <c r="R71" s="134"/>
-      <c r="S71" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T71" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U71" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S71" s="134"/>
+      <c r="T71" s="134"/>
+      <c r="U71" s="134"/>
       <c r="V71" s="135"/>
       <c r="W71" s="135"/>
       <c r="X71" s="135"/>
@@ -17313,7 +17350,10 @@
       <c r="CM71" s="140"/>
       <c r="CN71" s="140"/>
     </row>
-    <row r="72" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B72" s="134"/>
       <c r="C72" s="134"/>
       <c r="D72" s="134"/>
@@ -17331,15 +17371,9 @@
       <c r="P72" s="134"/>
       <c r="Q72" s="134"/>
       <c r="R72" s="134"/>
-      <c r="S72" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T72" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U72" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S72" s="134"/>
+      <c r="T72" s="134"/>
+      <c r="U72" s="134"/>
       <c r="V72" s="135"/>
       <c r="W72" s="135"/>
       <c r="X72" s="135"/>
@@ -17418,7 +17452,10 @@
       <c r="CM72" s="140"/>
       <c r="CN72" s="140"/>
     </row>
-    <row r="73" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B73" s="134"/>
       <c r="C73" s="134"/>
       <c r="D73" s="134"/>
@@ -17436,15 +17473,9 @@
       <c r="P73" s="134"/>
       <c r="Q73" s="134"/>
       <c r="R73" s="134"/>
-      <c r="S73" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T73" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U73" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S73" s="134"/>
+      <c r="T73" s="134"/>
+      <c r="U73" s="134"/>
       <c r="V73" s="135"/>
       <c r="W73" s="135"/>
       <c r="X73" s="135"/>
@@ -17523,7 +17554,10 @@
       <c r="CM73" s="140"/>
       <c r="CN73" s="140"/>
     </row>
-    <row r="74" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B74" s="134"/>
       <c r="C74" s="134"/>
       <c r="D74" s="134"/>
@@ -17541,15 +17575,9 @@
       <c r="P74" s="134"/>
       <c r="Q74" s="134"/>
       <c r="R74" s="134"/>
-      <c r="S74" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T74" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U74" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S74" s="134"/>
+      <c r="T74" s="134"/>
+      <c r="U74" s="134"/>
       <c r="V74" s="135"/>
       <c r="W74" s="135"/>
       <c r="X74" s="135"/>
@@ -17628,7 +17656,10 @@
       <c r="CM74" s="140"/>
       <c r="CN74" s="140"/>
     </row>
-    <row r="75" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B75" s="134"/>
       <c r="C75" s="134"/>
       <c r="D75" s="134"/>
@@ -17646,15 +17677,9 @@
       <c r="P75" s="134"/>
       <c r="Q75" s="134"/>
       <c r="R75" s="134"/>
-      <c r="S75" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T75" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U75" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S75" s="134"/>
+      <c r="T75" s="134"/>
+      <c r="U75" s="134"/>
       <c r="V75" s="135"/>
       <c r="W75" s="135"/>
       <c r="X75" s="135"/>
@@ -17733,7 +17758,10 @@
       <c r="CM75" s="140"/>
       <c r="CN75" s="140"/>
     </row>
-    <row r="76" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B76" s="134"/>
       <c r="C76" s="134"/>
       <c r="D76" s="134"/>
@@ -17751,15 +17779,9 @@
       <c r="P76" s="134"/>
       <c r="Q76" s="134"/>
       <c r="R76" s="134"/>
-      <c r="S76" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T76" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U76" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S76" s="134"/>
+      <c r="T76" s="134"/>
+      <c r="U76" s="134"/>
       <c r="V76" s="135"/>
       <c r="W76" s="135"/>
       <c r="X76" s="135"/>
@@ -17838,7 +17860,10 @@
       <c r="CM76" s="140"/>
       <c r="CN76" s="140"/>
     </row>
-    <row r="77" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B77" s="134"/>
       <c r="C77" s="134"/>
       <c r="D77" s="134"/>
@@ -17856,15 +17881,9 @@
       <c r="P77" s="134"/>
       <c r="Q77" s="134"/>
       <c r="R77" s="134"/>
-      <c r="S77" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T77" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U77" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S77" s="134"/>
+      <c r="T77" s="134"/>
+      <c r="U77" s="134"/>
       <c r="V77" s="135"/>
       <c r="W77" s="135"/>
       <c r="X77" s="135"/>
@@ -17943,7 +17962,10 @@
       <c r="CM77" s="140"/>
       <c r="CN77" s="140"/>
     </row>
-    <row r="78" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B78" s="134"/>
       <c r="C78" s="134"/>
       <c r="D78" s="134"/>
@@ -17961,15 +17983,9 @@
       <c r="P78" s="134"/>
       <c r="Q78" s="134"/>
       <c r="R78" s="134"/>
-      <c r="S78" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T78" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U78" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S78" s="134"/>
+      <c r="T78" s="134"/>
+      <c r="U78" s="134"/>
       <c r="V78" s="135"/>
       <c r="W78" s="135"/>
       <c r="X78" s="135"/>
@@ -18048,7 +18064,10 @@
       <c r="CM78" s="140"/>
       <c r="CN78" s="140"/>
     </row>
-    <row r="79" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B79" s="134"/>
       <c r="C79" s="134"/>
       <c r="D79" s="134"/>
@@ -18066,15 +18085,9 @@
       <c r="P79" s="134"/>
       <c r="Q79" s="134"/>
       <c r="R79" s="134"/>
-      <c r="S79" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T79" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U79" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S79" s="134"/>
+      <c r="T79" s="134"/>
+      <c r="U79" s="134"/>
       <c r="V79" s="135"/>
       <c r="W79" s="135"/>
       <c r="X79" s="135"/>
@@ -18153,7 +18166,10 @@
       <c r="CM79" s="140"/>
       <c r="CN79" s="140"/>
     </row>
-    <row r="80" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B80" s="134"/>
       <c r="C80" s="134"/>
       <c r="D80" s="134"/>
@@ -18171,15 +18187,9 @@
       <c r="P80" s="134"/>
       <c r="Q80" s="134"/>
       <c r="R80" s="134"/>
-      <c r="S80" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T80" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U80" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S80" s="134"/>
+      <c r="T80" s="134"/>
+      <c r="U80" s="134"/>
       <c r="V80" s="135"/>
       <c r="W80" s="135"/>
       <c r="X80" s="135"/>
@@ -18258,7 +18268,10 @@
       <c r="CM80" s="140"/>
       <c r="CN80" s="140"/>
     </row>
-    <row r="81" spans="2:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:92" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="205" t="b">
+        <v>1</v>
+      </c>
       <c r="B81" s="134"/>
       <c r="C81" s="134"/>
       <c r="D81" s="134"/>
@@ -18276,15 +18289,9 @@
       <c r="P81" s="134"/>
       <c r="Q81" s="134"/>
       <c r="R81" s="134"/>
-      <c r="S81" s="201" t="b">
-        <v>1</v>
-      </c>
-      <c r="T81" s="202" t="b">
-        <v>1</v>
-      </c>
-      <c r="U81" s="203" t="b">
-        <v>1</v>
-      </c>
+      <c r="S81" s="134"/>
+      <c r="T81" s="134"/>
+      <c r="U81" s="134"/>
       <c r="V81" s="135"/>
       <c r="W81" s="135"/>
       <c r="X81" s="135"/>
@@ -18840,7 +18847,7 @@
     </row>
     <row r="88" spans="2:92" ht="15" customHeight="1">
       <c r="B88" s="142" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -19564,27 +19571,27 @@
     <mergeCell ref="BV7:CB7"/>
     <mergeCell ref="CD7:CE7"/>
     <mergeCell ref="CF7:CN7"/>
-    <mergeCell ref="B61:R61"/>
-    <mergeCell ref="B62:R62"/>
-    <mergeCell ref="B63:R63"/>
-    <mergeCell ref="B64:R64"/>
-    <mergeCell ref="B65:R65"/>
-    <mergeCell ref="B66:R66"/>
-    <mergeCell ref="B67:R67"/>
-    <mergeCell ref="B68:R68"/>
-    <mergeCell ref="B69:R69"/>
-    <mergeCell ref="B70:R70"/>
-    <mergeCell ref="B71:R71"/>
-    <mergeCell ref="B72:R72"/>
-    <mergeCell ref="B73:R73"/>
-    <mergeCell ref="B74:R74"/>
-    <mergeCell ref="B75:R75"/>
-    <mergeCell ref="B76:R76"/>
-    <mergeCell ref="B77:R77"/>
-    <mergeCell ref="B78:R78"/>
-    <mergeCell ref="B79:R79"/>
-    <mergeCell ref="B80:R80"/>
-    <mergeCell ref="B81:R81"/>
+    <mergeCell ref="B61:U61"/>
+    <mergeCell ref="B62:U62"/>
+    <mergeCell ref="B63:U63"/>
+    <mergeCell ref="B64:U64"/>
+    <mergeCell ref="B65:U65"/>
+    <mergeCell ref="B66:U66"/>
+    <mergeCell ref="B67:U67"/>
+    <mergeCell ref="B68:U68"/>
+    <mergeCell ref="B69:U69"/>
+    <mergeCell ref="B70:U70"/>
+    <mergeCell ref="B71:U71"/>
+    <mergeCell ref="B72:U72"/>
+    <mergeCell ref="B73:U73"/>
+    <mergeCell ref="B74:U74"/>
+    <mergeCell ref="B75:U75"/>
+    <mergeCell ref="B76:U76"/>
+    <mergeCell ref="B77:U77"/>
+    <mergeCell ref="B78:U78"/>
+    <mergeCell ref="B79:U79"/>
+    <mergeCell ref="B80:U80"/>
+    <mergeCell ref="B81:U81"/>
   </mergeCells>
   <conditionalFormatting sqref="C13 F13 I13 L13 O13 R13 U13 C15 F15 I15 L15 O15 R15 U15 C17 F17 I17 L17 O17 R17 U17 C19 F19 I19 L19 O19 R19 U19 C21 F21 I21 L21 O21 R21 U21 C23 F23 I23 L23 O23 R23 U23">
     <cfRule type="expression" dxfId="136" priority="1">
@@ -20202,7 +20209,7 @@
       <formula>AND(ISNUMBER(BT45),WEEKDAY(DATE(Planungsjahr,12,BT45),2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Art der Bitte" prompt="Bitte auswählen: aktiv, passiv oder nein" sqref="BM62:BM81" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"aktiv,passiv,nein"</formula1>
     </dataValidation>
@@ -20222,9 +20229,10 @@
       <formula1>2000</formula1>
       <formula2>2100</formula2>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (S)" prompt="Häkchen = Start Selektion dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="S62:S81"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (I)" prompt="Häkchen = Start inhaltliche Arbeit dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="T62:T81"/>
-    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Im Kalender anzeigen (P)" prompt="Häkchen = PAL dieser Maßnahme wird im Kalender markiert. Häkchen entfernen = Marker ausgeblendet (die Tabelle bleibt unverändert)." sqref="U62:U81"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Maßnahme im Kalender" prompt="Häkchen = S, I und P dieser Maßnahme erscheinen im Kalender. Häkchen entfernen = alle Marker dieser Maßnahme ausgeblendet." sqref="A62:A81"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Alle Start Selektion (S)" prompt="Häkchen = Start Selektion aller Maßnahmen im Kalender anzeigen (sofern die Maßnahme unten angehakt ist). Häkchen entfernen = alle S-Marker ausgeblendet." sqref="BS4"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Alle Starts Inhalt (I)" prompt="Häkchen = Start inhaltliche Arbeit aller Maßnahmen im Kalender anzeigen (sofern die Maßnahme unten angehakt ist). Häkchen entfernen = alle I-Marker ausgeblendet." sqref="BS5"/>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Alle PAL (P)" prompt="Häkchen = PAL aller Maßnahmen im Kalender anzeigen (sofern die Maßnahme unten angehakt ist). Häkchen entfernen = alle P-Marker ausgeblendet." sqref="BS6"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>

--- a/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
+++ b/excel/260924_Jahresplanung_Aussenkommunikation_2027_MA.xlsx
@@ -30,6 +30,8 @@
     <definedName name="JP_Anzeige">Jahresplanung!$A$13:$A$32</definedName>
     <definedName name="JP_Auflage">Jahresplanung!$V$13:$V$32</definedName>
     <definedName name="JP_Farbe">Hilfsdaten!$E$2:$E$21</definedName>
+    <definedName name="Farbnamen">Hilfsdaten!$B$63:$B$73</definedName>
+    <definedName name="JP_FarbWahl">Jahresplanung!$Q$13:$Q$32</definedName>
     <definedName name="JP_Massnahme">Jahresplanung!$B$13:$B$32</definedName>
     <definedName name="JP_PAL">Jahresplanung!$BD$13:$BD$32</definedName>
     <definedName name="JP_StartInhalt">Jahresplanung!$AP$13:$AP$32</definedName>
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="189">
   <si>
     <t xml:space="preserve">Erstellen eines Gantt-Diagramms
 Geben Sie den Titel dieses Projekts in Zelle B2 ein.
@@ -370,7 +372,7 @@
     <t>So funktioniert es:</t>
   </si>
   <si>
-    <t>• PAL, Vorläufe, Auflage, Art der Bitte und Hinweis werden hier gepflegt. Start Selektion und Start inhaltliche Arbeit berechnen sich automatisch (PAL minus Vorlauf, Kalendertage).</t>
+    <t>• PAL, Vorläufe, Auflage, Farbe (Liste; leer = automatisch), Art der Bitte und Hinweis werden hier gepflegt. Start Selektion und Start Inhalt = PAL minus Vorlauf (Kalendertage).</t>
   </si>
   <si>
     <t>• Die Vorlauf-Spalten übernehmen den Standardwert oben. Für einzelne Maßnahmen einfach eine eigene Zahl eintragen; Zelle leeren = kein Termin für diesen Schritt.</t>
@@ -379,7 +381,7 @@
     <t>• Sommer- und Weihnachtsmailing: PAL, Start Selektion und Start inhaltliche Arbeit steuern die gleichnamigen Detailblätter (Gantt). Die Verknüpfung läuft über den Namen in Spalte „Maßnahme“.</t>
   </si>
   <si>
-    <t>• Neue Maßnahme: in die nächste freie Zeile schreiben. Steht eine PAL vor der darüberliegenden, wird sie rot markiert – dann Zeile an die passende Stelle verschieben (Zeile ausschneiden, „Ausgeschnittene Zellen einfügen“).</t>
+    <t>• Neue Maßnahme: in die nächste freie Zeile schreiben und eine Farbe wählen. Steht eine PAL vor der darüberliegenden, wird sie rot markiert – dann Zeile an die passende Stelle verschieben (Zeile ausschneiden, „Ausgeschnittene Zellen einfügen“).</t>
   </si>
   <si>
     <t>← wird von Blatt „Jahresplanung“ übernommen</t>
@@ -642,7 +644,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-◂ Kästchen links: nur angehakte Maßnahmen anzeigen</t>
+◂ Kästchen: nur angehakte anzeigen</t>
     </r>
   </si>
   <si>
@@ -693,6 +695,39 @@
   <si>
     <t xml:space="preserve">• Terminliste unter jedem Monat: eine Zeile je Maßnahme in ihrer Farbe (z. B. „Sommermailing: S 04.04. · I 22.04.“). Ab der dritten Maßnahme im Monat stehen weitere in der dritten Zeile. Die Liste folgt den Kontrollkästchen.</t>
   </si>
+  <si>
+    <t xml:space="preserve">Farbe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grün</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Türkis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dunkelblau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oliv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braun</t>
+  </si>
 </sst>
 </file>
 
@@ -706,12 +741,12 @@
     <numFmt numFmtId="168" formatCode="[$-407]ddd\ dd\.mm\.yyyy"/>
     <numFmt numFmtId="169" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="170" formatCode="[$-407]dddd"/>
-    <numFmt numFmtId="210" formatCode="&quot;S&quot;;&quot;S&quot;;&quot;S&quot;;@"/>
-    <numFmt numFmtId="211" formatCode="&quot;I&quot;;&quot;I&quot;;&quot;I&quot;;@"/>
-    <numFmt numFmtId="212" formatCode="&quot;P&quot;;&quot;P&quot;;&quot;P&quot;;@"/>
+    <numFmt numFmtId="210" formatCode=";;;&quot;S&quot;"/>
+    <numFmt numFmtId="211" formatCode=";;;&quot;I&quot;"/>
+    <numFmt numFmtId="212" formatCode=";;;&quot;P&quot;"/>
     <numFmt numFmtId="213" formatCode=";;;"/>
   </numFmts>
-  <fonts count="89" x14ac:knownFonts="1">
+  <fonts count="94" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1369,8 +1404,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8.5"/>
+      <color rgb="FF262626"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1517,6 +1591,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F77B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E0E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E0E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF595959"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2190,7 +2282,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2889,6 +2981,36 @@
     <xf applyFill="1" applyNumberFormat="1" numFmtId="212" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="212" fontId="49" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="210" fontId="49" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="211" fontId="49" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="212" fontId="49" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="212" fontId="49" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="212" fontId="49" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="210" fontId="49" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="211" fontId="49" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="212" fontId="49" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="212" fontId="49" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf applyFill="1" applyNumberFormat="1" numFmtId="213" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2903,6 +3025,42 @@
     </xf>
     <xf applyNumberFormat="1" numFmtId="0" fontId="49" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="0" fontId="89" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="0" fontId="90" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="0" fontId="91" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="0" fontId="92" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf applyFill="1" applyNumberFormat="1" numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -2919,7 +3077,7 @@
     <cellStyle name="Überschrift 3" xfId="8" builtinId="18" customBuiltin="1"/>
     <cellStyle name="zAusgeblText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="210">
+  <dxfs count="227">
     <dxf>
       <font>
         <i/>
@@ -4616,6 +4774,18 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FFB8860B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3E3B5"/>
+          <bgColor rgb="FFF3E3B5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color rgb="FF1F77B4"/>
       </font>
       <fill>
@@ -4730,6 +4900,18 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFE6D3C4"/>
           <bgColor rgb="FFE6D3C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFB8860B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF3E3B5"/>
+          <bgColor rgb="FFF3E3B5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4855,6 +5037,18 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8860B"/>
+          <bgColor rgb="FFB8860B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF1F77B4"/>
       </font>
       <fill>
@@ -4965,6 +5159,17 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFB8860B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8860B"/>
+          <bgColor rgb="FFB8860B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF1F77B4"/>
       </font>
     </dxf>
@@ -5011,6 +5216,11 @@
     <dxf>
       <font>
         <color rgb="FF8D5B3A"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB8860B"/>
       </font>
     </dxf>
     <dxf>
@@ -5072,6 +5282,144 @@
         <b/>
         <color rgb="FF8D5B3A"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFB8860B"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F77B4"/>
+          <bgColor rgb="FF1F77B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6550D"/>
+          <bgColor rgb="FFE6550D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF2CA02C"/>
+          <bgColor rgb="FF2CA02C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC2185B"/>
+          <bgColor rgb="FFC2185B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0097A7"/>
+          <bgColor rgb="FF0097A7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC62828"/>
+          <bgColor rgb="FFC62828"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF283593"/>
+          <bgColor rgb="FF283593"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7C8B1F"/>
+          <bgColor rgb="FF7C8B1F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7B3FA0"/>
+          <bgColor rgb="FF7B3FA0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8D5B3A"/>
+          <bgColor rgb="FF8D5B3A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8860B"/>
+          <bgColor rgb="FFB8860B"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultPivotStyle="PivotStyleLight16">
@@ -5946,10 +6294,10 @@
       <c r="BO4" s="116"/>
       <c r="BP4" s="116"/>
       <c r="BQ4" s="116"/>
-      <c r="BS4" s="206" t="b">
+      <c r="BS4" s="245" t="b">
         <v>1</v>
       </c>
-      <c r="BT4" s="228" t="s">
+      <c r="BT4" s="242" t="s">
         <v>58</v>
       </c>
       <c r="BV4" s="121" t="s">
@@ -6016,10 +6364,10 @@
       <c r="BO5" s="116"/>
       <c r="BP5" s="116"/>
       <c r="BQ5" s="116"/>
-      <c r="BS5" s="207" t="b">
+      <c r="BS5" s="246" t="b">
         <v>1</v>
       </c>
-      <c r="BT5" s="229" t="s">
+      <c r="BT5" s="243" t="s">
         <v>62</v>
       </c>
       <c r="BV5" s="121" t="s">
@@ -6086,10 +6434,10 @@
       <c r="BO6" s="116"/>
       <c r="BP6" s="116"/>
       <c r="BQ6" s="116"/>
-      <c r="BS6" s="208" t="b">
+      <c r="BS6" s="247" t="b">
         <v>1</v>
       </c>
-      <c r="BT6" s="230" t="s">
+      <c r="BT6" s="244" t="s">
         <v>66</v>
       </c>
       <c r="BV6" s="121" t="s">
@@ -6221,7 +6569,7 @@
     </row>
     <row r="9" spans="2:92" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="119" t="str">
-        <f>IF(Filter_Aktiv,"Filter aktiv: Der Kalender zeigt nur die in der Tabelle angehakten Maßnahmen ("&amp;COUNTIFS(JP_Anzeige,TRUE,JP_Massnahme,"&lt;&gt;")&amp;"). Häkchen links neben „Maßnahme“ entfernen = wieder alle anzeigen.","Jede Maßnahme hat eine eigene Farbe (siehe Tabelle): P kräftig, S und I im Pastellton. Unter jedem Monat: eine Zeile je Maßnahme mit ihren Terminen.")</f>
+        <f>IF(Filter_Aktiv,"Filter aktiv: Der Kalender zeigt nur die in der Tabelle angehakten Maßnahmen ("&amp;COUNTIFS(JP_Anzeige,TRUE,JP_Massnahme,"&lt;&gt;")&amp;"). Häkchen links neben „Maßnahme“ entfernen = wieder alle anzeigen.","Jede Maßnahme hat eine eigene Farbe (Spalte „Farbe“ in der Tabelle): P kräftig, S und I im Pastellton. Unter jedem Monat: eine Zeile je Maßnahme mit ihren Terminen.")</f>
       </c>
       <c r="C9" s="119"/>
       <c r="D9" s="119"/>
@@ -6434,11 +6782,13 @@
       <c r="N12" s="127"/>
       <c r="O12" s="127"/>
       <c r="P12" s="127"/>
-      <c r="Q12" s="127"/>
-      <c r="R12" s="127"/>
-      <c r="S12" s="127"/>
-      <c r="T12" s="127"/>
-      <c r="U12" s="127"/>
+      <c r="Q12" s="128" t="s">
+        <v>178</v>
+      </c>
+      <c r="R12" s="128"/>
+      <c r="S12" s="128"/>
+      <c r="T12" s="128"/>
+      <c r="U12" s="128"/>
       <c r="V12" s="128" t="s">
         <v>82</v>
       </c>
@@ -6548,11 +6898,13 @@
       <c r="N13" s="134"/>
       <c r="O13" s="134"/>
       <c r="P13" s="134"/>
-      <c r="Q13" s="134"/>
-      <c r="R13" s="134"/>
-      <c r="S13" s="134"/>
-      <c r="T13" s="134"/>
-      <c r="U13" s="134"/>
+      <c r="Q13" s="241" t="s">
+        <v>179</v>
+      </c>
+      <c r="R13" s="241"/>
+      <c r="S13" s="241"/>
+      <c r="T13" s="241"/>
+      <c r="U13" s="241"/>
       <c r="V13" s="135"/>
       <c r="W13" s="135"/>
       <c r="X13" s="135"/>
@@ -6660,11 +7012,13 @@
       <c r="N14" s="134"/>
       <c r="O14" s="134"/>
       <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="134"/>
-      <c r="S14" s="134"/>
-      <c r="T14" s="134"/>
-      <c r="U14" s="134"/>
+      <c r="Q14" s="241" t="s">
+        <v>180</v>
+      </c>
+      <c r="R14" s="241"/>
+      <c r="S14" s="241"/>
+      <c r="T14" s="241"/>
+      <c r="U14" s="241"/>
       <c r="V14" s="135"/>
       <c r="W14" s="135"/>
       <c r="X14" s="135"/>
@@ -6772,11 +7126,13 @@
       <c r="N15" s="134"/>
       <c r="O15" s="134"/>
       <c r="P15" s="134"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="134"/>
-      <c r="S15" s="134"/>
-      <c r="T15" s="134"/>
-      <c r="U15" s="134"/>
+      <c r="Q15" s="241" t="s">
+        <v>181</v>
+      </c>
+      <c r="R15" s="241"/>
+      <c r="S15" s="241"/>
+      <c r="T15" s="241"/>
+      <c r="U15" s="241"/>
       <c r="V15" s="135"/>
       <c r="W15" s="135"/>
       <c r="X15" s="135"/>
@@ -6884,11 +7240,13 @@
       <c r="N16" s="134"/>
       <c r="O16" s="134"/>
       <c r="P16" s="134"/>
-      <c r="Q16" s="134"/>
-      <c r="R16" s="134"/>
-      <c r="S16" s="134"/>
-      <c r="T16" s="134"/>
-      <c r="U16" s="134"/>
+      <c r="Q16" s="241" t="s">
+        <v>182</v>
+      </c>
+      <c r="R16" s="241"/>
+      <c r="S16" s="241"/>
+      <c r="T16" s="241"/>
+      <c r="U16" s="241"/>
       <c r="V16" s="135"/>
       <c r="W16" s="135"/>
       <c r="X16" s="135"/>
@@ -7000,11 +7358,13 @@
       <c r="N17" s="134"/>
       <c r="O17" s="134"/>
       <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
+      <c r="Q17" s="241" t="s">
+        <v>183</v>
+      </c>
+      <c r="R17" s="241"/>
+      <c r="S17" s="241"/>
+      <c r="T17" s="241"/>
+      <c r="U17" s="241"/>
       <c r="V17" s="135"/>
       <c r="W17" s="135"/>
       <c r="X17" s="135"/>
@@ -7112,11 +7472,13 @@
       <c r="N18" s="134"/>
       <c r="O18" s="134"/>
       <c r="P18" s="134"/>
-      <c r="Q18" s="134"/>
-      <c r="R18" s="134"/>
-      <c r="S18" s="134"/>
-      <c r="T18" s="134"/>
-      <c r="U18" s="134"/>
+      <c r="Q18" s="241" t="s">
+        <v>184</v>
+      </c>
+      <c r="R18" s="241"/>
+      <c r="S18" s="241"/>
+      <c r="T18" s="241"/>
+      <c r="U18" s="241"/>
       <c r="V18" s="135"/>
       <c r="W18" s="135"/>
       <c r="X18" s="135"/>
@@ -7224,11 +7586,13 @@
       <c r="N19" s="134"/>
       <c r="O19" s="134"/>
       <c r="P19" s="134"/>
-      <c r="Q19" s="134"/>
-      <c r="R19" s="134"/>
-      <c r="S19" s="134"/>
-      <c r="T19" s="134"/>
-      <c r="U19" s="134"/>
+      <c r="Q19" s="241" t="s">
+        <v>185</v>
+      </c>
+      <c r="R19" s="241"/>
+      <c r="S19" s="241"/>
+      <c r="T19" s="241"/>
+      <c r="U19" s="241"/>
       <c r="V19" s="135"/>
       <c r="W19" s="135"/>
       <c r="X19" s="135"/>
@@ -7338,11 +7702,13 @@
       <c r="N20" s="134"/>
       <c r="O20" s="134"/>
       <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
+      <c r="Q20" s="241" t="s">
+        <v>186</v>
+      </c>
+      <c r="R20" s="241"/>
+      <c r="S20" s="241"/>
+      <c r="T20" s="241"/>
+      <c r="U20" s="241"/>
       <c r="V20" s="135"/>
       <c r="W20" s="135"/>
       <c r="X20" s="135"/>
@@ -7450,11 +7816,13 @@
       <c r="N21" s="134"/>
       <c r="O21" s="134"/>
       <c r="P21" s="134"/>
-      <c r="Q21" s="134"/>
-      <c r="R21" s="134"/>
-      <c r="S21" s="134"/>
-      <c r="T21" s="134"/>
-      <c r="U21" s="134"/>
+      <c r="Q21" s="241" t="s">
+        <v>187</v>
+      </c>
+      <c r="R21" s="241"/>
+      <c r="S21" s="241"/>
+      <c r="T21" s="241"/>
+      <c r="U21" s="241"/>
       <c r="V21" s="135"/>
       <c r="W21" s="135"/>
       <c r="X21" s="135"/>
@@ -7566,11 +7934,13 @@
       <c r="N22" s="134"/>
       <c r="O22" s="134"/>
       <c r="P22" s="134"/>
-      <c r="Q22" s="134"/>
-      <c r="R22" s="134"/>
-      <c r="S22" s="134"/>
-      <c r="T22" s="134"/>
-      <c r="U22" s="134"/>
+      <c r="Q22" s="241" t="s">
+        <v>188</v>
+      </c>
+      <c r="R22" s="241"/>
+      <c r="S22" s="241"/>
+      <c r="T22" s="241"/>
+      <c r="U22" s="241"/>
       <c r="V22" s="135"/>
       <c r="W22" s="135"/>
       <c r="X22" s="135"/>
@@ -7676,11 +8046,11 @@
       <c r="N23" s="134"/>
       <c r="O23" s="134"/>
       <c r="P23" s="134"/>
-      <c r="Q23" s="134"/>
-      <c r="R23" s="134"/>
-      <c r="S23" s="134"/>
-      <c r="T23" s="134"/>
-      <c r="U23" s="134"/>
+      <c r="Q23" s="241"/>
+      <c r="R23" s="241"/>
+      <c r="S23" s="241"/>
+      <c r="T23" s="241"/>
+      <c r="U23" s="241"/>
       <c r="V23" s="135"/>
       <c r="W23" s="135"/>
       <c r="X23" s="135"/>
@@ -7778,11 +8148,11 @@
       <c r="N24" s="134"/>
       <c r="O24" s="134"/>
       <c r="P24" s="134"/>
-      <c r="Q24" s="134"/>
-      <c r="R24" s="134"/>
-      <c r="S24" s="134"/>
-      <c r="T24" s="134"/>
-      <c r="U24" s="134"/>
+      <c r="Q24" s="241"/>
+      <c r="R24" s="241"/>
+      <c r="S24" s="241"/>
+      <c r="T24" s="241"/>
+      <c r="U24" s="241"/>
       <c r="V24" s="135"/>
       <c r="W24" s="135"/>
       <c r="X24" s="135"/>
@@ -7880,11 +8250,11 @@
       <c r="N25" s="134"/>
       <c r="O25" s="134"/>
       <c r="P25" s="134"/>
-      <c r="Q25" s="134"/>
-      <c r="R25" s="134"/>
-      <c r="S25" s="134"/>
-      <c r="T25" s="134"/>
-      <c r="U25" s="134"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="241"/>
+      <c r="S25" s="241"/>
+      <c r="T25" s="241"/>
+      <c r="U25" s="241"/>
       <c r="V25" s="135"/>
       <c r="W25" s="135"/>
       <c r="X25" s="135"/>
@@ -7982,11 +8352,11 @@
       <c r="N26" s="134"/>
       <c r="O26" s="134"/>
       <c r="P26" s="134"/>
-      <c r="Q26" s="134"/>
-      <c r="R26" s="134"/>
-      <c r="S26" s="134"/>
-      <c r="T26" s="134"/>
-      <c r="U26" s="134"/>
+      <c r="Q26" s="241"/>
+      <c r="R26" s="241"/>
+      <c r="S26" s="241"/>
+      <c r="T26" s="241"/>
+      <c r="U26" s="241"/>
       <c r="V26" s="135"/>
       <c r="W26" s="135"/>
       <c r="X26" s="135"/>
@@ -8084,11 +8454,11 @@
       <c r="N27" s="134"/>
       <c r="O27" s="134"/>
       <c r="P27" s="134"/>
-      <c r="Q27" s="134"/>
-      <c r="R27" s="134"/>
-      <c r="S27" s="134"/>
-      <c r="T27" s="134"/>
-      <c r="U27" s="134"/>
+      <c r="Q27" s="241"/>
+      <c r="R27" s="241"/>
+      <c r="S27" s="241"/>
+      <c r="T27" s="241"/>
+      <c r="U27" s="241"/>
       <c r="V27" s="135"/>
       <c r="W27" s="135"/>
       <c r="X27" s="135"/>
@@ -8186,11 +8556,11 @@
       <c r="N28" s="134"/>
       <c r="O28" s="134"/>
       <c r="P28" s="134"/>
-      <c r="Q28" s="134"/>
-      <c r="R28" s="134"/>
-      <c r="S28" s="134"/>
-      <c r="T28" s="134"/>
-      <c r="U28" s="134"/>
+      <c r="Q28" s="241"/>
+      <c r="R28" s="241"/>
+      <c r="S28" s="241"/>
+      <c r="T28" s="241"/>
+      <c r="U28" s="241"/>
       <c r="V28" s="135"/>
       <c r="W28" s="135"/>
       <c r="X28" s="135"/>
@@ -8288,11 +8658,11 @@
       <c r="N29" s="134"/>
       <c r="O29" s="134"/>
       <c r="P29" s="134"/>
-      <c r="Q29" s="134"/>
-      <c r="R29" s="134"/>
-      <c r="S29" s="134"/>
-      <c r="T29" s="134"/>
-      <c r="U29" s="134"/>
+      <c r="Q29" s="241"/>
+      <c r="R29" s="241"/>
+      <c r="S29" s="241"/>
+      <c r="T29" s="241"/>
+      <c r="U29" s="241"/>
       <c r="V29" s="135"/>
       <c r="W29" s="135"/>
       <c r="X29" s="135"/>
@@ -8390,11 +8760,11 @@
       <c r="N30" s="134"/>
       <c r="O30" s="134"/>
       <c r="P30" s="134"/>
-      <c r="Q30" s="134"/>
-      <c r="R30" s="134"/>
-      <c r="S30" s="134"/>
-      <c r="T30" s="134"/>
-      <c r="U30" s="134"/>
+      <c r="Q30" s="241"/>
+      <c r="R30" s="241"/>
+      <c r="S30" s="241"/>
+      <c r="T30" s="241"/>
+      <c r="U30" s="241"/>
       <c r="V30" s="135"/>
       <c r="W30" s="135"/>
       <c r="X30" s="135"/>
@@ -8492,11 +8862,11 @@
       <c r="N31" s="134"/>
       <c r="O31" s="134"/>
       <c r="P31" s="134"/>
-      <c r="Q31" s="134"/>
-      <c r="R31" s="134"/>
-      <c r="S31" s="134"/>
-      <c r="T31" s="134"/>
-      <c r="U31" s="134"/>
+      <c r="Q31" s="241"/>
+      <c r="R31" s="241"/>
+      <c r="S31" s="241"/>
+      <c r="T31" s="241"/>
+      <c r="U31" s="241"/>
       <c r="V31" s="135"/>
       <c r="W31" s="135"/>
       <c r="X31" s="135"/>
@@ -8594,11 +8964,11 @@
       <c r="N32" s="134"/>
       <c r="O32" s="134"/>
       <c r="P32" s="134"/>
-      <c r="Q32" s="134"/>
-      <c r="R32" s="134"/>
-      <c r="S32" s="134"/>
-      <c r="T32" s="134"/>
-      <c r="U32" s="134"/>
+      <c r="Q32" s="241"/>
+      <c r="R32" s="241"/>
+      <c r="S32" s="241"/>
+      <c r="T32" s="241"/>
+      <c r="U32" s="241"/>
       <c r="V32" s="135"/>
       <c r="W32" s="135"/>
       <c r="X32" s="135"/>
@@ -9613,259 +9983,259 @@
     <row r="46" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="167"/>
       <c r="C46" s="223">
-        <f>IF(ISNUMBER(C45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D46" s="224">
-        <f>IF(ISNUMBER(C45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E46" s="225">
-        <f>IF(ISNUMBER(C45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F46" s="223">
-        <f>IF(ISNUMBER(F45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G46" s="224">
-        <f>IF(ISNUMBER(F45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H46" s="225">
-        <f>IF(ISNUMBER(F45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I46" s="223">
-        <f>IF(ISNUMBER(I45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J46" s="224">
-        <f>IF(ISNUMBER(I45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K46" s="225">
-        <f>IF(ISNUMBER(I45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L46" s="223">
-        <f>IF(ISNUMBER(L45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M46" s="224">
-        <f>IF(ISNUMBER(L45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N46" s="225">
-        <f>IF(ISNUMBER(L45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O46" s="223">
-        <f>IF(ISNUMBER(O45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P46" s="224">
-        <f>IF(ISNUMBER(O45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q46" s="225">
-        <f>IF(ISNUMBER(O45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R46" s="223">
-        <f>IF(ISNUMBER(R45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S46" s="224">
-        <f>IF(ISNUMBER(R45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T46" s="225">
-        <f>IF(ISNUMBER(R45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U46" s="223">
-        <f>IF(ISNUMBER(U45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V46" s="224">
-        <f>IF(ISNUMBER(U45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U45))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W46" s="225">
-        <f>IF(ISNUMBER(U45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U45))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W46" s="226">
+        <f>IF(ISNUMBER(U45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y46" s="179"/>
       <c r="Z46" s="223">
-        <f>IF(ISNUMBER(Z45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA46" s="224">
-        <f>IF(ISNUMBER(Z45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB46" s="225">
-        <f>IF(ISNUMBER(Z45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC46" s="223">
-        <f>IF(ISNUMBER(AC45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD46" s="224">
-        <f>IF(ISNUMBER(AC45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE46" s="225">
-        <f>IF(ISNUMBER(AC45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF46" s="223">
-        <f>IF(ISNUMBER(AF45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG46" s="224">
-        <f>IF(ISNUMBER(AF45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH46" s="225">
-        <f>IF(ISNUMBER(AF45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI46" s="223">
-        <f>IF(ISNUMBER(AI45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ46" s="224">
-        <f>IF(ISNUMBER(AI45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK46" s="225">
-        <f>IF(ISNUMBER(AI45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL46" s="223">
-        <f>IF(ISNUMBER(AL45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM46" s="224">
-        <f>IF(ISNUMBER(AL45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AN46" s="225">
-        <f>IF(ISNUMBER(AL45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AO46" s="223">
-        <f>IF(ISNUMBER(AO45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AP46" s="224">
-        <f>IF(ISNUMBER(AO45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AQ46" s="225">
-        <f>IF(ISNUMBER(AO45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AR46" s="223">
-        <f>IF(ISNUMBER(AR45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AS46" s="224">
-        <f>IF(ISNUMBER(AR45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR45))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT46" s="225">
-        <f>IF(ISNUMBER(AR45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR45))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT46" s="231">
+        <f>IF(ISNUMBER(AR45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV46" s="179"/>
       <c r="AW46" s="223">
-        <f>IF(ISNUMBER(AW45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AX46" s="224">
-        <f>IF(ISNUMBER(AW45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AY46" s="225">
-        <f>IF(ISNUMBER(AW45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AZ46" s="223">
-        <f>IF(ISNUMBER(AZ45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BA46" s="224">
-        <f>IF(ISNUMBER(AZ45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BB46" s="225">
-        <f>IF(ISNUMBER(AZ45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BC46" s="223">
-        <f>IF(ISNUMBER(BC45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BD46" s="224">
-        <f>IF(ISNUMBER(BC45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BE46" s="225">
-        <f>IF(ISNUMBER(BC45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BF46" s="223">
-        <f>IF(ISNUMBER(BF45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BG46" s="224">
-        <f>IF(ISNUMBER(BF45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BH46" s="225">
-        <f>IF(ISNUMBER(BF45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BI46" s="223">
-        <f>IF(ISNUMBER(BI45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BJ46" s="224">
-        <f>IF(ISNUMBER(BI45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BK46" s="225">
-        <f>IF(ISNUMBER(BI45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BL46" s="223">
-        <f>IF(ISNUMBER(BL45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BM46" s="224">
-        <f>IF(ISNUMBER(BL45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BN46" s="225">
-        <f>IF(ISNUMBER(BL45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BO46" s="223">
-        <f>IF(ISNUMBER(BO45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BP46" s="224">
-        <f>IF(ISNUMBER(BO45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO45))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ46" s="225">
-        <f>IF(ISNUMBER(BO45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO45))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ46" s="231">
+        <f>IF(ISNUMBER(BO45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS46" s="179"/>
       <c r="BT46" s="223">
-        <f>IF(ISNUMBER(BT45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BU46" s="224">
-        <f>IF(ISNUMBER(BT45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BV46" s="225">
-        <f>IF(ISNUMBER(BT45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BW46" s="223">
-        <f>IF(ISNUMBER(BW45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BX46" s="224">
-        <f>IF(ISNUMBER(BW45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BY46" s="225">
-        <f>IF(ISNUMBER(BW45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BZ46" s="223">
-        <f>IF(ISNUMBER(BZ45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CA46" s="224">
-        <f>IF(ISNUMBER(BZ45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CB46" s="225">
-        <f>IF(ISNUMBER(BZ45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CC46" s="223">
-        <f>IF(ISNUMBER(CC45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CD46" s="224">
-        <f>IF(ISNUMBER(CC45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CE46" s="225">
-        <f>IF(ISNUMBER(CC45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CF46" s="223">
-        <f>IF(ISNUMBER(CF45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CG46" s="224">
-        <f>IF(ISNUMBER(CF45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CH46" s="225">
-        <f>IF(ISNUMBER(CF45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF45))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF45))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF45))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF45),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF45))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CI46" s="223">
-        <f>IF(ISNUMBER(CI45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CJ46" s="224">
-        <f>IF(ISNUMBER(CI45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CK46" s="225">
-        <f>IF(ISNUMBER(CI45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CL46" s="223">
-        <f>IF(ISNUMBER(CL45),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL45))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL45))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CM46" s="224">
-        <f>IF(ISNUMBER(CL45),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL45))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN46" s="225">
-        <f>IF(ISNUMBER(CL45),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL45))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL45),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL45))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL45))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN46" s="231">
+        <f>IF(ISNUMBER(CL45),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL45))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL45))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="47" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10057,259 +10427,259 @@
     <row r="48" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="167"/>
       <c r="C48" s="223">
-        <f>IF(ISNUMBER(C47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D48" s="224">
-        <f>IF(ISNUMBER(C47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E48" s="225">
-        <f>IF(ISNUMBER(C47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F48" s="223">
-        <f>IF(ISNUMBER(F47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G48" s="224">
-        <f>IF(ISNUMBER(F47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H48" s="225">
-        <f>IF(ISNUMBER(F47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I48" s="223">
-        <f>IF(ISNUMBER(I47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J48" s="224">
-        <f>IF(ISNUMBER(I47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K48" s="225">
-        <f>IF(ISNUMBER(I47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L48" s="223">
-        <f>IF(ISNUMBER(L47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M48" s="224">
-        <f>IF(ISNUMBER(L47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N48" s="225">
-        <f>IF(ISNUMBER(L47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O48" s="223">
-        <f>IF(ISNUMBER(O47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P48" s="224">
-        <f>IF(ISNUMBER(O47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q48" s="225">
-        <f>IF(ISNUMBER(O47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R48" s="223">
-        <f>IF(ISNUMBER(R47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S48" s="224">
-        <f>IF(ISNUMBER(R47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T48" s="225">
-        <f>IF(ISNUMBER(R47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U48" s="223">
-        <f>IF(ISNUMBER(U47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V48" s="224">
-        <f>IF(ISNUMBER(U47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U47))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W48" s="225">
-        <f>IF(ISNUMBER(U47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U47))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W48" s="226">
+        <f>IF(ISNUMBER(U47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y48" s="179"/>
       <c r="Z48" s="223">
-        <f>IF(ISNUMBER(Z47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA48" s="224">
-        <f>IF(ISNUMBER(Z47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB48" s="225">
-        <f>IF(ISNUMBER(Z47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC48" s="223">
-        <f>IF(ISNUMBER(AC47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD48" s="224">
-        <f>IF(ISNUMBER(AC47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE48" s="225">
-        <f>IF(ISNUMBER(AC47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF48" s="223">
-        <f>IF(ISNUMBER(AF47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG48" s="224">
-        <f>IF(ISNUMBER(AF47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH48" s="225">
-        <f>IF(ISNUMBER(AF47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI48" s="223">
-        <f>IF(ISNUMBER(AI47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ48" s="224">
-        <f>IF(ISNUMBER(AI47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK48" s="225">
-        <f>IF(ISNUMBER(AI47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL48" s="223">
-        <f>IF(ISNUMBER(AL47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM48" s="224">
-        <f>IF(ISNUMBER(AL47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AN48" s="225">
-        <f>IF(ISNUMBER(AL47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AO48" s="223">
-        <f>IF(ISNUMBER(AO47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AP48" s="224">
-        <f>IF(ISNUMBER(AO47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AQ48" s="225">
-        <f>IF(ISNUMBER(AO47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AR48" s="223">
-        <f>IF(ISNUMBER(AR47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AS48" s="224">
-        <f>IF(ISNUMBER(AR47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR47))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT48" s="225">
-        <f>IF(ISNUMBER(AR47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR47))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT48" s="231">
+        <f>IF(ISNUMBER(AR47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV48" s="179"/>
       <c r="AW48" s="223">
-        <f>IF(ISNUMBER(AW47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AX48" s="224">
-        <f>IF(ISNUMBER(AW47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AY48" s="225">
-        <f>IF(ISNUMBER(AW47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AZ48" s="223">
-        <f>IF(ISNUMBER(AZ47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BA48" s="224">
-        <f>IF(ISNUMBER(AZ47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BB48" s="225">
-        <f>IF(ISNUMBER(AZ47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BC48" s="223">
-        <f>IF(ISNUMBER(BC47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BD48" s="224">
-        <f>IF(ISNUMBER(BC47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BE48" s="225">
-        <f>IF(ISNUMBER(BC47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BF48" s="223">
-        <f>IF(ISNUMBER(BF47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BG48" s="224">
-        <f>IF(ISNUMBER(BF47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BH48" s="225">
-        <f>IF(ISNUMBER(BF47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BI48" s="223">
-        <f>IF(ISNUMBER(BI47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BJ48" s="224">
-        <f>IF(ISNUMBER(BI47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BK48" s="225">
-        <f>IF(ISNUMBER(BI47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BL48" s="223">
-        <f>IF(ISNUMBER(BL47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BM48" s="224">
-        <f>IF(ISNUMBER(BL47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BN48" s="225">
-        <f>IF(ISNUMBER(BL47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BO48" s="223">
-        <f>IF(ISNUMBER(BO47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BP48" s="224">
-        <f>IF(ISNUMBER(BO47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO47))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ48" s="225">
-        <f>IF(ISNUMBER(BO47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO47))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ48" s="231">
+        <f>IF(ISNUMBER(BO47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS48" s="179"/>
       <c r="BT48" s="223">
-        <f>IF(ISNUMBER(BT47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BU48" s="224">
-        <f>IF(ISNUMBER(BT47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BV48" s="225">
-        <f>IF(ISNUMBER(BT47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BW48" s="223">
-        <f>IF(ISNUMBER(BW47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BX48" s="224">
-        <f>IF(ISNUMBER(BW47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BY48" s="225">
-        <f>IF(ISNUMBER(BW47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BZ48" s="223">
-        <f>IF(ISNUMBER(BZ47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CA48" s="224">
-        <f>IF(ISNUMBER(BZ47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CB48" s="225">
-        <f>IF(ISNUMBER(BZ47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CC48" s="223">
-        <f>IF(ISNUMBER(CC47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CD48" s="224">
-        <f>IF(ISNUMBER(CC47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CE48" s="225">
-        <f>IF(ISNUMBER(CC47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CF48" s="223">
-        <f>IF(ISNUMBER(CF47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CG48" s="224">
-        <f>IF(ISNUMBER(CF47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CH48" s="225">
-        <f>IF(ISNUMBER(CF47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF47))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF47))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF47))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF47),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF47))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CI48" s="223">
-        <f>IF(ISNUMBER(CI47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CJ48" s="224">
-        <f>IF(ISNUMBER(CI47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CK48" s="225">
-        <f>IF(ISNUMBER(CI47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CL48" s="223">
-        <f>IF(ISNUMBER(CL47),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL47))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL47))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CM48" s="224">
-        <f>IF(ISNUMBER(CL47),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL47))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN48" s="225">
-        <f>IF(ISNUMBER(CL47),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL47))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL47),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL47))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL47))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN48" s="231">
+        <f>IF(ISNUMBER(CL47),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL47))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL47))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="49" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10501,259 +10871,259 @@
     <row r="50" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="167"/>
       <c r="C50" s="223">
-        <f>IF(ISNUMBER(C49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D50" s="224">
-        <f>IF(ISNUMBER(C49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E50" s="225">
-        <f>IF(ISNUMBER(C49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F50" s="223">
-        <f>IF(ISNUMBER(F49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G50" s="224">
-        <f>IF(ISNUMBER(F49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H50" s="225">
-        <f>IF(ISNUMBER(F49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I50" s="223">
-        <f>IF(ISNUMBER(I49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J50" s="224">
-        <f>IF(ISNUMBER(I49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K50" s="225">
-        <f>IF(ISNUMBER(I49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L50" s="223">
-        <f>IF(ISNUMBER(L49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M50" s="224">
-        <f>IF(ISNUMBER(L49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N50" s="225">
-        <f>IF(ISNUMBER(L49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O50" s="223">
-        <f>IF(ISNUMBER(O49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P50" s="224">
-        <f>IF(ISNUMBER(O49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q50" s="225">
-        <f>IF(ISNUMBER(O49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R50" s="223">
-        <f>IF(ISNUMBER(R49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S50" s="224">
-        <f>IF(ISNUMBER(R49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T50" s="225">
-        <f>IF(ISNUMBER(R49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U50" s="223">
-        <f>IF(ISNUMBER(U49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V50" s="224">
-        <f>IF(ISNUMBER(U49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U49))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W50" s="225">
-        <f>IF(ISNUMBER(U49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U49))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W50" s="226">
+        <f>IF(ISNUMBER(U49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y50" s="179"/>
       <c r="Z50" s="223">
-        <f>IF(ISNUMBER(Z49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA50" s="224">
-        <f>IF(ISNUMBER(Z49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB50" s="225">
-        <f>IF(ISNUMBER(Z49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC50" s="223">
-        <f>IF(ISNUMBER(AC49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD50" s="224">
-        <f>IF(ISNUMBER(AC49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE50" s="225">
-        <f>IF(ISNUMBER(AC49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF50" s="223">
-        <f>IF(ISNUMBER(AF49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG50" s="224">
-        <f>IF(ISNUMBER(AF49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH50" s="225">
-        <f>IF(ISNUMBER(AF49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI50" s="223">
-        <f>IF(ISNUMBER(AI49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ50" s="224">
-        <f>IF(ISNUMBER(AI49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK50" s="225">
-        <f>IF(ISNUMBER(AI49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL50" s="223">
-        <f>IF(ISNUMBER(AL49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM50" s="224">
-        <f>IF(ISNUMBER(AL49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AN50" s="225">
-        <f>IF(ISNUMBER(AL49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AO50" s="223">
-        <f>IF(ISNUMBER(AO49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AP50" s="224">
-        <f>IF(ISNUMBER(AO49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AQ50" s="225">
-        <f>IF(ISNUMBER(AO49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AR50" s="223">
-        <f>IF(ISNUMBER(AR49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AS50" s="224">
-        <f>IF(ISNUMBER(AR49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR49))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT50" s="225">
-        <f>IF(ISNUMBER(AR49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR49))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT50" s="231">
+        <f>IF(ISNUMBER(AR49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV50" s="179"/>
       <c r="AW50" s="223">
-        <f>IF(ISNUMBER(AW49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AX50" s="224">
-        <f>IF(ISNUMBER(AW49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AY50" s="225">
-        <f>IF(ISNUMBER(AW49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AZ50" s="223">
-        <f>IF(ISNUMBER(AZ49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BA50" s="224">
-        <f>IF(ISNUMBER(AZ49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BB50" s="225">
-        <f>IF(ISNUMBER(AZ49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BC50" s="223">
-        <f>IF(ISNUMBER(BC49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BD50" s="224">
-        <f>IF(ISNUMBER(BC49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BE50" s="225">
-        <f>IF(ISNUMBER(BC49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BF50" s="223">
-        <f>IF(ISNUMBER(BF49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BG50" s="224">
-        <f>IF(ISNUMBER(BF49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BH50" s="225">
-        <f>IF(ISNUMBER(BF49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BI50" s="223">
-        <f>IF(ISNUMBER(BI49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BJ50" s="224">
-        <f>IF(ISNUMBER(BI49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BK50" s="225">
-        <f>IF(ISNUMBER(BI49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BL50" s="223">
-        <f>IF(ISNUMBER(BL49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BM50" s="224">
-        <f>IF(ISNUMBER(BL49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BN50" s="225">
-        <f>IF(ISNUMBER(BL49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BO50" s="223">
-        <f>IF(ISNUMBER(BO49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BP50" s="224">
-        <f>IF(ISNUMBER(BO49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO49))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ50" s="225">
-        <f>IF(ISNUMBER(BO49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO49))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ50" s="231">
+        <f>IF(ISNUMBER(BO49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS50" s="179"/>
       <c r="BT50" s="223">
-        <f>IF(ISNUMBER(BT49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BU50" s="224">
-        <f>IF(ISNUMBER(BT49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BV50" s="225">
-        <f>IF(ISNUMBER(BT49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BW50" s="223">
-        <f>IF(ISNUMBER(BW49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BX50" s="224">
-        <f>IF(ISNUMBER(BW49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BY50" s="225">
-        <f>IF(ISNUMBER(BW49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BZ50" s="223">
-        <f>IF(ISNUMBER(BZ49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CA50" s="224">
-        <f>IF(ISNUMBER(BZ49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CB50" s="225">
-        <f>IF(ISNUMBER(BZ49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CC50" s="223">
-        <f>IF(ISNUMBER(CC49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CD50" s="224">
-        <f>IF(ISNUMBER(CC49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CE50" s="225">
-        <f>IF(ISNUMBER(CC49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CF50" s="223">
-        <f>IF(ISNUMBER(CF49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CG50" s="224">
-        <f>IF(ISNUMBER(CF49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CH50" s="225">
-        <f>IF(ISNUMBER(CF49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF49))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF49))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF49))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF49),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF49))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CI50" s="223">
-        <f>IF(ISNUMBER(CI49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CJ50" s="224">
-        <f>IF(ISNUMBER(CI49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CK50" s="225">
-        <f>IF(ISNUMBER(CI49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CL50" s="223">
-        <f>IF(ISNUMBER(CL49),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL49))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL49))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CM50" s="224">
-        <f>IF(ISNUMBER(CL49),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL49))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN50" s="225">
-        <f>IF(ISNUMBER(CL49),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL49))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL49),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL49))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL49))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN50" s="231">
+        <f>IF(ISNUMBER(CL49),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL49))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL49))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="51" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -10945,259 +11315,259 @@
     <row r="52" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="167"/>
       <c r="C52" s="223">
-        <f>IF(ISNUMBER(C51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D52" s="224">
-        <f>IF(ISNUMBER(C51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E52" s="225">
-        <f>IF(ISNUMBER(C51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F52" s="223">
-        <f>IF(ISNUMBER(F51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G52" s="224">
-        <f>IF(ISNUMBER(F51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H52" s="225">
-        <f>IF(ISNUMBER(F51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I52" s="223">
-        <f>IF(ISNUMBER(I51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J52" s="224">
-        <f>IF(ISNUMBER(I51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K52" s="225">
-        <f>IF(ISNUMBER(I51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L52" s="223">
-        <f>IF(ISNUMBER(L51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M52" s="224">
-        <f>IF(ISNUMBER(L51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N52" s="225">
-        <f>IF(ISNUMBER(L51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O52" s="223">
-        <f>IF(ISNUMBER(O51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P52" s="224">
-        <f>IF(ISNUMBER(O51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q52" s="225">
-        <f>IF(ISNUMBER(O51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R52" s="223">
-        <f>IF(ISNUMBER(R51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S52" s="224">
-        <f>IF(ISNUMBER(R51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T52" s="225">
-        <f>IF(ISNUMBER(R51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U52" s="223">
-        <f>IF(ISNUMBER(U51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V52" s="224">
-        <f>IF(ISNUMBER(U51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U51))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W52" s="225">
-        <f>IF(ISNUMBER(U51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U51))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W52" s="226">
+        <f>IF(ISNUMBER(U51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y52" s="179"/>
       <c r="Z52" s="223">
-        <f>IF(ISNUMBER(Z51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA52" s="224">
-        <f>IF(ISNUMBER(Z51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB52" s="225">
-        <f>IF(ISNUMBER(Z51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC52" s="223">
-        <f>IF(ISNUMBER(AC51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD52" s="224">
-        <f>IF(ISNUMBER(AC51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE52" s="225">
-        <f>IF(ISNUMBER(AC51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF52" s="223">
-        <f>IF(ISNUMBER(AF51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG52" s="224">
-        <f>IF(ISNUMBER(AF51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH52" s="225">
-        <f>IF(ISNUMBER(AF51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI52" s="223">
-        <f>IF(ISNUMBER(AI51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ52" s="224">
-        <f>IF(ISNUMBER(AI51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK52" s="225">
-        <f>IF(ISNUMBER(AI51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL52" s="223">
-        <f>IF(ISNUMBER(AL51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM52" s="224">
-        <f>IF(ISNUMBER(AL51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AN52" s="225">
-        <f>IF(ISNUMBER(AL51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AO52" s="223">
-        <f>IF(ISNUMBER(AO51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AP52" s="224">
-        <f>IF(ISNUMBER(AO51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AQ52" s="225">
-        <f>IF(ISNUMBER(AO51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AR52" s="223">
-        <f>IF(ISNUMBER(AR51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AS52" s="224">
-        <f>IF(ISNUMBER(AR51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR51))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT52" s="225">
-        <f>IF(ISNUMBER(AR51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR51))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT52" s="231">
+        <f>IF(ISNUMBER(AR51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV52" s="179"/>
       <c r="AW52" s="223">
-        <f>IF(ISNUMBER(AW51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AX52" s="224">
-        <f>IF(ISNUMBER(AW51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AY52" s="225">
-        <f>IF(ISNUMBER(AW51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AZ52" s="223">
-        <f>IF(ISNUMBER(AZ51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BA52" s="224">
-        <f>IF(ISNUMBER(AZ51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BB52" s="225">
-        <f>IF(ISNUMBER(AZ51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BC52" s="223">
-        <f>IF(ISNUMBER(BC51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BD52" s="224">
-        <f>IF(ISNUMBER(BC51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BE52" s="225">
-        <f>IF(ISNUMBER(BC51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BF52" s="223">
-        <f>IF(ISNUMBER(BF51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BG52" s="224">
-        <f>IF(ISNUMBER(BF51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BH52" s="225">
-        <f>IF(ISNUMBER(BF51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BI52" s="223">
-        <f>IF(ISNUMBER(BI51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BJ52" s="224">
-        <f>IF(ISNUMBER(BI51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BK52" s="225">
-        <f>IF(ISNUMBER(BI51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BL52" s="223">
-        <f>IF(ISNUMBER(BL51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BM52" s="224">
-        <f>IF(ISNUMBER(BL51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BN52" s="225">
-        <f>IF(ISNUMBER(BL51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BO52" s="223">
-        <f>IF(ISNUMBER(BO51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BP52" s="224">
-        <f>IF(ISNUMBER(BO51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO51))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ52" s="225">
-        <f>IF(ISNUMBER(BO51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO51))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ52" s="231">
+        <f>IF(ISNUMBER(BO51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS52" s="179"/>
       <c r="BT52" s="223">
-        <f>IF(ISNUMBER(BT51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BU52" s="224">
-        <f>IF(ISNUMBER(BT51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BV52" s="225">
-        <f>IF(ISNUMBER(BT51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BW52" s="223">
-        <f>IF(ISNUMBER(BW51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BX52" s="224">
-        <f>IF(ISNUMBER(BW51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BY52" s="225">
-        <f>IF(ISNUMBER(BW51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BZ52" s="223">
-        <f>IF(ISNUMBER(BZ51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CA52" s="224">
-        <f>IF(ISNUMBER(BZ51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CB52" s="225">
-        <f>IF(ISNUMBER(BZ51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CC52" s="223">
-        <f>IF(ISNUMBER(CC51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CD52" s="224">
-        <f>IF(ISNUMBER(CC51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CE52" s="225">
-        <f>IF(ISNUMBER(CC51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CF52" s="223">
-        <f>IF(ISNUMBER(CF51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CG52" s="224">
-        <f>IF(ISNUMBER(CF51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CH52" s="225">
-        <f>IF(ISNUMBER(CF51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF51))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF51))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF51))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF51),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF51))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CI52" s="223">
-        <f>IF(ISNUMBER(CI51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CJ52" s="224">
-        <f>IF(ISNUMBER(CI51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CK52" s="225">
-        <f>IF(ISNUMBER(CI51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CL52" s="223">
-        <f>IF(ISNUMBER(CL51),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL51))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL51))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CM52" s="224">
-        <f>IF(ISNUMBER(CL51),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL51))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN52" s="225">
-        <f>IF(ISNUMBER(CL51),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL51))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL51),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL51))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL51))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN52" s="231">
+        <f>IF(ISNUMBER(CL51),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL51))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL51))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="53" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11389,259 +11759,259 @@
     <row r="54" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="167"/>
       <c r="C54" s="223">
-        <f>IF(ISNUMBER(C53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D54" s="224">
-        <f>IF(ISNUMBER(C53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E54" s="225">
-        <f>IF(ISNUMBER(C53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F54" s="223">
-        <f>IF(ISNUMBER(F53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G54" s="224">
-        <f>IF(ISNUMBER(F53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H54" s="225">
-        <f>IF(ISNUMBER(F53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I54" s="223">
-        <f>IF(ISNUMBER(I53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J54" s="224">
-        <f>IF(ISNUMBER(I53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K54" s="225">
-        <f>IF(ISNUMBER(I53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L54" s="223">
-        <f>IF(ISNUMBER(L53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M54" s="224">
-        <f>IF(ISNUMBER(L53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N54" s="225">
-        <f>IF(ISNUMBER(L53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O54" s="223">
-        <f>IF(ISNUMBER(O53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P54" s="224">
-        <f>IF(ISNUMBER(O53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q54" s="225">
-        <f>IF(ISNUMBER(O53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R54" s="223">
-        <f>IF(ISNUMBER(R53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S54" s="224">
-        <f>IF(ISNUMBER(R53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T54" s="225">
-        <f>IF(ISNUMBER(R53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U54" s="223">
-        <f>IF(ISNUMBER(U53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V54" s="224">
-        <f>IF(ISNUMBER(U53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U53))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W54" s="225">
-        <f>IF(ISNUMBER(U53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U53))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W54" s="226">
+        <f>IF(ISNUMBER(U53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y54" s="179"/>
       <c r="Z54" s="223">
-        <f>IF(ISNUMBER(Z53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA54" s="224">
-        <f>IF(ISNUMBER(Z53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB54" s="225">
-        <f>IF(ISNUMBER(Z53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC54" s="223">
-        <f>IF(ISNUMBER(AC53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD54" s="224">
-        <f>IF(ISNUMBER(AC53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE54" s="225">
-        <f>IF(ISNUMBER(AC53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF54" s="223">
-        <f>IF(ISNUMBER(AF53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG54" s="224">
-        <f>IF(ISNUMBER(AF53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH54" s="225">
-        <f>IF(ISNUMBER(AF53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI54" s="223">
-        <f>IF(ISNUMBER(AI53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ54" s="224">
-        <f>IF(ISNUMBER(AI53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK54" s="225">
-        <f>IF(ISNUMBER(AI53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL54" s="223">
-        <f>IF(ISNUMBER(AL53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM54" s="224">
-        <f>IF(ISNUMBER(AL53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AN54" s="225">
-        <f>IF(ISNUMBER(AL53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AO54" s="223">
-        <f>IF(ISNUMBER(AO53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AP54" s="224">
-        <f>IF(ISNUMBER(AO53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AQ54" s="225">
-        <f>IF(ISNUMBER(AO53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AR54" s="223">
-        <f>IF(ISNUMBER(AR53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AS54" s="224">
-        <f>IF(ISNUMBER(AR53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR53))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT54" s="225">
-        <f>IF(ISNUMBER(AR53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR53))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT54" s="231">
+        <f>IF(ISNUMBER(AR53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV54" s="179"/>
       <c r="AW54" s="223">
-        <f>IF(ISNUMBER(AW53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AX54" s="224">
-        <f>IF(ISNUMBER(AW53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AY54" s="225">
-        <f>IF(ISNUMBER(AW53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AZ54" s="223">
-        <f>IF(ISNUMBER(AZ53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BA54" s="224">
-        <f>IF(ISNUMBER(AZ53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BB54" s="225">
-        <f>IF(ISNUMBER(AZ53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BC54" s="223">
-        <f>IF(ISNUMBER(BC53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BD54" s="224">
-        <f>IF(ISNUMBER(BC53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BE54" s="225">
-        <f>IF(ISNUMBER(BC53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BF54" s="223">
-        <f>IF(ISNUMBER(BF53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BG54" s="224">
-        <f>IF(ISNUMBER(BF53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BH54" s="225">
-        <f>IF(ISNUMBER(BF53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BI54" s="223">
-        <f>IF(ISNUMBER(BI53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BJ54" s="224">
-        <f>IF(ISNUMBER(BI53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BK54" s="225">
-        <f>IF(ISNUMBER(BI53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BL54" s="223">
-        <f>IF(ISNUMBER(BL53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BM54" s="224">
-        <f>IF(ISNUMBER(BL53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BN54" s="225">
-        <f>IF(ISNUMBER(BL53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BO54" s="223">
-        <f>IF(ISNUMBER(BO53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BP54" s="224">
-        <f>IF(ISNUMBER(BO53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO53))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ54" s="225">
-        <f>IF(ISNUMBER(BO53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO53))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ54" s="231">
+        <f>IF(ISNUMBER(BO53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS54" s="179"/>
       <c r="BT54" s="223">
-        <f>IF(ISNUMBER(BT53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BU54" s="224">
-        <f>IF(ISNUMBER(BT53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BV54" s="225">
-        <f>IF(ISNUMBER(BT53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BW54" s="223">
-        <f>IF(ISNUMBER(BW53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BX54" s="224">
-        <f>IF(ISNUMBER(BW53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BY54" s="225">
-        <f>IF(ISNUMBER(BW53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BZ54" s="223">
-        <f>IF(ISNUMBER(BZ53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CA54" s="224">
-        <f>IF(ISNUMBER(BZ53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CB54" s="225">
-        <f>IF(ISNUMBER(BZ53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CC54" s="223">
-        <f>IF(ISNUMBER(CC53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CD54" s="224">
-        <f>IF(ISNUMBER(CC53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CE54" s="225">
-        <f>IF(ISNUMBER(CC53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CF54" s="223">
-        <f>IF(ISNUMBER(CF53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CG54" s="224">
-        <f>IF(ISNUMBER(CF53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CH54" s="225">
-        <f>IF(ISNUMBER(CF53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF53))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF53))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF53))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF53),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF53))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CI54" s="223">
-        <f>IF(ISNUMBER(CI53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CJ54" s="224">
-        <f>IF(ISNUMBER(CI53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CK54" s="225">
-        <f>IF(ISNUMBER(CI53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CL54" s="223">
-        <f>IF(ISNUMBER(CL53),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL53))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL53))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CM54" s="224">
-        <f>IF(ISNUMBER(CL53),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL53))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN54" s="225">
-        <f>IF(ISNUMBER(CL53),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL53))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL53),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL53))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL53))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN54" s="231">
+        <f>IF(ISNUMBER(CL53),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL53))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL53))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="55" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11832,260 +12202,260 @@
     </row>
     <row r="56" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="169"/>
-      <c r="C56" s="223">
-        <f>IF(ISNUMBER(C55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="D56" s="224">
-        <f>IF(ISNUMBER(C55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="E56" s="225">
-        <f>IF(ISNUMBER(C55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="F56" s="223">
-        <f>IF(ISNUMBER(F55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="G56" s="224">
-        <f>IF(ISNUMBER(F55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="H56" s="225">
-        <f>IF(ISNUMBER(F55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="I56" s="223">
-        <f>IF(ISNUMBER(I55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="J56" s="224">
-        <f>IF(ISNUMBER(I55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="K56" s="225">
-        <f>IF(ISNUMBER(I55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="L56" s="223">
-        <f>IF(ISNUMBER(L55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="M56" s="224">
-        <f>IF(ISNUMBER(L55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="N56" s="225">
-        <f>IF(ISNUMBER(L55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="O56" s="223">
-        <f>IF(ISNUMBER(O55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="P56" s="224">
-        <f>IF(ISNUMBER(O55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="Q56" s="225">
-        <f>IF(ISNUMBER(O55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="R56" s="223">
-        <f>IF(ISNUMBER(R55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="S56" s="224">
-        <f>IF(ISNUMBER(R55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="T56" s="225">
-        <f>IF(ISNUMBER(R55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="U56" s="223">
-        <f>IF(ISNUMBER(U55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="V56" s="224">
-        <f>IF(ISNUMBER(U55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W56" s="225">
-        <f>IF(ISNUMBER(U55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U55))&gt;0,"h","w")),"")</f>
+      <c r="C56" s="227">
+        <f>IF(ISNUMBER(C55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,C55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="D56" s="228">
+        <f>IF(ISNUMBER(C55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,C55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="E56" s="229">
+        <f>IF(ISNUMBER(C55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,C55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,C55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,C55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,C55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="F56" s="227">
+        <f>IF(ISNUMBER(F55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,F55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="G56" s="228">
+        <f>IF(ISNUMBER(F55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,F55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="H56" s="229">
+        <f>IF(ISNUMBER(F55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,F55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,F55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,F55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,F55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="I56" s="227">
+        <f>IF(ISNUMBER(I55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,I55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="J56" s="228">
+        <f>IF(ISNUMBER(I55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,I55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="K56" s="229">
+        <f>IF(ISNUMBER(I55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,I55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,I55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,I55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,I55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="L56" s="227">
+        <f>IF(ISNUMBER(L55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,L55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="M56" s="228">
+        <f>IF(ISNUMBER(L55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,L55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="N56" s="229">
+        <f>IF(ISNUMBER(L55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,L55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,L55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,L55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,L55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="O56" s="227">
+        <f>IF(ISNUMBER(O55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,O55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="P56" s="228">
+        <f>IF(ISNUMBER(O55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,O55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="Q56" s="229">
+        <f>IF(ISNUMBER(O55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,O55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,O55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,1,O55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,1,O55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="R56" s="227">
+        <f>IF(ISNUMBER(R55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,R55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="S56" s="228">
+        <f>IF(ISNUMBER(R55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,R55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="T56" s="229">
+        <f>IF(ISNUMBER(R55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,R55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,R55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="U56" s="227">
+        <f>IF(ISNUMBER(U55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,1,U55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="V56" s="228">
+        <f>IF(ISNUMBER(U55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,1,U55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W56" s="230">
+        <f>IF(ISNUMBER(U55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,1,U55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,1,U55))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y56" s="181"/>
-      <c r="Z56" s="223">
-        <f>IF(ISNUMBER(Z55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AA56" s="224">
-        <f>IF(ISNUMBER(Z55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AB56" s="225">
-        <f>IF(ISNUMBER(Z55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AC56" s="223">
-        <f>IF(ISNUMBER(AC55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AD56" s="224">
-        <f>IF(ISNUMBER(AC55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AE56" s="225">
-        <f>IF(ISNUMBER(AC55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AF56" s="223">
-        <f>IF(ISNUMBER(AF55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AG56" s="224">
-        <f>IF(ISNUMBER(AF55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AH56" s="225">
-        <f>IF(ISNUMBER(AF55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AI56" s="223">
-        <f>IF(ISNUMBER(AI55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AJ56" s="224">
-        <f>IF(ISNUMBER(AI55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AK56" s="225">
-        <f>IF(ISNUMBER(AI55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AL56" s="223">
-        <f>IF(ISNUMBER(AL55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AM56" s="224">
-        <f>IF(ISNUMBER(AL55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AN56" s="225">
-        <f>IF(ISNUMBER(AL55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AO56" s="223">
-        <f>IF(ISNUMBER(AO55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AP56" s="224">
-        <f>IF(ISNUMBER(AO55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AQ56" s="225">
-        <f>IF(ISNUMBER(AO55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AR56" s="223">
-        <f>IF(ISNUMBER(AR55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AS56" s="224">
-        <f>IF(ISNUMBER(AR55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT56" s="225">
-        <f>IF(ISNUMBER(AR55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR55))&gt;0,"h","w")),"")</f>
+      <c r="Z56" s="232">
+        <f>IF(ISNUMBER(Z55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,Z55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AA56" s="233">
+        <f>IF(ISNUMBER(Z55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,Z55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AB56" s="234">
+        <f>IF(ISNUMBER(Z55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,Z55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,Z55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,Z55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,Z55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AC56" s="232">
+        <f>IF(ISNUMBER(AC55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AC55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AD56" s="233">
+        <f>IF(ISNUMBER(AC55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AC55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AE56" s="234">
+        <f>IF(ISNUMBER(AC55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AC55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AF56" s="232">
+        <f>IF(ISNUMBER(AF55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AF55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AG56" s="233">
+        <f>IF(ISNUMBER(AF55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AF55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AH56" s="234">
+        <f>IF(ISNUMBER(AF55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AF55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AI56" s="232">
+        <f>IF(ISNUMBER(AI55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AI55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AJ56" s="233">
+        <f>IF(ISNUMBER(AI55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AI55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AK56" s="234">
+        <f>IF(ISNUMBER(AI55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AI55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AI55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AI55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AL56" s="232">
+        <f>IF(ISNUMBER(AL55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AL55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AM56" s="233">
+        <f>IF(ISNUMBER(AL55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AL55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AN56" s="234">
+        <f>IF(ISNUMBER(AL55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AL55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AL55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,2,AL55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,2,AL55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AO56" s="232">
+        <f>IF(ISNUMBER(AO55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AO55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AP56" s="233">
+        <f>IF(ISNUMBER(AO55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AO55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AQ56" s="234">
+        <f>IF(ISNUMBER(AO55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AO55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AO55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AR56" s="232">
+        <f>IF(ISNUMBER(AR55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,2,AR55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AS56" s="233">
+        <f>IF(ISNUMBER(AR55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,2,AR55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT56" s="235">
+        <f>IF(ISNUMBER(AR55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,2,AR55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,2,AR55))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV56" s="181"/>
-      <c r="AW56" s="223">
-        <f>IF(ISNUMBER(AW55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AX56" s="224">
-        <f>IF(ISNUMBER(AW55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AY56" s="225">
-        <f>IF(ISNUMBER(AW55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="AZ56" s="223">
-        <f>IF(ISNUMBER(AZ55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BA56" s="224">
-        <f>IF(ISNUMBER(AZ55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BB56" s="225">
-        <f>IF(ISNUMBER(AZ55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BC56" s="223">
-        <f>IF(ISNUMBER(BC55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BD56" s="224">
-        <f>IF(ISNUMBER(BC55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BE56" s="225">
-        <f>IF(ISNUMBER(BC55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BF56" s="223">
-        <f>IF(ISNUMBER(BF55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BG56" s="224">
-        <f>IF(ISNUMBER(BF55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BH56" s="225">
-        <f>IF(ISNUMBER(BF55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BI56" s="223">
-        <f>IF(ISNUMBER(BI55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BJ56" s="224">
-        <f>IF(ISNUMBER(BI55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BK56" s="225">
-        <f>IF(ISNUMBER(BI55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BL56" s="223">
-        <f>IF(ISNUMBER(BL55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BM56" s="224">
-        <f>IF(ISNUMBER(BL55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BN56" s="225">
-        <f>IF(ISNUMBER(BL55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BO56" s="223">
-        <f>IF(ISNUMBER(BO55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BP56" s="224">
-        <f>IF(ISNUMBER(BO55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ56" s="225">
-        <f>IF(ISNUMBER(BO55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO55))&gt;0,"h","w")),"")</f>
+      <c r="AW56" s="232">
+        <f>IF(ISNUMBER(AW55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AW55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AX56" s="233">
+        <f>IF(ISNUMBER(AW55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AW55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AY56" s="234">
+        <f>IF(ISNUMBER(AW55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AW55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AW55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AW55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="AZ56" s="232">
+        <f>IF(ISNUMBER(AZ55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,AZ55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BA56" s="233">
+        <f>IF(ISNUMBER(AZ55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,AZ55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BB56" s="234">
+        <f>IF(ISNUMBER(AZ55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,AZ55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,AZ55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,AZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,AZ55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BC56" s="232">
+        <f>IF(ISNUMBER(BC55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BC55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BD56" s="233">
+        <f>IF(ISNUMBER(BC55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BC55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BE56" s="234">
+        <f>IF(ISNUMBER(BC55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BC55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BF56" s="232">
+        <f>IF(ISNUMBER(BF55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BF55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BG56" s="233">
+        <f>IF(ISNUMBER(BF55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BF55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BH56" s="234">
+        <f>IF(ISNUMBER(BF55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BF55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BI56" s="232">
+        <f>IF(ISNUMBER(BI55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BI55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BJ56" s="233">
+        <f>IF(ISNUMBER(BI55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BI55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BK56" s="234">
+        <f>IF(ISNUMBER(BI55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BI55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BI55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,3,BI55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,3,BI55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BL56" s="232">
+        <f>IF(ISNUMBER(BL55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BL55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BM56" s="233">
+        <f>IF(ISNUMBER(BL55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BL55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BN56" s="234">
+        <f>IF(ISNUMBER(BL55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BL55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BL55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BO56" s="232">
+        <f>IF(ISNUMBER(BO55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,3,BO55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BP56" s="233">
+        <f>IF(ISNUMBER(BO55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,3,BO55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ56" s="235">
+        <f>IF(ISNUMBER(BO55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,3,BO55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,3,BO55))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS56" s="181"/>
-      <c r="BT56" s="223">
-        <f>IF(ISNUMBER(BT55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BU56" s="224">
-        <f>IF(ISNUMBER(BT55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BV56" s="225">
-        <f>IF(ISNUMBER(BT55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BW56" s="223">
-        <f>IF(ISNUMBER(BW55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BX56" s="224">
-        <f>IF(ISNUMBER(BW55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BY56" s="225">
-        <f>IF(ISNUMBER(BW55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="BZ56" s="223">
-        <f>IF(ISNUMBER(BZ55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CA56" s="224">
-        <f>IF(ISNUMBER(BZ55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CB56" s="225">
-        <f>IF(ISNUMBER(BZ55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CC56" s="223">
-        <f>IF(ISNUMBER(CC55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CD56" s="224">
-        <f>IF(ISNUMBER(CC55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CE56" s="225">
-        <f>IF(ISNUMBER(CC55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CF56" s="223">
-        <f>IF(ISNUMBER(CF55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CG56" s="224">
-        <f>IF(ISNUMBER(CF55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CH56" s="225">
-        <f>IF(ISNUMBER(CF55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF55))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF55))&gt;0,"u",""))),"")</f>
-      </c>
-      <c r="CI56" s="223">
-        <f>IF(ISNUMBER(CI55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CJ56" s="224">
-        <f>IF(ISNUMBER(CI55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CK56" s="225">
-        <f>IF(ISNUMBER(CI55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CL56" s="223">
-        <f>IF(ISNUMBER(CL55),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CM56" s="224">
-        <f>IF(ISNUMBER(CL55),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL55))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN56" s="225">
-        <f>IF(ISNUMBER(CL55),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL55))&gt;0,"h","w")),"")</f>
+      <c r="BT56" s="232">
+        <f>IF(ISNUMBER(BT55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BT55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BU56" s="233">
+        <f>IF(ISNUMBER(BT55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BT55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BV56" s="234">
+        <f>IF(ISNUMBER(BT55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BT55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BT55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BT55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BT55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BW56" s="232">
+        <f>IF(ISNUMBER(BW55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BW55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BX56" s="233">
+        <f>IF(ISNUMBER(BW55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BW55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BY56" s="234">
+        <f>IF(ISNUMBER(BW55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BW55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BW55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BW55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BW55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="BZ56" s="232">
+        <f>IF(ISNUMBER(BZ55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,BZ55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CA56" s="233">
+        <f>IF(ISNUMBER(BZ55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,BZ55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CB56" s="234">
+        <f>IF(ISNUMBER(BZ55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,BZ55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,BZ55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,BZ55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,BZ55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CC56" s="232">
+        <f>IF(ISNUMBER(CC55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CC55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CD56" s="233">
+        <f>IF(ISNUMBER(CC55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CC55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CE56" s="234">
+        <f>IF(ISNUMBER(CC55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CC55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CC55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CC55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CC55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CF56" s="232">
+        <f>IF(ISNUMBER(CF55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CF55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CG56" s="233">
+        <f>IF(ISNUMBER(CF55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CF55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CH56" s="234">
+        <f>IF(ISNUMBER(CF55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CF55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CF55))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,4,CF55),U_Bis,"&gt;="&amp;DATE(Planungsjahr,4,CF55))&gt;0,-3,0))),0)</f>
+      </c>
+      <c r="CI56" s="232">
+        <f>IF(ISNUMBER(CI55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CI55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CJ56" s="233">
+        <f>IF(ISNUMBER(CI55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CI55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CK56" s="234">
+        <f>IF(ISNUMBER(CI55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CI55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CI55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CL56" s="232">
+        <f>IF(ISNUMBER(CL55),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,4,CL55))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CM56" s="233">
+        <f>IF(ISNUMBER(CL55),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,4,CL55))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL55))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN56" s="235">
+        <f>IF(ISNUMBER(CL55),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,4,CL55))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,4,CL55))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="57" spans="2:92" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -12187,10 +12557,10 @@
       <c r="CN57" s="184"/>
     </row>
     <row r="58" x14ac:dyDescent="0.25" ht="11.5" customHeight="1">
-      <c r="B58" s="226">
+      <c r="B58" s="236">
         <f>Hilfsdaten!$D$24</f>
       </c>
-      <c r="C58" s="227" t="str">
+      <c r="C58" s="237" t="str">
         <f>Hilfsdaten!$C$24</f>
       </c>
       <c r="D58" s="215"/>
@@ -12213,10 +12583,10 @@
       <c r="U58" s="215"/>
       <c r="V58" s="215"/>
       <c r="W58" s="215"/>
-      <c r="Y58" s="226">
+      <c r="Y58" s="236">
         <f>Hilfsdaten!$D$27</f>
       </c>
-      <c r="Z58" s="227" t="str">
+      <c r="Z58" s="237" t="str">
         <f>Hilfsdaten!$C$27</f>
       </c>
       <c r="AA58" s="215"/>
@@ -12239,10 +12609,10 @@
       <c r="AR58" s="215"/>
       <c r="AS58" s="215"/>
       <c r="AT58" s="215"/>
-      <c r="AV58" s="226">
+      <c r="AV58" s="236">
         <f>Hilfsdaten!$D$30</f>
       </c>
-      <c r="AW58" s="227" t="str">
+      <c r="AW58" s="237" t="str">
         <f>Hilfsdaten!$C$30</f>
       </c>
       <c r="AX58" s="215"/>
@@ -12265,10 +12635,10 @@
       <c r="BO58" s="215"/>
       <c r="BP58" s="215"/>
       <c r="BQ58" s="215"/>
-      <c r="BS58" s="226">
+      <c r="BS58" s="236">
         <f>Hilfsdaten!$D$33</f>
       </c>
-      <c r="BT58" s="227" t="str">
+      <c r="BT58" s="237" t="str">
         <f>Hilfsdaten!$C$33</f>
       </c>
       <c r="BU58" s="215"/>
@@ -12293,10 +12663,10 @@
       <c r="CN58" s="215"/>
     </row>
     <row r="59" ht="11.5" customHeight="1">
-      <c r="B59" s="226">
+      <c r="B59" s="236">
         <f>Hilfsdaten!$D$25</f>
       </c>
-      <c r="C59" s="227" t="str">
+      <c r="C59" s="237" t="str">
         <f>Hilfsdaten!$C$25</f>
       </c>
       <c r="D59" s="217"/>
@@ -12319,10 +12689,10 @@
       <c r="U59" s="217"/>
       <c r="V59" s="217"/>
       <c r="W59" s="217"/>
-      <c r="Y59" s="226">
+      <c r="Y59" s="236">
         <f>Hilfsdaten!$D$28</f>
       </c>
-      <c r="Z59" s="227" t="str">
+      <c r="Z59" s="237" t="str">
         <f>Hilfsdaten!$C$28</f>
       </c>
       <c r="AA59" s="217"/>
@@ -12345,10 +12715,10 @@
       <c r="AR59" s="217"/>
       <c r="AS59" s="217"/>
       <c r="AT59" s="217"/>
-      <c r="AV59" s="226">
+      <c r="AV59" s="236">
         <f>Hilfsdaten!$D$31</f>
       </c>
-      <c r="AW59" s="227" t="str">
+      <c r="AW59" s="237" t="str">
         <f>Hilfsdaten!$C$31</f>
       </c>
       <c r="AX59" s="217"/>
@@ -12371,10 +12741,10 @@
       <c r="BO59" s="217"/>
       <c r="BP59" s="217"/>
       <c r="BQ59" s="217"/>
-      <c r="BS59" s="226">
+      <c r="BS59" s="236">
         <f>Hilfsdaten!$D$34</f>
       </c>
-      <c r="BT59" s="227" t="str">
+      <c r="BT59" s="237" t="str">
         <f>Hilfsdaten!$C$34</f>
       </c>
       <c r="BU59" s="217"/>
@@ -12399,10 +12769,10 @@
       <c r="CN59" s="217"/>
     </row>
     <row r="60" ht="11.5" customHeight="1">
-      <c r="B60" s="226">
+      <c r="B60" s="236">
         <f>Hilfsdaten!$D$26</f>
       </c>
-      <c r="C60" s="227" t="str">
+      <c r="C60" s="237" t="str">
         <f>Hilfsdaten!$C$26</f>
       </c>
       <c r="D60" s="219"/>
@@ -12425,10 +12795,10 @@
       <c r="U60" s="219"/>
       <c r="V60" s="219"/>
       <c r="W60" s="219"/>
-      <c r="Y60" s="226">
+      <c r="Y60" s="236">
         <f>Hilfsdaten!$D$29</f>
       </c>
-      <c r="Z60" s="227" t="str">
+      <c r="Z60" s="237" t="str">
         <f>Hilfsdaten!$C$29</f>
       </c>
       <c r="AA60" s="219"/>
@@ -12451,10 +12821,10 @@
       <c r="AR60" s="219"/>
       <c r="AS60" s="219"/>
       <c r="AT60" s="219"/>
-      <c r="AV60" s="226">
+      <c r="AV60" s="236">
         <f>Hilfsdaten!$D$32</f>
       </c>
-      <c r="AW60" s="227" t="str">
+      <c r="AW60" s="237" t="str">
         <f>Hilfsdaten!$C$32</f>
       </c>
       <c r="AX60" s="219"/>
@@ -12477,10 +12847,10 @@
       <c r="BO60" s="219"/>
       <c r="BP60" s="219"/>
       <c r="BQ60" s="219"/>
-      <c r="BS60" s="226">
+      <c r="BS60" s="236">
         <f>Hilfsdaten!$D$35</f>
       </c>
-      <c r="BT60" s="227" t="str">
+      <c r="BT60" s="237" t="str">
         <f>Hilfsdaten!$C$35</f>
       </c>
       <c r="BU60" s="219"/>
@@ -12949,259 +13319,259 @@
     <row r="64" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="179"/>
       <c r="C64" s="223">
-        <f>IF(ISNUMBER(C63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,C63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,C63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D64" s="224">
-        <f>IF(ISNUMBER(C63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,C63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,C63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E64" s="225">
-        <f>IF(ISNUMBER(C63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,C63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,C63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F64" s="223">
-        <f>IF(ISNUMBER(F63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,F63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,F63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G64" s="224">
-        <f>IF(ISNUMBER(F63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,F63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,F63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H64" s="225">
-        <f>IF(ISNUMBER(F63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,F63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,F63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I64" s="223">
-        <f>IF(ISNUMBER(I63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,I63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,I63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J64" s="224">
-        <f>IF(ISNUMBER(I63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,I63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,I63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K64" s="225">
-        <f>IF(ISNUMBER(I63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,I63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,I63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L64" s="223">
-        <f>IF(ISNUMBER(L63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,L63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,L63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M64" s="224">
-        <f>IF(ISNUMBER(L63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,L63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,L63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N64" s="225">
-        <f>IF(ISNUMBER(L63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,L63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,L63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O64" s="223">
-        <f>IF(ISNUMBER(O63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,O63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,O63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P64" s="224">
-        <f>IF(ISNUMBER(O63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,O63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,O63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q64" s="225">
-        <f>IF(ISNUMBER(O63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,O63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,O63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R64" s="223">
-        <f>IF(ISNUMBER(R63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,R63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,R63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S64" s="224">
-        <f>IF(ISNUMBER(R63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,R63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,R63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T64" s="225">
-        <f>IF(ISNUMBER(R63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,R63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,R63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U64" s="223">
-        <f>IF(ISNUMBER(U63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,U63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,U63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V64" s="224">
-        <f>IF(ISNUMBER(U63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,U63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U63))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W64" s="225">
-        <f>IF(ISNUMBER(U63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,U63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,U63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U63))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W64" s="231">
+        <f>IF(ISNUMBER(U63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,U63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y64" s="179"/>
       <c r="Z64" s="223">
-        <f>IF(ISNUMBER(Z63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,Z63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,Z63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA64" s="224">
-        <f>IF(ISNUMBER(Z63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,Z63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,Z63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB64" s="225">
-        <f>IF(ISNUMBER(Z63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,Z63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,Z63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC64" s="223">
-        <f>IF(ISNUMBER(AC63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AC63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AC63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD64" s="224">
-        <f>IF(ISNUMBER(AC63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AC63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AC63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE64" s="225">
-        <f>IF(ISNUMBER(AC63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AC63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AC63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF64" s="223">
-        <f>IF(ISNUMBER(AF63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AF63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AF63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG64" s="224">
-        <f>IF(ISNUMBER(AF63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AF63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AF63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH64" s="225">
-        <f>IF(ISNUMBER(AF63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AF63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AF63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI64" s="223">
-        <f>IF(ISNUMBER(AI63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AI63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AI63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ64" s="224">
-        <f>IF(ISNUMBER(AI63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AI63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AI63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK64" s="225">
-        <f>IF(ISNUMBER(AI63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AI63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AI63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL64" s="223">
-        <f>IF(ISNUMBER(AL63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AL63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AL63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM64" s="224">
-        <f>IF(ISNUMBER(AL63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AL63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AL63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AN64" s="225">
-        <f>IF(ISNUMBER(AL63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AL63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AL63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AO64" s="223">
-        <f>IF(ISNUMBER(AO63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AO63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AO63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AP64" s="224">
-        <f>IF(ISNUMBER(AO63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AO63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AO63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AQ64" s="225">
-        <f>IF(ISNUMBER(AO63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AO63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AO63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AR64" s="223">
-        <f>IF(ISNUMBER(AR63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AR63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AR63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AS64" s="224">
-        <f>IF(ISNUMBER(AR63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AR63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR63))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT64" s="225">
-        <f>IF(ISNUMBER(AR63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AR63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AR63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR63))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT64" s="231">
+        <f>IF(ISNUMBER(AR63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AR63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV64" s="179"/>
       <c r="AW64" s="223">
-        <f>IF(ISNUMBER(AW63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AW63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AW63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AX64" s="224">
-        <f>IF(ISNUMBER(AW63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AW63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AW63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AY64" s="225">
-        <f>IF(ISNUMBER(AW63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AW63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AW63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AZ64" s="223">
-        <f>IF(ISNUMBER(AZ63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AZ63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AZ63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BA64" s="224">
-        <f>IF(ISNUMBER(AZ63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AZ63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AZ63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BB64" s="225">
-        <f>IF(ISNUMBER(AZ63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AZ63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AZ63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BC64" s="223">
-        <f>IF(ISNUMBER(BC63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BC63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BC63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BD64" s="224">
-        <f>IF(ISNUMBER(BC63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BC63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BC63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BE64" s="225">
-        <f>IF(ISNUMBER(BC63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BC63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BC63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BF64" s="223">
-        <f>IF(ISNUMBER(BF63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BF63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BF63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BG64" s="224">
-        <f>IF(ISNUMBER(BF63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BF63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BF63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BH64" s="225">
-        <f>IF(ISNUMBER(BF63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BF63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BF63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BI64" s="223">
-        <f>IF(ISNUMBER(BI63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BI63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BI63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BJ64" s="224">
-        <f>IF(ISNUMBER(BI63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BI63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BI63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BK64" s="225">
-        <f>IF(ISNUMBER(BI63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BI63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BI63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BL64" s="223">
-        <f>IF(ISNUMBER(BL63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BL63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BL63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BM64" s="224">
-        <f>IF(ISNUMBER(BL63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BL63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BL63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BN64" s="225">
-        <f>IF(ISNUMBER(BL63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BL63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BL63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BO64" s="223">
-        <f>IF(ISNUMBER(BO63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BO63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BO63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BP64" s="224">
-        <f>IF(ISNUMBER(BO63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BO63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO63))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ64" s="225">
-        <f>IF(ISNUMBER(BO63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BO63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BO63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO63))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ64" s="231">
+        <f>IF(ISNUMBER(BO63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BO63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS64" s="179"/>
       <c r="BT64" s="223">
-        <f>IF(ISNUMBER(BT63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BT63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BT63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BU64" s="224">
-        <f>IF(ISNUMBER(BT63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BT63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BT63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BV64" s="225">
-        <f>IF(ISNUMBER(BT63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BT63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BT63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BW64" s="223">
-        <f>IF(ISNUMBER(BW63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BW63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BW63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BX64" s="224">
-        <f>IF(ISNUMBER(BW63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BW63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BW63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BY64" s="225">
-        <f>IF(ISNUMBER(BW63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BW63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BW63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BZ64" s="223">
-        <f>IF(ISNUMBER(BZ63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BZ63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BZ63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CA64" s="224">
-        <f>IF(ISNUMBER(BZ63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BZ63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BZ63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CB64" s="225">
-        <f>IF(ISNUMBER(BZ63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BZ63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BZ63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CC64" s="223">
-        <f>IF(ISNUMBER(CC63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CC63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CC63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CD64" s="224">
-        <f>IF(ISNUMBER(CC63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CC63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CC63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CE64" s="225">
-        <f>IF(ISNUMBER(CC63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CC63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CC63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CF64" s="223">
-        <f>IF(ISNUMBER(CF63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CF63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CF63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CG64" s="224">
-        <f>IF(ISNUMBER(CF63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CF63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CF63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CH64" s="225">
-        <f>IF(ISNUMBER(CF63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CF63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF63))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF63))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CF63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF63))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF63),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF63))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CI64" s="223">
-        <f>IF(ISNUMBER(CI63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CI63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CI63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CJ64" s="224">
-        <f>IF(ISNUMBER(CI63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CI63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CI63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CK64" s="225">
-        <f>IF(ISNUMBER(CI63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CI63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CI63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CL64" s="223">
-        <f>IF(ISNUMBER(CL63),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CL63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL63),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CL63))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL63))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CM64" s="224">
-        <f>IF(ISNUMBER(CL63),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CL63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL63))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN64" s="225">
-        <f>IF(ISNUMBER(CL63),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CL63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL63))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL63),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CL63))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL63))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN64" s="231">
+        <f>IF(ISNUMBER(CL63),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CL63))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL63))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="65" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13393,259 +13763,259 @@
     <row r="66" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="179"/>
       <c r="C66" s="223">
-        <f>IF(ISNUMBER(C65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,C65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,C65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D66" s="224">
-        <f>IF(ISNUMBER(C65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,C65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,C65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E66" s="225">
-        <f>IF(ISNUMBER(C65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,C65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,C65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F66" s="223">
-        <f>IF(ISNUMBER(F65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,F65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,F65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G66" s="224">
-        <f>IF(ISNUMBER(F65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,F65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,F65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H66" s="225">
-        <f>IF(ISNUMBER(F65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,F65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,F65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I66" s="223">
-        <f>IF(ISNUMBER(I65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,I65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,I65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J66" s="224">
-        <f>IF(ISNUMBER(I65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,I65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,I65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K66" s="225">
-        <f>IF(ISNUMBER(I65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,I65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,I65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L66" s="223">
-        <f>IF(ISNUMBER(L65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,L65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,L65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M66" s="224">
-        <f>IF(ISNUMBER(L65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,L65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,L65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N66" s="225">
-        <f>IF(ISNUMBER(L65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,L65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,L65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O66" s="223">
-        <f>IF(ISNUMBER(O65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,O65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,O65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P66" s="224">
-        <f>IF(ISNUMBER(O65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,O65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,O65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q66" s="225">
-        <f>IF(ISNUMBER(O65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,O65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,O65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R66" s="223">
-        <f>IF(ISNUMBER(R65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,R65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,R65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S66" s="224">
-        <f>IF(ISNUMBER(R65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,R65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,R65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T66" s="225">
-        <f>IF(ISNUMBER(R65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,R65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,R65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U66" s="223">
-        <f>IF(ISNUMBER(U65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,U65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,U65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V66" s="224">
-        <f>IF(ISNUMBER(U65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,U65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U65))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W66" s="225">
-        <f>IF(ISNUMBER(U65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,U65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,U65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U65))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W66" s="231">
+        <f>IF(ISNUMBER(U65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,U65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y66" s="179"/>
       <c r="Z66" s="223">
-        <f>IF(ISNUMBER(Z65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,Z65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,Z65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA66" s="224">
-        <f>IF(ISNUMBER(Z65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,Z65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,Z65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB66" s="225">
-        <f>IF(ISNUMBER(Z65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,Z65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,Z65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC66" s="223">
-        <f>IF(ISNUMBER(AC65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AC65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AC65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD66" s="224">
-        <f>IF(ISNUMBER(AC65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AC65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AC65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE66" s="225">
-        <f>IF(ISNUMBER(AC65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AC65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AC65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF66" s="223">
-        <f>IF(ISNUMBER(AF65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AF65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AF65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG66" s="224">
-        <f>IF(ISNUMBER(AF65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AF65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AF65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH66" s="225">
-        <f>IF(ISNUMBER(AF65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AF65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AF65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI66" s="223">
-        <f>IF(ISNUMBER(AI65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AI65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AI65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ66" s="224">
-        <f>IF(ISNUMBER(AI65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AI65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AI65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK66" s="225">
-        <f>IF(ISNUMBER(AI65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AI65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AI65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL66" s="223">
-        <f>IF(ISNUMBER(AL65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AL65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AL65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM66" s="224">
-        <f>IF(ISNUMBER(AL65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AL65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AL65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AN66" s="225">
-        <f>IF(ISNUMBER(AL65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AL65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AL65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AO66" s="223">
-        <f>IF(ISNUMBER(AO65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AO65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AO65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AP66" s="224">
-        <f>IF(ISNUMBER(AO65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AO65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AO65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AQ66" s="225">
-        <f>IF(ISNUMBER(AO65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AO65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AO65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AO65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AO65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AR66" s="223">
-        <f>IF(ISNUMBER(AR65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AR65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AR65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AS66" s="224">
-        <f>IF(ISNUMBER(AR65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AR65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR65))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="AT66" s="225">
-        <f>IF(ISNUMBER(AR65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AR65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(AR65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AR65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR65))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="AT66" s="231">
+        <f>IF(ISNUMBER(AR65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AR65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AR65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="AV66" s="179"/>
       <c r="AW66" s="223">
-        <f>IF(ISNUMBER(AW65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AW65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AW65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AX66" s="224">
-        <f>IF(ISNUMBER(AW65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AW65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AW65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AY66" s="225">
-        <f>IF(ISNUMBER(AW65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AW65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AW65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AW65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AW65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AW65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AZ66" s="223">
-        <f>IF(ISNUMBER(AZ65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AZ65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,AZ65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BA66" s="224">
-        <f>IF(ISNUMBER(AZ65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AZ65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,AZ65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BB66" s="225">
-        <f>IF(ISNUMBER(AZ65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AZ65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AZ65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,AZ65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,AZ65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,AZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,AZ65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BC66" s="223">
-        <f>IF(ISNUMBER(BC65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BC65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BC65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BD66" s="224">
-        <f>IF(ISNUMBER(BC65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BC65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BC65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BE66" s="225">
-        <f>IF(ISNUMBER(BC65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BC65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BC65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BC65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BF66" s="223">
-        <f>IF(ISNUMBER(BF65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BF65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BF65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BG66" s="224">
-        <f>IF(ISNUMBER(BF65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BF65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BF65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BH66" s="225">
-        <f>IF(ISNUMBER(BF65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BF65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BF65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BF65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BI66" s="223">
-        <f>IF(ISNUMBER(BI65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BI65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BI65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BJ66" s="224">
-        <f>IF(ISNUMBER(BI65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BI65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BI65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BK66" s="225">
-        <f>IF(ISNUMBER(BI65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BI65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BI65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BI65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BI65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,7,BI65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,7,BI65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BL66" s="223">
-        <f>IF(ISNUMBER(BL65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BL65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BL65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BM66" s="224">
-        <f>IF(ISNUMBER(BL65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BL65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BL65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BN66" s="225">
-        <f>IF(ISNUMBER(BL65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BL65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BL65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BL65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BL65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BO66" s="223">
-        <f>IF(ISNUMBER(BO65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BO65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,7,BO65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BP66" s="224">
-        <f>IF(ISNUMBER(BO65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BO65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO65))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="BQ66" s="225">
-        <f>IF(ISNUMBER(BO65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BO65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(BO65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,7,BO65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO65))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="BQ66" s="231">
+        <f>IF(ISNUMBER(BO65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,7,BO65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,7,BO65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="BS66" s="179"/>
       <c r="BT66" s="223">
-        <f>IF(ISNUMBER(BT65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BT65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BT65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BU66" s="224">
-        <f>IF(ISNUMBER(BT65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BT65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BT65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BV66" s="225">
-        <f>IF(ISNUMBER(BT65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BT65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BT65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BT65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BT65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BT65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BT65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BW66" s="223">
-        <f>IF(ISNUMBER(BW65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BW65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BW65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BX66" s="224">
-        <f>IF(ISNUMBER(BW65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BW65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BW65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BY66" s="225">
-        <f>IF(ISNUMBER(BW65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BW65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BW65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BW65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BW65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BW65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BW65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="BZ66" s="223">
-        <f>IF(ISNUMBER(BZ65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BZ65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,BZ65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CA66" s="224">
-        <f>IF(ISNUMBER(BZ65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BZ65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,BZ65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CB66" s="225">
-        <f>IF(ISNUMBER(BZ65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BZ65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(BZ65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,BZ65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,BZ65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,BZ65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,BZ65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CC66" s="223">
-        <f>IF(ISNUMBER(CC65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CC65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CC65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CD66" s="224">
-        <f>IF(ISNUMBER(CC65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CC65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CC65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CE66" s="225">
-        <f>IF(ISNUMBER(CC65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CC65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CC65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CC65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CC65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CC65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CC65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CF66" s="223">
-        <f>IF(ISNUMBER(CF65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CF65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CF65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CG66" s="224">
-        <f>IF(ISNUMBER(CF65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CF65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CF65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CH66" s="225">
-        <f>IF(ISNUMBER(CF65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CF65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF65))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF65))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(CF65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CF65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CF65))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,8,CF65),U_Bis,"&gt;="&amp;DATE(Planungsjahr,8,CF65))&gt;0,-3,0))),0)</f>
       </c>
       <c r="CI66" s="223">
-        <f>IF(ISNUMBER(CI65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CI65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CI65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CJ66" s="224">
-        <f>IF(ISNUMBER(CI65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CI65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CI65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CK66" s="225">
-        <f>IF(ISNUMBER(CI65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CI65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CI65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CI65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CI65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CL66" s="223">
-        <f>IF(ISNUMBER(CL65),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CL65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL65),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,8,CL65))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL65))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="CM66" s="224">
-        <f>IF(ISNUMBER(CL65),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CL65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL65))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="CN66" s="225">
-        <f>IF(ISNUMBER(CL65),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CL65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL65))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(CL65),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,8,CL65))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL65))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="CN66" s="231">
+        <f>IF(ISNUMBER(CL65),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,8,CL65))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,8,CL65))&gt;0,-2,-1)),0)</f>
       </c>
     </row>
     <row r="67" spans="2:92" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13837,259 +14207,259 @@
     <row r="68" spans="2:92" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="179"/>
       <c r="C68" s="223">
-        <f>IF(ISNUMBER(C67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,C67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,C67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="D68" s="224">
-        <f>IF(ISNUMBER(C67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,C67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,C67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="E68" s="225">
-        <f>IF(ISNUMBER(C67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,C67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(C67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,C67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,C67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,C67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,C67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="F68" s="223">
-        <f>IF(ISNUMBER(F67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,F67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,F67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="G68" s="224">
-        <f>IF(ISNUMBER(F67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,F67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,F67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="H68" s="225">
-        <f>IF(ISNUMBER(F67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,F67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(F67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,F67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,F67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,F67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,F67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="I68" s="223">
-        <f>IF(ISNUMBER(I67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,I67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,I67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="J68" s="224">
-        <f>IF(ISNUMBER(I67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,I67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,I67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="K68" s="225">
-        <f>IF(ISNUMBER(I67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,I67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(I67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,I67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,I67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,I67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,I67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="L68" s="223">
-        <f>IF(ISNUMBER(L67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,L67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,L67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="M68" s="224">
-        <f>IF(ISNUMBER(L67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,L67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,L67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="N68" s="225">
-        <f>IF(ISNUMBER(L67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,L67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(L67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,L67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,L67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,L67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,L67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="O68" s="223">
-        <f>IF(ISNUMBER(O67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,O67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,O67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="P68" s="224">
-        <f>IF(ISNUMBER(O67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,O67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,O67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="Q68" s="225">
-        <f>IF(ISNUMBER(O67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,O67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(O67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,O67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,O67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,5,O67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,5,O67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="R68" s="223">
-        <f>IF(ISNUMBER(R67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,R67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R67))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,R67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R67))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="S68" s="224">
-        <f>IF(ISNUMBER(R67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,R67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R67))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,R67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R67))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="T68" s="225">
-        <f>IF(ISNUMBER(R67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,R67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R67))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(R67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,R67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,R67))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="U68" s="223">
-        <f>IF(ISNUMBER(U67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,U67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U67))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,5,U67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U67))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="V68" s="224">
-        <f>IF(ISNUMBER(U67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,U67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U67))&gt;0,"h","w")),"")</f>
-      </c>
-      <c r="W68" s="225">
-        <f>IF(ISNUMBER(U67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,U67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U67))&gt;0,"h","w")),"")</f>
+        <f>IF(ISNUMBER(U67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,5,U67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U67))&gt;0,-2,-1)),0)</f>
+      </c>
+      <c r="W68" s="231">
+        <f>IF(ISNUMBER(U67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,5,U67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,5,U67))&gt;0,-2,-1)),0)</f>
       </c>
       <c r="Y68" s="179"/>
       <c r="Z68" s="223">
-        <f>IF(ISNUMBER(Z67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,Z67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,Z67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AA68" s="224">
-        <f>IF(ISNUMBER(Z67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,Z67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,Z67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AB68" s="225">
-        <f>IF(ISNUMBER(Z67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,Z67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(Z67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,Z67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,Z67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,Z67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,Z67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AC68" s="223">
-        <f>IF(ISNUMBER(AC67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AC67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AC67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AD68" s="224">
-        <f>IF(ISNUMBER(AC67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AC67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AC67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AE68" s="225">
-        <f>IF(ISNUMBER(AC67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AC67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AC67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AC67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AC67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AC67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AC67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AF68" s="223">
-        <f>IF(ISNUMBER(AF67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AF67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AF67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AG68" s="224">
-        <f>IF(ISNUMBER(AF67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AF67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AF67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AH68" s="225">
-        <f>IF(ISNUMBER(AF67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AF67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AF67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AF67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AF67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AF67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AF67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AI68" s="223">
-        <f>IF(ISNUMBER(AI67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AI67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AI67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AJ68" s="224">
-        <f>IF(ISNUMBER(AI67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AI67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AI67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AK68" s="225">
-        <f>IF(ISNUMBER(AI67),IFERROR(31-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AI67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AI67),IFERROR("c"&amp;(34-1/(1/SUMPRODUCT(MAX((JP_PAL=DATE(Planungsjahr,6,AI67))*Anzeige_P*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AI67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AI67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AI67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AL68" s="223">
-        <f>IF(ISNUMBER(AL67),IFERROR(11-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AL67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL67),IFERROR("c"&amp;(12-1/(1/SUMPRODUCT(MAX((JP_StartSel=DATE(Planungsjahr,6,AL67))*Anzeige_S*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL67))&gt;0,-3,0))),0)</f>
       </c>
       <c r="AM68" s="224">
-        <f>IF(ISNUMBER(AL67),IFERROR(21-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AL67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(11-JP_Farbe)))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL67))&gt;0,"h",IF(COUNTIFS(U_Von,"&lt;="&amp;DATE(Planungsjahr,6,AL67),U_Bis,"&gt;="&amp;DATE(Planungsjahr,6,AL67))&gt;0,"u",""))),"")</f>
+        <f>IF(ISNUMBER(AL67),IFERROR("c"&amp;(23-1/(1/SUMPRODUCT(MAX((JP_StartInhalt=DATE(Planungsjahr,6,AL67))*Anzeige_I*((JP_Anzeige=TRUE)+NOT(Filter_Aktiv)&gt;0)*(12-JP_Farbe))))),IF(COUNTIF(Feiertage,DATE(Planungsjahr,6,AL67))&gt;0,-2,IF(COUNTIFS(U_Von,"&lt;="&amp;D